--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="1190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="1191">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23958873748779</t>
+    <t xml:space="preserve">9.23958778381348</t>
   </si>
   <si>
     <t xml:space="preserve">CMB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55656623840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31377506256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40144824981689</t>
+    <t xml:space="preserve">9.55656719207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31377410888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40144920349121</t>
   </si>
   <si>
     <t xml:space="preserve">9.40819358825684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44191265106201</t>
+    <t xml:space="preserve">9.44191360473633</t>
   </si>
   <si>
     <t xml:space="preserve">9.36098289489746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13842391967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32051944732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26656532287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3407506942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27330875396729</t>
+    <t xml:space="preserve">9.13842487335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32051849365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26656341552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34075164794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2733097076416</t>
   </si>
   <si>
     <t xml:space="preserve">9.19237804412842</t>
@@ -83,73 +83,73 @@
     <t xml:space="preserve">9.19912242889404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10470390319824</t>
+    <t xml:space="preserve">9.10470294952393</t>
   </si>
   <si>
     <t xml:space="preserve">8.84167861938477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77423667907715</t>
+    <t xml:space="preserve">8.77423763275146</t>
   </si>
   <si>
     <t xml:space="preserve">8.84842300415039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36283779144287</t>
+    <t xml:space="preserve">8.3628396987915</t>
   </si>
   <si>
     <t xml:space="preserve">8.3291187286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61911964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45051383972168</t>
+    <t xml:space="preserve">8.61911869049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45051193237305</t>
   </si>
   <si>
     <t xml:space="preserve">8.43028259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63260841369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80121326446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22609996795654</t>
+    <t xml:space="preserve">8.63260746002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80121421813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22609901428223</t>
   </si>
   <si>
     <t xml:space="preserve">9.25981998443604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07098293304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87539863586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96981906890869</t>
+    <t xml:space="preserve">9.0709810256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87539958953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96982002258301</t>
   </si>
   <si>
     <t xml:space="preserve">8.71353816986084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66632843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89563274383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81470203399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99679660797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01028537750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90237712860107</t>
+    <t xml:space="preserve">8.6663293838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89563179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8147029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99679565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01028442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90237522125244</t>
   </si>
   <si>
     <t xml:space="preserve">8.97656345367432</t>
@@ -161,49 +161,49 @@
     <t xml:space="preserve">9.17214584350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13168048858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34749507904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25307655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15865802764893</t>
+    <t xml:space="preserve">9.13167953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34749603271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25307750701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15865707397461</t>
   </si>
   <si>
     <t xml:space="preserve">9.08447074890137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16540145874023</t>
+    <t xml:space="preserve">9.16540241241455</t>
   </si>
   <si>
     <t xml:space="preserve">8.98330688476562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78772449493408</t>
+    <t xml:space="preserve">8.78772354125977</t>
   </si>
   <si>
     <t xml:space="preserve">8.78098106384277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12493705749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03726100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21261024475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04400539398193</t>
+    <t xml:space="preserve">9.1249361038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03726005554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21261215209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04400634765625</t>
   </si>
   <si>
     <t xml:space="preserve">9.0979585647583</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20586776733398</t>
+    <t xml:space="preserve">9.20586681365967</t>
   </si>
   <si>
     <t xml:space="preserve">9.38121604919434</t>
@@ -212,19 +212,19 @@
     <t xml:space="preserve">9.28679752349854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22100830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22798919677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19308757781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35363292694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40947723388672</t>
+    <t xml:space="preserve">9.22100734710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22798824310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19308662414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35363388061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4094762802124</t>
   </si>
   <si>
     <t xml:space="preserve">9.52116298675537</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">9.49324131011963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38853645324707</t>
+    <t xml:space="preserve">9.38853549957275</t>
   </si>
   <si>
     <t xml:space="preserve">9.94696140289307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76547336578369</t>
+    <t xml:space="preserve">9.76547241210938</t>
   </si>
   <si>
     <t xml:space="preserve">9.77245330810547</t>
@@ -248,25 +248,25 @@
     <t xml:space="preserve">9.66774940490723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82829666137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75151252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57002353668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57700443267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55606460571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47927951812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42343807220459</t>
+    <t xml:space="preserve">9.82829761505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75151348114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57002449035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57700538635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55606269836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47928047180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42343711853027</t>
   </si>
   <si>
     <t xml:space="preserve">9.39551639556885</t>
@@ -281,19 +281,19 @@
     <t xml:space="preserve">9.58398532867432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62586784362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63284778594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46531867980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48625946044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59096527099609</t>
+    <t xml:space="preserve">9.62586688995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63284873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46531963348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48626041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59096431732178</t>
   </si>
   <si>
     <t xml:space="preserve">9.56304359436035</t>
@@ -302,22 +302,22 @@
     <t xml:space="preserve">9.53512191772461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12328433990479</t>
+    <t xml:space="preserve">9.1232852935791</t>
   </si>
   <si>
     <t xml:space="preserve">9.30477237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2838306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20704746246338</t>
+    <t xml:space="preserve">9.28383255004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20704650878906</t>
   </si>
   <si>
     <t xml:space="preserve">9.27685070037842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36061382293701</t>
+    <t xml:space="preserve">9.36061477661133</t>
   </si>
   <si>
     <t xml:space="preserve">9.29081153869629</t>
@@ -326,91 +326,91 @@
     <t xml:space="preserve">9.29779148101807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31873226165771</t>
+    <t xml:space="preserve">9.31873321533203</t>
   </si>
   <si>
     <t xml:space="preserve">9.36759471893311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47229862213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52814292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5072021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44437885284424</t>
+    <t xml:space="preserve">9.47229957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52814197540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50720119476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44437789916992</t>
   </si>
   <si>
     <t xml:space="preserve">9.50022125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3326940536499</t>
+    <t xml:space="preserve">9.33269309997559</t>
   </si>
   <si>
     <t xml:space="preserve">9.32571411132812</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13724422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14422416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15120410919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10932445526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03951930999756</t>
+    <t xml:space="preserve">9.13724327087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14422512054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15120506286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10932350158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03952026367188</t>
   </si>
   <si>
     <t xml:space="preserve">8.92783451080322</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01159763336182</t>
+    <t xml:space="preserve">9.01159858703613</t>
   </si>
   <si>
     <t xml:space="preserve">9.07442188262939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97669792175293</t>
+    <t xml:space="preserve">8.97669696807861</t>
   </si>
   <si>
     <t xml:space="preserve">8.86501121520996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85105228424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93481540679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92085361480713</t>
+    <t xml:space="preserve">8.85105037689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.934814453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92085456848145</t>
   </si>
   <si>
     <t xml:space="preserve">8.95575618743896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96971607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00461864471436</t>
+    <t xml:space="preserve">8.96971702575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00461673736572</t>
   </si>
   <si>
     <t xml:space="preserve">8.91387367248535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87897300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80916976928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59975814819336</t>
+    <t xml:space="preserve">8.87897396087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80916881561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59976005554199</t>
   </si>
   <si>
     <t xml:space="preserve">8.56485843658447</t>
@@ -425,28 +425,28 @@
     <t xml:space="preserve">8.8999137878418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99763870239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83010959625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96273612976074</t>
+    <t xml:space="preserve">8.99763774871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83010864257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96273708343506</t>
   </si>
   <si>
     <t xml:space="preserve">9.08838176727295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04649925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09536075592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66076946258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64680862426758</t>
+    <t xml:space="preserve">9.04650020599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09536170959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66076850891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64680767059326</t>
   </si>
   <si>
     <t xml:space="preserve">9.70265007019043</t>
@@ -455,58 +455,58 @@
     <t xml:space="preserve">9.79339408874512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92602157592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9818639755249</t>
+    <t xml:space="preserve">9.92602062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98186492919922</t>
   </si>
   <si>
     <t xml:space="preserve">10.0516662597656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.414644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1912746429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2471151351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493911743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1354303359985</t>
+    <t xml:space="preserve">10.4146432876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1912727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2471160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493902206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1354322433472</t>
   </si>
   <si>
     <t xml:space="preserve">10.2680568695068</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3937044143677</t>
+    <t xml:space="preserve">10.3937015533447</t>
   </si>
   <si>
     <t xml:space="preserve">10.5402898788452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.589150428772</t>
+    <t xml:space="preserve">10.5891532897949</t>
   </si>
   <si>
     <t xml:space="preserve">10.484447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6310338973999</t>
+    <t xml:space="preserve">10.6310329437256</t>
   </si>
   <si>
     <t xml:space="preserve">10.3588018417358</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98884391784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95394229888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1005296707153</t>
+    <t xml:space="preserve">9.988844871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95394134521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.100528717041</t>
   </si>
   <si>
     <t xml:space="preserve">10.4704866409302</t>
@@ -518,124 +518,124 @@
     <t xml:space="preserve">10.5472688674927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.344841003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.477466583252</t>
+    <t xml:space="preserve">10.3448400497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4774656295776</t>
   </si>
   <si>
     <t xml:space="preserve">10.4006824493408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.435583114624</t>
+    <t xml:space="preserve">10.4355840682983</t>
   </si>
   <si>
     <t xml:space="preserve">10.3727607727051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3657817840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3378601074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.282018661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3797426223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6100921630859</t>
+    <t xml:space="preserve">10.3657827377319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3378610610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2820177078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3797435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6100931167603</t>
   </si>
   <si>
     <t xml:space="preserve">10.5542497634888</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6938562393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0917348861694</t>
+    <t xml:space="preserve">10.6938571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0917358398438</t>
   </si>
   <si>
     <t xml:space="preserve">11.042872428894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0358924865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0638151168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0847549438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3569889068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5175342559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0899229049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9991769790649</t>
+    <t xml:space="preserve">11.0358934402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.063814163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.084755897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.356987953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5175352096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0899219512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9991788864136</t>
   </si>
   <si>
     <t xml:space="preserve">12.0689811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1038818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2853708267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8228540420532</t>
+    <t xml:space="preserve">12.1038808822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2853717803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8228578567505</t>
   </si>
   <si>
     <t xml:space="preserve">12.9764213562012</t>
   </si>
   <si>
-    <t xml:space="preserve">12.990382194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2486543655396</t>
+    <t xml:space="preserve">12.9903831481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2486534118652</t>
   </si>
   <si>
     <t xml:space="preserve">13.1090497970581</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1230087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8926601409912</t>
+    <t xml:space="preserve">13.1230096817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8926572799683</t>
   </si>
   <si>
     <t xml:space="preserve">12.9135999679565</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8437967300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9624624252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1928157806396</t>
+    <t xml:space="preserve">12.8437957763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9624614715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1928129196167</t>
   </si>
   <si>
     <t xml:space="preserve">13.3952436447144</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8978252410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9815902709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9327278137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0234708786011</t>
+    <t xml:space="preserve">13.8978242874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9815883636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9327268600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0234718322754</t>
   </si>
   <si>
     <t xml:space="preserve">14.0304517745972</t>
@@ -644,112 +644,112 @@
     <t xml:space="preserve">14.135157585144</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0723333358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0025300979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.211254119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197374343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1461629867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0810747146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9942903518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6688442230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3558988571167</t>
+    <t xml:space="preserve">14.0723323822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0025310516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.211256980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197383880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.146164894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0810775756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9942932128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6688413619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.355899810791</t>
   </si>
   <si>
     <t xml:space="preserve">13.6833066940308</t>
   </si>
   <si>
-    <t xml:space="preserve">14.001522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9870557785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2691135406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3486680984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3414363861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.276346206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4282236099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5656328201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3322467803955</t>
+    <t xml:space="preserve">14.0015239715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9870576858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2691125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.348669052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3414354324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2763452529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.42822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5656318664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3322458267212</t>
   </si>
   <si>
     <t xml:space="preserve">15.8457307815552</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7589464187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3611755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1876010894775</t>
+    <t xml:space="preserve">15.7589454650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3611745834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1876020431519</t>
   </si>
   <si>
     <t xml:space="preserve">14.9200115203857</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6307229995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636739730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3105506896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9272422790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0718879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5492105484009</t>
+    <t xml:space="preserve">14.6307258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636768341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3105478286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9272432327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0718870162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5492124557495</t>
   </si>
   <si>
     <t xml:space="preserve">15.4551944732666</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2671585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1731376647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8332262039185</t>
+    <t xml:space="preserve">15.2671566009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1731386184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8332271575928</t>
   </si>
   <si>
     <t xml:space="preserve">15.1369781494141</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1152801513672</t>
+    <t xml:space="preserve">15.1152791976929</t>
   </si>
   <si>
     <t xml:space="preserve">14.9851016998291</t>
@@ -758,121 +758,121 @@
     <t xml:space="preserve">15.1514415740967</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0284938812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.209300994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6649265289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6938552856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7661771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9325170516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0410022735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9469814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6432275772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2816200256348</t>
+    <t xml:space="preserve">15.0284948348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2093000411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.664924621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6938533782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7661781311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9325180053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0409984588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.946982383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6432294845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2816190719604</t>
   </si>
   <si>
     <t xml:space="preserve">15.2888507843018</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2599239349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3250141143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2382278442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1586723327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0574226379395</t>
+    <t xml:space="preserve">15.2599248886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3250131607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2382259368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1586713790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0574235916138</t>
   </si>
   <si>
     <t xml:space="preserve">15.1803693771362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2454605102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8983154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.869384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8259925842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9634037017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9706382751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6813488006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7536725997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6958122253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8910827636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.493311882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8549222946167</t>
+    <t xml:space="preserve">15.245457649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8983144760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8693828582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8259916305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9634065628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9706354141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6813497543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7536706924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6958150863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8910799026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4933109283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.854923248291</t>
   </si>
   <si>
     <t xml:space="preserve">14.6524200439453</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6090288162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8476886749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1948356628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3394794464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4334955215454</t>
+    <t xml:space="preserve">14.6090269088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8476905822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1948328018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3394784927368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4334983825684</t>
   </si>
   <si>
     <t xml:space="preserve">16.2651977539062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9956493377686</t>
+    <t xml:space="preserve">16.9956474304199</t>
   </si>
   <si>
     <t xml:space="preserve">17.5742244720459</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6879825592041</t>
+    <t xml:space="preserve">18.6879844665527</t>
   </si>
   <si>
     <t xml:space="preserve">18.3986968994141</t>
@@ -881,10 +881,10 @@
     <t xml:space="preserve">18.4420890808105</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2178897857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0804786682129</t>
+    <t xml:space="preserve">18.2178916931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0804805755615</t>
   </si>
   <si>
     <t xml:space="preserve">18.1889629364014</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">17.9719944000244</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0081577301025</t>
+    <t xml:space="preserve">18.0081539154053</t>
   </si>
   <si>
     <t xml:space="preserve">17.8562812805176</t>
@@ -902,49 +902,49 @@
     <t xml:space="preserve">17.9647617340088</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6393146514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7622623443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6031532287598</t>
+    <t xml:space="preserve">17.6393127441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7622604370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6031551361084</t>
   </si>
   <si>
     <t xml:space="preserve">17.5886898040771</t>
   </si>
   <si>
-    <t xml:space="preserve">17.538064956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5019035339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3861885070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3210964202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2849349975586</t>
+    <t xml:space="preserve">17.5380630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5019016265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3861904144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3211002349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2849388122559</t>
   </si>
   <si>
     <t xml:space="preserve">17.0462760925293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.263240814209</t>
+    <t xml:space="preserve">17.2632389068604</t>
   </si>
   <si>
     <t xml:space="preserve">17.0969009399414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3283309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3572578430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4006500244141</t>
+    <t xml:space="preserve">17.3283271789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3572616577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4006519317627</t>
   </si>
   <si>
     <t xml:space="preserve">17.3789577484131</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">17.2921695709229</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3427963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1692237854004</t>
+    <t xml:space="preserve">17.342794418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1692199707031</t>
   </si>
   <si>
     <t xml:space="preserve">16.590648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6268100738525</t>
+    <t xml:space="preserve">16.6268081665039</t>
   </si>
   <si>
     <t xml:space="preserve">16.9233283996582</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">15.9180536270142</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6504611968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4749355316162</t>
+    <t xml:space="preserve">15.6504640579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4749336242676</t>
   </si>
   <si>
     <t xml:space="preserve">16.301362991333</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5761814117432</t>
+    <t xml:space="preserve">16.5761833190918</t>
   </si>
   <si>
     <t xml:space="preserve">16.5110950469971</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">16.0699291229248</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5255584716797</t>
+    <t xml:space="preserve">16.5255565643311</t>
   </si>
   <si>
     <t xml:space="preserve">16.4098434448242</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">16.2073421478271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8746604919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2435035705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4460067749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2001094818115</t>
+    <t xml:space="preserve">15.874659538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2434997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4460048675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2001075744629</t>
   </si>
   <si>
     <t xml:space="preserve">15.8312664031982</t>
@@ -1028,49 +1028,49 @@
     <t xml:space="preserve">15.8601951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8529634475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6287631988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4696588516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.462423324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215324401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9976100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2362728118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1639499664307</t>
+    <t xml:space="preserve">15.8529653549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6287670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4696578979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4624252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215333938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9976062774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2362689971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1639461517334</t>
   </si>
   <si>
     <t xml:space="preserve">16.2724323272705</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7786846160889</t>
+    <t xml:space="preserve">16.7786865234375</t>
   </si>
   <si>
     <t xml:space="preserve">16.6340408325195</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4532356262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7425212860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5978813171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7063636779785</t>
+    <t xml:space="preserve">16.4532337188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7425231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.59787940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7063617706299</t>
   </si>
   <si>
     <t xml:space="preserve">16.8510055541992</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">17.0318088531494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2126159667969</t>
+    <t xml:space="preserve">17.2126140594482</t>
   </si>
   <si>
     <t xml:space="preserve">17.4295806884766</t>
@@ -1091,13 +1091,13 @@
     <t xml:space="preserve">16.3809146881104</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9831428527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9108219146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7300157546997</t>
+    <t xml:space="preserve">15.9831457138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9108190536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7300148010254</t>
   </si>
   <si>
     <t xml:space="preserve">15.3684062957764</t>
@@ -1106,10 +1106,10 @@
     <t xml:space="preserve">15.4045677185059</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4768896102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8023386001587</t>
+    <t xml:space="preserve">15.4768915176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8023376464844</t>
   </si>
   <si>
     <t xml:space="preserve">16.6702003479004</t>
@@ -1124,49 +1124,49 @@
     <t xml:space="preserve">16.8148460388184</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0679702758789</t>
+    <t xml:space="preserve">17.0679721832275</t>
   </si>
   <si>
     <t xml:space="preserve">16.8871669769287</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8273525238037</t>
+    <t xml:space="preserve">17.8273487091064</t>
   </si>
   <si>
     <t xml:space="preserve">17.6827087402344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3934173583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.248779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7550277709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8996753692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5867290496826</t>
+    <t xml:space="preserve">17.3934192657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2487773895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7550315856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8996715545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5867347717285</t>
   </si>
   <si>
     <t xml:space="preserve">18.6590538024902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0206604003906</t>
+    <t xml:space="preserve">19.0206642150879</t>
   </si>
   <si>
     <t xml:space="preserve">19.5428009033203</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2444381713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9157562255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4378910064697</t>
+    <t xml:space="preserve">19.2444362640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9157543182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4378890991211</t>
   </si>
   <si>
     <t xml:space="preserve">19.6546840667725</t>
@@ -1184,40 +1184,40 @@
     <t xml:space="preserve">18.8714809417725</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9460735321045</t>
+    <t xml:space="preserve">18.9460716247559</t>
   </si>
   <si>
     <t xml:space="preserve">18.7968921661377</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9018001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3050746917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7899188995361</t>
+    <t xml:space="preserve">17.9018020629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3050765991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7899150848389</t>
   </si>
   <si>
     <t xml:space="preserve">18.8341865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1698455810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3936195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5055027008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8038673400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8784599304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6919803619385</t>
+    <t xml:space="preserve">19.1698474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3936176300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5055065155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8038692474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8784561157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6919784545898</t>
   </si>
   <si>
     <t xml:space="preserve">19.3190288543701</t>
@@ -1226,28 +1226,31 @@
     <t xml:space="preserve">18.4239387512207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1325492858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3563251495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7292785644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7223014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9087791442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6477088928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5731182098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5358238220215</t>
+    <t xml:space="preserve">19.1325511932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3563213348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0206661224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7292766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7223033905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9087772369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6477108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5731163024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5358219146729</t>
   </si>
   <si>
     <t xml:space="preserve">17.9763927459717</t>
@@ -1256,88 +1259,88 @@
     <t xml:space="preserve">18.1255722045898</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4612312316895</t>
+    <t xml:space="preserve">18.4612331390381</t>
   </si>
   <si>
     <t xml:space="preserve">18.7595977783203</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6104145050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3493499755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6850051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3120498657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4985275268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2817325592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0579566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1628704071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0136890411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3866424560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1558933258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1862144470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5894832611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1419401168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9554634094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0370311737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5218696594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6640748977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1046457290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9927597045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0300531387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7689847946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3661947250366</t>
+    <t xml:space="preserve">18.6104164123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.34934425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6850032806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3120517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4985294342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2817344665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0579586029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1628684997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0136871337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3866405487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1558952331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1862106323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.589485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1419410705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9554643630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0370292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5218677520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6640758514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1046466827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9927587509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0300512313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.768985748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3661956787109</t>
   </si>
   <si>
     <t xml:space="preserve">14.5153751373291</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6198034286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8883304595947</t>
+    <t xml:space="preserve">14.6198043823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.888331413269</t>
   </si>
   <si>
     <t xml:space="preserve">15.2538280487061</t>
@@ -1349,10 +1352,10 @@
     <t xml:space="preserve">15.9251441955566</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7759628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7013731002808</t>
+    <t xml:space="preserve">15.7759618759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7013702392578</t>
   </si>
   <si>
     <t xml:space="preserve">15.5521898269653</t>
@@ -1361,37 +1364,37 @@
     <t xml:space="preserve">15.626781463623</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5148935317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2911224365234</t>
+    <t xml:space="preserve">15.5148954391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2911205291748</t>
   </si>
   <si>
     <t xml:space="preserve">15.21653175354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1792364120483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8505544662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8132591247559</t>
+    <t xml:space="preserve">15.179235458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8505535125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8132562637329</t>
   </si>
   <si>
     <t xml:space="preserve">16.0743255615234</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8878507614136</t>
+    <t xml:space="preserve">15.8878479003906</t>
   </si>
   <si>
     <t xml:space="preserve">15.4030065536499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9032497406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7093124389648</t>
+    <t xml:space="preserve">14.9032468795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7093133926392</t>
   </si>
   <si>
     <t xml:space="preserve">15.4403038024902</t>
@@ -1400,7 +1403,7 @@
     <t xml:space="preserve">16.1116199493408</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9624366760254</t>
+    <t xml:space="preserve">15.9624404907227</t>
   </si>
   <si>
     <t xml:space="preserve">16.5591659545898</t>
@@ -1409,52 +1412,52 @@
     <t xml:space="preserve">16.3726902008057</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4845733642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.78293800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8948268890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7386665344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657131195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8435745239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8584957122803</t>
+    <t xml:space="preserve">16.4845771789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7829399108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8948249816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7386674880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657121658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8435764312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8584938049316</t>
   </si>
   <si>
     <t xml:space="preserve">15.0673503875732</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8734130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9181699752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.409984588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2235088348389</t>
+    <t xml:space="preserve">14.8734140396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9181680679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4099826812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2235050201416</t>
   </si>
   <si>
     <t xml:space="preserve">16.2980976104736</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6710548400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7083492279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7456455230713</t>
+    <t xml:space="preserve">16.6710529327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7083473205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7456436157227</t>
   </si>
   <si>
     <t xml:space="preserve">16.6337566375732</t>
@@ -1466,73 +1469,73 @@
     <t xml:space="preserve">16.8575305938721</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0067100524902</t>
+    <t xml:space="preserve">17.0067119598389</t>
   </si>
   <si>
     <t xml:space="preserve">17.3796653747559</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2304859161377</t>
+    <t xml:space="preserve">17.2304840087891</t>
   </si>
   <si>
     <t xml:space="preserve">17.5288467407227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3432426452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.722749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6756725311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7532348632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3654289245605</t>
+    <t xml:space="preserve">18.343240737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7227516174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6756744384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7532329559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3654308319092</t>
   </si>
   <si>
     <t xml:space="preserve">16.0939636230469</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6673765182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6285963058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0468854904175</t>
+    <t xml:space="preserve">15.6673774719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6285943984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0468864440918</t>
   </si>
   <si>
     <t xml:space="preserve">15.2640590667725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7061576843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5898160934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5122528076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7449378967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950839996338</t>
+    <t xml:space="preserve">15.7061595916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5898170471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5122537612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7449388504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950811386108</t>
   </si>
   <si>
     <t xml:space="preserve">15.0158624649048</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1864986419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4191789627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4967403411865</t>
+    <t xml:space="preserve">15.1864957809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4191808700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4967422485352</t>
   </si>
   <si>
     <t xml:space="preserve">15.5510349273682</t>
@@ -1541,43 +1544,43 @@
     <t xml:space="preserve">15.3261079788208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2795715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8612794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0164012908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9388399124146</t>
+    <t xml:space="preserve">15.2795705795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8612813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0164031982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9388408660889</t>
   </si>
   <si>
     <t xml:space="preserve">15.9000597000122</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7837200164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8225002288818</t>
+    <t xml:space="preserve">15.7837209701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8225021362305</t>
   </si>
   <si>
     <t xml:space="preserve">16.3266468048096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.792013168335</t>
+    <t xml:space="preserve">16.7920150756836</t>
   </si>
   <si>
     <t xml:space="preserve">17.0247001647949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9083557128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4817695617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5593299865723</t>
+    <t xml:space="preserve">16.9083576202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4817714691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5593338012695</t>
   </si>
   <si>
     <t xml:space="preserve">16.0551834106445</t>
@@ -1589,13 +1592,13 @@
     <t xml:space="preserve">16.1327457427979</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2878684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1715278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9776220321655</t>
+    <t xml:space="preserve">16.2878665924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1715240478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9776201248169</t>
   </si>
   <si>
     <t xml:space="preserve">15.3881559371948</t>
@@ -1604,103 +1607,103 @@
     <t xml:space="preserve">15.4346923828125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2103061676025</t>
+    <t xml:space="preserve">16.2103042602539</t>
   </si>
   <si>
     <t xml:space="preserve">16.4429893493652</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5981101989746</t>
+    <t xml:space="preserve">16.5981140136719</t>
   </si>
   <si>
     <t xml:space="preserve">16.5205497741699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6368923187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2490863800049</t>
+    <t xml:space="preserve">16.6368942260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2490882873535</t>
   </si>
   <si>
     <t xml:space="preserve">16.8307952880859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9859161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8390922546387</t>
+    <t xml:space="preserve">16.9859180450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8390941619873</t>
   </si>
   <si>
     <t xml:space="preserve">17.567626953125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9942169189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6147041320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2656784057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8473873138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5371437072754</t>
+    <t xml:space="preserve">17.9942150115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6147060394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2656803131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8473892211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5371417999268</t>
   </si>
   <si>
     <t xml:space="preserve">18.0717754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4595794677734</t>
+    <t xml:space="preserve">18.4595813751221</t>
   </si>
   <si>
     <t xml:space="preserve">18.7698268890381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9249515533447</t>
+    <t xml:space="preserve">18.9249534606934</t>
   </si>
   <si>
     <t xml:space="preserve">19.1576347351074</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0025100708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0412902832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3044605255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1493377685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0329971313477</t>
+    <t xml:space="preserve">19.0025119781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0412940979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3044586181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1493396759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.032995223999</t>
   </si>
   <si>
     <t xml:space="preserve">18.226900100708</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4208011627197</t>
+    <t xml:space="preserve">18.4207992553711</t>
   </si>
   <si>
     <t xml:space="preserve">18.498363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1105575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6839694976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8086071014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3820209503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.188117980957</t>
+    <t xml:space="preserve">18.110559463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.683967590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8086090087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.382022857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1881198883057</t>
   </si>
   <si>
     <t xml:space="preserve">17.916654586792</t>
@@ -1712,10 +1715,10 @@
     <t xml:space="preserve">17.6064109802246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.645191192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.141040802002</t>
+    <t xml:space="preserve">17.6451873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1410427093506</t>
   </si>
   <si>
     <t xml:space="preserve">17.1022605895996</t>
@@ -1724,19 +1727,19 @@
     <t xml:space="preserve">17.2961616516113</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1244478225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7676668167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.557710647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9610300064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0302934646606</t>
+    <t xml:space="preserve">15.1244487762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7676658630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5577096939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9610290527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0302925109863</t>
   </si>
   <si>
     <t xml:space="preserve">13.1854152679443</t>
@@ -1748,19 +1751,19 @@
     <t xml:space="preserve">13.573221206665</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2629776000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1699028015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9527339935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5649261474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7582883834839</t>
+    <t xml:space="preserve">13.262978553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.169903755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.952733039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5649271011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7582893371582</t>
   </si>
   <si>
     <t xml:space="preserve">11.5566291809082</t>
@@ -1772,13 +1775,13 @@
     <t xml:space="preserve">10.7810163497925</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3156490325928</t>
+    <t xml:space="preserve">10.3156499862671</t>
   </si>
   <si>
     <t xml:space="preserve">10.8197975158691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1300430297852</t>
+    <t xml:space="preserve">11.1300439834595</t>
   </si>
   <si>
     <t xml:space="preserve">11.7893133163452</t>
@@ -1793,25 +1796,25 @@
     <t xml:space="preserve">11.6341896057129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0219974517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0607786178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8280944824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4790678024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7117519378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6729717254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5954103469849</t>
+    <t xml:space="preserve">12.0219964981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0607767105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8280935287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4790687561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7117538452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6729707717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5954113006592</t>
   </si>
   <si>
     <t xml:space="preserve">11.2851648330688</t>
@@ -1820,37 +1823,37 @@
     <t xml:space="preserve">11.4015064239502</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7505331039429</t>
+    <t xml:space="preserve">11.7505321502686</t>
   </si>
   <si>
     <t xml:space="preserve">10.9749193191528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5095520019531</t>
+    <t xml:space="preserve">10.5095529556274</t>
   </si>
   <si>
     <t xml:space="preserve">10.5871133804321</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6646757125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2463846206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2158994674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.371021270752</t>
+    <t xml:space="preserve">10.6646738052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2463836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2159013748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3710231781006</t>
   </si>
   <si>
     <t xml:space="preserve">14.0773696899414</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1181735992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.036566734314</t>
+    <t xml:space="preserve">14.1181745529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0365676879883</t>
   </si>
   <si>
     <t xml:space="preserve">13.8733501434326</t>
@@ -1862,34 +1865,34 @@
     <t xml:space="preserve">14.199782371521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6078233718872</t>
+    <t xml:space="preserve">14.6078224182129</t>
   </si>
   <si>
     <t xml:space="preserve">14.2813892364502</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4245071411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5469198226929</t>
+    <t xml:space="preserve">13.4245080947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5469179153442</t>
   </si>
   <si>
     <t xml:space="preserve">13.5061140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7509393692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9549579620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5262145996094</t>
+    <t xml:space="preserve">13.7509384155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9549589157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5262136459351</t>
   </si>
   <si>
     <t xml:space="preserve">14.7710380554199</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6894311904907</t>
+    <t xml:space="preserve">14.6894292831421</t>
   </si>
   <si>
     <t xml:space="preserve">14.322193145752</t>
@@ -1898,25 +1901,25 @@
     <t xml:space="preserve">14.4038019180298</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5877227783203</t>
+    <t xml:space="preserve">13.587721824646</t>
   </si>
   <si>
     <t xml:space="preserve">13.465311050415</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6285285949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9141530990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2405881881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9957618713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1589794158936</t>
+    <t xml:space="preserve">13.6285276412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9141550064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2405872344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9957628250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1589784622192</t>
   </si>
   <si>
     <t xml:space="preserve">13.7917423248291</t>
@@ -1928,22 +1931,16 @@
     <t xml:space="preserve">13.2204875946045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0773706436157</t>
-  </si>
-  <si>
     <t xml:space="preserve">13.3428993225098</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7101354598999</t>
+    <t xml:space="preserve">13.7101345062256</t>
   </si>
   <si>
     <t xml:space="preserve">13.0572710037231</t>
   </si>
   <si>
-    <t xml:space="preserve">13.138879776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2612905502319</t>
+    <t xml:space="preserve">13.2612915039062</t>
   </si>
   <si>
     <t xml:space="preserve">13.0980739593506</t>
@@ -1958,13 +1955,13 @@
     <t xml:space="preserve">12.7308387756348</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6900367736816</t>
+    <t xml:space="preserve">12.690034866333</t>
   </si>
   <si>
     <t xml:space="preserve">12.9756631851196</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7716426849365</t>
+    <t xml:space="preserve">12.7716436386108</t>
   </si>
   <si>
     <t xml:space="preserve">14.8526468276978</t>
@@ -1973,7 +1970,7 @@
     <t xml:space="preserve">15.2606868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.423900604248</t>
+    <t xml:space="preserve">15.4239015579224</t>
   </si>
   <si>
     <t xml:space="preserve">16.0767669677734</t>
@@ -1985,28 +1982,28 @@
     <t xml:space="preserve">15.5055084228516</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6687259674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5871181488037</t>
+    <t xml:space="preserve">15.6687250137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5871171951294</t>
   </si>
   <si>
     <t xml:space="preserve">15.3014898300171</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3830976486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3422918319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7503318786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2198829650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1790800094604</t>
+    <t xml:space="preserve">15.3830986022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3422927856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7503337860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2198810577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1790781021118</t>
   </si>
   <si>
     <t xml:space="preserve">15.4647054672241</t>
@@ -2018,28 +2015,28 @@
     <t xml:space="preserve">16.1583728790283</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8112354278564</t>
+    <t xml:space="preserve">16.8112373352051</t>
   </si>
   <si>
     <t xml:space="preserve">17.7089233398438</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1376705169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3824901580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8928451538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1991767883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.484806060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6480197906494</t>
+    <t xml:space="preserve">17.1376686096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3824920654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.89284324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1991786956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4848041534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.648021697998</t>
   </si>
   <si>
     <t xml:space="preserve">16.5664138793945</t>
@@ -2048,10 +2045,10 @@
     <t xml:space="preserve">16.2399806976318</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4031982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7296276092529</t>
+    <t xml:space="preserve">16.4031963348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7296295166016</t>
   </si>
   <si>
     <t xml:space="preserve">17.2192764282227</t>
@@ -2060,10 +2057,10 @@
     <t xml:space="preserve">17.4640998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5457077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9537487030029</t>
+    <t xml:space="preserve">17.5457096099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9537467956543</t>
   </si>
   <si>
     <t xml:space="preserve">18.0353565216064</t>
@@ -2072,25 +2069,25 @@
     <t xml:space="preserve">16.9744529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8721389770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1169662475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1985702514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3617858886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1778678894043</t>
+    <t xml:space="preserve">17.8721408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1169624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1985721588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3617877960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1778659820557</t>
   </si>
   <si>
     <t xml:space="preserve">18.8514366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6882190704346</t>
+    <t xml:space="preserve">18.6882209777832</t>
   </si>
   <si>
     <t xml:space="preserve">19.0962600708008</t>
@@ -2099,7 +2096,7 @@
     <t xml:space="preserve">18.6066112518311</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9330444335938</t>
+    <t xml:space="preserve">18.9330425262451</t>
   </si>
   <si>
     <t xml:space="preserve">19.2594757080078</t>
@@ -2111,25 +2108,28 @@
     <t xml:space="preserve">19.4226894378662</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0146522521973</t>
+    <t xml:space="preserve">19.0146503448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9123401641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8276062011719</t>
   </si>
   <si>
     <t xml:space="preserve">19.9123382568359</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8276062011719</t>
-  </si>
-  <si>
     <t xml:space="preserve">19.4886722564697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6581401824951</t>
+    <t xml:space="preserve">19.6581382751465</t>
   </si>
   <si>
     <t xml:space="preserve">19.5734062194824</t>
   </si>
   <si>
-    <t xml:space="preserve">19.403938293457</t>
+    <t xml:space="preserve">19.4039402008057</t>
   </si>
   <si>
     <t xml:space="preserve">19.9970722198486</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">20.1665382385254</t>
   </si>
   <si>
-    <t xml:space="preserve">19.319206237793</t>
+    <t xml:space="preserve">19.3192043304443</t>
   </si>
   <si>
     <t xml:space="preserve">19.0650062561035</t>
@@ -2150,19 +2150,19 @@
     <t xml:space="preserve">18.6413383483887</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7428722381592</t>
+    <t xml:space="preserve">19.7428703308105</t>
   </si>
   <si>
     <t xml:space="preserve">20.0818061828613</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4207382202148</t>
+    <t xml:space="preserve">20.4207401275635</t>
   </si>
   <si>
     <t xml:space="preserve">20.5054721832275</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6749382019043</t>
+    <t xml:space="preserve">20.6749401092529</t>
   </si>
   <si>
     <t xml:space="preserve">20.9291400909424</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">22.0306739807129</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4543380737305</t>
+    <t xml:space="preserve">22.4543399810791</t>
   </si>
   <si>
     <t xml:space="preserve">22.2001399993896</t>
@@ -2204,16 +2204,16 @@
     <t xml:space="preserve">23.555871963501</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3016738891602</t>
+    <t xml:space="preserve">23.3016719818115</t>
   </si>
   <si>
     <t xml:space="preserve">23.4711399078369</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3864059448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.725341796875</t>
+    <t xml:space="preserve">23.3864078521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7253398895264</t>
   </si>
   <si>
     <t xml:space="preserve">23.1322059631348</t>
@@ -2228,13 +2228,13 @@
     <t xml:space="preserve">22.8780059814453</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1490077972412</t>
+    <t xml:space="preserve">24.1490058898926</t>
   </si>
   <si>
     <t xml:space="preserve">25.165807723999</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9116058349609</t>
+    <t xml:space="preserve">24.9116077423096</t>
   </si>
   <si>
     <t xml:space="preserve">24.2337417602539</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">24.5726718902588</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4032039642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4879379272461</t>
+    <t xml:space="preserve">24.403205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4879398345947</t>
   </si>
   <si>
     <t xml:space="preserve">25.0810737609863</t>
@@ -2270,28 +2270,28 @@
     <t xml:space="preserve">25.7589416503906</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2673416137695</t>
+    <t xml:space="preserve">26.2673397064209</t>
   </si>
   <si>
     <t xml:space="preserve">26.4368057250977</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5215396881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8772754669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5719451904297</t>
+    <t xml:space="preserve">26.521541595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8772773742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5719432830811</t>
   </si>
   <si>
     <t xml:space="preserve">29.317741394043</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9788074493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1482753753662</t>
+    <t xml:space="preserve">28.9788093566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1482772827148</t>
   </si>
   <si>
     <t xml:space="preserve">29.2330074310303</t>
@@ -2300,25 +2300,25 @@
     <t xml:space="preserve">27.962007522583</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0299396514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4704093933105</t>
+    <t xml:space="preserve">27.0299415588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4704074859619</t>
   </si>
   <si>
     <t xml:space="preserve">27.4536094665527</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3856773376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7078094482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1314754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2841415405273</t>
+    <t xml:space="preserve">28.3856754302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7078075408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1314735412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2841396331787</t>
   </si>
   <si>
     <t xml:space="preserve">25.6742076873779</t>
@@ -2327,13 +2327,13 @@
     <t xml:space="preserve">26.0131416320801</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8436756134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3520755767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.606273651123</t>
+    <t xml:space="preserve">25.8436737060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3520736694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6062755584717</t>
   </si>
   <si>
     <t xml:space="preserve">24.8268737792969</t>
@@ -2351,13 +2351,13 @@
     <t xml:space="preserve">26.6910076141357</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5390720367432</t>
+    <t xml:space="preserve">22.5390739440918</t>
   </si>
   <si>
     <t xml:space="preserve">24.0642738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">22.962739944458</t>
+    <t xml:space="preserve">22.9627418518066</t>
   </si>
   <si>
     <t xml:space="preserve">24.318473815918</t>
@@ -3582,6 +3582,9 @@
   </si>
   <si>
     <t xml:space="preserve">57.7000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.4000015258789</t>
   </si>
 </sst>
 </file>
@@ -20422,7 +20425,7 @@
         <v>25.5</v>
       </c>
       <c r="G635" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20448,7 +20451,7 @@
         <v>25.5</v>
       </c>
       <c r="G636" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20474,7 +20477,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G637" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20500,7 +20503,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G638" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20526,7 +20529,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G639" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20552,7 +20555,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G640" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20630,7 +20633,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G643" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20656,7 +20659,7 @@
         <v>25</v>
       </c>
       <c r="G644" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20682,7 +20685,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G645" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20708,7 +20711,7 @@
         <v>25</v>
       </c>
       <c r="G646" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20734,7 +20737,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G647" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20760,7 +20763,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G648" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20786,7 +20789,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G649" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20812,7 +20815,7 @@
         <v>24.75</v>
       </c>
       <c r="G650" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20838,7 +20841,7 @@
         <v>24.75</v>
       </c>
       <c r="G651" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20864,7 +20867,7 @@
         <v>24.75</v>
       </c>
       <c r="G652" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20942,7 +20945,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G655" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20968,7 +20971,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G656" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -21020,7 +21023,7 @@
         <v>25</v>
       </c>
       <c r="G658" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -21046,7 +21049,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G659" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -21098,7 +21101,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G661" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -21124,7 +21127,7 @@
         <v>25</v>
       </c>
       <c r="G662" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -21150,7 +21153,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G663" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -21176,7 +21179,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G664" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -21202,7 +21205,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G665" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21228,7 +21231,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G666" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21280,7 +21283,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G668" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21306,7 +21309,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G669" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21358,7 +21361,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G671" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21384,7 +21387,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G672" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21410,7 +21413,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G673" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21462,7 +21465,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21488,7 +21491,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G676" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21540,7 +21543,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G678" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21592,7 +21595,7 @@
         <v>25</v>
       </c>
       <c r="G680" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21618,7 +21621,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G681" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21644,7 +21647,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G682" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21670,7 +21673,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G683" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21696,7 +21699,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G684" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21722,7 +21725,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21852,7 +21855,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G690" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21878,7 +21881,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G691" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21904,7 +21907,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G692" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21930,7 +21933,7 @@
         <v>25</v>
       </c>
       <c r="G693" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21956,7 +21959,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G694" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -22008,7 +22011,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G696" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -22034,7 +22037,7 @@
         <v>24.75</v>
       </c>
       <c r="G697" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -22060,7 +22063,7 @@
         <v>24.75</v>
       </c>
       <c r="G698" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -22086,7 +22089,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G699" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -22112,7 +22115,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -22138,7 +22141,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G701" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -22164,7 +22167,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G702" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -22190,7 +22193,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G703" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22216,7 +22219,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G704" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -22242,7 +22245,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G705" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -22294,7 +22297,7 @@
         <v>23</v>
       </c>
       <c r="G707" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22320,7 +22323,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G708" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22346,7 +22349,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G709" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22372,7 +22375,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G710" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22398,7 +22401,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G711" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22424,7 +22427,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G712" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22450,7 +22453,7 @@
         <v>21.5</v>
       </c>
       <c r="G713" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22476,7 +22479,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22502,7 +22505,7 @@
         <v>21</v>
       </c>
       <c r="G715" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22528,7 +22531,7 @@
         <v>20.25</v>
       </c>
       <c r="G716" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22554,7 +22557,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22580,7 +22583,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G718" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22606,7 +22609,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G719" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22632,7 +22635,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G720" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22658,7 +22661,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G721" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22684,7 +22687,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G722" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22710,7 +22713,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G723" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22736,7 +22739,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G724" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22762,7 +22765,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G725" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22788,7 +22791,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G726" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22814,7 +22817,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G727" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22840,7 +22843,7 @@
         <v>21</v>
       </c>
       <c r="G728" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22866,7 +22869,7 @@
         <v>21.5</v>
       </c>
       <c r="G729" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22892,7 +22895,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G730" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22918,7 +22921,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G731" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22944,7 +22947,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G732" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22970,7 +22973,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G733" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22996,7 +22999,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G734" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -23022,7 +23025,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -23048,7 +23051,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G736" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -23074,7 +23077,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G737" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -23100,7 +23103,7 @@
         <v>20.5</v>
       </c>
       <c r="G738" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -23126,7 +23129,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G739" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -23152,7 +23155,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G740" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -23178,7 +23181,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G741" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -23204,7 +23207,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G742" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23230,7 +23233,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23256,7 +23259,7 @@
         <v>21.25</v>
       </c>
       <c r="G744" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23282,7 +23285,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G745" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23308,7 +23311,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G746" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23334,7 +23337,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G747" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23360,7 +23363,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G748" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23386,7 +23389,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G749" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23412,7 +23415,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G750" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23438,7 +23441,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G751" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23464,7 +23467,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G752" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23490,7 +23493,7 @@
         <v>21</v>
       </c>
       <c r="G753" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23516,7 +23519,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G754" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23542,7 +23545,7 @@
         <v>21</v>
       </c>
       <c r="G755" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23568,7 +23571,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G756" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23594,7 +23597,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G757" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23620,7 +23623,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G758" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23646,7 +23649,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G759" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23672,7 +23675,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G760" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23698,7 +23701,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G761" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23724,7 +23727,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G762" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23750,7 +23753,7 @@
         <v>20.25</v>
       </c>
       <c r="G763" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23776,7 +23779,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G764" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23802,7 +23805,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G765" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23828,7 +23831,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G766" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23854,7 +23857,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G767" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23880,7 +23883,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G768" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23906,7 +23909,7 @@
         <v>21</v>
       </c>
       <c r="G769" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23932,7 +23935,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G770" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23958,7 +23961,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G771" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23984,7 +23987,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G772" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -24010,7 +24013,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G773" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -24036,7 +24039,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G774" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -24062,7 +24065,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G775" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -24088,7 +24091,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G776" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -24114,7 +24117,7 @@
         <v>22.5</v>
       </c>
       <c r="G777" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -24140,7 +24143,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G778" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -24166,7 +24169,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G779" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -24192,7 +24195,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G780" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -24218,7 +24221,7 @@
         <v>21.5</v>
       </c>
       <c r="G781" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -24244,7 +24247,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G782" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -24270,7 +24273,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G783" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -24296,7 +24299,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G784" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -24322,7 +24325,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G785" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -24348,7 +24351,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G786" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -24374,7 +24377,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G787" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -24400,7 +24403,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G788" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -24426,7 +24429,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G789" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -24452,7 +24455,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G790" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -24478,7 +24481,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G791" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -24504,7 +24507,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G792" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -24530,7 +24533,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G793" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24556,7 +24559,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G794" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24582,7 +24585,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G795" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24608,7 +24611,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G796" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24634,7 +24637,7 @@
         <v>20.25</v>
       </c>
       <c r="G797" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24660,7 +24663,7 @@
         <v>20</v>
       </c>
       <c r="G798" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24686,7 +24689,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G799" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24712,7 +24715,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G800" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24738,7 +24741,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G801" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24764,7 +24767,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G802" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24790,7 +24793,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G803" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24816,7 +24819,7 @@
         <v>20.25</v>
       </c>
       <c r="G804" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24842,7 +24845,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G805" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24868,7 +24871,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G806" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24894,7 +24897,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G807" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24920,7 +24923,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G808" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24946,7 +24949,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G809" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24972,7 +24975,7 @@
         <v>20.5</v>
       </c>
       <c r="G810" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24998,7 +25001,7 @@
         <v>20</v>
       </c>
       <c r="G811" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -25024,7 +25027,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G812" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -25050,7 +25053,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G813" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -25076,7 +25079,7 @@
         <v>20.25</v>
       </c>
       <c r="G814" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -25102,7 +25105,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G815" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -25128,7 +25131,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G816" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -25154,7 +25157,7 @@
         <v>20.25</v>
       </c>
       <c r="G817" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -25180,7 +25183,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -25206,7 +25209,7 @@
         <v>21</v>
       </c>
       <c r="G819" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -25232,7 +25235,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G820" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -25258,7 +25261,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G821" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -25284,7 +25287,7 @@
         <v>21.5</v>
       </c>
       <c r="G822" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -25310,7 +25313,7 @@
         <v>22</v>
       </c>
       <c r="G823" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -25336,7 +25339,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G824" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -25362,7 +25365,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G825" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -25388,7 +25391,7 @@
         <v>21.75</v>
       </c>
       <c r="G826" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -25414,7 +25417,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G827" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -25440,7 +25443,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G828" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -25466,7 +25469,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G829" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -25492,7 +25495,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -25518,7 +25521,7 @@
         <v>21.75</v>
       </c>
       <c r="G831" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25544,7 +25547,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G832" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25570,7 +25573,7 @@
         <v>22</v>
       </c>
       <c r="G833" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25596,7 +25599,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G834" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25622,7 +25625,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G835" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25648,7 +25651,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G836" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25674,7 +25677,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G837" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25700,7 +25703,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G838" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25726,7 +25729,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G839" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25752,7 +25755,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25778,7 +25781,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G841" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25804,7 +25807,7 @@
         <v>22.5</v>
       </c>
       <c r="G842" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25830,7 +25833,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G843" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25856,7 +25859,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G844" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25882,7 +25885,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G845" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25908,7 +25911,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G846" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25934,7 +25937,7 @@
         <v>23.5</v>
       </c>
       <c r="G847" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25960,7 +25963,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25986,7 +25989,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G849" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -26012,7 +26015,7 @@
         <v>21.5</v>
       </c>
       <c r="G850" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -26038,7 +26041,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -26064,7 +26067,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -26090,7 +26093,7 @@
         <v>20.75</v>
       </c>
       <c r="G853" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -26116,7 +26119,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G854" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -26142,7 +26145,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G855" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -26168,7 +26171,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G856" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -26194,7 +26197,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G857" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26220,7 +26223,7 @@
         <v>20.25</v>
       </c>
       <c r="G858" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26246,7 +26249,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G859" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -26272,7 +26275,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G860" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -26298,7 +26301,7 @@
         <v>20</v>
       </c>
       <c r="G861" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -26324,7 +26327,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G862" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -26350,7 +26353,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G863" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -26376,7 +26379,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G864" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -26402,7 +26405,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G865" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26428,7 +26431,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G866" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -26454,7 +26457,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G867" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -26480,7 +26483,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G868" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -26506,7 +26509,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G869" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -26532,7 +26535,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -26558,7 +26561,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G871" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -26584,7 +26587,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G872" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26610,7 +26613,7 @@
         <v>20</v>
       </c>
       <c r="G873" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -26636,7 +26639,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G874" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26662,7 +26665,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G875" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26688,7 +26691,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G876" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26714,7 +26717,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G877" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26740,7 +26743,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G878" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26766,7 +26769,7 @@
         <v>20.25</v>
       </c>
       <c r="G879" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26792,7 +26795,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26818,7 +26821,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G881" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26844,7 +26847,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G882" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26870,7 +26873,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G883" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26896,7 +26899,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G884" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26922,7 +26925,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G885" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26948,7 +26951,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G886" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26974,7 +26977,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G887" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -27000,7 +27003,7 @@
         <v>20.25</v>
       </c>
       <c r="G888" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -27026,7 +27029,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G889" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -27052,7 +27055,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G890" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -27078,7 +27081,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G891" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -27104,7 +27107,7 @@
         <v>20.5</v>
       </c>
       <c r="G892" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -27130,7 +27133,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G893" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -27156,7 +27159,7 @@
         <v>20.25</v>
       </c>
       <c r="G894" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -27182,7 +27185,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -27208,7 +27211,7 @@
         <v>20.25</v>
       </c>
       <c r="G896" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -27234,7 +27237,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G897" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -27260,7 +27263,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G898" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -27286,7 +27289,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G899" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -27312,7 +27315,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G900" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -27338,7 +27341,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G901" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -27364,7 +27367,7 @@
         <v>20.25</v>
       </c>
       <c r="G902" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -27390,7 +27393,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G903" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -27416,7 +27419,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G904" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -27442,7 +27445,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G905" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -27468,7 +27471,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G906" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -27494,7 +27497,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G907" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -27520,7 +27523,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G908" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -27546,7 +27549,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G909" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -27572,7 +27575,7 @@
         <v>21.25</v>
       </c>
       <c r="G910" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27598,7 +27601,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G911" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27624,7 +27627,7 @@
         <v>21.5</v>
       </c>
       <c r="G912" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27650,7 +27653,7 @@
         <v>21.5</v>
       </c>
       <c r="G913" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27676,7 +27679,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G914" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27702,7 +27705,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G915" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27728,7 +27731,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G916" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27754,7 +27757,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G917" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -27780,7 +27783,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G918" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27806,7 +27809,7 @@
         <v>21</v>
       </c>
       <c r="G919" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27832,7 +27835,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G920" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27858,7 +27861,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G921" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27884,7 +27887,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G922" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27910,7 +27913,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G923" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27936,7 +27939,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G924" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27962,7 +27965,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G925" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27988,7 +27991,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G926" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -28014,7 +28017,7 @@
         <v>20</v>
       </c>
       <c r="G927" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -28040,7 +28043,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G928" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -28066,7 +28069,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G929" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -28092,7 +28095,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G930" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -28118,7 +28121,7 @@
         <v>20</v>
       </c>
       <c r="G931" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -28144,7 +28147,7 @@
         <v>20</v>
       </c>
       <c r="G932" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -28170,7 +28173,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G933" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -28196,7 +28199,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G934" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -28222,7 +28225,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G935" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -28248,7 +28251,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G936" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -28274,7 +28277,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G937" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -28300,7 +28303,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G938" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -28326,7 +28329,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G939" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -28352,7 +28355,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G940" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -28378,7 +28381,7 @@
         <v>21.25</v>
       </c>
       <c r="G941" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -28404,7 +28407,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G942" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -28430,7 +28433,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G943" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -28456,7 +28459,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G944" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -28482,7 +28485,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G945" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -28508,7 +28511,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G946" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -28534,7 +28537,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G947" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -28560,7 +28563,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G948" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -28586,7 +28589,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G949" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -28612,7 +28615,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G950" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -28638,7 +28641,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G951" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28664,7 +28667,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G952" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -28690,7 +28693,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G953" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28716,7 +28719,7 @@
         <v>21.25</v>
       </c>
       <c r="G954" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -28742,7 +28745,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G955" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28768,7 +28771,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28794,7 +28797,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G957" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28820,7 +28823,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G958" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28846,7 +28849,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G959" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28872,7 +28875,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G960" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28898,7 +28901,7 @@
         <v>21.25</v>
       </c>
       <c r="G961" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28924,7 +28927,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G962" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28950,7 +28953,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G963" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28976,7 +28979,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G964" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -29002,7 +29005,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G965" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -29028,7 +29031,7 @@
         <v>21.5</v>
       </c>
       <c r="G966" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -29054,7 +29057,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G967" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -29080,7 +29083,7 @@
         <v>21.25</v>
       </c>
       <c r="G968" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -29106,7 +29109,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G969" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -29132,7 +29135,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G970" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -29158,7 +29161,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G971" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -29184,7 +29187,7 @@
         <v>21.5</v>
       </c>
       <c r="G972" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -29210,7 +29213,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G973" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -29236,7 +29239,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G974" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -29262,7 +29265,7 @@
         <v>21</v>
       </c>
       <c r="G975" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -29288,7 +29291,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G976" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -29314,7 +29317,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G977" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -29340,7 +29343,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G978" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -29366,7 +29369,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G979" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -29392,7 +29395,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G980" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -29418,7 +29421,7 @@
         <v>23</v>
       </c>
       <c r="G981" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -29444,7 +29447,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G982" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -29470,7 +29473,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G983" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -29496,7 +29499,7 @@
         <v>24</v>
       </c>
       <c r="G984" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -29522,7 +29525,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G985" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -29548,7 +29551,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G986" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -29574,7 +29577,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G987" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29600,7 +29603,7 @@
         <v>24</v>
       </c>
       <c r="G988" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29626,7 +29629,7 @@
         <v>24</v>
       </c>
       <c r="G989" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29652,7 +29655,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G990" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29678,7 +29681,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G991" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29704,7 +29707,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G992" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29730,7 +29733,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G993" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29756,7 +29759,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G994" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29782,7 +29785,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G995" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29808,7 +29811,7 @@
         <v>24.5</v>
       </c>
       <c r="G996" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29834,7 +29837,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G997" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29860,7 +29863,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G998" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29886,7 +29889,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G999" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29912,7 +29915,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1000" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29938,7 +29941,7 @@
         <v>23.25</v>
       </c>
       <c r="G1001" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29964,7 +29967,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1002" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29990,7 +29993,7 @@
         <v>23.5</v>
       </c>
       <c r="G1003" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -30016,7 +30019,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1004" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -30042,7 +30045,7 @@
         <v>23.75</v>
       </c>
       <c r="G1005" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -30068,7 +30071,7 @@
         <v>23.75</v>
       </c>
       <c r="G1006" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -30094,7 +30097,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1007" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -30120,7 +30123,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1008" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -30146,7 +30149,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1009" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -30172,7 +30175,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1010" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -30198,7 +30201,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1011" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -30224,7 +30227,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1012" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -30250,7 +30253,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1013" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -30276,7 +30279,7 @@
         <v>24.25</v>
       </c>
       <c r="G1014" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -30302,7 +30305,7 @@
         <v>24</v>
       </c>
       <c r="G1015" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -30328,7 +30331,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1016" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -30354,7 +30357,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1017" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -30380,7 +30383,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1018" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -30406,7 +30409,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1019" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -30432,7 +30435,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1020" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -30458,7 +30461,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1021" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -30484,7 +30487,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G1022" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -30510,7 +30513,7 @@
         <v>23.5</v>
       </c>
       <c r="G1023" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -30536,7 +30539,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1024" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -30562,7 +30565,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1025" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -30588,7 +30591,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1026" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -30614,7 +30617,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1027" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -30640,7 +30643,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1028" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30666,7 +30669,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1029" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30692,7 +30695,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1030" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30718,7 +30721,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1031" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30744,7 +30747,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1032" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30770,7 +30773,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1033" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -30796,7 +30799,7 @@
         <v>22.75</v>
       </c>
       <c r="G1034" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -30822,7 +30825,7 @@
         <v>23.25</v>
       </c>
       <c r="G1035" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -30848,7 +30851,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1036" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -30874,7 +30877,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1037" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -30900,7 +30903,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1038" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -30926,7 +30929,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1039" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30952,7 +30955,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1040" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30978,7 +30981,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1041" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -31004,7 +31007,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1042" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -31030,7 +31033,7 @@
         <v>23.75</v>
       </c>
       <c r="G1043" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -31056,7 +31059,7 @@
         <v>23.75</v>
       </c>
       <c r="G1044" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -31082,7 +31085,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1045" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -31108,7 +31111,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1046" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -31134,7 +31137,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1047" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -31160,7 +31163,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1048" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -31186,7 +31189,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1049" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -31212,7 +31215,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1050" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -31238,7 +31241,7 @@
         <v>23.25</v>
       </c>
       <c r="G1051" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -31264,7 +31267,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1052" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -31290,7 +31293,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1053" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -31316,7 +31319,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1054" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -31342,7 +31345,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1055" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -31368,7 +31371,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1056" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -31394,7 +31397,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -31420,7 +31423,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1058" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -31446,7 +31449,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1059" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -31472,7 +31475,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1060" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -31498,7 +31501,7 @@
         <v>20.75</v>
       </c>
       <c r="G1061" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -31524,7 +31527,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1062" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -31550,7 +31553,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1063" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -31576,7 +31579,7 @@
         <v>19.5</v>
       </c>
       <c r="G1064" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -31602,7 +31605,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1065" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31628,7 +31631,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1066" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31654,7 +31657,7 @@
         <v>18</v>
       </c>
       <c r="G1067" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31680,7 +31683,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1068" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31706,7 +31709,7 @@
         <v>17</v>
       </c>
       <c r="G1069" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -31732,7 +31735,7 @@
         <v>17</v>
       </c>
       <c r="G1070" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -31758,7 +31761,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1071" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31784,7 +31787,7 @@
         <v>17.5</v>
       </c>
       <c r="G1072" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31810,7 +31813,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1073" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -31836,7 +31839,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1074" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -31862,7 +31865,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1075" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31888,7 +31891,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1076" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31914,7 +31917,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1077" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31940,7 +31943,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1078" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31966,7 +31969,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1079" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31992,7 +31995,7 @@
         <v>14</v>
       </c>
       <c r="G1080" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -32018,7 +32021,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1081" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -32044,7 +32047,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1082" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -32070,7 +32073,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1083" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -32096,7 +32099,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1084" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -32122,7 +32125,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1085" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32148,7 +32151,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1086" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -32174,7 +32177,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1087" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -32200,7 +32203,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1088" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -32226,7 +32229,7 @@
         <v>15</v>
       </c>
       <c r="G1089" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -32252,7 +32255,7 @@
         <v>15.5</v>
       </c>
       <c r="G1090" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -32278,7 +32281,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1091" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -32304,7 +32307,7 @@
         <v>15.25</v>
       </c>
       <c r="G1092" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -32330,7 +32333,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1093" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -32356,7 +32359,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1094" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -32382,7 +32385,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1095" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -32408,7 +32411,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1096" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -32434,7 +32437,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1097" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -32460,7 +32463,7 @@
         <v>15</v>
       </c>
       <c r="G1098" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -32486,7 +32489,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1099" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -32512,7 +32515,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1100" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -32538,7 +32541,7 @@
         <v>15</v>
       </c>
       <c r="G1101" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -32564,7 +32567,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1102" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -32590,7 +32593,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1103" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -32616,7 +32619,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1104" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32642,7 +32645,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1105" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -32668,7 +32671,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1106" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32694,7 +32697,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1107" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32720,7 +32723,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1108" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32746,7 +32749,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1109" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32772,7 +32775,7 @@
         <v>13.75</v>
       </c>
       <c r="G1110" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32798,7 +32801,7 @@
         <v>14</v>
       </c>
       <c r="G1111" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32824,7 +32827,7 @@
         <v>14</v>
       </c>
       <c r="G1112" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32850,7 +32853,7 @@
         <v>14.5</v>
       </c>
       <c r="G1113" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32876,7 +32879,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1114" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -32902,7 +32905,7 @@
         <v>15</v>
       </c>
       <c r="G1115" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -32928,7 +32931,7 @@
         <v>15.75</v>
       </c>
       <c r="G1116" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -32954,7 +32957,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1117" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -32980,7 +32983,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1118" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -33006,7 +33009,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1119" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -33032,7 +33035,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1120" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -33058,7 +33061,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1121" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -33084,7 +33087,7 @@
         <v>17</v>
       </c>
       <c r="G1122" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -33110,7 +33113,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1123" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -33136,7 +33139,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1124" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -33162,7 +33165,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1125" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -33188,7 +33191,7 @@
         <v>17.5</v>
       </c>
       <c r="G1126" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -33214,7 +33217,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1127" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -33240,7 +33243,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1128" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -33266,7 +33269,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1129" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -33292,7 +33295,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1130" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -33318,7 +33321,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1131" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -33344,7 +33347,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1132" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -33370,7 +33373,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1133" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -33396,7 +33399,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1134" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -33422,7 +33425,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1135" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -33448,7 +33451,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1136" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -33474,7 +33477,7 @@
         <v>18</v>
       </c>
       <c r="G1137" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -33500,7 +33503,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1138" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -33526,7 +33529,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1139" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -33552,7 +33555,7 @@
         <v>17.5</v>
       </c>
       <c r="G1140" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -33578,7 +33581,7 @@
         <v>17</v>
       </c>
       <c r="G1141" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33604,7 +33607,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1142" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33630,7 +33633,7 @@
         <v>16.5</v>
       </c>
       <c r="G1143" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33656,7 +33659,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1144" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33682,7 +33685,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1145" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33708,7 +33711,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1146" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33734,7 +33737,7 @@
         <v>17.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33760,7 +33763,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1148" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33786,7 +33789,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1149" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33812,7 +33815,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1150" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33838,7 +33841,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1151" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33864,7 +33867,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1152" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33890,7 +33893,7 @@
         <v>17.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33916,7 +33919,7 @@
         <v>17</v>
       </c>
       <c r="G1154" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33942,7 +33945,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1155" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33968,7 +33971,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1156" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -33994,7 +33997,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1157" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -34020,7 +34023,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1158" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -34046,7 +34049,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1159" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -34072,7 +34075,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1160" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -34098,7 +34101,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1161" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -34124,7 +34127,7 @@
         <v>16.5</v>
       </c>
       <c r="G1162" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -34150,7 +34153,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1163" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -34176,7 +34179,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1164" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -34202,7 +34205,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1165" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -34228,7 +34231,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1166" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -34254,7 +34257,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1167" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -34280,7 +34283,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1168" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -34306,7 +34309,7 @@
         <v>17.25</v>
       </c>
       <c r="G1169" t="s">
-        <v>638</v>
+        <v>611</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34332,7 +34335,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1170" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -34358,7 +34361,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1171" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -34384,7 +34387,7 @@
         <v>17</v>
       </c>
       <c r="G1172" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -34410,7 +34413,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1173" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -34436,7 +34439,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1174" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -34462,7 +34465,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1175" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -34488,7 +34491,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -34514,7 +34517,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1177" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34566,7 +34569,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1179" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34592,7 +34595,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1180" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34618,7 +34621,7 @@
         <v>17</v>
       </c>
       <c r="G1181" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34644,7 +34647,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1182" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34670,7 +34673,7 @@
         <v>17</v>
       </c>
       <c r="G1183" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34696,7 +34699,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1184" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34722,7 +34725,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1185" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34774,7 +34777,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1187" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34800,7 +34803,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1188" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34826,7 +34829,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1189" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34852,7 +34855,7 @@
         <v>17.25</v>
       </c>
       <c r="G1190" t="s">
-        <v>638</v>
+        <v>611</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34878,7 +34881,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1191" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34904,7 +34907,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1192" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -34930,7 +34933,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1193" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -34956,7 +34959,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1194" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34982,7 +34985,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1195" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -35008,7 +35011,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1196" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -35086,7 +35089,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1199" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35138,7 +35141,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1201" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -35164,7 +35167,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1202" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -35190,7 +35193,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1203" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -35242,7 +35245,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1205" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -35268,7 +35271,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1206" t="s">
-        <v>642</v>
+        <v>577</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35346,7 +35349,7 @@
         <v>16.25</v>
       </c>
       <c r="G1209" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -35372,7 +35375,7 @@
         <v>16.5</v>
       </c>
       <c r="G1210" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -35398,7 +35401,7 @@
         <v>16.5</v>
       </c>
       <c r="G1211" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -35424,7 +35427,7 @@
         <v>17.25</v>
       </c>
       <c r="G1212" t="s">
-        <v>638</v>
+        <v>611</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -35450,7 +35453,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1213" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -35476,7 +35479,7 @@
         <v>17</v>
       </c>
       <c r="G1214" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -35502,7 +35505,7 @@
         <v>17.25</v>
       </c>
       <c r="G1215" t="s">
-        <v>638</v>
+        <v>611</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35528,7 +35531,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1216" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35554,7 +35557,7 @@
         <v>17</v>
       </c>
       <c r="G1217" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -35580,7 +35583,7 @@
         <v>17</v>
       </c>
       <c r="G1218" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35606,7 +35609,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1219" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35632,7 +35635,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1220" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35658,7 +35661,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1221" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35684,7 +35687,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1222" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35710,7 +35713,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1223" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35736,7 +35739,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1224" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35788,7 +35791,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1226" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35814,7 +35817,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35840,7 +35843,7 @@
         <v>15.75</v>
       </c>
       <c r="G1228" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35866,7 +35869,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1229" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35892,7 +35895,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1230" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35918,7 +35921,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1231" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -35944,7 +35947,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35970,7 +35973,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35996,7 +35999,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1234" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -36048,7 +36051,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1236" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -36074,7 +36077,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1237" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -36100,7 +36103,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1238" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -36126,7 +36129,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1239" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -36152,7 +36155,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -36178,7 +36181,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1241" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -36204,7 +36207,7 @@
         <v>19.5</v>
       </c>
       <c r="G1242" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -36230,7 +36233,7 @@
         <v>19</v>
       </c>
       <c r="G1243" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -36256,7 +36259,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1244" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -36282,7 +36285,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1245" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -36308,7 +36311,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1246" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -36334,7 +36337,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1247" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -36360,7 +36363,7 @@
         <v>18.75</v>
       </c>
       <c r="G1248" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -36386,7 +36389,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1249" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -36412,7 +36415,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1250" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -36438,7 +36441,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1251" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -36464,7 +36467,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -36490,7 +36493,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1253" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -36516,7 +36519,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -36542,7 +36545,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1255" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -36568,7 +36571,7 @@
         <v>19</v>
       </c>
       <c r="G1256" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36594,7 +36597,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36620,7 +36623,7 @@
         <v>19</v>
       </c>
       <c r="G1258" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36646,7 +36649,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1259" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36672,7 +36675,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1260" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36698,7 +36701,7 @@
         <v>19</v>
       </c>
       <c r="G1261" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36724,7 +36727,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1262" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36750,7 +36753,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36776,7 +36779,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1264" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36802,7 +36805,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1265" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36828,7 +36831,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1266" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36854,7 +36857,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1267" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36880,7 +36883,7 @@
         <v>18.75</v>
       </c>
       <c r="G1268" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36906,7 +36909,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1269" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -36932,7 +36935,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1270" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -36958,7 +36961,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1271" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36984,7 +36987,7 @@
         <v>19</v>
       </c>
       <c r="G1272" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -37010,7 +37013,7 @@
         <v>20</v>
       </c>
       <c r="G1273" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -37036,7 +37039,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1274" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -37062,7 +37065,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1275" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -37088,7 +37091,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1276" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -37114,7 +37117,7 @@
         <v>21</v>
       </c>
       <c r="G1277" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -37140,7 +37143,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1278" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -37166,7 +37169,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1279" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -37192,7 +37195,7 @@
         <v>20</v>
       </c>
       <c r="G1280" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -37218,7 +37221,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1281" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -37244,7 +37247,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1282" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -37270,7 +37273,7 @@
         <v>20</v>
       </c>
       <c r="G1283" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -37296,7 +37299,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1284" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -37322,7 +37325,7 @@
         <v>20</v>
       </c>
       <c r="G1285" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -37348,7 +37351,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1286" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -37374,7 +37377,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1287" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -37400,7 +37403,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -37426,7 +37429,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1289" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -37452,7 +37455,7 @@
         <v>20</v>
       </c>
       <c r="G1290" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -37478,7 +37481,7 @@
         <v>20</v>
       </c>
       <c r="G1291" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -37504,7 +37507,7 @@
         <v>20.5</v>
       </c>
       <c r="G1292" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -37530,7 +37533,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1293" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -37556,7 +37559,7 @@
         <v>21</v>
       </c>
       <c r="G1294" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -37582,7 +37585,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1295" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -37608,7 +37611,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1296" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -37634,7 +37637,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1297" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37660,7 +37663,7 @@
         <v>21.5</v>
       </c>
       <c r="G1298" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -37686,7 +37689,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1299" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37712,7 +37715,7 @@
         <v>22</v>
       </c>
       <c r="G1300" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -37738,7 +37741,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1301" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37764,7 +37767,7 @@
         <v>22</v>
       </c>
       <c r="G1302" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37790,7 +37793,7 @@
         <v>21.5</v>
       </c>
       <c r="G1303" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37816,7 +37819,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1304" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37842,7 +37845,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1305" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37868,7 +37871,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -37894,7 +37897,7 @@
         <v>21</v>
       </c>
       <c r="G1307" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -37920,7 +37923,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1308" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -37946,7 +37949,7 @@
         <v>21</v>
       </c>
       <c r="G1309" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37972,7 +37975,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1310" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -37998,7 +38001,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -38024,7 +38027,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1312" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -38050,7 +38053,7 @@
         <v>21.5</v>
       </c>
       <c r="G1313" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -38076,7 +38079,7 @@
         <v>21.5</v>
       </c>
       <c r="G1314" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -38102,7 +38105,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1315" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -38128,7 +38131,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1316" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -38154,7 +38157,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1317" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -38180,7 +38183,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1318" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -38206,7 +38209,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1319" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -38232,7 +38235,7 @@
         <v>22.5</v>
       </c>
       <c r="G1320" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38258,7 +38261,7 @@
         <v>23.5</v>
       </c>
       <c r="G1321" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -38284,7 +38287,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1322" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -38310,7 +38313,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1323" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -38336,7 +38339,7 @@
         <v>23.5</v>
       </c>
       <c r="G1324" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -38362,7 +38365,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1325" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -38388,7 +38391,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1326" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -38414,7 +38417,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -38440,7 +38443,7 @@
         <v>23</v>
       </c>
       <c r="G1328" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -38466,7 +38469,7 @@
         <v>23.5</v>
       </c>
       <c r="G1329" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -38492,7 +38495,7 @@
         <v>23.5</v>
       </c>
       <c r="G1330" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38518,7 +38521,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1331" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -38544,7 +38547,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1332" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -38570,7 +38573,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1333" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -38596,7 +38599,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -38622,7 +38625,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1335" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -38648,7 +38651,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -38674,7 +38677,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1337" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -38700,7 +38703,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1338" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -38726,7 +38729,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1339" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -38752,7 +38755,7 @@
         <v>23.5</v>
       </c>
       <c r="G1340" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -38778,7 +38781,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1341" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -38804,7 +38807,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1342" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -38830,7 +38833,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1343" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -38856,7 +38859,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1344" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -38882,7 +38885,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1345" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -38908,7 +38911,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1346" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -38934,7 +38937,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1347" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -38960,7 +38963,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1348" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -38986,7 +38989,7 @@
         <v>23.5</v>
       </c>
       <c r="G1349" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -39012,7 +39015,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1350" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -39038,7 +39041,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1351" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -39064,7 +39067,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1352" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -39090,7 +39093,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1353" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -39116,7 +39119,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -39142,7 +39145,7 @@
         <v>23</v>
       </c>
       <c r="G1355" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39168,7 +39171,7 @@
         <v>23</v>
       </c>
       <c r="G1356" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -39194,7 +39197,7 @@
         <v>23</v>
       </c>
       <c r="G1357" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39220,7 +39223,7 @@
         <v>23</v>
       </c>
       <c r="G1358" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39246,7 +39249,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -39272,7 +39275,7 @@
         <v>23</v>
       </c>
       <c r="G1360" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -39298,7 +39301,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1361" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -39324,7 +39327,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1362" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -39350,7 +39353,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -39376,7 +39379,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -39402,7 +39405,7 @@
         <v>23.5</v>
       </c>
       <c r="G1365" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -39532,7 +39535,7 @@
         <v>23.5</v>
       </c>
       <c r="G1370" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -39558,7 +39561,7 @@
         <v>23.5</v>
       </c>
       <c r="G1371" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -39584,7 +39587,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1372" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -39636,7 +39639,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1374" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -39662,7 +39665,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1375" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -39688,7 +39691,7 @@
         <v>23.5</v>
       </c>
       <c r="G1376" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -39714,7 +39717,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1377" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -39766,7 +39769,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1379" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -39792,7 +39795,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1380" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -39818,7 +39821,7 @@
         <v>23.5</v>
       </c>
       <c r="G1381" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -39844,7 +39847,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1382" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -39870,7 +39873,7 @@
         <v>23.5</v>
       </c>
       <c r="G1383" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -39896,7 +39899,7 @@
         <v>23.5</v>
       </c>
       <c r="G1384" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -40026,7 +40029,7 @@
         <v>23.5</v>
       </c>
       <c r="G1389" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -40052,7 +40055,7 @@
         <v>23.5</v>
       </c>
       <c r="G1390" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40156,7 +40159,7 @@
         <v>23.5</v>
       </c>
       <c r="G1394" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -40182,7 +40185,7 @@
         <v>23.5</v>
       </c>
       <c r="G1395" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -40728,7 +40731,7 @@
         <v>23.5</v>
       </c>
       <c r="G1416" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -40754,7 +40757,7 @@
         <v>23.5</v>
       </c>
       <c r="G1417" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -68556,10 +68559,10 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6494560185</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
-        <v>14956</v>
+        <v>19705</v>
       </c>
       <c r="C2487" t="n">
         <v>59.4000015258789</v>
@@ -68577,6 +68580,32 @@
         <v>1157</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6494212963</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>24390</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>59.7999992370605</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>58.5999984741211</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>59</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>59.4000015258789</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1190</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -44,19 +44,19 @@
     <t xml:space="preserve">CMB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55656719207764</t>
+    <t xml:space="preserve">9.55656623840332</t>
   </si>
   <si>
     <t xml:space="preserve">9.31377410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40144920349121</t>
+    <t xml:space="preserve">9.40145015716553</t>
   </si>
   <si>
     <t xml:space="preserve">9.40819358825684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44191360473633</t>
+    <t xml:space="preserve">9.44191455841064</t>
   </si>
   <si>
     <t xml:space="preserve">9.36098289489746</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">9.32051849365234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26656341552734</t>
+    <t xml:space="preserve">9.26656532287598</t>
   </si>
   <si>
     <t xml:space="preserve">9.34075164794922</t>
@@ -80,124 +80,124 @@
     <t xml:space="preserve">9.19237804412842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19912242889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10470294952393</t>
+    <t xml:space="preserve">9.19912338256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10470390319824</t>
   </si>
   <si>
     <t xml:space="preserve">8.84167861938477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77423763275146</t>
+    <t xml:space="preserve">8.77423667907715</t>
   </si>
   <si>
     <t xml:space="preserve">8.84842300415039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3628396987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3291187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61911869049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45051193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43028259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63260746002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80121421813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22609901428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25981998443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0709810256958</t>
+    <t xml:space="preserve">8.36283874511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32911777496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61911964416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45051383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4302806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63260936737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80121326446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22609996795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25982093811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07098293304443</t>
   </si>
   <si>
     <t xml:space="preserve">8.87539958953857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96982002258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71353816986084</t>
+    <t xml:space="preserve">8.96981811523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71353721618652</t>
   </si>
   <si>
     <t xml:space="preserve">8.6663293838501</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89563179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8147029876709</t>
+    <t xml:space="preserve">8.89563369750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81470203399658</t>
   </si>
   <si>
     <t xml:space="preserve">8.99679565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01028442382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90237522125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97656345367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18563461303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17214584350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13167953491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34749603271484</t>
+    <t xml:space="preserve">9.01028347015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90237617492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97656440734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18563270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17214488983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13168048858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34749698638916</t>
   </si>
   <si>
     <t xml:space="preserve">9.25307750701904</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15865707397461</t>
+    <t xml:space="preserve">9.15865802764893</t>
   </si>
   <si>
     <t xml:space="preserve">9.08447074890137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16540241241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98330688476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78772354125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78098106384277</t>
+    <t xml:space="preserve">9.16540145874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98330783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7877254486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78098011016846</t>
   </si>
   <si>
     <t xml:space="preserve">9.1249361038208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03726005554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21261215209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04400634765625</t>
+    <t xml:space="preserve">9.03726291656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21261119842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04400444030762</t>
   </si>
   <si>
     <t xml:space="preserve">9.0979585647583</t>
@@ -209,37 +209,37 @@
     <t xml:space="preserve">9.38121604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28679752349854</t>
+    <t xml:space="preserve">9.28679943084717</t>
   </si>
   <si>
     <t xml:space="preserve">9.22100734710693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22798824310303</t>
+    <t xml:space="preserve">9.22798919677734</t>
   </si>
   <si>
     <t xml:space="preserve">9.19308662414551</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35363388061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4094762802124</t>
+    <t xml:space="preserve">9.35363578796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40947818756104</t>
   </si>
   <si>
     <t xml:space="preserve">9.52116298675537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49324131011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38853549957275</t>
+    <t xml:space="preserve">9.49324035644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38853645324707</t>
   </si>
   <si>
     <t xml:space="preserve">9.94696140289307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76547241210938</t>
+    <t xml:space="preserve">9.76547431945801</t>
   </si>
   <si>
     <t xml:space="preserve">9.77245330810547</t>
@@ -248,10 +248,10 @@
     <t xml:space="preserve">9.66774940490723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82829761505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75151348114014</t>
+    <t xml:space="preserve">9.82829570770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75151252746582</t>
   </si>
   <si>
     <t xml:space="preserve">9.57002449035645</t>
@@ -260,76 +260,76 @@
     <t xml:space="preserve">9.57700538635254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55606269836426</t>
+    <t xml:space="preserve">9.55606365203857</t>
   </si>
   <si>
     <t xml:space="preserve">9.47928047180176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42343711853027</t>
+    <t xml:space="preserve">9.42343807220459</t>
   </si>
   <si>
     <t xml:space="preserve">9.39551639556885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4164571762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34665393829346</t>
+    <t xml:space="preserve">9.41645622253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34665489196777</t>
   </si>
   <si>
     <t xml:space="preserve">9.58398532867432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62586688995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63284873962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46531963348389</t>
+    <t xml:space="preserve">9.6258659362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63284778594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4653205871582</t>
   </si>
   <si>
     <t xml:space="preserve">9.48626041412354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59096431732178</t>
+    <t xml:space="preserve">9.59096622467041</t>
   </si>
   <si>
     <t xml:space="preserve">9.56304359436035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53512191772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1232852935791</t>
+    <t xml:space="preserve">9.53512287139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12328433990479</t>
   </si>
   <si>
     <t xml:space="preserve">9.30477237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28383255004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20704650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27685070037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36061477661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29081153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29779148101807</t>
+    <t xml:space="preserve">9.2838306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2070484161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27685165405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36061382293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29081249237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29779243469238</t>
   </si>
   <si>
     <t xml:space="preserve">9.31873321533203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36759471893311</t>
+    <t xml:space="preserve">9.36759567260742</t>
   </si>
   <si>
     <t xml:space="preserve">9.47229957580566</t>
@@ -338,19 +338,19 @@
     <t xml:space="preserve">9.52814197540283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50720119476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44437789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50022125244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33269309997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32571411132812</t>
+    <t xml:space="preserve">9.50720024108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44437885284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50022029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3326940536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32571220397949</t>
   </si>
   <si>
     <t xml:space="preserve">9.13724327087402</t>
@@ -362,22 +362,22 @@
     <t xml:space="preserve">9.15120506286621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10932350158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03952026367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92783451080322</t>
+    <t xml:space="preserve">9.1093225479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03951930999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92783546447754</t>
   </si>
   <si>
     <t xml:space="preserve">9.01159858703613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07442188262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97669696807861</t>
+    <t xml:space="preserve">9.07442092895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9766960144043</t>
   </si>
   <si>
     <t xml:space="preserve">8.86501121520996</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">8.85105037689209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.934814453125</t>
+    <t xml:space="preserve">8.93481636047363</t>
   </si>
   <si>
     <t xml:space="preserve">8.92085456848145</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">8.91387367248535</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87897396087646</t>
+    <t xml:space="preserve">8.87897300720215</t>
   </si>
   <si>
     <t xml:space="preserve">8.80916881561279</t>
@@ -422,16 +422,16 @@
     <t xml:space="preserve">8.83709049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8999137878418</t>
+    <t xml:space="preserve">8.89991283416748</t>
   </si>
   <si>
     <t xml:space="preserve">8.99763774871826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83010864257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96273708343506</t>
+    <t xml:space="preserve">8.83010959625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96273612976074</t>
   </si>
   <si>
     <t xml:space="preserve">9.08838176727295</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">9.04650020599365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09536170959473</t>
+    <t xml:space="preserve">9.09536266326904</t>
   </si>
   <si>
     <t xml:space="preserve">9.66076850891113</t>
@@ -455,94 +455,94 @@
     <t xml:space="preserve">9.79339408874512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92602062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98186492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0516662597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4146432876587</t>
+    <t xml:space="preserve">9.9260196685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9818639755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0516653060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4146423339844</t>
   </si>
   <si>
     <t xml:space="preserve">10.1912727355957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2471160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493902206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1354322433472</t>
+    <t xml:space="preserve">10.2471151351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493921279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1354303359985</t>
   </si>
   <si>
     <t xml:space="preserve">10.2680568695068</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3937015533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402898788452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5891532897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.484447479248</t>
+    <t xml:space="preserve">10.393702507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402889251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5891523361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4844465255737</t>
   </si>
   <si>
     <t xml:space="preserve">10.6310329437256</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3588018417358</t>
+    <t xml:space="preserve">10.3587999343872</t>
   </si>
   <si>
     <t xml:space="preserve">9.988844871521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95394134521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.100528717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4704866409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3867225646973</t>
+    <t xml:space="preserve">9.95394229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1005296707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4704856872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3867235183716</t>
   </si>
   <si>
     <t xml:space="preserve">10.5472688674927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3448400497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4774656295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4006824493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4355840682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3727607727051</t>
+    <t xml:space="preserve">10.344841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.477466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4006834030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4355850219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3727617263794</t>
   </si>
   <si>
     <t xml:space="preserve">10.3657827377319</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3378610610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2820177078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3797435760498</t>
+    <t xml:space="preserve">10.3378601074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2820167541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3797416687012</t>
   </si>
   <si>
     <t xml:space="preserve">10.6100931167603</t>
@@ -551,70 +551,70 @@
     <t xml:space="preserve">10.5542497634888</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6938571929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0917358398438</t>
+    <t xml:space="preserve">10.6938552856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0917329788208</t>
   </si>
   <si>
     <t xml:space="preserve">11.042872428894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0358934402466</t>
+    <t xml:space="preserve">11.0358924865723</t>
   </si>
   <si>
     <t xml:space="preserve">11.063814163208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.084755897522</t>
+    <t xml:space="preserve">11.0847549438477</t>
   </si>
   <si>
     <t xml:space="preserve">11.356987953186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5175352096558</t>
+    <t xml:space="preserve">11.5175342559814</t>
   </si>
   <si>
     <t xml:space="preserve">12.0899219512939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9991788864136</t>
+    <t xml:space="preserve">11.9991779327393</t>
   </si>
   <si>
     <t xml:space="preserve">12.0689811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1038808822632</t>
+    <t xml:space="preserve">12.1038818359375</t>
   </si>
   <si>
     <t xml:space="preserve">12.2853717803955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8228578567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9764213562012</t>
+    <t xml:space="preserve">12.8228569030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9764242172241</t>
   </si>
   <si>
     <t xml:space="preserve">12.9903831481934</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2486534118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1090497970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1230096817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8926572799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9135999679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8437957763672</t>
+    <t xml:space="preserve">13.2486543655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1090478897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1230087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8926591873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9136009216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8437976837158</t>
   </si>
   <si>
     <t xml:space="preserve">12.9624614715576</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">13.1928129196167</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3952436447144</t>
+    <t xml:space="preserve">13.3952445983887</t>
   </si>
   <si>
     <t xml:space="preserve">13.8978242874146</t>
@@ -632,103 +632,103 @@
     <t xml:space="preserve">13.9815883636475</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9327268600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0234718322754</t>
+    <t xml:space="preserve">13.9327259063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0234699249268</t>
   </si>
   <si>
     <t xml:space="preserve">14.0304517745972</t>
   </si>
   <si>
-    <t xml:space="preserve">14.135157585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0723323822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0025310516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.211256980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197383880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.146164894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0810775756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9942932128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6688413619995</t>
+    <t xml:space="preserve">14.1351556777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0723333358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0025281906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2112550735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197374343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1461658477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.081075668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.994288444519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6688423156738</t>
   </si>
   <si>
     <t xml:space="preserve">14.355899810791</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6833066940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0015239715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9870576858521</t>
+    <t xml:space="preserve">13.6833076477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.001522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9870586395264</t>
   </si>
   <si>
     <t xml:space="preserve">14.2691125869751</t>
   </si>
   <si>
-    <t xml:space="preserve">14.348669052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3414354324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2763452529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.42822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5656318664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3322458267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8457307815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7589454650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3611745834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1876020431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9200115203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6307258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636768341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3105478286743</t>
+    <t xml:space="preserve">14.3486700057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3414363861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2763481140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4282217025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.565634727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3322477340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8457298278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7589483261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3611736297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1876039505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9200086593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6307229995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636796951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3105497360229</t>
   </si>
   <si>
     <t xml:space="preserve">14.9272432327271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0718870162964</t>
+    <t xml:space="preserve">15.0718898773193</t>
   </si>
   <si>
     <t xml:space="preserve">15.5492124557495</t>
@@ -740,22 +740,22 @@
     <t xml:space="preserve">15.2671566009521</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1731386184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8332271575928</t>
+    <t xml:space="preserve">15.1731367111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8332242965698</t>
   </si>
   <si>
     <t xml:space="preserve">15.1369781494141</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1152791976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9851016998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1514415740967</t>
+    <t xml:space="preserve">15.1152801513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9850988388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1514406204224</t>
   </si>
   <si>
     <t xml:space="preserve">15.0284948348999</t>
@@ -767,145 +767,145 @@
     <t xml:space="preserve">15.664924621582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6938533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7661781311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9325180053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0409984588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.946982383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6432294845581</t>
+    <t xml:space="preserve">15.6938562393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7661762237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9325170516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0410022735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9469814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6432304382324</t>
   </si>
   <si>
     <t xml:space="preserve">15.2816190719604</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2888507843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2599248886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3250131607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2382259368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1586713790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0574235916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1803693771362</t>
+    <t xml:space="preserve">15.2888536453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2599220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3250141143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.238226890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1586723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0574254989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1803712844849</t>
   </si>
   <si>
     <t xml:space="preserve">15.245457649231</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8983144760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8693828582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8259916305542</t>
+    <t xml:space="preserve">14.8983125686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8693819046021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8259906768799</t>
   </si>
   <si>
     <t xml:space="preserve">14.9634065628052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9706354141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6813497543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7536706924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6958150863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8910799026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4933109283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.854923248291</t>
+    <t xml:space="preserve">14.9706363677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6813468933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7536697387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6958131790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8910818099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4933128356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8549222946167</t>
   </si>
   <si>
     <t xml:space="preserve">14.6524200439453</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6090269088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8476905822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1948328018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3394784927368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4334983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2651977539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9956474304199</t>
+    <t xml:space="preserve">14.6090278625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8476896286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1948366165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3394765853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.433497428894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2652015686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9956493377686</t>
   </si>
   <si>
     <t xml:space="preserve">17.5742244720459</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6879844665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3986968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4420890808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2178916931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0804805755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1889629364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9719944000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0081539154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8562812805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9647617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6393127441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7622604370117</t>
+    <t xml:space="preserve">18.6879806518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3986930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4420871734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2178859710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0804786682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1889610290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9719924926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0081577301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8562793731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9647636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6393165588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7622623443604</t>
   </si>
   <si>
     <t xml:space="preserve">17.6031551361084</t>
@@ -914,49 +914,49 @@
     <t xml:space="preserve">17.5886898040771</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5380630493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5019016265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3861904144287</t>
+    <t xml:space="preserve">17.538064956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5019035339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3861865997314</t>
   </si>
   <si>
     <t xml:space="preserve">17.3211002349854</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2849388122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0462760925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2632389068604</t>
+    <t xml:space="preserve">17.2849369049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0462741851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2632427215576</t>
   </si>
   <si>
     <t xml:space="preserve">17.0969009399414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3283271789551</t>
+    <t xml:space="preserve">17.328332901001</t>
   </si>
   <si>
     <t xml:space="preserve">17.3572616577148</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4006519317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3789577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2921695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.342794418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1692199707031</t>
+    <t xml:space="preserve">17.4006500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3789558410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2921714782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3427963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1692237854004</t>
   </si>
   <si>
     <t xml:space="preserve">16.590648651123</t>
@@ -971,43 +971,43 @@
     <t xml:space="preserve">16.3447532653809</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7083168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1133232116699</t>
+    <t xml:space="preserve">15.7083196640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1133213043213</t>
   </si>
   <si>
     <t xml:space="preserve">15.9180536270142</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6504640579224</t>
+    <t xml:space="preserve">15.650463104248</t>
   </si>
   <si>
     <t xml:space="preserve">16.4749336242676</t>
   </si>
   <si>
-    <t xml:space="preserve">16.301362991333</t>
+    <t xml:space="preserve">16.3013591766357</t>
   </si>
   <si>
     <t xml:space="preserve">16.5761833190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5110950469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5617179870605</t>
+    <t xml:space="preserve">16.5110931396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5617160797119</t>
   </si>
   <si>
     <t xml:space="preserve">16.0699291229248</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5255565643311</t>
+    <t xml:space="preserve">16.5255584716797</t>
   </si>
   <si>
     <t xml:space="preserve">16.4098434448242</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2073421478271</t>
+    <t xml:space="preserve">16.2073402404785</t>
   </si>
   <si>
     <t xml:space="preserve">15.874659538269</t>
@@ -1019,124 +1019,124 @@
     <t xml:space="preserve">16.4460048675537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2001075744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8312664031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8601951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8529653549194</t>
+    <t xml:space="preserve">16.2001056671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8312644958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8601961135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8529615402222</t>
   </si>
   <si>
     <t xml:space="preserve">15.6287670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4696578979492</t>
+    <t xml:space="preserve">15.4696569442749</t>
   </si>
   <si>
     <t xml:space="preserve">15.4624252319336</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6215333938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9976062774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2362689971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1639461517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2724323272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7786865234375</t>
+    <t xml:space="preserve">15.6215343475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9976081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.236270904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.163948059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2724304199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7786827087402</t>
   </si>
   <si>
     <t xml:space="preserve">16.6340408325195</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4532337188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7425231933594</t>
+    <t xml:space="preserve">16.4532356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.742525100708</t>
   </si>
   <si>
     <t xml:space="preserve">16.59787940979</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7063617706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8510055541992</t>
+    <t xml:space="preserve">16.7063636779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8510074615479</t>
   </si>
   <si>
     <t xml:space="preserve">17.0318088531494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2126140594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4295806884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9594879150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3809146881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9831457138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9108190536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7300148010254</t>
+    <t xml:space="preserve">17.2126159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4295825958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9594898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3809127807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9831409454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9108228683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7300157546997</t>
   </si>
   <si>
     <t xml:space="preserve">15.3684062957764</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4045677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4768915176392</t>
+    <t xml:space="preserve">15.4045648574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4768877029419</t>
   </si>
   <si>
     <t xml:space="preserve">15.8023376464844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6702003479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1402950286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1041316986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8148460388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0679721832275</t>
+    <t xml:space="preserve">16.6701984405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1402931213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.104133605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8148441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0679702758789</t>
   </si>
   <si>
     <t xml:space="preserve">16.8871669769287</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8273487091064</t>
+    <t xml:space="preserve">17.8273506164551</t>
   </si>
   <si>
     <t xml:space="preserve">17.6827087402344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3934192657471</t>
+    <t xml:space="preserve">17.3934173583984</t>
   </si>
   <si>
     <t xml:space="preserve">17.2487773895264</t>
@@ -1145,13 +1145,13 @@
     <t xml:space="preserve">17.7550315856934</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8996715545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5867347717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6590538024902</t>
+    <t xml:space="preserve">17.8996734619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5867328643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6590518951416</t>
   </si>
   <si>
     <t xml:space="preserve">19.0206642150879</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">19.5428009033203</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2444362640381</t>
+    <t xml:space="preserve">19.2444343566895</t>
   </si>
   <si>
     <t xml:space="preserve">19.9157543182373</t>
@@ -1169,16 +1169,16 @@
     <t xml:space="preserve">20.4378890991211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6546840667725</t>
+    <t xml:space="preserve">19.6546878814697</t>
   </si>
   <si>
     <t xml:space="preserve">19.4682083129883</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6173896789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0952548980713</t>
+    <t xml:space="preserve">19.6173915863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0952568054199</t>
   </si>
   <si>
     <t xml:space="preserve">18.8714809417725</t>
@@ -1190,10 +1190,10 @@
     <t xml:space="preserve">18.7968921661377</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9018020629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3050765991211</t>
+    <t xml:space="preserve">17.9018039703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3050727844238</t>
   </si>
   <si>
     <t xml:space="preserve">17.7899150848389</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">18.8341865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1698474884033</t>
+    <t xml:space="preserve">19.1698455810547</t>
   </si>
   <si>
     <t xml:space="preserve">19.3936176300049</t>
@@ -1211,46 +1211,46 @@
     <t xml:space="preserve">19.5055065155029</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8038692474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8784561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6919784545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3190288543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4239387512207</t>
+    <t xml:space="preserve">19.8038673400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8784580230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6919803619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3190269470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4239368438721</t>
   </si>
   <si>
     <t xml:space="preserve">19.1325511932373</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3563213348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0206661224365</t>
+    <t xml:space="preserve">19.3563232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0206623077393</t>
   </si>
   <si>
     <t xml:space="preserve">19.7292766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7223033905029</t>
+    <t xml:space="preserve">18.7223014831543</t>
   </si>
   <si>
     <t xml:space="preserve">18.9087772369385</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6477108001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5731163024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5358219146729</t>
+    <t xml:space="preserve">18.6477088928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5731201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5358200073242</t>
   </si>
   <si>
     <t xml:space="preserve">17.9763927459717</t>
@@ -1262,190 +1262,190 @@
     <t xml:space="preserve">18.4612331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7595977783203</t>
+    <t xml:space="preserve">18.7595958709717</t>
   </si>
   <si>
     <t xml:space="preserve">18.6104164123535</t>
   </si>
   <si>
-    <t xml:space="preserve">18.34934425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6850032806396</t>
+    <t xml:space="preserve">18.3493461608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6850051879883</t>
   </si>
   <si>
     <t xml:space="preserve">18.3120517730713</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4985294342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2817344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0579586029053</t>
+    <t xml:space="preserve">18.4985275268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2817325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0579566955566</t>
   </si>
   <si>
     <t xml:space="preserve">18.1628684997559</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0136871337891</t>
+    <t xml:space="preserve">18.0136852264404</t>
   </si>
   <si>
     <t xml:space="preserve">18.3866405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1558952331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1862106323242</t>
+    <t xml:space="preserve">17.1558933258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1862125396729</t>
   </si>
   <si>
     <t xml:space="preserve">15.589485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1419410705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9554643630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0370292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5218677520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6640758514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1046466827393</t>
+    <t xml:space="preserve">15.1419382095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9554624557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0370311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5218734741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6640777587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1046447753906</t>
   </si>
   <si>
     <t xml:space="preserve">14.9927587509155</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0300512313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.768985748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3661956787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5153751373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6198043823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.888331413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2538280487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2608032226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9251441955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7759618759155</t>
+    <t xml:space="preserve">15.0300521850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7689847946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3661947250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5153760910034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6198034286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8883304595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2538251876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2608013153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.925145149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7759590148926</t>
   </si>
   <si>
     <t xml:space="preserve">15.7013702392578</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5521898269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.626781463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5148954391479</t>
+    <t xml:space="preserve">15.5521907806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6267805099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5148935317993</t>
   </si>
   <si>
     <t xml:space="preserve">15.2911205291748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.21653175354</t>
+    <t xml:space="preserve">15.2165307998657</t>
   </si>
   <si>
     <t xml:space="preserve">15.179235458374</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8505535125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8132562637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0743255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8878479003906</t>
+    <t xml:space="preserve">15.8505525588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8132600784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0743236541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.887845993042</t>
   </si>
   <si>
     <t xml:space="preserve">15.4030065536499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9032468795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7093133926392</t>
+    <t xml:space="preserve">14.9032487869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7093152999878</t>
   </si>
   <si>
     <t xml:space="preserve">15.4403038024902</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1116199493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9624404907227</t>
+    <t xml:space="preserve">16.1116218566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9624376296997</t>
   </si>
   <si>
     <t xml:space="preserve">16.5591659545898</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3726902008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4845771789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7829399108887</t>
+    <t xml:space="preserve">16.372688293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4845733642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.78293800354</t>
   </si>
   <si>
     <t xml:space="preserve">16.8948249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7386674880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657121658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8435764312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8584938049316</t>
+    <t xml:space="preserve">15.7386655807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657112121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8435745239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.858494758606</t>
   </si>
   <si>
     <t xml:space="preserve">15.0673503875732</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8734140396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9181680679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4099826812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2235050201416</t>
+    <t xml:space="preserve">14.8734121322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9181671142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4099864959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2235069274902</t>
   </si>
   <si>
     <t xml:space="preserve">16.2980976104736</t>
@@ -1454,10 +1454,10 @@
     <t xml:space="preserve">16.6710529327393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7083473205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7456436157227</t>
+    <t xml:space="preserve">16.708345413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7456455230713</t>
   </si>
   <si>
     <t xml:space="preserve">16.6337566375732</t>
@@ -1469,13 +1469,13 @@
     <t xml:space="preserve">16.8575305938721</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0067119598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3796653747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2304840087891</t>
+    <t xml:space="preserve">17.0067100524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3796672821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2304859161377</t>
   </si>
   <si>
     <t xml:space="preserve">17.5288467407227</t>
@@ -1490,55 +1490,55 @@
     <t xml:space="preserve">16.6756744384766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7532329559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3654308319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0939636230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6673774719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6285943984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0468864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2640590667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7061595916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5898170471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5122537612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7449388504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950811386108</t>
+    <t xml:space="preserve">16.7532348632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3654270172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0939617156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6673784255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6285953521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0468883514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2640581130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7061576843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5898151397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5122528076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7449369430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950839996338</t>
   </si>
   <si>
     <t xml:space="preserve">15.0158624649048</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1864957809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4191808700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4967422485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5510349273682</t>
+    <t xml:space="preserve">15.1864976882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4191789627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4967412948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5510339736938</t>
   </si>
   <si>
     <t xml:space="preserve">15.3261079788208</t>
@@ -1547,82 +1547,82 @@
     <t xml:space="preserve">15.2795705795288</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8612813949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0164031982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9388408660889</t>
+    <t xml:space="preserve">15.8612785339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0164012908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9388389587402</t>
   </si>
   <si>
     <t xml:space="preserve">15.9000597000122</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7837209701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8225021362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3266468048096</t>
+    <t xml:space="preserve">15.7837181091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8224992752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3266448974609</t>
   </si>
   <si>
     <t xml:space="preserve">16.7920150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0247001647949</t>
+    <t xml:space="preserve">17.0246982574463</t>
   </si>
   <si>
     <t xml:space="preserve">16.9083576202393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4817714691162</t>
+    <t xml:space="preserve">16.4817695617676</t>
   </si>
   <si>
     <t xml:space="preserve">16.5593338012695</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0551834106445</t>
+    <t xml:space="preserve">16.0551853179932</t>
   </si>
   <si>
     <t xml:space="preserve">16.4042072296143</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1327457427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2878665924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1715240478516</t>
+    <t xml:space="preserve">16.1327438354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2878684997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1715259552002</t>
   </si>
   <si>
     <t xml:space="preserve">15.9776201248169</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3881559371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346923828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2103042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4429893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5981140136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5205497741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6368942260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2490882873535</t>
+    <t xml:space="preserve">15.3881578445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346904754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2103061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4429912567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5981101989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5205478668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6368923187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2490863800049</t>
   </si>
   <si>
     <t xml:space="preserve">16.8307952880859</t>
@@ -1631,10 +1631,10 @@
     <t xml:space="preserve">16.9859180450439</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8390941619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.567626953125</t>
+    <t xml:space="preserve">17.8390922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5676288604736</t>
   </si>
   <si>
     <t xml:space="preserve">17.9942150115967</t>
@@ -1643,67 +1643,67 @@
     <t xml:space="preserve">18.6147060394287</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2656803131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8473892211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5371417999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0717754364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4595813751221</t>
+    <t xml:space="preserve">18.2656764984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8473873138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5371437072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.07177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4595832824707</t>
   </si>
   <si>
     <t xml:space="preserve">18.7698268890381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9249534606934</t>
+    <t xml:space="preserve">18.9249496459961</t>
   </si>
   <si>
     <t xml:space="preserve">19.1576347351074</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0025119781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0412940979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3044586181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1493396759033</t>
+    <t xml:space="preserve">19.002513885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0412921905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3044605255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1493377685547</t>
   </si>
   <si>
     <t xml:space="preserve">18.032995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">18.226900100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4207992553711</t>
+    <t xml:space="preserve">18.2268981933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4208011627197</t>
   </si>
   <si>
     <t xml:space="preserve">18.498363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">18.110559463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.683967590332</t>
+    <t xml:space="preserve">18.1105575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6839694976807</t>
   </si>
   <si>
     <t xml:space="preserve">18.8086090087891</t>
   </si>
   <si>
-    <t xml:space="preserve">18.382022857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1881198883057</t>
+    <t xml:space="preserve">18.3820209503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.188117980957</t>
   </si>
   <si>
     <t xml:space="preserve">17.916654586792</t>
@@ -1712,31 +1712,31 @@
     <t xml:space="preserve">17.9554347991943</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6064109802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6451873779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1410427093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1022605895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2961616516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1244487762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7676658630371</t>
+    <t xml:space="preserve">17.606409072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6451892852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.141040802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.102258682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.29616355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1244468688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7676668167114</t>
   </si>
   <si>
     <t xml:space="preserve">13.5577096939087</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9610290527344</t>
+    <t xml:space="preserve">13.961030960083</t>
   </si>
   <si>
     <t xml:space="preserve">13.0302925109863</t>
@@ -1748,19 +1748,19 @@
     <t xml:space="preserve">13.1388788223267</t>
   </si>
   <si>
-    <t xml:space="preserve">13.573221206665</t>
+    <t xml:space="preserve">13.5732231140137</t>
   </si>
   <si>
     <t xml:space="preserve">13.262978553772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.169903755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.952733039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5649271011353</t>
+    <t xml:space="preserve">13.1699028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9527339935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5649261474609</t>
   </si>
   <si>
     <t xml:space="preserve">11.7582893371582</t>
@@ -1772,55 +1772,55 @@
     <t xml:space="preserve">10.8585777282715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7810163497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3156499862671</t>
+    <t xml:space="preserve">10.7810173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3156490325928</t>
   </si>
   <si>
     <t xml:space="preserve">10.8197975158691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1300439834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7893133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2546806335449</t>
+    <t xml:space="preserve">11.1300430297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7893142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2546815872192</t>
   </si>
   <si>
     <t xml:space="preserve">11.9056558609009</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6341896057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0219964981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0607767105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8280935287476</t>
+    <t xml:space="preserve">11.6341905593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0219974517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0607786178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8280944824219</t>
   </si>
   <si>
     <t xml:space="preserve">11.4790687561035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7117538452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6729707717896</t>
+    <t xml:space="preserve">11.7117528915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6729726791382</t>
   </si>
   <si>
     <t xml:space="preserve">11.5954113006592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2851648330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4015064239502</t>
+    <t xml:space="preserve">11.2851657867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4015073776245</t>
   </si>
   <si>
     <t xml:space="preserve">11.7505321502686</t>
@@ -1832,13 +1832,13 @@
     <t xml:space="preserve">10.5095529556274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871133804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6646738052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2463836669922</t>
+    <t xml:space="preserve">10.5871143341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6646757125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2463846206665</t>
   </si>
   <si>
     <t xml:space="preserve">12.2159013748169</t>
@@ -1847,13 +1847,13 @@
     <t xml:space="preserve">12.3710231781006</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0773696899414</t>
+    <t xml:space="preserve">14.0773706436157</t>
   </si>
   <si>
     <t xml:space="preserve">14.1181745529175</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0365676879883</t>
+    <t xml:space="preserve">14.036566734314</t>
   </si>
   <si>
     <t xml:space="preserve">13.8733501434326</t>
@@ -1862,67 +1862,67 @@
     <t xml:space="preserve">13.8325471878052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.199782371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6078224182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2813892364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4245080947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5469179153442</t>
+    <t xml:space="preserve">14.1997833251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6078233718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2813901901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4245071411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5469188690186</t>
   </si>
   <si>
     <t xml:space="preserve">13.5061140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7509384155273</t>
+    <t xml:space="preserve">13.7509393692017</t>
   </si>
   <si>
     <t xml:space="preserve">13.9549589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5262136459351</t>
+    <t xml:space="preserve">14.5262145996094</t>
   </si>
   <si>
     <t xml:space="preserve">14.7710380554199</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6894292831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.322193145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4038019180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.587721824646</t>
+    <t xml:space="preserve">14.689432144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3221940994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4038028717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5877227783203</t>
   </si>
   <si>
     <t xml:space="preserve">13.465311050415</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6285276412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9141550064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2405872344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9957628250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1589784622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7917423248291</t>
+    <t xml:space="preserve">13.6285285949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9141540527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2405891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9957618713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1589794158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7917413711548</t>
   </si>
   <si>
     <t xml:space="preserve">13.3837032318115</t>
@@ -1931,31 +1931,34 @@
     <t xml:space="preserve">13.2204875946045</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3428993225098</t>
+    <t xml:space="preserve">13.3429002761841</t>
   </si>
   <si>
     <t xml:space="preserve">13.7101345062256</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0572710037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2612915039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0980739593506</t>
+    <t xml:space="preserve">13.0572729110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.138879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2612905502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0980758666992</t>
   </si>
   <si>
     <t xml:space="preserve">12.4860153198242</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8532514572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7308387756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.690034866333</t>
+    <t xml:space="preserve">12.8532524108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7308406829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6900367736816</t>
   </si>
   <si>
     <t xml:space="preserve">12.9756631851196</t>
@@ -1970,22 +1973,22 @@
     <t xml:space="preserve">15.2606868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4239015579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0767669677734</t>
+    <t xml:space="preserve">15.4239025115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0767650604248</t>
   </si>
   <si>
     <t xml:space="preserve">15.9135494232178</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5055084228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6687250137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5871171951294</t>
+    <t xml:space="preserve">15.5055122375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6687269210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5871181488037</t>
   </si>
   <si>
     <t xml:space="preserve">15.3014898300171</t>
@@ -1994,19 +1997,19 @@
     <t xml:space="preserve">15.3830986022949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3422927856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7503337860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2198810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1790781021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4647054672241</t>
+    <t xml:space="preserve">15.3422937393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7503328323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2198839187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1790790557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4647064208984</t>
   </si>
   <si>
     <t xml:space="preserve">16.3215885162354</t>
@@ -2027,55 +2030,55 @@
     <t xml:space="preserve">17.3824920654297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.89284324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1991786956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4848041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.648021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5664138793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2399806976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4031963348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7296295166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2192764282227</t>
+    <t xml:space="preserve">16.8928451538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1991748809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.484806060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6480197906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5664119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2399787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4031982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7296276092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.219274520874</t>
   </si>
   <si>
     <t xml:space="preserve">17.4640998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5457096099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9537467956543</t>
+    <t xml:space="preserve">17.5457077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9537487030029</t>
   </si>
   <si>
     <t xml:space="preserve">18.0353565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9744529724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8721408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1169624328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1985721588135</t>
+    <t xml:space="preserve">16.9744510650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8721389770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.11696434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1985702514648</t>
   </si>
   <si>
     <t xml:space="preserve">18.3617877960205</t>
@@ -2087,25 +2090,28 @@
     <t xml:space="preserve">18.8514366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6882209777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0962600708008</t>
+    <t xml:space="preserve">18.6882171630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0962581634521</t>
   </si>
   <si>
     <t xml:space="preserve">18.6066112518311</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9330425262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2594757080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3410835266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4226894378662</t>
+    <t xml:space="preserve">18.9330444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7698249816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2594738006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3410816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4226913452148</t>
   </si>
   <si>
     <t xml:space="preserve">19.0146503448486</t>
@@ -2117,19 +2123,16 @@
     <t xml:space="preserve">19.8276062011719</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9123382568359</t>
-  </si>
-  <si>
     <t xml:space="preserve">19.4886722564697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6581382751465</t>
+    <t xml:space="preserve">19.6581401824951</t>
   </si>
   <si>
     <t xml:space="preserve">19.5734062194824</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4039402008057</t>
+    <t xml:space="preserve">19.403938293457</t>
   </si>
   <si>
     <t xml:space="preserve">19.9970722198486</t>
@@ -2138,19 +2141,19 @@
     <t xml:space="preserve">20.3360061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1665382385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3192043304443</t>
+    <t xml:space="preserve">20.166540145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.319206237793</t>
   </si>
   <si>
     <t xml:space="preserve">19.0650062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6413383483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7428703308105</t>
+    <t xml:space="preserve">18.6413402557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7428722381592</t>
   </si>
   <si>
     <t xml:space="preserve">20.0818061828613</t>
@@ -2174,22 +2177,22 @@
     <t xml:space="preserve">20.759672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4375381469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7085380554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0306739807129</t>
+    <t xml:space="preserve">21.4375400543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7085418701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0306720733643</t>
   </si>
   <si>
     <t xml:space="preserve">22.4543399810791</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2001399993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6238059997559</t>
+    <t xml:space="preserve">22.2001419067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6238079071045</t>
   </si>
   <si>
     <t xml:space="preserve">22.7932739257812</t>
@@ -2198,28 +2201,28 @@
     <t xml:space="preserve">23.0474739074707</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6406059265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.555871963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3016719818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4711399078369</t>
+    <t xml:space="preserve">23.6406078338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5558738708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3016738891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4711418151855</t>
   </si>
   <si>
     <t xml:space="preserve">23.3864078521729</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7253398895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1322059631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2169399261475</t>
+    <t xml:space="preserve">23.725341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1322078704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2169418334961</t>
   </si>
   <si>
     <t xml:space="preserve">21.9459400177002</t>
@@ -2228,10 +2231,10 @@
     <t xml:space="preserve">22.8780059814453</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1490058898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.165807723999</t>
+    <t xml:space="preserve">24.1490077972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1658096313477</t>
   </si>
   <si>
     <t xml:space="preserve">24.9116077423096</t>
@@ -2240,49 +2243,49 @@
     <t xml:space="preserve">24.2337417602539</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2505397796631</t>
+    <t xml:space="preserve">25.2505416870117</t>
   </si>
   <si>
     <t xml:space="preserve">23.8100757598877</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5726718902588</t>
+    <t xml:space="preserve">24.5726737976074</t>
   </si>
   <si>
     <t xml:space="preserve">24.403205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4879398345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0810737609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5047397613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3352737426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4200057983398</t>
+    <t xml:space="preserve">24.4879417419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.081075668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5047416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3352756500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4200077056885</t>
   </si>
   <si>
     <t xml:space="preserve">25.7589416503906</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2673397064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4368057250977</t>
+    <t xml:space="preserve">26.2673416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4368095397949</t>
   </si>
   <si>
     <t xml:space="preserve">26.521541595459</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8772773742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5719432830811</t>
+    <t xml:space="preserve">27.8772754669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5719451904297</t>
   </si>
   <si>
     <t xml:space="preserve">29.317741394043</t>
@@ -2291,10 +2294,10 @@
     <t xml:space="preserve">28.9788093566895</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1482772827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2330074310303</t>
+    <t xml:space="preserve">29.1482753753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2330093383789</t>
   </si>
   <si>
     <t xml:space="preserve">27.962007522583</t>
@@ -2312,13 +2315,13 @@
     <t xml:space="preserve">28.3856754302979</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7078075408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1314735412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2841396331787</t>
+    <t xml:space="preserve">27.7078094482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1314754486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2841415405273</t>
   </si>
   <si>
     <t xml:space="preserve">25.6742076873779</t>
@@ -2327,10 +2330,10 @@
     <t xml:space="preserve">26.0131416320801</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8436737060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3520736694336</t>
+    <t xml:space="preserve">25.8436756134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3520755767822</t>
   </si>
   <si>
     <t xml:space="preserve">26.6062755584717</t>
@@ -2339,7 +2342,7 @@
     <t xml:space="preserve">24.8268737792969</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1826076507568</t>
+    <t xml:space="preserve">26.1826095581055</t>
   </si>
   <si>
     <t xml:space="preserve">26.0978736877441</t>
@@ -2348,7 +2351,7 @@
     <t xml:space="preserve">25.9284076690674</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6910076141357</t>
+    <t xml:space="preserve">26.6910095214844</t>
   </si>
   <si>
     <t xml:space="preserve">22.5390739440918</t>
@@ -2360,7 +2363,7 @@
     <t xml:space="preserve">22.9627418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">24.318473815918</t>
+    <t xml:space="preserve">24.3184757232666</t>
   </si>
   <si>
     <t xml:space="preserve">23.8948078155518</t>
@@ -2378,13 +2381,10 @@
     <t xml:space="preserve">23.2608528137207</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2337398529053</t>
-  </si>
-  <si>
     <t xml:space="preserve">23.9684085845947</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7030735015869</t>
+    <t xml:space="preserve">23.7030754089355</t>
   </si>
   <si>
     <t xml:space="preserve">24.0568523406982</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">25.295072555542</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2066268920898</t>
+    <t xml:space="preserve">25.2066287994385</t>
   </si>
   <si>
     <t xml:space="preserve">24.587516784668</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">25.1181831359863</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6759605407715</t>
+    <t xml:space="preserve">24.6759624481201</t>
   </si>
   <si>
     <t xml:space="preserve">22.9955196380615</t>
@@ -2474,13 +2474,13 @@
     <t xml:space="preserve">23.614631652832</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6417427062988</t>
+    <t xml:space="preserve">22.6417446136475</t>
   </si>
   <si>
     <t xml:space="preserve">23.0839653015137</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1724090576172</t>
+    <t xml:space="preserve">23.1724109649658</t>
   </si>
   <si>
     <t xml:space="preserve">22.3764095306396</t>
@@ -2504,10 +2504,10 @@
     <t xml:space="preserve">21.3150787353516</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7644062042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7372932434082</t>
+    <t xml:space="preserve">24.7644081115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7372951507568</t>
   </si>
   <si>
     <t xml:space="preserve">25.0297393798828</t>
@@ -2531,10 +2531,10 @@
     <t xml:space="preserve">27.0639591217041</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2408447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1524047851562</t>
+    <t xml:space="preserve">27.2408466339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1524028778076</t>
   </si>
   <si>
     <t xml:space="preserve">27.5061817169189</t>
@@ -2543,13 +2543,13 @@
     <t xml:space="preserve">27.5946254730225</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3292903900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7101802825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7986240386963</t>
+    <t xml:space="preserve">27.3292922973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7101821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7986259460449</t>
   </si>
   <si>
     <t xml:space="preserve">26.8870697021484</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">26.4448490142822</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3564033508301</t>
+    <t xml:space="preserve">26.3564052581787</t>
   </si>
   <si>
     <t xml:space="preserve">25.8257389068604</t>
@@ -2582,22 +2582,22 @@
     <t xml:space="preserve">26.179515838623</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6217384338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2679595947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.859956741333</t>
+    <t xml:space="preserve">26.6217365264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2679615020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8599586486816</t>
   </si>
   <si>
     <t xml:space="preserve">28.7855377197266</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1557674407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3227481842041</t>
+    <t xml:space="preserve">29.1557693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3227462768555</t>
   </si>
   <si>
     <t xml:space="preserve">27.7673988342285</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">30.3590221405029</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8036766052246</t>
+    <t xml:space="preserve">29.803674697876</t>
   </si>
   <si>
     <t xml:space="preserve">29.3408851623535</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">28.8780956268311</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1739063262939</t>
+    <t xml:space="preserve">30.1739044189453</t>
   </si>
   <si>
     <t xml:space="preserve">29.06321144104</t>
@@ -2654,25 +2654,25 @@
     <t xml:space="preserve">27.2120513916016</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3971691131592</t>
+    <t xml:space="preserve">27.3971672058105</t>
   </si>
   <si>
     <t xml:space="preserve">27.489725112915</t>
   </si>
   <si>
-    <t xml:space="preserve">27.674840927124</t>
+    <t xml:space="preserve">27.6748390197754</t>
   </si>
   <si>
     <t xml:space="preserve">28.6004199981689</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6929798126221</t>
+    <t xml:space="preserve">28.6929779052734</t>
   </si>
   <si>
     <t xml:space="preserve">29.7111167907715</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5441379547119</t>
+    <t xml:space="preserve">30.5441398620605</t>
   </si>
   <si>
     <t xml:space="preserve">29.9887924194336</t>
@@ -2681,31 +2681,31 @@
     <t xml:space="preserve">30.2664661407471</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4515838623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0994873046875</t>
+    <t xml:space="preserve">30.4515819549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0994834899902</t>
   </si>
   <si>
     <t xml:space="preserve">30.6366958618164</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9143714904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7292556762695</t>
+    <t xml:space="preserve">30.9143733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7292537689209</t>
   </si>
   <si>
     <t xml:space="preserve">30.821813583374</t>
   </si>
   <si>
-    <t xml:space="preserve">31.192045211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0069274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5622749328613</t>
+    <t xml:space="preserve">31.1920471191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.006929397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.56227684021</t>
   </si>
   <si>
     <t xml:space="preserve">32.6729736328125</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">32.1176223754883</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9325084686279</t>
+    <t xml:space="preserve">31.9325103759766</t>
   </si>
   <si>
     <t xml:space="preserve">30.0813503265381</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">33.0432052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3208808898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5059928894043</t>
+    <t xml:space="preserve">33.3208770751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5059967041016</t>
   </si>
   <si>
     <t xml:space="preserve">33.6911125183105</t>
@@ -2771,25 +2771,25 @@
     <t xml:space="preserve">34.1539001464844</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7092514038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9687881469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8762245178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4134368896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2464561462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8943634033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5241317749023</t>
+    <t xml:space="preserve">34.7092475891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9687843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8762283325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4134330749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2464599609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8943672180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5241355895996</t>
   </si>
   <si>
     <t xml:space="preserve">34.4315757751465</t>
@@ -2804,28 +2804,28 @@
     <t xml:space="preserve">34.3390159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1720390319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5422706604004</t>
+    <t xml:space="preserve">35.1720352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5422744750977</t>
   </si>
   <si>
     <t xml:space="preserve">35.0794830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9869194030762</t>
+    <t xml:space="preserve">34.9869232177734</t>
   </si>
   <si>
     <t xml:space="preserve">35.3571548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8199462890625</t>
+    <t xml:space="preserve">35.8199424743652</t>
   </si>
   <si>
     <t xml:space="preserve">35.7273864746094</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9306411743164</t>
+    <t xml:space="preserve">36.9306449890137</t>
   </si>
   <si>
     <t xml:space="preserve">37.7636604309082</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">38.8743591308594</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5966835021973</t>
+    <t xml:space="preserve">38.5966873168945</t>
   </si>
   <si>
     <t xml:space="preserve">38.6892433166504</t>
@@ -2867,13 +2867,13 @@
     <t xml:space="preserve">39.0594749450684</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2445907592773</t>
+    <t xml:space="preserve">39.2445945739746</t>
   </si>
   <si>
     <t xml:space="preserve">38.0413360595703</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8380851745605</t>
+    <t xml:space="preserve">36.8380813598633</t>
   </si>
   <si>
     <t xml:space="preserve">37.8562202453613</t>
@@ -2900,7 +2900,7 @@
     <t xml:space="preserve">41.3734245300293</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0957489013672</t>
+    <t xml:space="preserve">41.0957527160645</t>
   </si>
   <si>
     <t xml:space="preserve">41.0031929016113</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">40.9106369018555</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8180770874023</t>
+    <t xml:space="preserve">40.8180732727051</t>
   </si>
   <si>
     <t xml:space="preserve">40.2164497375488</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">40.5866813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6792411804199</t>
+    <t xml:space="preserve">40.6792373657227</t>
   </si>
   <si>
     <t xml:space="preserve">39.7999382019043</t>
@@ -2939,10 +2939,10 @@
     <t xml:space="preserve">40.6329612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0776138305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5222663879395</t>
+    <t xml:space="preserve">40.0776100158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5222625732422</t>
   </si>
   <si>
     <t xml:space="preserve">40.4478454589844</t>
@@ -35271,7 +35271,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1206" t="s">
-        <v>577</v>
+        <v>642</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35349,7 +35349,7 @@
         <v>16.25</v>
       </c>
       <c r="G1209" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -35713,7 +35713,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1223" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35739,7 +35739,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1224" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35791,7 +35791,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1226" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35817,7 +35817,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35843,7 +35843,7 @@
         <v>15.75</v>
       </c>
       <c r="G1228" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35869,7 +35869,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1229" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35895,7 +35895,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1230" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35921,7 +35921,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1231" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -35947,7 +35947,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35999,7 +35999,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1234" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -36103,7 +36103,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1238" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -36129,7 +36129,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1239" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -36155,7 +36155,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -36181,7 +36181,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1241" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -36207,7 +36207,7 @@
         <v>19.5</v>
       </c>
       <c r="G1242" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -36233,7 +36233,7 @@
         <v>19</v>
       </c>
       <c r="G1243" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -36259,7 +36259,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1244" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -36285,7 +36285,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1245" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -36311,7 +36311,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1246" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -36337,7 +36337,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1247" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -36363,7 +36363,7 @@
         <v>18.75</v>
       </c>
       <c r="G1248" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -36389,7 +36389,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1249" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -36415,7 +36415,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1250" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -36441,7 +36441,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1251" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -36467,7 +36467,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -36493,7 +36493,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1253" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -36519,7 +36519,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -36545,7 +36545,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1255" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -36571,7 +36571,7 @@
         <v>19</v>
       </c>
       <c r="G1256" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36597,7 +36597,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36623,7 +36623,7 @@
         <v>19</v>
       </c>
       <c r="G1258" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36649,7 +36649,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1259" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36675,7 +36675,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1260" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36701,7 +36701,7 @@
         <v>19</v>
       </c>
       <c r="G1261" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36727,7 +36727,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1262" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36753,7 +36753,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36779,7 +36779,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1264" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36805,7 +36805,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1265" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36831,7 +36831,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1266" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36857,7 +36857,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1267" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36883,7 +36883,7 @@
         <v>18.75</v>
       </c>
       <c r="G1268" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36909,7 +36909,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1269" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -36935,7 +36935,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1270" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -36961,7 +36961,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1271" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36987,7 +36987,7 @@
         <v>19</v>
       </c>
       <c r="G1272" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -37013,7 +37013,7 @@
         <v>20</v>
       </c>
       <c r="G1273" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -37039,7 +37039,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1274" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -37065,7 +37065,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1275" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -37091,7 +37091,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1276" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -37117,7 +37117,7 @@
         <v>21</v>
       </c>
       <c r="G1277" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -37143,7 +37143,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1278" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -37169,7 +37169,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1279" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -37195,7 +37195,7 @@
         <v>20</v>
       </c>
       <c r="G1280" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -37221,7 +37221,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1281" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -37247,7 +37247,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1282" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -37273,7 +37273,7 @@
         <v>20</v>
       </c>
       <c r="G1283" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -37299,7 +37299,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1284" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -37325,7 +37325,7 @@
         <v>20</v>
       </c>
       <c r="G1285" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -37351,7 +37351,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1286" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -37377,7 +37377,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1287" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -37403,7 +37403,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -37429,7 +37429,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1289" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -37455,7 +37455,7 @@
         <v>20</v>
       </c>
       <c r="G1290" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -37481,7 +37481,7 @@
         <v>20</v>
       </c>
       <c r="G1291" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -37507,7 +37507,7 @@
         <v>20.5</v>
       </c>
       <c r="G1292" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -37533,7 +37533,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1293" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -37559,7 +37559,7 @@
         <v>21</v>
       </c>
       <c r="G1294" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -37585,7 +37585,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1295" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -37611,7 +37611,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1296" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -37637,7 +37637,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1297" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37663,7 +37663,7 @@
         <v>21.5</v>
       </c>
       <c r="G1298" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -37689,7 +37689,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1299" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37715,7 +37715,7 @@
         <v>22</v>
       </c>
       <c r="G1300" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -37741,7 +37741,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1301" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37767,7 +37767,7 @@
         <v>22</v>
       </c>
       <c r="G1302" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37793,7 +37793,7 @@
         <v>21.5</v>
       </c>
       <c r="G1303" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37819,7 +37819,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1304" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37845,7 +37845,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1305" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37871,7 +37871,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -37897,7 +37897,7 @@
         <v>21</v>
       </c>
       <c r="G1307" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -37923,7 +37923,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1308" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -37949,7 +37949,7 @@
         <v>21</v>
       </c>
       <c r="G1309" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37975,7 +37975,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1310" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -38001,7 +38001,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -38027,7 +38027,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1312" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -38053,7 +38053,7 @@
         <v>21.5</v>
       </c>
       <c r="G1313" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -38079,7 +38079,7 @@
         <v>21.5</v>
       </c>
       <c r="G1314" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -38105,7 +38105,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1315" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -38131,7 +38131,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1316" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -38157,7 +38157,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1317" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -38183,7 +38183,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1318" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -38209,7 +38209,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1319" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -38235,7 +38235,7 @@
         <v>22.5</v>
       </c>
       <c r="G1320" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38261,7 +38261,7 @@
         <v>23.5</v>
       </c>
       <c r="G1321" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -38287,7 +38287,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1322" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -38313,7 +38313,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1323" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -38339,7 +38339,7 @@
         <v>23.5</v>
       </c>
       <c r="G1324" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -38365,7 +38365,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1325" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -38391,7 +38391,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1326" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -38417,7 +38417,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -38443,7 +38443,7 @@
         <v>23</v>
       </c>
       <c r="G1328" t="s">
-        <v>548</v>
+        <v>696</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -38469,7 +38469,7 @@
         <v>23.5</v>
       </c>
       <c r="G1329" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -38495,7 +38495,7 @@
         <v>23.5</v>
       </c>
       <c r="G1330" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38521,7 +38521,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1331" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -38547,7 +38547,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1332" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -38573,7 +38573,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1333" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -38599,7 +38599,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -38625,7 +38625,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1335" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -38651,7 +38651,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -38677,7 +38677,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1337" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -38703,7 +38703,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1338" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -38729,7 +38729,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1339" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -38755,7 +38755,7 @@
         <v>23.5</v>
       </c>
       <c r="G1340" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -38781,7 +38781,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1341" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -38807,7 +38807,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1342" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -38833,7 +38833,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1343" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -38859,7 +38859,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1344" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -38885,7 +38885,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1345" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -38911,7 +38911,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1346" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -38937,7 +38937,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1347" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -38963,7 +38963,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1348" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -38989,7 +38989,7 @@
         <v>23.5</v>
       </c>
       <c r="G1349" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -39015,7 +39015,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1350" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -39041,7 +39041,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1351" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -39067,7 +39067,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1352" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -39093,7 +39093,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1353" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -39119,7 +39119,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -39145,7 +39145,7 @@
         <v>23</v>
       </c>
       <c r="G1355" t="s">
-        <v>548</v>
+        <v>696</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39171,7 +39171,7 @@
         <v>23</v>
       </c>
       <c r="G1356" t="s">
-        <v>548</v>
+        <v>696</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -39197,7 +39197,7 @@
         <v>23</v>
       </c>
       <c r="G1357" t="s">
-        <v>548</v>
+        <v>696</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39223,7 +39223,7 @@
         <v>23</v>
       </c>
       <c r="G1358" t="s">
-        <v>548</v>
+        <v>696</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39249,7 +39249,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -39275,7 +39275,7 @@
         <v>23</v>
       </c>
       <c r="G1360" t="s">
-        <v>548</v>
+        <v>696</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -39301,7 +39301,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1361" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -39327,7 +39327,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1362" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -39353,7 +39353,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -39379,7 +39379,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -39431,7 +39431,7 @@
         <v>23</v>
       </c>
       <c r="G1366" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -39457,7 +39457,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1367" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -39483,7 +39483,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1368" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -39509,7 +39509,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1369" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -39587,7 +39587,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1372" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -39613,7 +39613,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1373" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -39639,7 +39639,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1374" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -39665,7 +39665,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1375" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -39717,7 +39717,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1377" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -39743,7 +39743,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1378" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -39769,7 +39769,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1379" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -39795,7 +39795,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1380" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -39847,7 +39847,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1382" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -39925,7 +39925,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1385" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -39951,7 +39951,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -39977,7 +39977,7 @@
         <v>24</v>
       </c>
       <c r="G1387" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -40003,7 +40003,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1388" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -40081,7 +40081,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1391" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -40107,7 +40107,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1392" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -40133,7 +40133,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1393" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -40211,7 +40211,7 @@
         <v>23</v>
       </c>
       <c r="G1396" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -40237,7 +40237,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1397" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -40263,7 +40263,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1398" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -40289,7 +40289,7 @@
         <v>23</v>
       </c>
       <c r="G1399" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -40315,7 +40315,7 @@
         <v>23</v>
       </c>
       <c r="G1400" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -40341,7 +40341,7 @@
         <v>23</v>
       </c>
       <c r="G1401" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -40367,7 +40367,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1402" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -40393,7 +40393,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1403" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -40419,7 +40419,7 @@
         <v>23</v>
       </c>
       <c r="G1404" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -40445,7 +40445,7 @@
         <v>23</v>
       </c>
       <c r="G1405" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -40471,7 +40471,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1406" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -40497,7 +40497,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1407" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -40523,7 +40523,7 @@
         <v>22.5</v>
       </c>
       <c r="G1408" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -40549,7 +40549,7 @@
         <v>22</v>
       </c>
       <c r="G1409" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -40575,7 +40575,7 @@
         <v>22.5</v>
       </c>
       <c r="G1410" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -40601,7 +40601,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1411" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -40627,7 +40627,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1412" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -40653,7 +40653,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1413" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -40679,7 +40679,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1414" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -40705,7 +40705,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1415" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -40783,7 +40783,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1418" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -40809,7 +40809,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -40835,7 +40835,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1420" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -40861,7 +40861,7 @@
         <v>24</v>
       </c>
       <c r="G1421" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -40887,7 +40887,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1422" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -40913,7 +40913,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1423" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -40939,7 +40939,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1424" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -40965,7 +40965,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1425" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -40991,7 +40991,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1426" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -41017,7 +41017,7 @@
         <v>25</v>
       </c>
       <c r="G1427" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -41043,7 +41043,7 @@
         <v>25</v>
       </c>
       <c r="G1428" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -41069,7 +41069,7 @@
         <v>25</v>
       </c>
       <c r="G1429" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -41095,7 +41095,7 @@
         <v>24.5</v>
       </c>
       <c r="G1430" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -41121,7 +41121,7 @@
         <v>24.5</v>
       </c>
       <c r="G1431" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -41147,7 +41147,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1432" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -41173,7 +41173,7 @@
         <v>24.5</v>
       </c>
       <c r="G1433" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -41199,7 +41199,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1434" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -41225,7 +41225,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1435" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -41251,7 +41251,7 @@
         <v>26</v>
       </c>
       <c r="G1436" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -41277,7 +41277,7 @@
         <v>26.5</v>
       </c>
       <c r="G1437" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -41303,7 +41303,7 @@
         <v>26</v>
       </c>
       <c r="G1438" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -41329,7 +41329,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1439" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -41355,7 +41355,7 @@
         <v>26</v>
       </c>
       <c r="G1440" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -41381,7 +41381,7 @@
         <v>26.5</v>
       </c>
       <c r="G1441" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -41407,7 +41407,7 @@
         <v>26.5</v>
       </c>
       <c r="G1442" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -41433,7 +41433,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1443" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -41459,7 +41459,7 @@
         <v>26.5</v>
       </c>
       <c r="G1444" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -41485,7 +41485,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1445" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -41511,7 +41511,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1446" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -41537,7 +41537,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1447" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -41563,7 +41563,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1448" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -41589,7 +41589,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1449" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -41615,7 +41615,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1450" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -41641,7 +41641,7 @@
         <v>27.5</v>
       </c>
       <c r="G1451" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -41667,7 +41667,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1452" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -41693,7 +41693,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -41719,7 +41719,7 @@
         <v>27.5</v>
       </c>
       <c r="G1454" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -41745,7 +41745,7 @@
         <v>27.5</v>
       </c>
       <c r="G1455" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -41771,7 +41771,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1456" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -41797,7 +41797,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1457" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -41823,7 +41823,7 @@
         <v>28</v>
       </c>
       <c r="G1458" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -41849,7 +41849,7 @@
         <v>28</v>
       </c>
       <c r="G1459" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -41875,7 +41875,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -41901,7 +41901,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1461" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -41927,7 +41927,7 @@
         <v>27.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -41953,7 +41953,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1463" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -41979,7 +41979,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1464" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -42005,7 +42005,7 @@
         <v>26.5</v>
       </c>
       <c r="G1465" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -42031,7 +42031,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1466" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -42057,7 +42057,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1467" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -42083,7 +42083,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1468" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -42109,7 +42109,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1469" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -42135,7 +42135,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1470" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -42161,7 +42161,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1471" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -42187,7 +42187,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1472" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -42213,7 +42213,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1473" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -42239,7 +42239,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1474" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -42265,7 +42265,7 @@
         <v>27.5</v>
       </c>
       <c r="G1475" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -42291,7 +42291,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1476" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -42317,7 +42317,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1477" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -42343,7 +42343,7 @@
         <v>27.5</v>
       </c>
       <c r="G1478" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -42369,7 +42369,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1479" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -42395,7 +42395,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1480" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -42421,7 +42421,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1481" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -42447,7 +42447,7 @@
         <v>27</v>
       </c>
       <c r="G1482" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -42473,7 +42473,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1483" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -42499,7 +42499,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1484" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -42525,7 +42525,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1485" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -42551,7 +42551,7 @@
         <v>27.5</v>
       </c>
       <c r="G1486" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -42577,7 +42577,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1487" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -42603,7 +42603,7 @@
         <v>27.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -42629,7 +42629,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1489" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -42655,7 +42655,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1490" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -42681,7 +42681,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1491" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -42707,7 +42707,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -42733,7 +42733,7 @@
         <v>28</v>
       </c>
       <c r="G1493" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -42759,7 +42759,7 @@
         <v>28</v>
       </c>
       <c r="G1494" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -42785,7 +42785,7 @@
         <v>28.5</v>
       </c>
       <c r="G1495" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -42811,7 +42811,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1496" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -42837,7 +42837,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1497" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -42863,7 +42863,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1498" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -42889,7 +42889,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1499" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -42915,7 +42915,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1500" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -42941,7 +42941,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1501" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -42967,7 +42967,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1502" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -42993,7 +42993,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1503" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -43019,7 +43019,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1504" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -43045,7 +43045,7 @@
         <v>29</v>
       </c>
       <c r="G1505" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -43071,7 +43071,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1506" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -43097,7 +43097,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1507" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43123,7 +43123,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1508" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43149,7 +43149,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1509" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -43175,7 +43175,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1510" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -43201,7 +43201,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1511" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -43227,7 +43227,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1512" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -43253,7 +43253,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1513" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43279,7 +43279,7 @@
         <v>30</v>
       </c>
       <c r="G1514" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -43305,7 +43305,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1515" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -43331,7 +43331,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1516" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -43357,7 +43357,7 @@
         <v>30</v>
       </c>
       <c r="G1517" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -43383,7 +43383,7 @@
         <v>31</v>
       </c>
       <c r="G1518" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -43409,7 +43409,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1519" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43435,7 +43435,7 @@
         <v>31</v>
       </c>
       <c r="G1520" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -43461,7 +43461,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1521" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -43487,7 +43487,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1522" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -43513,7 +43513,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1523" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -43539,7 +43539,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1524" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -43565,7 +43565,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1525" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43591,7 +43591,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1526" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -43617,7 +43617,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1527" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43643,7 +43643,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1528" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -43669,7 +43669,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1529" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -43695,7 +43695,7 @@
         <v>34.5</v>
       </c>
       <c r="G1530" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -43721,7 +43721,7 @@
         <v>33</v>
       </c>
       <c r="G1531" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -43747,7 +43747,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1532" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -43773,7 +43773,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1533" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -43799,7 +43799,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1534" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -43825,7 +43825,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1535" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -43851,7 +43851,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1536" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -43877,7 +43877,7 @@
         <v>33.5</v>
       </c>
       <c r="G1537" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -43903,7 +43903,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1538" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -43929,7 +43929,7 @@
         <v>33</v>
       </c>
       <c r="G1539" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -43955,7 +43955,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1540" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -43981,7 +43981,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1541" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -44007,7 +44007,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1542" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -44033,7 +44033,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1543" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -44059,7 +44059,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1544" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44085,7 +44085,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1545" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44111,7 +44111,7 @@
         <v>30.5</v>
       </c>
       <c r="G1546" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44137,7 +44137,7 @@
         <v>30.5</v>
       </c>
       <c r="G1547" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -44163,7 +44163,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1548" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -44189,7 +44189,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1549" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -44215,7 +44215,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1550" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -44241,7 +44241,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1551" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -44267,7 +44267,7 @@
         <v>30.5</v>
       </c>
       <c r="G1552" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -44293,7 +44293,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1553" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -44319,7 +44319,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1554" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -44345,7 +44345,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1555" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -44371,7 +44371,7 @@
         <v>30</v>
       </c>
       <c r="G1556" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44397,7 +44397,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1557" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -44423,7 +44423,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1558" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -44449,7 +44449,7 @@
         <v>31</v>
       </c>
       <c r="G1559" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -44475,7 +44475,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1560" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -44501,7 +44501,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1561" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -44527,7 +44527,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1562" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -44553,7 +44553,7 @@
         <v>30.5</v>
       </c>
       <c r="G1563" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -44579,7 +44579,7 @@
         <v>31.5</v>
       </c>
       <c r="G1564" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44605,7 +44605,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1565" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -44631,7 +44631,7 @@
         <v>30.5</v>
       </c>
       <c r="G1566" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -44657,7 +44657,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1567" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -44683,7 +44683,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1568" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44709,7 +44709,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1569" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -44735,7 +44735,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1570" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -44761,7 +44761,7 @@
         <v>27</v>
       </c>
       <c r="G1571" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -44787,7 +44787,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1572" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -44813,7 +44813,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1573" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -44839,7 +44839,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1574" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -44865,7 +44865,7 @@
         <v>27</v>
       </c>
       <c r="G1575" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -44891,7 +44891,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1576" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -44917,7 +44917,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1577" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -44943,7 +44943,7 @@
         <v>26</v>
       </c>
       <c r="G1578" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -44969,7 +44969,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1579" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -44995,7 +44995,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1580" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -45021,7 +45021,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1581" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -45047,7 +45047,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1582" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -45073,7 +45073,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1583" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45099,7 +45099,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1584" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45125,7 +45125,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1585" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45151,7 +45151,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1586" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -45177,7 +45177,7 @@
         <v>28.5</v>
       </c>
       <c r="G1587" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -45203,7 +45203,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1588" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -45229,7 +45229,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1589" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45255,7 +45255,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1590" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -45281,7 +45281,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1591" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45307,7 +45307,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1592" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -45333,7 +45333,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1593" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -45359,7 +45359,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1594" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -45385,7 +45385,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1595" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45411,7 +45411,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1596" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -45437,7 +45437,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1597" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -45463,7 +45463,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1598" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -45489,7 +45489,7 @@
         <v>27.5</v>
       </c>
       <c r="G1599" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -45515,7 +45515,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1600" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45541,7 +45541,7 @@
         <v>28</v>
       </c>
       <c r="G1601" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45567,7 +45567,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1602" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45593,7 +45593,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1603" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -45619,7 +45619,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1604" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -45645,7 +45645,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1605" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45671,7 +45671,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1606" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45697,7 +45697,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1607" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -45723,7 +45723,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1608" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -45749,7 +45749,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1609" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -45775,7 +45775,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1610" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -45801,7 +45801,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1611" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -45827,7 +45827,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1612" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -45853,7 +45853,7 @@
         <v>28</v>
       </c>
       <c r="G1613" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -45879,7 +45879,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1614" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -45905,7 +45905,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1615" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -45931,7 +45931,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1616" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -45957,7 +45957,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1617" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -45983,7 +45983,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1618" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -46009,7 +46009,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1619" t="s">
-        <v>788</v>
+        <v>742</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -46165,7 +46165,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1625" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46269,7 +46269,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1629" t="s">
-        <v>788</v>
+        <v>742</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -47101,7 +47101,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1661" t="s">
-        <v>788</v>
+        <v>742</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47231,7 +47231,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1666" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47309,7 +47309,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1669" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -47491,7 +47491,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>788</v>
+        <v>742</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -47621,7 +47621,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1681" t="s">
-        <v>788</v>
+        <v>742</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -48089,7 +48089,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1699" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -48167,7 +48167,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1702" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -48193,7 +48193,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1703" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -48271,7 +48271,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1706" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -48921,7 +48921,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1731" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -49155,7 +49155,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1740" t="s">
-        <v>788</v>
+        <v>742</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -68585,7 +68585,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6494212963</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>24390</v>
@@ -68606,6 +68606,32 @@
         <v>1190</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6494097222</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>14338</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>60.4000015258789</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>59.4000015258789</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>60</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="1197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="1198">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23958873748779</t>
+    <t xml:space="preserve">9.23958683013916</t>
   </si>
   <si>
     <t xml:space="preserve">CMB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.556565284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31377506256104</t>
+    <t xml:space="preserve">9.55656719207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31377410888672</t>
   </si>
   <si>
     <t xml:space="preserve">9.40144920349121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40819358825684</t>
+    <t xml:space="preserve">9.40819454193115</t>
   </si>
   <si>
     <t xml:space="preserve">9.44191455841064</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36098289489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13842487335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32051944732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26656436920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34075164794922</t>
+    <t xml:space="preserve">9.36098384857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13842391967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32051753997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26656532287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34075260162354</t>
   </si>
   <si>
     <t xml:space="preserve">9.27330875396729</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">9.19912242889404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10470199584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84167957305908</t>
+    <t xml:space="preserve">9.10470294952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84167861938477</t>
   </si>
   <si>
     <t xml:space="preserve">8.77423667907715</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">8.84842300415039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3628396987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32911682128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61911964416504</t>
+    <t xml:space="preserve">8.36283874511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32911777496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61911869049072</t>
   </si>
   <si>
     <t xml:space="preserve">8.45051288604736</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">8.4302806854248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63260650634766</t>
+    <t xml:space="preserve">8.63260746002197</t>
   </si>
   <si>
     <t xml:space="preserve">8.80121421813965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22609996795654</t>
+    <t xml:space="preserve">9.22610092163086</t>
   </si>
   <si>
     <t xml:space="preserve">9.25982093811035</t>
@@ -128,28 +128,28 @@
     <t xml:space="preserve">8.87539958953857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96981811523438</t>
+    <t xml:space="preserve">8.96982002258301</t>
   </si>
   <si>
     <t xml:space="preserve">8.71353816986084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6663293838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89563179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81470108032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99679565429688</t>
+    <t xml:space="preserve">8.66632843017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89563274383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81470012664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99679470062256</t>
   </si>
   <si>
     <t xml:space="preserve">9.01028442382812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90237617492676</t>
+    <t xml:space="preserve">8.90237712860107</t>
   </si>
   <si>
     <t xml:space="preserve">8.97656440734863</t>
@@ -161,61 +161,61 @@
     <t xml:space="preserve">9.17214584350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13168048858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34749603271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25307750701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15865707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08447265625</t>
+    <t xml:space="preserve">9.13167953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34749507904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25307655334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15865802764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08447074890137</t>
   </si>
   <si>
     <t xml:space="preserve">9.16540145874023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98330783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78772449493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78098011016846</t>
+    <t xml:space="preserve">8.98330688476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7877254486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78098106384277</t>
   </si>
   <si>
     <t xml:space="preserve">9.12493515014648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03726005554199</t>
+    <t xml:space="preserve">9.03726100921631</t>
   </si>
   <si>
     <t xml:space="preserve">9.21261119842529</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0440034866333</t>
+    <t xml:space="preserve">9.04400444030762</t>
   </si>
   <si>
     <t xml:space="preserve">9.09795951843262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20586681365967</t>
+    <t xml:space="preserve">9.20586490631104</t>
   </si>
   <si>
     <t xml:space="preserve">9.38121604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28679656982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22100925445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22798919677734</t>
+    <t xml:space="preserve">9.28679847717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22100734710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22798824310303</t>
   </si>
   <si>
     <t xml:space="preserve">9.19308757781982</t>
@@ -224,10 +224,10 @@
     <t xml:space="preserve">9.35363292694092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40947723388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52116203308105</t>
+    <t xml:space="preserve">9.4094762802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52116394042969</t>
   </si>
   <si>
     <t xml:space="preserve">9.49324131011963</t>
@@ -236,40 +236,40 @@
     <t xml:space="preserve">9.38853645324707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9469633102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76547145843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77245330810547</t>
+    <t xml:space="preserve">9.94696235656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76547241210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77245426177979</t>
   </si>
   <si>
     <t xml:space="preserve">9.66774940490723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82829666137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75151252746582</t>
+    <t xml:space="preserve">9.82829570770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75151348114014</t>
   </si>
   <si>
     <t xml:space="preserve">9.57002449035645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57700538635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55606365203857</t>
+    <t xml:space="preserve">9.57700443267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55606174468994</t>
   </si>
   <si>
     <t xml:space="preserve">9.47927951812744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42343616485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39551639556885</t>
+    <t xml:space="preserve">9.42343711853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39551544189453</t>
   </si>
   <si>
     <t xml:space="preserve">9.4164571762085</t>
@@ -278,31 +278,31 @@
     <t xml:space="preserve">9.34665298461914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58398532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6258659362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63284778594971</t>
+    <t xml:space="preserve">9.583984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62586688995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63284683227539</t>
   </si>
   <si>
     <t xml:space="preserve">9.46532154083252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48626041412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59096527099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56304454803467</t>
+    <t xml:space="preserve">9.48626136779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59096622467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56304359436035</t>
   </si>
   <si>
     <t xml:space="preserve">9.53512287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12328338623047</t>
+    <t xml:space="preserve">9.12328243255615</t>
   </si>
   <si>
     <t xml:space="preserve">9.30477237701416</t>
@@ -311,88 +311,88 @@
     <t xml:space="preserve">9.2838306427002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20704650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2768497467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3606128692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29081249237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29779243469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31873321533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36759376525879</t>
+    <t xml:space="preserve">9.20704746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27685070037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36061477661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29081153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29779052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31873512268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36759471893311</t>
   </si>
   <si>
     <t xml:space="preserve">9.47230052947998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52814197540283</t>
+    <t xml:space="preserve">9.52814102172852</t>
   </si>
   <si>
     <t xml:space="preserve">9.50720119476318</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44437789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50022029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3326940536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32571315765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13724422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14422512054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15120601654053</t>
+    <t xml:space="preserve">9.44437885284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50021934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33269309997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32571220397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13724517822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14422416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15120410919189</t>
   </si>
   <si>
     <t xml:space="preserve">9.10932350158691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03951930999756</t>
+    <t xml:space="preserve">9.03952026367188</t>
   </si>
   <si>
     <t xml:space="preserve">8.92783546447754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01159763336182</t>
+    <t xml:space="preserve">9.01159954071045</t>
   </si>
   <si>
     <t xml:space="preserve">9.07442092895508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97669696807861</t>
+    <t xml:space="preserve">8.97669792175293</t>
   </si>
   <si>
     <t xml:space="preserve">8.86501121520996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85105133056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93481349945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92085456848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95575618743896</t>
+    <t xml:space="preserve">8.85105228424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.934814453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92085361480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95575523376465</t>
   </si>
   <si>
     <t xml:space="preserve">8.96971702575684</t>
@@ -401,46 +401,46 @@
     <t xml:space="preserve">9.00461769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91387462615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87897300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80916976928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59975814819336</t>
+    <t xml:space="preserve">8.91387367248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87897205352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80916881561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59975910186768</t>
   </si>
   <si>
     <t xml:space="preserve">8.56485843658447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81614971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83709144592285</t>
+    <t xml:space="preserve">8.81614875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83708953857422</t>
   </si>
   <si>
     <t xml:space="preserve">8.89991283416748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99763870239258</t>
+    <t xml:space="preserve">8.99763774871826</t>
   </si>
   <si>
     <t xml:space="preserve">8.83010959625244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96273612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08838176727295</t>
+    <t xml:space="preserve">8.96273517608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08838272094727</t>
   </si>
   <si>
     <t xml:space="preserve">9.04649925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09536170959473</t>
+    <t xml:space="preserve">9.09536266326904</t>
   </si>
   <si>
     <t xml:space="preserve">9.66076850891113</t>
@@ -449,40 +449,40 @@
     <t xml:space="preserve">9.64680862426758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70265007019043</t>
+    <t xml:space="preserve">9.70265102386475</t>
   </si>
   <si>
     <t xml:space="preserve">9.79339504241943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92602062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98186302185059</t>
+    <t xml:space="preserve">9.92602252960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9818639755249</t>
   </si>
   <si>
     <t xml:space="preserve">10.0516662597656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4146423339844</t>
+    <t xml:space="preserve">10.414644241333</t>
   </si>
   <si>
     <t xml:space="preserve">10.19127368927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2471151351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493911743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1354322433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2680568695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.393702507019</t>
+    <t xml:space="preserve">10.2471160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493921279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1354312896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2680559158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3937034606934</t>
   </si>
   <si>
     <t xml:space="preserve">10.5402898788452</t>
@@ -491,43 +491,43 @@
     <t xml:space="preserve">10.5891513824463</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844465255737</t>
+    <t xml:space="preserve">10.484447479248</t>
   </si>
   <si>
     <t xml:space="preserve">10.6310329437256</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3588027954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.988844871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95394229888916</t>
+    <t xml:space="preserve">10.3588008880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98884391784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95394325256348</t>
   </si>
   <si>
     <t xml:space="preserve">10.100528717041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4704856872559</t>
+    <t xml:space="preserve">10.4704866409302</t>
   </si>
   <si>
     <t xml:space="preserve">10.3867225646973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5472707748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.344841003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4774675369263</t>
+    <t xml:space="preserve">10.547269821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3448400497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.477466583252</t>
   </si>
   <si>
     <t xml:space="preserve">10.4006824493408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.435585975647</t>
+    <t xml:space="preserve">10.4355850219727</t>
   </si>
   <si>
     <t xml:space="preserve">10.3727607727051</t>
@@ -536,49 +536,49 @@
     <t xml:space="preserve">10.3657817840576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3378591537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2820177078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3797407150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6100931167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5542507171631</t>
+    <t xml:space="preserve">10.3378601074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2820167541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3797416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6100921630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5542497634888</t>
   </si>
   <si>
     <t xml:space="preserve">10.6938562393188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0917339324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0428733825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0358934402466</t>
+    <t xml:space="preserve">11.0917348861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0428714752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0358915328979</t>
   </si>
   <si>
     <t xml:space="preserve">11.0638132095337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.084755897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3569869995117</t>
+    <t xml:space="preserve">11.0847539901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.356987953186</t>
   </si>
   <si>
     <t xml:space="preserve">11.5175352096558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0899219512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9991788864136</t>
+    <t xml:space="preserve">12.0899209976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9991779327393</t>
   </si>
   <si>
     <t xml:space="preserve">12.0689821243286</t>
@@ -587,31 +587,31 @@
     <t xml:space="preserve">12.1038818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2853698730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8228549957275</t>
+    <t xml:space="preserve">12.2853717803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8228559494019</t>
   </si>
   <si>
     <t xml:space="preserve">12.9764232635498</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9903841018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2486543655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1090488433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1230087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8926582336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9136009216309</t>
+    <t xml:space="preserve">12.9903831481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2486553192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1090507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1230058670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8926572799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9135990142822</t>
   </si>
   <si>
     <t xml:space="preserve">12.8437967300415</t>
@@ -620,130 +620,130 @@
     <t xml:space="preserve">12.9624643325806</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1928129196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3952398300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8978252410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9815921783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9327259063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0234708786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0304508209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1351556777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0723314285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0025300979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.211256980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197383880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.146164894104</t>
+    <t xml:space="preserve">13.1928119659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.39524269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8978271484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9815902709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9327278137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0234699249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0304536819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1351537704468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0723323822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0025281906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2112550735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197393417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.146167755127</t>
   </si>
   <si>
     <t xml:space="preserve">14.0810747146606</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942893981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6688423156738</t>
+    <t xml:space="preserve">13.994288444519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6688413619995</t>
   </si>
   <si>
     <t xml:space="preserve">14.3559007644653</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6833066940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.001522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9870576858521</t>
+    <t xml:space="preserve">13.6833057403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0015249252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9870586395264</t>
   </si>
   <si>
     <t xml:space="preserve">14.2691125869751</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3486680984497</t>
+    <t xml:space="preserve">14.3486671447754</t>
   </si>
   <si>
     <t xml:space="preserve">14.3414363861084</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2763452529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4282217025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5656328201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3322467803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8457317352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7589483261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3611745834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1876039505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9200086593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6307229995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636777877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3105497360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9272422790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0718860626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5492105484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4551935195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2671566009521</t>
+    <t xml:space="preserve">14.2763471603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4282207489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5656318664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3322496414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8457307815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7589464187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3611736297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1876010894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9200105667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6307220458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636749267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3105506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9272403717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0718870162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5492124557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4551944732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2671546936035</t>
   </si>
   <si>
     <t xml:space="preserve">15.1731367111206</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8332262039185</t>
+    <t xml:space="preserve">14.8332271575928</t>
   </si>
   <si>
     <t xml:space="preserve">15.1369781494141</t>
@@ -752,58 +752,58 @@
     <t xml:space="preserve">15.1152801513672</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9850988388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1514387130737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0284929275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.209300994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6649265289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6938543319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7661771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9325170516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0410022735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9469814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6432304382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2816228866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2888536453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2599239349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3250141143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2382249832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1586723327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0574235916138</t>
+    <t xml:space="preserve">14.9850997924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1514415740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0284938812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2092962265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.664924621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6938571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7661752700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9325189590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0410003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9469833374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6432294845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2816200256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2888498306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2599248886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3250122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2382278442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1586713790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0574226379395</t>
   </si>
   <si>
     <t xml:space="preserve">15.1803693771362</t>
@@ -812,25 +812,25 @@
     <t xml:space="preserve">15.2454595565796</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8983125686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.869384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8259925842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9634046554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9706401824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6813497543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7536678314209</t>
+    <t xml:space="preserve">14.8983144760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8693828582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8259935379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9634056091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9706363677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6813478469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7536725997925</t>
   </si>
   <si>
     <t xml:space="preserve">14.6958131790161</t>
@@ -839,22 +839,22 @@
     <t xml:space="preserve">14.8910808563232</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4933128356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8549213409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6524200439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6090288162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8476915359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1948366165161</t>
+    <t xml:space="preserve">14.493311882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.854923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6524181365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6090269088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8476896286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1948347091675</t>
   </si>
   <si>
     <t xml:space="preserve">15.3394765853882</t>
@@ -866,22 +866,22 @@
     <t xml:space="preserve">16.2651977539062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9956512451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5742244720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6879825592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3986968994141</t>
+    <t xml:space="preserve">16.9956474304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5742225646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6879806518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3986949920654</t>
   </si>
   <si>
     <t xml:space="preserve">18.4420871734619</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2178859710693</t>
+    <t xml:space="preserve">18.2178897857666</t>
   </si>
   <si>
     <t xml:space="preserve">18.0804786682129</t>
@@ -893,16 +893,16 @@
     <t xml:space="preserve">17.971996307373</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0081577301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8562793731689</t>
+    <t xml:space="preserve">18.0081558227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8562831878662</t>
   </si>
   <si>
     <t xml:space="preserve">17.9647617340088</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6393146514893</t>
+    <t xml:space="preserve">17.6393165588379</t>
   </si>
   <si>
     <t xml:space="preserve">17.7622623443604</t>
@@ -911,31 +911,31 @@
     <t xml:space="preserve">17.6031551361084</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5886878967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.538064956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5019016265869</t>
+    <t xml:space="preserve">17.5886859893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5380630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5019035339355</t>
   </si>
   <si>
     <t xml:space="preserve">17.3861885070801</t>
   </si>
   <si>
-    <t xml:space="preserve">17.321102142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2849369049072</t>
+    <t xml:space="preserve">17.3211002349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2849388122559</t>
   </si>
   <si>
     <t xml:space="preserve">17.0462760925293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2632427215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0969009399414</t>
+    <t xml:space="preserve">17.2632446289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0968990325928</t>
   </si>
   <si>
     <t xml:space="preserve">17.3283309936523</t>
@@ -944,22 +944,22 @@
     <t xml:space="preserve">17.3572578430176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4006519317627</t>
+    <t xml:space="preserve">17.4006538391113</t>
   </si>
   <si>
     <t xml:space="preserve">17.3789558410645</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2921695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.342794418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1692199707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.590648651123</t>
+    <t xml:space="preserve">17.2921676635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3427963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1692218780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5906467437744</t>
   </si>
   <si>
     <t xml:space="preserve">16.6268081665039</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">16.9233303070068</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3447513580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7083196640015</t>
+    <t xml:space="preserve">16.3447532653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7083206176758</t>
   </si>
   <si>
     <t xml:space="preserve">16.1133232116699</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9180536270142</t>
+    <t xml:space="preserve">15.9180526733398</t>
   </si>
   <si>
     <t xml:space="preserve">15.650463104248</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">16.3013591766357</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5761833190918</t>
+    <t xml:space="preserve">16.5761814117432</t>
   </si>
   <si>
     <t xml:space="preserve">16.5110931396484</t>
@@ -998,19 +998,19 @@
     <t xml:space="preserve">16.5617160797119</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0699310302734</t>
+    <t xml:space="preserve">16.0699291229248</t>
   </si>
   <si>
     <t xml:space="preserve">16.5255584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4098415374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2073402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8746614456177</t>
+    <t xml:space="preserve">16.4098453521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2073421478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.874662399292</t>
   </si>
   <si>
     <t xml:space="preserve">16.2434997558594</t>
@@ -1025,25 +1025,25 @@
     <t xml:space="preserve">15.8312664031982</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8601942062378</t>
+    <t xml:space="preserve">15.8601961135864</t>
   </si>
   <si>
     <t xml:space="preserve">15.8529634475708</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6287651062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4696559906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.462423324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215343475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9976100921631</t>
+    <t xml:space="preserve">15.6287679672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4696588516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4624242782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215305328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9976081848145</t>
   </si>
   <si>
     <t xml:space="preserve">16.236270904541</t>
@@ -1055,10 +1055,10 @@
     <t xml:space="preserve">16.2724323272705</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7786865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6340408325195</t>
+    <t xml:space="preserve">16.7786846160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6340389251709</t>
   </si>
   <si>
     <t xml:space="preserve">16.4532356262207</t>
@@ -1067,55 +1067,55 @@
     <t xml:space="preserve">16.7425231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">16.59787940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7063598632812</t>
+    <t xml:space="preserve">16.5978755950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7063655853271</t>
   </si>
   <si>
     <t xml:space="preserve">16.8510055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0318088531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2126140594482</t>
+    <t xml:space="preserve">17.031810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2126159667969</t>
   </si>
   <si>
     <t xml:space="preserve">17.4295825958252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9594898223877</t>
+    <t xml:space="preserve">16.9594879150391</t>
   </si>
   <si>
     <t xml:space="preserve">16.3809127807617</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9831447601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9108209609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7300176620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.368408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4045648574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4768896102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8023376464844</t>
+    <t xml:space="preserve">15.9831418991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9108219146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.730019569397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3684062957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4045658111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4768886566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8023386001587</t>
   </si>
   <si>
     <t xml:space="preserve">16.670202255249</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1402931213379</t>
+    <t xml:space="preserve">17.1402950286865</t>
   </si>
   <si>
     <t xml:space="preserve">17.1041316986084</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">16.8148460388184</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0679702758789</t>
+    <t xml:space="preserve">17.0679721832275</t>
   </si>
   <si>
     <t xml:space="preserve">16.8871669769287</t>
@@ -1136,16 +1136,16 @@
     <t xml:space="preserve">17.6827087402344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3934173583984</t>
+    <t xml:space="preserve">17.3934192657471</t>
   </si>
   <si>
     <t xml:space="preserve">17.2487773895264</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7550296783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8996734619141</t>
+    <t xml:space="preserve">17.7550277709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8996753692627</t>
   </si>
   <si>
     <t xml:space="preserve">18.5867328643799</t>
@@ -1154,100 +1154,100 @@
     <t xml:space="preserve">18.6590538024902</t>
   </si>
   <si>
+    <t xml:space="preserve">19.0206623077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5427989959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2444381713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9157562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4378890991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6546878814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4682121276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6173896789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0952548980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8714828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9460716247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7968940734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9018001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3050746917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7899150848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8341884613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1698436737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3936176300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5055046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8038673400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8784599304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6919822692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3190269470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4239387512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1325454711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3563213348389</t>
+  </si>
+  <si>
     <t xml:space="preserve">19.0206642150879</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5428009033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2444362640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9157543182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4378910064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6546840667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4682102203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6173915863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0952529907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8714809417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9460735321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7968940734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9018001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3050765991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7899150848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8341884613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1698455810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3936176300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5055046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8038673400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8784599304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6919803619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3190269470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4239368438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1325511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3563213348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0206623077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7292785644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7222995758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9087791442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6477088928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5731201171875</t>
+    <t xml:space="preserve">19.7292766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.722297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9087772369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6477108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5731182098389</t>
   </si>
   <si>
     <t xml:space="preserve">18.5358238220215</t>
@@ -1256,19 +1256,19 @@
     <t xml:space="preserve">17.9763927459717</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1255741119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4612331390381</t>
+    <t xml:space="preserve">18.1255702972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4612350463867</t>
   </si>
   <si>
     <t xml:space="preserve">18.7595958709717</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6104125976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3493461608887</t>
+    <t xml:space="preserve">18.6104145050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.34934425354</t>
   </si>
   <si>
     <t xml:space="preserve">18.6850051879883</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">18.4985275268555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2817306518555</t>
+    <t xml:space="preserve">19.2817325592041</t>
   </si>
   <si>
     <t xml:space="preserve">19.0579605102539</t>
@@ -1295,352 +1295,352 @@
     <t xml:space="preserve">18.3866424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1558933258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1862106323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.589485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1419410705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9554624557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0370292663574</t>
+    <t xml:space="preserve">17.155891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1862125396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5894870758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1419401168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9554615020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0370311737061</t>
   </si>
   <si>
     <t xml:space="preserve">16.5218715667725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6640777587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1046447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9927577972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0300550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.768985748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3661947250366</t>
+    <t xml:space="preserve">15.6640768051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.104642868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9927606582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0300540924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7689867019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3661966323853</t>
   </si>
   <si>
     <t xml:space="preserve">14.5153760910034</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6198043823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8883304595947</t>
+    <t xml:space="preserve">14.6198024749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8883323669434</t>
   </si>
   <si>
     <t xml:space="preserve">15.2538251876831</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2608032226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9251441955566</t>
+    <t xml:space="preserve">16.2608013153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.925142288208</t>
   </si>
   <si>
     <t xml:space="preserve">15.7759628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7013702392578</t>
+    <t xml:space="preserve">15.7013711929321</t>
   </si>
   <si>
     <t xml:space="preserve">15.5521907806396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6267786026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5148935317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2911224365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2165288925171</t>
+    <t xml:space="preserve">15.6267824172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.514892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2911233901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2165327072144</t>
   </si>
   <si>
     <t xml:space="preserve">15.1792364120483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8505544662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8132591247559</t>
+    <t xml:space="preserve">15.8505525588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8132600784302</t>
   </si>
   <si>
     <t xml:space="preserve">16.0743255615234</t>
   </si>
   <si>
-    <t xml:space="preserve">15.887845993042</t>
+    <t xml:space="preserve">15.8878469467163</t>
   </si>
   <si>
     <t xml:space="preserve">15.4030084609985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9032487869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7093133926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4403076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1116218566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9624395370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5591659545898</t>
+    <t xml:space="preserve">14.903247833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7093143463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4403028488159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1116199493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.962438583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5591678619385</t>
   </si>
   <si>
     <t xml:space="preserve">16.3726902008057</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4845771789551</t>
+    <t xml:space="preserve">16.4845752716064</t>
   </si>
   <si>
     <t xml:space="preserve">16.7829399108887</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8948249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7386674880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657112121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8435745239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8584966659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0673513412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8734140396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9181680679321</t>
+    <t xml:space="preserve">16.8948230743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7386684417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657131195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8435754776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.858494758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0673503875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8734149932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9181671142578</t>
   </si>
   <si>
     <t xml:space="preserve">16.409984588623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2235088348389</t>
+    <t xml:space="preserve">16.2235107421875</t>
   </si>
   <si>
     <t xml:space="preserve">16.2980976104736</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6710529327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7083473205566</t>
+    <t xml:space="preserve">16.6710510253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.708345413208</t>
   </si>
   <si>
     <t xml:space="preserve">16.7456436157227</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6337566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9321212768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8575286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0067081451416</t>
+    <t xml:space="preserve">16.6337585449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9321193695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8575305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0067119598389</t>
   </si>
   <si>
     <t xml:space="preserve">17.3796653747559</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2304821014404</t>
+    <t xml:space="preserve">17.2304859161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5288467407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3432388305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7227516174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6756725311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7532329559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3654308319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0939636230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6673774719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6285972595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0468854904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2640562057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7061567306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5898180007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5122537612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7449388504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950820922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0158634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1864957809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4191808700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4967403411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5510339736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3261060714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2795705795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8612785339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0164031982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9388399124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9000616073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7837190628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8225002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3266468048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7920150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0247020721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.908353805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4817695617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5593318939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0551853179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4042091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1327438354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2878684997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1715278625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9776220321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3881568908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346904754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2103080749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4429893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5981121063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5205497741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6368942260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2490882873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8307952880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9859180450439</t>
   </si>
   <si>
     <t xml:space="preserve">17.5288486480713</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3432388305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7227516174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6756725311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7532348632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3654289245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0939636230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6673784255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6285972595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0468883514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2640600204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7061576843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5898151397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5122547149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7449388504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950830459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0158624649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1864957809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4191818237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4967412948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5510339736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3261070251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2795705795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8612785339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0164031982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9388408660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9000616073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7837200164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8224973678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3266468048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7920150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0247001647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9083576202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4817714691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5593318939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0551872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4042091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1327438354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2878684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1715259552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9776201248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3881559371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346904754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2103061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4429912567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5981121063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5205478668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6368942260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2490844726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8307952880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9859180450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5288467407227</t>
-  </si>
-  <si>
     <t xml:space="preserve">17.8390922546387</t>
   </si>
   <si>
     <t xml:space="preserve">17.5676288604736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9942169189453</t>
+    <t xml:space="preserve">17.9942150115967</t>
   </si>
   <si>
     <t xml:space="preserve">18.6147041320801</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">18.0717754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4595813751221</t>
+    <t xml:space="preserve">18.4595832824707</t>
   </si>
   <si>
     <t xml:space="preserve">18.7698268890381</t>
@@ -1670,22 +1670,22 @@
     <t xml:space="preserve">19.1576347351074</t>
   </si>
   <si>
-    <t xml:space="preserve">19.002513885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0412902832031</t>
+    <t xml:space="preserve">19.0025119781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0412921905518</t>
   </si>
   <si>
     <t xml:space="preserve">18.3044605255127</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1493396759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0329971313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.226900100708</t>
+    <t xml:space="preserve">18.1493377685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.032995223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2268981933594</t>
   </si>
   <si>
     <t xml:space="preserve">18.4208030700684</t>
@@ -1694,328 +1694,328 @@
     <t xml:space="preserve">18.498363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1105575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.683967590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8086090087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3820209503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.188117980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9166526794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9554328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.606409072876</t>
+    <t xml:space="preserve">18.1105556488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6839694976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8086071014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.382022857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1881160736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9166564941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9554347991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6064109802246</t>
   </si>
   <si>
     <t xml:space="preserve">17.6451892852783</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1410427093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.102258682251</t>
+    <t xml:space="preserve">17.141040802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1022605895996</t>
   </si>
   <si>
     <t xml:space="preserve">17.29616355896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1244468688965</t>
+    <t xml:space="preserve">15.1244487762451</t>
   </si>
   <si>
     <t xml:space="preserve">14.7676687240601</t>
   </si>
   <si>
-    <t xml:space="preserve">13.557710647583</t>
+    <t xml:space="preserve">13.5577116012573</t>
   </si>
   <si>
     <t xml:space="preserve">13.9610290527344</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0302925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1854181289673</t>
+    <t xml:space="preserve">13.030291557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.185417175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.138879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5732221603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2629776000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.169903755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.952733039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5649271011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7582883834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5566291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8585786819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7810163497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3156490325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8197965621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1300430297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7893133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2546815872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9056558609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6341905593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0219974517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0607786178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8280944824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4790687561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7117519378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6729707717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5954093933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2851667404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4015073776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7505321502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9749202728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5095520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5871133804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6646747589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2463846206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2159004211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3710222244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.07737159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1181745529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0365676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8733520507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8325471878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1997833251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6078214645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2813901901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4245080947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5469188690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5061140060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7509393692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9549589157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5262136459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7710399627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6894302368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3221950531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4038019180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5877237319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4653120040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6285276412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9141550064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2405872344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9957618713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1589775085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7917423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3837022781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2204885482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3429002761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.710132598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0572710037231</t>
   </si>
   <si>
     <t xml:space="preserve">13.1388807296753</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5732221603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.262978553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1699028015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9527339935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5649271011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7582883834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5566291809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8585777282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7810163497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3156490325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8197975158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1300430297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7893133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2546815872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9056558609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6341905593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0219964981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0607786178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8280935287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4790678024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7117528915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6729717254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5954113006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2851648330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4015073776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7505321502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9749193191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5095529556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5871133804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6646747589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2463846206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2159004211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3710222244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0773706436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1181735992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0365686416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8733520507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8325481414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1997833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6078224182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2813901901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4245090484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5469188690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5061149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.750940322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9549589157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5262136459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7710380554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6894302368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3221950531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4038019180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5877237319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4653120040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6285285949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9141540527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2405862808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9957618713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1589784622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7917423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3837022781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2204885482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.07737159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3429002761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7101345062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0572719573975</t>
-  </si>
-  <si>
     <t xml:space="preserve">13.2612915039062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0980749130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4860143661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8532524108887</t>
+    <t xml:space="preserve">13.0980758666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4860153198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8532514572144</t>
   </si>
   <si>
     <t xml:space="preserve">12.7308406829834</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6900358200073</t>
+    <t xml:space="preserve">12.6900367736816</t>
   </si>
   <si>
     <t xml:space="preserve">12.9756631851196</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7716426849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8526468276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2606868743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4239025115967</t>
+    <t xml:space="preserve">12.7716436386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8526487350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2606859207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4239015579224</t>
   </si>
   <si>
     <t xml:space="preserve">16.0767650604248</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9135494232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5055084228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6687288284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5871181488037</t>
+    <t xml:space="preserve">15.9135503768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5055093765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6687269210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5871171951294</t>
   </si>
   <si>
     <t xml:space="preserve">15.3014898300171</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3830986022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3422918319702</t>
+    <t xml:space="preserve">15.3830976486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3422908782959</t>
   </si>
   <si>
     <t xml:space="preserve">15.7503328323364</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2198820114136</t>
+    <t xml:space="preserve">15.2198829650879</t>
   </si>
   <si>
     <t xml:space="preserve">15.1790771484375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4647045135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.321590423584</t>
+    <t xml:space="preserve">15.4647073745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3215885162354</t>
   </si>
   <si>
     <t xml:space="preserve">16.1583728790283</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">17.7089233398438</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1376686096191</t>
+    <t xml:space="preserve">17.1376705169678</t>
   </si>
   <si>
     <t xml:space="preserve">17.3824920654297</t>
@@ -2042,25 +2042,25 @@
     <t xml:space="preserve">16.484806060791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6480197906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5664119720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2399806976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4031982421875</t>
+    <t xml:space="preserve">16.648021697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5664138793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2399787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4032001495361</t>
   </si>
   <si>
     <t xml:space="preserve">16.7296295166016</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2192764282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4641017913818</t>
+    <t xml:space="preserve">17.2192783355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4640998840332</t>
   </si>
   <si>
     <t xml:space="preserve">17.5457077026367</t>
@@ -2072,16 +2072,16 @@
     <t xml:space="preserve">18.0353565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9744510650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8721408843994</t>
+    <t xml:space="preserve">16.9744529724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8721389770508</t>
   </si>
   <si>
     <t xml:space="preserve">18.11696434021</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1985702514648</t>
+    <t xml:space="preserve">18.1985721588135</t>
   </si>
   <si>
     <t xml:space="preserve">18.3617897033691</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">19.1778659820557</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8514347076416</t>
+    <t xml:space="preserve">18.8514385223389</t>
   </si>
   <si>
     <t xml:space="preserve">18.6882190704346</t>
@@ -2099,19 +2099,16 @@
     <t xml:space="preserve">19.0962600708008</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6066093444824</t>
+    <t xml:space="preserve">18.6066112518311</t>
   </si>
   <si>
     <t xml:space="preserve">18.9330444335938</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7698249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2594738006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3410816192627</t>
+    <t xml:space="preserve">19.2594757080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.34108543396</t>
   </si>
   <si>
     <t xml:space="preserve">19.4226913452148</t>
@@ -2120,28 +2117,31 @@
     <t xml:space="preserve">19.0146503448486</t>
   </si>
   <si>
+    <t xml:space="preserve">19.9123382568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8276062011719</t>
+  </si>
+  <si>
     <t xml:space="preserve">19.9123401641846</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8276062011719</t>
-  </si>
-  <si>
     <t xml:space="preserve">19.4886722564697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6581401824951</t>
+    <t xml:space="preserve">19.6581420898438</t>
   </si>
   <si>
     <t xml:space="preserve">19.5734062194824</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4039402008057</t>
+    <t xml:space="preserve">19.403938293457</t>
   </si>
   <si>
     <t xml:space="preserve">19.9970741271973</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3360061645508</t>
+    <t xml:space="preserve">20.3360080718994</t>
   </si>
   <si>
     <t xml:space="preserve">20.166540145874</t>
@@ -2150,28 +2150,28 @@
     <t xml:space="preserve">19.3192043304443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0650081634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6413402557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7428722381592</t>
+    <t xml:space="preserve">19.0650062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6413383483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7428703308105</t>
   </si>
   <si>
     <t xml:space="preserve">20.0818061828613</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4207420349121</t>
+    <t xml:space="preserve">20.4207401275635</t>
   </si>
   <si>
     <t xml:space="preserve">20.5054721832275</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6749401092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.929141998291</t>
+    <t xml:space="preserve">20.6749382019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9291400909424</t>
   </si>
   <si>
     <t xml:space="preserve">21.1833400726318</t>
@@ -2180,16 +2180,16 @@
     <t xml:space="preserve">20.759672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4375400543213</t>
+    <t xml:space="preserve">21.4375381469727</t>
   </si>
   <si>
     <t xml:space="preserve">22.7085399627686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0306720733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4543399810791</t>
+    <t xml:space="preserve">22.0306739807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4543418884277</t>
   </si>
   <si>
     <t xml:space="preserve">22.2001419067383</t>
@@ -2213,19 +2213,19 @@
     <t xml:space="preserve">23.3016719818115</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4711418151855</t>
+    <t xml:space="preserve">23.4711399078369</t>
   </si>
   <si>
     <t xml:space="preserve">23.3864078521729</t>
   </si>
   <si>
-    <t xml:space="preserve">23.725341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1322078704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2169418334961</t>
+    <t xml:space="preserve">23.7253398895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1322059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2169399261475</t>
   </si>
   <si>
     <t xml:space="preserve">21.9459400177002</t>
@@ -2237,13 +2237,13 @@
     <t xml:space="preserve">24.1490077972412</t>
   </si>
   <si>
-    <t xml:space="preserve">25.165807723999</t>
+    <t xml:space="preserve">25.1658096313477</t>
   </si>
   <si>
     <t xml:space="preserve">24.9116077423096</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2337417602539</t>
+    <t xml:space="preserve">24.2337398529053</t>
   </si>
   <si>
     <t xml:space="preserve">25.2505416870117</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">23.8100757598877</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5726737976074</t>
+    <t xml:space="preserve">24.5726757049561</t>
   </si>
   <si>
     <t xml:space="preserve">24.403205871582</t>
@@ -2264,40 +2264,40 @@
     <t xml:space="preserve">25.081075668335</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5047416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3352737426758</t>
+    <t xml:space="preserve">25.5047397613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3352718353271</t>
   </si>
   <si>
     <t xml:space="preserve">25.4200077056885</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7589416503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2673416137695</t>
+    <t xml:space="preserve">25.758939743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2673397064209</t>
   </si>
   <si>
     <t xml:space="preserve">26.4368095397949</t>
   </si>
   <si>
-    <t xml:space="preserve">26.521541595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8772773742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5719413757324</t>
+    <t xml:space="preserve">26.5215396881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8772754669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5719432830811</t>
   </si>
   <si>
     <t xml:space="preserve">29.317741394043</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9788112640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1482772827148</t>
+    <t xml:space="preserve">28.9788093566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1482791900635</t>
   </si>
   <si>
     <t xml:space="preserve">29.2330093383789</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">28.4704055786133</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4536113739014</t>
+    <t xml:space="preserve">27.4536094665527</t>
   </si>
   <si>
     <t xml:space="preserve">28.3856754302979</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">27.7078094482422</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1314754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2841415405273</t>
+    <t xml:space="preserve">28.1314735412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.284143447876</t>
   </si>
   <si>
     <t xml:space="preserve">25.6742076873779</t>
@@ -2336,19 +2336,19 @@
     <t xml:space="preserve">25.8436737060547</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3520736694336</t>
+    <t xml:space="preserve">26.3520755767822</t>
   </si>
   <si>
     <t xml:space="preserve">26.6062755584717</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8268718719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1826095581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0978717803955</t>
+    <t xml:space="preserve">24.8268737792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1826076507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0978736877441</t>
   </si>
   <si>
     <t xml:space="preserve">25.9284076690674</t>
@@ -2363,10 +2363,10 @@
     <t xml:space="preserve">24.0642738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9627418518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.318473815918</t>
+    <t xml:space="preserve">22.962739944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3184757232666</t>
   </si>
   <si>
     <t xml:space="preserve">23.8948078155518</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">23.7030735015869</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0568523406982</t>
+    <t xml:space="preserve">24.0568542480469</t>
   </si>
   <si>
     <t xml:space="preserve">23.8799629211426</t>
@@ -2399,13 +2399,13 @@
     <t xml:space="preserve">24.4106292724609</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4990749359131</t>
+    <t xml:space="preserve">24.4990730285645</t>
   </si>
   <si>
     <t xml:space="preserve">24.8528518676758</t>
   </si>
   <si>
-    <t xml:space="preserve">25.295072555542</t>
+    <t xml:space="preserve">25.2950706481934</t>
   </si>
   <si>
     <t xml:space="preserve">25.2066287994385</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">24.587516784668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3221836090088</t>
+    <t xml:space="preserve">24.3221855163574</t>
   </si>
   <si>
     <t xml:space="preserve">23.3492965698242</t>
@@ -2423,31 +2423,31 @@
     <t xml:space="preserve">22.2879676818848</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4648532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8457469940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7572994232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4035224914551</t>
+    <t xml:space="preserve">22.4648551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8457450866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7573013305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4035243988037</t>
   </si>
   <si>
     <t xml:space="preserve">21.6688556671143</t>
   </si>
   <si>
-    <t xml:space="preserve">21.226634979248</t>
+    <t xml:space="preserve">21.2266330718994</t>
   </si>
   <si>
     <t xml:space="preserve">21.9341869354248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5804119110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1381874084473</t>
+    <t xml:space="preserve">21.5804100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1381893157959</t>
   </si>
   <si>
     <t xml:space="preserve">22.1110782623291</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">25.1181831359863</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6759605407715</t>
+    <t xml:space="preserve">24.6759624481201</t>
   </si>
   <si>
     <t xml:space="preserve">22.9955196380615</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">22.907075881958</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1452960968018</t>
+    <t xml:space="preserve">24.1452941894531</t>
   </si>
   <si>
     <t xml:space="preserve">23.4377422332764</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">23.614631652832</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6417446136475</t>
+    <t xml:space="preserve">22.6417427062988</t>
   </si>
   <si>
     <t xml:space="preserve">23.0839653015137</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">23.1724109649658</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3764095306396</t>
+    <t xml:space="preserve">22.376407623291</t>
   </si>
   <si>
     <t xml:space="preserve">22.1995220184326</t>
@@ -2504,10 +2504,10 @@
     <t xml:space="preserve">20.6959686279297</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3150806427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7644081115723</t>
+    <t xml:space="preserve">21.3150787353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7644062042236</t>
   </si>
   <si>
     <t xml:space="preserve">25.7372951507568</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">24.9412956237793</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5604057312012</t>
+    <t xml:space="preserve">25.5604038238525</t>
   </si>
   <si>
     <t xml:space="preserve">25.471960067749</t>
@@ -2531,10 +2531,10 @@
     <t xml:space="preserve">25.9141807556152</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0639591217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2408447265625</t>
+    <t xml:space="preserve">27.0639572143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2408466339111</t>
   </si>
   <si>
     <t xml:space="preserve">27.1524028778076</t>
@@ -2546,22 +2546,22 @@
     <t xml:space="preserve">27.5946254730225</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3292922973633</t>
+    <t xml:space="preserve">27.3292903900146</t>
   </si>
   <si>
     <t xml:space="preserve">26.7101821899414</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7986259460449</t>
+    <t xml:space="preserve">26.7986240386963</t>
   </si>
   <si>
     <t xml:space="preserve">26.8870697021484</t>
   </si>
   <si>
-    <t xml:space="preserve">26.975513458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4177360534668</t>
+    <t xml:space="preserve">26.9755153656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4177341461182</t>
   </si>
   <si>
     <t xml:space="preserve">26.5332927703857</t>
@@ -2573,10 +2573,10 @@
     <t xml:space="preserve">26.4448471069336</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3564052581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8257389068604</t>
+    <t xml:space="preserve">26.3564033508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.825740814209</t>
   </si>
   <si>
     <t xml:space="preserve">26.0026264190674</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">26.179515838623</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6217365264893</t>
+    <t xml:space="preserve">26.6217384338379</t>
   </si>
   <si>
     <t xml:space="preserve">26.2679595947266</t>
@@ -3603,6 +3603,9 @@
   </si>
   <si>
     <t xml:space="preserve">64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2000007629395</t>
   </si>
 </sst>
 </file>
@@ -34327,7 +34330,7 @@
         <v>17.25</v>
       </c>
       <c r="G1169" t="s">
-        <v>640</v>
+        <v>612</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34561,7 +34564,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1178" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -34769,7 +34772,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1186" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34873,7 +34876,7 @@
         <v>17.25</v>
       </c>
       <c r="G1190" t="s">
-        <v>640</v>
+        <v>612</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -35055,7 +35058,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1197" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35081,7 +35084,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -35133,7 +35136,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1200" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -35237,7 +35240,7 @@
         <v>16</v>
       </c>
       <c r="G1204" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -35289,7 +35292,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1206" t="s">
-        <v>578</v>
+        <v>643</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35315,7 +35318,7 @@
         <v>16</v>
       </c>
       <c r="G1207" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -35341,7 +35344,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1208" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -35445,7 +35448,7 @@
         <v>17.25</v>
       </c>
       <c r="G1212" t="s">
-        <v>640</v>
+        <v>612</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -35523,7 +35526,7 @@
         <v>17.25</v>
       </c>
       <c r="G1215" t="s">
-        <v>640</v>
+        <v>612</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35783,7 +35786,7 @@
         <v>16</v>
       </c>
       <c r="G1225" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -36043,7 +36046,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1235" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -38461,7 +38464,7 @@
         <v>23</v>
       </c>
       <c r="G1328" t="s">
-        <v>697</v>
+        <v>549</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -38799,7 +38802,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1341" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -38825,7 +38828,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1342" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -38851,7 +38854,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1343" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -38877,7 +38880,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1344" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -38929,7 +38932,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1346" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -38955,7 +38958,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1347" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -38981,7 +38984,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1348" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -39033,7 +39036,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1350" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -39059,7 +39062,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1351" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -39085,7 +39088,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1352" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -39111,7 +39114,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1353" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -39163,7 +39166,7 @@
         <v>23</v>
       </c>
       <c r="G1355" t="s">
-        <v>697</v>
+        <v>549</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39189,7 +39192,7 @@
         <v>23</v>
       </c>
       <c r="G1356" t="s">
-        <v>697</v>
+        <v>549</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -39215,7 +39218,7 @@
         <v>23</v>
       </c>
       <c r="G1357" t="s">
-        <v>697</v>
+        <v>549</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39241,7 +39244,7 @@
         <v>23</v>
       </c>
       <c r="G1358" t="s">
-        <v>697</v>
+        <v>549</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39267,7 +39270,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -39293,7 +39296,7 @@
         <v>23</v>
       </c>
       <c r="G1360" t="s">
-        <v>697</v>
+        <v>549</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -39319,7 +39322,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1361" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -39345,7 +39348,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1362" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -39371,7 +39374,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -39397,7 +39400,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -39423,7 +39426,7 @@
         <v>23.5</v>
       </c>
       <c r="G1365" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -39553,7 +39556,7 @@
         <v>23.5</v>
       </c>
       <c r="G1370" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -39579,7 +39582,7 @@
         <v>23.5</v>
       </c>
       <c r="G1371" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -39605,7 +39608,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1372" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -39657,7 +39660,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1374" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -39683,7 +39686,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1375" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -39709,7 +39712,7 @@
         <v>23.5</v>
       </c>
       <c r="G1376" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -39735,7 +39738,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1377" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -39787,7 +39790,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1379" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -39813,7 +39816,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1380" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -39839,7 +39842,7 @@
         <v>23.5</v>
       </c>
       <c r="G1381" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -39865,7 +39868,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1382" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -39891,7 +39894,7 @@
         <v>23.5</v>
       </c>
       <c r="G1383" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -39917,7 +39920,7 @@
         <v>23.5</v>
       </c>
       <c r="G1384" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -40047,7 +40050,7 @@
         <v>23.5</v>
       </c>
       <c r="G1389" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -40073,7 +40076,7 @@
         <v>23.5</v>
       </c>
       <c r="G1390" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40177,7 +40180,7 @@
         <v>23.5</v>
       </c>
       <c r="G1394" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -40203,7 +40206,7 @@
         <v>23.5</v>
       </c>
       <c r="G1395" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -40749,7 +40752,7 @@
         <v>23.5</v>
       </c>
       <c r="G1416" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -40775,7 +40778,7 @@
         <v>23.5</v>
       </c>
       <c r="G1417" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -68941,7 +68944,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6942592593</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>8903</v>
@@ -68962,6 +68965,32 @@
         <v>1170</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6935648148</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>7946</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>64</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>62.7999992370605</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>63</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>63.2000007629395</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="1197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="1198">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">CMB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55656623840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31377506256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40144920349121</t>
+    <t xml:space="preserve">9.55656719207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31377410888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40144824981689</t>
   </si>
   <si>
     <t xml:space="preserve">9.40819358825684</t>
@@ -59,40 +59,40 @@
     <t xml:space="preserve">9.44191551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36098480224609</t>
+    <t xml:space="preserve">9.36098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">9.13842582702637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32051753997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26656627655029</t>
+    <t xml:space="preserve">9.32051849365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26656436920166</t>
   </si>
   <si>
     <t xml:space="preserve">9.34075164794922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27330684661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19237804412842</t>
+    <t xml:space="preserve">9.2733097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19237899780273</t>
   </si>
   <si>
     <t xml:space="preserve">9.19912242889404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10470294952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84167861938477</t>
+    <t xml:space="preserve">9.10470390319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84167766571045</t>
   </si>
   <si>
     <t xml:space="preserve">8.77423667907715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84842300415039</t>
+    <t xml:space="preserve">8.84842395782471</t>
   </si>
   <si>
     <t xml:space="preserve">8.36283874511719</t>
@@ -104,34 +104,34 @@
     <t xml:space="preserve">8.61911964416504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45051383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43028163909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63260746002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80121421813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22609901428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25981903076172</t>
+    <t xml:space="preserve">8.45051193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43027973175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63260841369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80121326446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22609996795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25981998443604</t>
   </si>
   <si>
     <t xml:space="preserve">9.07098197937012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87539958953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96982002258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71353816986084</t>
+    <t xml:space="preserve">8.87539768218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96981906890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71354007720947</t>
   </si>
   <si>
     <t xml:space="preserve">8.6663293838501</t>
@@ -140,61 +140,61 @@
     <t xml:space="preserve">8.89563274383545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81470203399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99679565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01028347015381</t>
+    <t xml:space="preserve">8.81470108032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99679660797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01028537750244</t>
   </si>
   <si>
     <t xml:space="preserve">8.90237712860107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97656345367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18563461303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17214679718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13167953491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34749603271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25307750701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15865802764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08446979522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540050506592</t>
+    <t xml:space="preserve">8.9765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18563365936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17214584350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13168048858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34749507904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25307846069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15865612030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08447074890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540145874023</t>
   </si>
   <si>
     <t xml:space="preserve">8.98330688476562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78772449493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78098201751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1249361038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03726005554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21260929107666</t>
+    <t xml:space="preserve">8.7877254486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78098106384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12493515014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03726100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21261119842529</t>
   </si>
   <si>
     <t xml:space="preserve">9.04400539398193</t>
@@ -203,13 +203,13 @@
     <t xml:space="preserve">9.09796047210693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20586776733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38121700286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28679943084717</t>
+    <t xml:space="preserve">9.20586585998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38121604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28679847717285</t>
   </si>
   <si>
     <t xml:space="preserve">9.22100830078125</t>
@@ -221,22 +221,22 @@
     <t xml:space="preserve">9.19308757781982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35363292694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4094762802124</t>
+    <t xml:space="preserve">9.35363483428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40947818756104</t>
   </si>
   <si>
     <t xml:space="preserve">9.52116203308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49324131011963</t>
+    <t xml:space="preserve">9.49324035644531</t>
   </si>
   <si>
     <t xml:space="preserve">9.38853645324707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94696140289307</t>
+    <t xml:space="preserve">9.94696235656738</t>
   </si>
   <si>
     <t xml:space="preserve">9.76547336578369</t>
@@ -251,64 +251,64 @@
     <t xml:space="preserve">9.82829570770264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75151252746582</t>
+    <t xml:space="preserve">9.75151348114014</t>
   </si>
   <si>
     <t xml:space="preserve">9.57002353668213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57700538635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55606460571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47928237915039</t>
+    <t xml:space="preserve">9.57700634002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55606365203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47927951812744</t>
   </si>
   <si>
     <t xml:space="preserve">9.42343711853027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39551544189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4164571762085</t>
+    <t xml:space="preserve">9.39551639556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41645812988281</t>
   </si>
   <si>
     <t xml:space="preserve">9.34665393829346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62586688995361</t>
+    <t xml:space="preserve">9.58398342132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6258659362793</t>
   </si>
   <si>
     <t xml:space="preserve">9.63284778594971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4653205871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48625946044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59096622467041</t>
+    <t xml:space="preserve">9.46531963348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48626041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59096527099609</t>
   </si>
   <si>
     <t xml:space="preserve">9.56304454803467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53512191772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12328338623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30477237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2838306427002</t>
+    <t xml:space="preserve">9.53512382507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12328243255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30477142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28383159637451</t>
   </si>
   <si>
     <t xml:space="preserve">9.20704746246338</t>
@@ -317,91 +317,91 @@
     <t xml:space="preserve">9.27685165405273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36061382293701</t>
+    <t xml:space="preserve">9.3606128692627</t>
   </si>
   <si>
     <t xml:space="preserve">9.29081153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29779148101807</t>
+    <t xml:space="preserve">9.29779243469238</t>
   </si>
   <si>
     <t xml:space="preserve">9.31873416900635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36759662628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47229862213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52814197540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50720119476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44437980651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50022029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3326940536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32571220397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13724517822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14422512054443</t>
+    <t xml:space="preserve">9.36759567260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47229957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52814102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50720024108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44437885284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50022125244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33269214630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32571315765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13724422454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14422416687012</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120506286621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10932159423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03951930999756</t>
+    <t xml:space="preserve">9.1093225479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03951835632324</t>
   </si>
   <si>
     <t xml:space="preserve">8.92783451080322</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01159763336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07442092895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9766960144043</t>
+    <t xml:space="preserve">9.01159954071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07442188262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97669696807861</t>
   </si>
   <si>
     <t xml:space="preserve">8.86501121520996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85105037689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.934814453125</t>
+    <t xml:space="preserve">8.85105133056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93481636047363</t>
   </si>
   <si>
     <t xml:space="preserve">8.92085456848145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95575618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96971797943115</t>
+    <t xml:space="preserve">8.95575714111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96971702575684</t>
   </si>
   <si>
     <t xml:space="preserve">9.00461769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91387271881104</t>
+    <t xml:space="preserve">8.91387367248535</t>
   </si>
   <si>
     <t xml:space="preserve">8.87897300720215</t>
@@ -413,19 +413,19 @@
     <t xml:space="preserve">8.59975910186768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56485843658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81614875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83708953857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89991283416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99763679504395</t>
+    <t xml:space="preserve">8.56485652923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81614971160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83709049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8999137878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99763774871826</t>
   </si>
   <si>
     <t xml:space="preserve">8.83010959625244</t>
@@ -437,25 +437,25 @@
     <t xml:space="preserve">9.08838272094727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04650020599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09536266326904</t>
+    <t xml:space="preserve">9.04650115966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09536170959473</t>
   </si>
   <si>
     <t xml:space="preserve">9.66076850891113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64680671691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70264911651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79339408874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9260196685791</t>
+    <t xml:space="preserve">9.64680767059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70265007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7933931350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92602062225342</t>
   </si>
   <si>
     <t xml:space="preserve">9.98186302185059</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">10.0516672134399</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4146423339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.19127368927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2471160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493921279907</t>
+    <t xml:space="preserve">10.4146432876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1912727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2471141815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493902206421</t>
   </si>
   <si>
     <t xml:space="preserve">10.1354303359985</t>
@@ -482,13 +482,13 @@
     <t xml:space="preserve">10.2680568695068</t>
   </si>
   <si>
-    <t xml:space="preserve">10.393702507019</t>
+    <t xml:space="preserve">10.3937015533447</t>
   </si>
   <si>
     <t xml:space="preserve">10.5402898788452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5891532897949</t>
+    <t xml:space="preserve">10.5891513824463</t>
   </si>
   <si>
     <t xml:space="preserve">10.4844465255737</t>
@@ -497,64 +497,64 @@
     <t xml:space="preserve">10.6310329437256</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3588008880615</t>
+    <t xml:space="preserve">10.3588018417358</t>
   </si>
   <si>
     <t xml:space="preserve">9.98884391784668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95394325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1005296707153</t>
+    <t xml:space="preserve">9.95394134521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.100528717041</t>
   </si>
   <si>
     <t xml:space="preserve">10.4704856872559</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3867225646973</t>
+    <t xml:space="preserve">10.3867216110229</t>
   </si>
   <si>
     <t xml:space="preserve">10.5472688674927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3448419570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.477466583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4006834030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4355840682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3727607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3657817840576</t>
+    <t xml:space="preserve">10.344841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4774675369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4006843566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4355850219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3727617263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3657808303833</t>
   </si>
   <si>
     <t xml:space="preserve">10.3378601074219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2820158004761</t>
+    <t xml:space="preserve">10.2820167541504</t>
   </si>
   <si>
     <t xml:space="preserve">10.3797416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6100912094116</t>
+    <t xml:space="preserve">10.6100931167603</t>
   </si>
   <si>
     <t xml:space="preserve">10.5542507171631</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6938552856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0917358398438</t>
+    <t xml:space="preserve">10.6938562393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0917339324951</t>
   </si>
   <si>
     <t xml:space="preserve">11.0428733825684</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">11.063814163208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0847539901733</t>
+    <t xml:space="preserve">11.084755897522</t>
   </si>
   <si>
     <t xml:space="preserve">11.3569869995117</t>
@@ -575,43 +575,43 @@
     <t xml:space="preserve">11.5175352096558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0899229049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9991769790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0689811706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1038818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2853727340698</t>
+    <t xml:space="preserve">12.0899219512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9991798400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.06898021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1038837432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2853708267212</t>
   </si>
   <si>
     <t xml:space="preserve">12.8228559494019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9764223098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9903841018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2486543655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1090497970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1230096817017</t>
+    <t xml:space="preserve">12.9764232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.990385055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2486553192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1090488433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1230087280273</t>
   </si>
   <si>
     <t xml:space="preserve">12.8926582336426</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9135990142822</t>
+    <t xml:space="preserve">12.9135999679565</t>
   </si>
   <si>
     <t xml:space="preserve">12.8437957763672</t>
@@ -620,112 +620,112 @@
     <t xml:space="preserve">12.9624633789062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1928110122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3952398300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8978261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9815883636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9327268600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0234699249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0304536819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1351566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0723342895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0025300979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2112550735474</t>
+    <t xml:space="preserve">13.1928119659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3952407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8978233337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9815902709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9327278137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0234708786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0304508209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.135157585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0723323822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0025291442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.211256980896</t>
   </si>
   <si>
     <t xml:space="preserve">14.3197383880615</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1461658477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0810747146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9942903518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6688404083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.355899810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6833038330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0015239715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9870567321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2691135406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3486661911011</t>
+    <t xml:space="preserve">14.1461668014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0810766220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9942922592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6688413619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3558988571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6833076477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.001522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9870595932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2691116333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3486700057983</t>
   </si>
   <si>
     <t xml:space="preserve">14.3414373397827</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2763452529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4282236099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5656337738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3322439193726</t>
+    <t xml:space="preserve">14.2763442993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.42822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5656328201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3322467803955</t>
   </si>
   <si>
     <t xml:space="preserve">15.8457298278809</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7589483261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3611736297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1876039505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9200077056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6307229995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636758804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3105497360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9272422790527</t>
+    <t xml:space="preserve">15.7589445114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3611745834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1876020431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9200086593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6307239532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636777877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3105478286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9272413253784</t>
   </si>
   <si>
     <t xml:space="preserve">15.0718860626221</t>
@@ -734,73 +734,73 @@
     <t xml:space="preserve">15.5492124557495</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4551963806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2671546936035</t>
+    <t xml:space="preserve">15.4551935195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2671566009521</t>
   </si>
   <si>
     <t xml:space="preserve">15.1731367111206</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8332233428955</t>
+    <t xml:space="preserve">14.8332252502441</t>
   </si>
   <si>
     <t xml:space="preserve">15.1369762420654</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1152820587158</t>
+    <t xml:space="preserve">15.1152791976929</t>
   </si>
   <si>
     <t xml:space="preserve">14.9851007461548</t>
   </si>
   <si>
-    <t xml:space="preserve">15.151442527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0284929275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2093000411987</t>
+    <t xml:space="preserve">15.1514406204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0284948348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.209300994873</t>
   </si>
   <si>
     <t xml:space="preserve">15.664924621582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6938562393188</t>
+    <t xml:space="preserve">15.6938543319702</t>
   </si>
   <si>
     <t xml:space="preserve">15.7661762237549</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9325170516968</t>
+    <t xml:space="preserve">15.9325189590454</t>
   </si>
   <si>
     <t xml:space="preserve">16.0410003662109</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9469814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6432285308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2816209793091</t>
+    <t xml:space="preserve">15.9469833374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6432304382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2816190719604</t>
   </si>
   <si>
     <t xml:space="preserve">15.2888536453247</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2599220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3250122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.238226890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1586694717407</t>
+    <t xml:space="preserve">15.2599239349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3250160217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2382259368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.158670425415</t>
   </si>
   <si>
     <t xml:space="preserve">15.0574216842651</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">15.1803693771362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2454614639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8983125686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8693838119507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8259916305542</t>
+    <t xml:space="preserve">15.2454595565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8983144760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8693857192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8259906768799</t>
   </si>
   <si>
     <t xml:space="preserve">14.9634046554565</t>
@@ -827,64 +827,64 @@
     <t xml:space="preserve">14.9706363677979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6813488006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7536687850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6958122253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8910808563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.493311882019</t>
+    <t xml:space="preserve">14.6813497543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7536706924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6958150863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8910799026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4933109283447</t>
   </si>
   <si>
     <t xml:space="preserve">14.8549213409424</t>
   </si>
   <si>
-    <t xml:space="preserve">14.652419090271</t>
+    <t xml:space="preserve">14.6524219512939</t>
   </si>
   <si>
     <t xml:space="preserve">14.6090288162231</t>
   </si>
   <si>
-    <t xml:space="preserve">14.847692489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1948347091675</t>
+    <t xml:space="preserve">14.8476896286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1948328018188</t>
   </si>
   <si>
     <t xml:space="preserve">15.3394784927368</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4334964752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2651996612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9956493377686</t>
+    <t xml:space="preserve">15.433497428894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2651977539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9956512451172</t>
   </si>
   <si>
     <t xml:space="preserve">17.5742244720459</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6879825592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3986930847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4420871734619</t>
+    <t xml:space="preserve">18.6879844665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3986949920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4420890808105</t>
   </si>
   <si>
     <t xml:space="preserve">18.2178897857666</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0804786682129</t>
+    <t xml:space="preserve">18.0804767608643</t>
   </si>
   <si>
     <t xml:space="preserve">18.1889610290527</t>
@@ -893,70 +893,70 @@
     <t xml:space="preserve">17.9719944000244</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0081558227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8562812805176</t>
+    <t xml:space="preserve">18.0081577301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8562793731689</t>
   </si>
   <si>
     <t xml:space="preserve">17.9647636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6393146514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7622604370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6031551361084</t>
+    <t xml:space="preserve">17.6393127441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7622623443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.603157043457</t>
   </si>
   <si>
     <t xml:space="preserve">17.5886878967285</t>
   </si>
   <si>
-    <t xml:space="preserve">17.538064956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5019035339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3861865997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3210983276367</t>
+    <t xml:space="preserve">17.5380668640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5019016265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3861885070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3211002349854</t>
   </si>
   <si>
     <t xml:space="preserve">17.2849349975586</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0462741851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2632427215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0968990325928</t>
+    <t xml:space="preserve">17.0462760925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2632446289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0969009399414</t>
   </si>
   <si>
     <t xml:space="preserve">17.3283290863037</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3572578430176</t>
+    <t xml:space="preserve">17.3572597503662</t>
   </si>
   <si>
     <t xml:space="preserve">17.4006519317627</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3789577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2921695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3427963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1692218780518</t>
+    <t xml:space="preserve">17.3789558410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2921714782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.342794418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1692199707031</t>
   </si>
   <si>
     <t xml:space="preserve">16.590648651123</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">16.6268081665039</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9233283996582</t>
+    <t xml:space="preserve">16.9233303070068</t>
   </si>
   <si>
     <t xml:space="preserve">16.3447513580322</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">15.7083196640015</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1133213043213</t>
+    <t xml:space="preserve">16.1133232116699</t>
   </si>
   <si>
     <t xml:space="preserve">15.9180536270142</t>
@@ -983,16 +983,16 @@
     <t xml:space="preserve">15.650463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4749317169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.301362991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5761795043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5110893249512</t>
+    <t xml:space="preserve">16.4749336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3013591766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5761852264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5110912322998</t>
   </si>
   <si>
     <t xml:space="preserve">16.5617179870605</t>
@@ -1004,67 +1004,67 @@
     <t xml:space="preserve">16.5255584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4098434448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2073383331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.874659538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2434997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4460010528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2001094818115</t>
+    <t xml:space="preserve">16.4098415374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2073402404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8746614456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.243501663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4460029602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2001075744629</t>
   </si>
   <si>
     <t xml:space="preserve">15.8312664031982</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8601980209351</t>
+    <t xml:space="preserve">15.8601942062378</t>
   </si>
   <si>
     <t xml:space="preserve">15.8529634475708</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6287670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4696569442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4624214172363</t>
+    <t xml:space="preserve">15.6287689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.469654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.462423324585</t>
   </si>
   <si>
     <t xml:space="preserve">15.6215343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9976119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2362689971924</t>
+    <t xml:space="preserve">15.9976062774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.236270904541</t>
   </si>
   <si>
     <t xml:space="preserve">16.163948059082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2724285125732</t>
+    <t xml:space="preserve">16.2724304199219</t>
   </si>
   <si>
     <t xml:space="preserve">16.7786846160889</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6340408325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4532375335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7425231933594</t>
+    <t xml:space="preserve">16.6340427398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4532337188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.742525100708</t>
   </si>
   <si>
     <t xml:space="preserve">16.59787940979</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">17.031810760498</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2126178741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4295806884766</t>
+    <t xml:space="preserve">17.2126159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4295845031738</t>
   </si>
   <si>
     <t xml:space="preserve">16.9594898223877</t>
@@ -1091,31 +1091,31 @@
     <t xml:space="preserve">16.3809108734131</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9831428527832</t>
+    <t xml:space="preserve">15.9831447601318</t>
   </si>
   <si>
     <t xml:space="preserve">15.9108209609985</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7300157546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.368408203125</t>
+    <t xml:space="preserve">15.7300176620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3684062957764</t>
   </si>
   <si>
     <t xml:space="preserve">15.4045686721802</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4768905639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8023376464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.670202255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1402950286865</t>
+    <t xml:space="preserve">15.4768896102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8023357391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6702003479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1402931213379</t>
   </si>
   <si>
     <t xml:space="preserve">17.104133605957</t>
@@ -1127,40 +1127,40 @@
     <t xml:space="preserve">17.0679702758789</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8871650695801</t>
+    <t xml:space="preserve">16.8871669769287</t>
   </si>
   <si>
     <t xml:space="preserve">17.8273525238037</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6827068328857</t>
+    <t xml:space="preserve">17.6827087402344</t>
   </si>
   <si>
     <t xml:space="preserve">17.3934173583984</t>
   </si>
   <si>
-    <t xml:space="preserve">17.248779296875</t>
+    <t xml:space="preserve">17.2487773895264</t>
   </si>
   <si>
     <t xml:space="preserve">17.7550315856934</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8996715545654</t>
+    <t xml:space="preserve">17.8996734619141</t>
   </si>
   <si>
     <t xml:space="preserve">18.5867328643799</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6590557098389</t>
+    <t xml:space="preserve">18.6590538024902</t>
   </si>
   <si>
     <t xml:space="preserve">19.0206642150879</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5428009033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2444381713867</t>
+    <t xml:space="preserve">19.5427989959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2444362640381</t>
   </si>
   <si>
     <t xml:space="preserve">19.9157562255859</t>
@@ -1172,13 +1172,13 @@
     <t xml:space="preserve">19.6546859741211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4682064056396</t>
+    <t xml:space="preserve">19.4682083129883</t>
   </si>
   <si>
     <t xml:space="preserve">19.6173915863037</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0952529907227</t>
+    <t xml:space="preserve">19.0952568054199</t>
   </si>
   <si>
     <t xml:space="preserve">18.8714809417725</t>
@@ -1187,28 +1187,28 @@
     <t xml:space="preserve">18.9460716247559</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7968940734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9018001556396</t>
+    <t xml:space="preserve">18.796895980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9018020629883</t>
   </si>
   <si>
     <t xml:space="preserve">17.3050746917725</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7899169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8341903686523</t>
+    <t xml:space="preserve">17.7899150848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8341865539551</t>
   </si>
   <si>
     <t xml:space="preserve">19.1698474884033</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3936176300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5055046081543</t>
+    <t xml:space="preserve">19.3936195373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5055065155029</t>
   </si>
   <si>
     <t xml:space="preserve">19.8038673400879</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">19.6919803619385</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3190269470215</t>
+    <t xml:space="preserve">19.3190250396729</t>
   </si>
   <si>
     <t xml:space="preserve">18.4239368438721</t>
@@ -1229,46 +1229,43 @@
     <t xml:space="preserve">19.1325511932373</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3563251495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0206623077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7292785644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7223014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9087753295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6477088928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5731182098389</t>
+    <t xml:space="preserve">19.3563194274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7292766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.722297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9087791442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6477069854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5731201171875</t>
   </si>
   <si>
     <t xml:space="preserve">18.5358219146729</t>
   </si>
   <si>
-    <t xml:space="preserve">17.976390838623</t>
+    <t xml:space="preserve">17.9763946533203</t>
   </si>
   <si>
     <t xml:space="preserve">18.1255741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4612312316895</t>
+    <t xml:space="preserve">18.4612331390381</t>
   </si>
   <si>
     <t xml:space="preserve">18.7595958709717</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6104164123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3493423461914</t>
+    <t xml:space="preserve">18.6104125976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3493480682373</t>
   </si>
   <si>
     <t xml:space="preserve">18.6850051879883</t>
@@ -1277,124 +1274,124 @@
     <t xml:space="preserve">18.3120517730713</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4985275268555</t>
+    <t xml:space="preserve">18.4985256195068</t>
   </si>
   <si>
     <t xml:space="preserve">19.2817325592041</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0579586029053</t>
+    <t xml:space="preserve">19.0579605102539</t>
   </si>
   <si>
     <t xml:space="preserve">18.1628704071045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0136871337891</t>
+    <t xml:space="preserve">18.0136852264404</t>
   </si>
   <si>
     <t xml:space="preserve">18.3866424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1558933258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1862125396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5894870758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1419401168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9554624557495</t>
+    <t xml:space="preserve">17.1558952331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1862106323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5894842147827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1419410705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9554634094238</t>
   </si>
   <si>
     <t xml:space="preserve">16.0370311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5218715667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6640777587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1046457290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9927606582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0300531387329</t>
+    <t xml:space="preserve">16.5218696594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6640758514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1046466827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9927577972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0300521850586</t>
   </si>
   <si>
     <t xml:space="preserve">14.768985748291</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3661966323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5153770446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6198024749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.888331413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2538251876831</t>
+    <t xml:space="preserve">14.3661956787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5153779983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6198053359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8883323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2538280487061</t>
   </si>
   <si>
     <t xml:space="preserve">16.2608013153076</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9251432418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7759609222412</t>
+    <t xml:space="preserve">15.9251461029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7759647369385</t>
   </si>
   <si>
     <t xml:space="preserve">15.7013702392578</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5521926879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6267824172974</t>
+    <t xml:space="preserve">15.5521907806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6267805099487</t>
   </si>
   <si>
     <t xml:space="preserve">15.5148954391479</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2911214828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2165298461914</t>
+    <t xml:space="preserve">15.2911205291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.21653175354</t>
   </si>
   <si>
     <t xml:space="preserve">15.179235458374</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8505544662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8132562637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0743274688721</t>
+    <t xml:space="preserve">15.8505525588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8132591247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0743236541748</t>
   </si>
   <si>
     <t xml:space="preserve">15.8878498077393</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4030084609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9032487869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7093133926392</t>
+    <t xml:space="preserve">15.4030065536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9032497406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7093114852905</t>
   </si>
   <si>
     <t xml:space="preserve">15.4403038024902</t>
@@ -1403,64 +1400,64 @@
     <t xml:space="preserve">16.1116218566895</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9624404907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5591659545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.372688293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4845752716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7829360961914</t>
+    <t xml:space="preserve">15.9624395370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5591678619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3726902008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4845771789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.78293800354</t>
   </si>
   <si>
     <t xml:space="preserve">16.8948230743408</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7386655807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657112121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8435754776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8584966659546</t>
+    <t xml:space="preserve">15.7386674880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657131195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.843578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8584938049316</t>
   </si>
   <si>
     <t xml:space="preserve">15.0673513412476</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8734121322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9181680679321</t>
+    <t xml:space="preserve">14.8734149932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9181671142578</t>
   </si>
   <si>
     <t xml:space="preserve">16.409984588623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2235069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2980976104736</t>
+    <t xml:space="preserve">16.2235088348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.298095703125</t>
   </si>
   <si>
     <t xml:space="preserve">16.6710529327393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7083492279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.745641708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6337604522705</t>
+    <t xml:space="preserve">16.7083473205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7456436157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6337566375732</t>
   </si>
   <si>
     <t xml:space="preserve">16.9321212768555</t>
@@ -1469,7 +1466,7 @@
     <t xml:space="preserve">16.8575286865234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0067100524902</t>
+    <t xml:space="preserve">17.0067081451416</t>
   </si>
   <si>
     <t xml:space="preserve">17.3796653747559</t>
@@ -1478,172 +1475,175 @@
     <t xml:space="preserve">17.2304840087891</t>
   </si>
   <si>
+    <t xml:space="preserve">17.5288486480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.343240737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7227516174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6756744384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7532348632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3654289245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0939636230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6673793792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6285943984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0468883514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2640590667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7061595916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5898151397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5122537612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7449388504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950811386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0158624649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1864957809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4191808700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4967422485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5510349273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3261060714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2795705795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8612813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0164012908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9388389587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9000597000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7837190628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8225002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3266468048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7920150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0247001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9083557128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4817695617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5593338012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0551834106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4042110443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1327457427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2878665924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1715259552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9776220321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3881578445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346942901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2103042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4429912567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5981121063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5205516815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6368942260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2490863800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8307952880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9859180450439</t>
+  </si>
+  <si>
     <t xml:space="preserve">17.5288467407227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.343240737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7227516174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6756725311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7532348632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3654289245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0939617156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6673784255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6285972595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0468864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2640600204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7061576843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5898170471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5122547149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7449388504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950830459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0158643722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1864957809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4191818237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4967412948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5510339736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3261070251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2795686721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8612785339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0164031982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9388408660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9000616073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7837200164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8224973678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3266448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7920150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0247001647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9083576202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4817714691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5593318939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0551872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4042091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1327438354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2878704071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1715278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9776201248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3881559371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346904754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2103061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4429912567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5981121063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5205497741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6368942260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2490863800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8307952880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9859161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8390922546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5676288604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9942169189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6147041320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2656784057617</t>
+    <t xml:space="preserve">17.8390941619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.567626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9942150115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6147060394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2656803131104</t>
   </si>
   <si>
     <t xml:space="preserve">18.8473892211914</t>
@@ -1661,22 +1661,22 @@
     <t xml:space="preserve">18.7698268890381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9249496459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1576328277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.002513885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0412902832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3044624328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1493377685547</t>
+    <t xml:space="preserve">18.9249515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1576347351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0025119781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0412921905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3044586181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1493396759033</t>
   </si>
   <si>
     <t xml:space="preserve">18.032995223999</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">18.226900100708</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4208030700684</t>
+    <t xml:space="preserve">18.4207992553711</t>
   </si>
   <si>
     <t xml:space="preserve">18.498363494873</t>
@@ -1697,13 +1697,13 @@
     <t xml:space="preserve">17.683967590332</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8086090087891</t>
+    <t xml:space="preserve">18.8086109161377</t>
   </si>
   <si>
     <t xml:space="preserve">18.3820209503174</t>
   </si>
   <si>
-    <t xml:space="preserve">18.188117980957</t>
+    <t xml:space="preserve">18.1881198883057</t>
   </si>
   <si>
     <t xml:space="preserve">17.916654586792</t>
@@ -1715,16 +1715,16 @@
     <t xml:space="preserve">17.606409072876</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6451892852783</t>
+    <t xml:space="preserve">17.6451873779297</t>
   </si>
   <si>
     <t xml:space="preserve">17.1410427093506</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1022567749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2961654663086</t>
+    <t xml:space="preserve">17.1022605895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.29616355896</t>
   </si>
   <si>
     <t xml:space="preserve">15.1244487762451</t>
@@ -1733,28 +1733,28 @@
     <t xml:space="preserve">14.7676668167114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5577116012573</t>
+    <t xml:space="preserve">13.5577096939087</t>
   </si>
   <si>
     <t xml:space="preserve">13.9610290527344</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0302925109863</t>
+    <t xml:space="preserve">13.0302934646606</t>
   </si>
   <si>
     <t xml:space="preserve">13.185417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1388807296753</t>
+    <t xml:space="preserve">13.138879776001</t>
   </si>
   <si>
     <t xml:space="preserve">13.5732221603394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.262978553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1699028015137</t>
+    <t xml:space="preserve">13.2629766464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.169903755188</t>
   </si>
   <si>
     <t xml:space="preserve">12.952733039856</t>
@@ -1763,16 +1763,16 @@
     <t xml:space="preserve">12.5649271011353</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7582883834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5566291809082</t>
+    <t xml:space="preserve">11.7582893371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5566301345825</t>
   </si>
   <si>
     <t xml:space="preserve">10.8585777282715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7810163497925</t>
+    <t xml:space="preserve">10.7810173034668</t>
   </si>
   <si>
     <t xml:space="preserve">10.3156499862671</t>
@@ -1781,49 +1781,49 @@
     <t xml:space="preserve">10.8197975158691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1300430297852</t>
+    <t xml:space="preserve">11.1300439834595</t>
   </si>
   <si>
     <t xml:space="preserve">11.7893133163452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2546815872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9056558609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6341915130615</t>
+    <t xml:space="preserve">12.2546806335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9056568145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6341905593872</t>
   </si>
   <si>
     <t xml:space="preserve">12.0219974517822</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0607786178589</t>
+    <t xml:space="preserve">12.0607776641846</t>
   </si>
   <si>
     <t xml:space="preserve">11.8280935287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4790678024292</t>
+    <t xml:space="preserve">11.4790697097778</t>
   </si>
   <si>
     <t xml:space="preserve">11.7117528915405</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6729726791382</t>
+    <t xml:space="preserve">11.6729717254639</t>
   </si>
   <si>
     <t xml:space="preserve">11.5954103469849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2851657867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4015073776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7505321502686</t>
+    <t xml:space="preserve">11.2851648330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4015064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7505311965942</t>
   </si>
   <si>
     <t xml:space="preserve">10.9749193191528</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">10.5095529556274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871143341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6646738052368</t>
+    <t xml:space="preserve">10.5871124267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6646757125854</t>
   </si>
   <si>
     <t xml:space="preserve">11.2463846206665</t>
@@ -1844,34 +1844,34 @@
     <t xml:space="preserve">12.2159004211426</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3710222244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.07737159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1181735992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0365686416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8733520507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8325481414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1997833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6078224182129</t>
+    <t xml:space="preserve">12.3710231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0773706436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1181755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0365676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8733510971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8325471878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.199782371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6078214645386</t>
   </si>
   <si>
     <t xml:space="preserve">14.2813901901245</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4245090484619</t>
+    <t xml:space="preserve">13.4245080947876</t>
   </si>
   <si>
     <t xml:space="preserve">13.5469188690186</t>
@@ -1880,13 +1880,13 @@
     <t xml:space="preserve">13.5061149597168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.750940322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9549589157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5262136459351</t>
+    <t xml:space="preserve">13.7509393692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9549598693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5262145996094</t>
   </si>
   <si>
     <t xml:space="preserve">14.7710380554199</t>
@@ -1895,73 +1895,73 @@
     <t xml:space="preserve">14.6894302368164</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3221950531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4038019180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5877237319946</t>
+    <t xml:space="preserve">14.322193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4038038253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5877227783203</t>
   </si>
   <si>
     <t xml:space="preserve">13.4653120040894</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6285285949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9141540527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2405862808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9957618713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1589784622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7917423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3837022781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2204885482788</t>
+    <t xml:space="preserve">13.6285276412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.914155960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2405881881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9957637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1589794158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7917432785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3837041854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2204875946045</t>
   </si>
   <si>
     <t xml:space="preserve">13.3429002761841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7101345062256</t>
+    <t xml:space="preserve">13.7101354598999</t>
   </si>
   <si>
     <t xml:space="preserve">13.0572719573975</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2612915039062</t>
+    <t xml:space="preserve">13.2612924575806</t>
   </si>
   <si>
     <t xml:space="preserve">13.0980749130249</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4860143661499</t>
+    <t xml:space="preserve">12.4860153198242</t>
   </si>
   <si>
     <t xml:space="preserve">12.8532524108887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7308406829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6900358200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9756631851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7716426849365</t>
+    <t xml:space="preserve">12.7308397293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.690034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9756641387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7716436386108</t>
   </si>
   <si>
     <t xml:space="preserve">14.8526468276978</t>
@@ -1970,10 +1970,10 @@
     <t xml:space="preserve">15.2606868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4239025115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0767650604248</t>
+    <t xml:space="preserve">15.4239015579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0767669677734</t>
   </si>
   <si>
     <t xml:space="preserve">15.9135494232178</t>
@@ -1982,34 +1982,34 @@
     <t xml:space="preserve">15.5055084228516</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6687288284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5871181488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3014898300171</t>
+    <t xml:space="preserve">15.6687250137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5871171951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3014917373657</t>
   </si>
   <si>
     <t xml:space="preserve">15.3830986022949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3422918319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7503328323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2198820114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1790771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4647045135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.321590423584</t>
+    <t xml:space="preserve">15.3422927856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7503337860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2198829650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1790781021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4647064208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3215885162354</t>
   </si>
   <si>
     <t xml:space="preserve">16.1583728790283</t>
@@ -2027,25 +2027,25 @@
     <t xml:space="preserve">17.3824920654297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8928470611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1991767883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.484806060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6480197906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5664119720459</t>
+    <t xml:space="preserve">16.89284324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1991786956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4848041534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.648021697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5664138793945</t>
   </si>
   <si>
     <t xml:space="preserve">16.2399806976318</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4031982421875</t>
+    <t xml:space="preserve">16.4031963348389</t>
   </si>
   <si>
     <t xml:space="preserve">16.7296295166016</t>
@@ -2054,61 +2054,58 @@
     <t xml:space="preserve">17.2192764282227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4641017913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5457077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9537487030029</t>
+    <t xml:space="preserve">17.4640998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5457096099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9537467956543</t>
   </si>
   <si>
     <t xml:space="preserve">18.0353565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9744510650635</t>
+    <t xml:space="preserve">16.9744529724121</t>
   </si>
   <si>
     <t xml:space="preserve">17.8721408843994</t>
   </si>
   <si>
-    <t xml:space="preserve">18.11696434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1985702514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3617897033691</t>
+    <t xml:space="preserve">18.1169624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1985721588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3617877960205</t>
   </si>
   <si>
     <t xml:space="preserve">19.1778659820557</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8514347076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6882190704346</t>
+    <t xml:space="preserve">18.8514366149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6882209777832</t>
   </si>
   <si>
     <t xml:space="preserve">19.0962600708008</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6066093444824</t>
+    <t xml:space="preserve">18.6066112518311</t>
   </si>
   <si>
     <t xml:space="preserve">18.9330444335938</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7698249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2594738006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3410816192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4226913452148</t>
+    <t xml:space="preserve">19.2594757080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.34108543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4226894378662</t>
   </si>
   <si>
     <t xml:space="preserve">19.0146503448486</t>
@@ -2120,6 +2117,9 @@
     <t xml:space="preserve">19.8276062011719</t>
   </si>
   <si>
+    <t xml:space="preserve">19.9123382568359</t>
+  </si>
+  <si>
     <t xml:space="preserve">19.4886722564697</t>
   </si>
   <si>
@@ -2132,40 +2132,40 @@
     <t xml:space="preserve">19.4039402008057</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9970741271973</t>
+    <t xml:space="preserve">19.9970722198486</t>
   </si>
   <si>
     <t xml:space="preserve">20.3360061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">20.166540145874</t>
+    <t xml:space="preserve">20.1665382385254</t>
   </si>
   <si>
     <t xml:space="preserve">19.3192043304443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0650081634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6413402557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7428722381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0818061828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4207420349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5054721832275</t>
+    <t xml:space="preserve">19.0650062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6413383483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7428703308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.08180809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4207401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5054740905762</t>
   </si>
   <si>
     <t xml:space="preserve">20.6749401092529</t>
   </si>
   <si>
-    <t xml:space="preserve">20.929141998291</t>
+    <t xml:space="preserve">20.9291400909424</t>
   </si>
   <si>
     <t xml:space="preserve">21.1833400726318</t>
@@ -2174,16 +2174,16 @@
     <t xml:space="preserve">20.759672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4375400543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7085399627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0306720733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4543399810791</t>
+    <t xml:space="preserve">21.4375381469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7085380554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0306758880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4543418884277</t>
   </si>
   <si>
     <t xml:space="preserve">22.2001419067383</t>
@@ -2195,16 +2195,16 @@
     <t xml:space="preserve">22.7932739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0474739074707</t>
+    <t xml:space="preserve">23.0474758148193</t>
   </si>
   <si>
     <t xml:space="preserve">23.6406059265137</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5558738708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3016719818115</t>
+    <t xml:space="preserve">23.555871963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3016738891602</t>
   </si>
   <si>
     <t xml:space="preserve">23.4711418151855</t>
@@ -2216,22 +2216,22 @@
     <t xml:space="preserve">23.725341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1322078704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2169418334961</t>
+    <t xml:space="preserve">23.1322059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2169399261475</t>
   </si>
   <si>
     <t xml:space="preserve">21.9459400177002</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8780059814453</t>
+    <t xml:space="preserve">22.8780078887939</t>
   </si>
   <si>
     <t xml:space="preserve">24.1490077972412</t>
   </si>
   <si>
-    <t xml:space="preserve">25.165807723999</t>
+    <t xml:space="preserve">25.1658096313477</t>
   </si>
   <si>
     <t xml:space="preserve">24.9116077423096</t>
@@ -2249,16 +2249,16 @@
     <t xml:space="preserve">24.5726737976074</t>
   </si>
   <si>
-    <t xml:space="preserve">24.403205871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4879417419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.081075668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5047416687012</t>
+    <t xml:space="preserve">24.4032077789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4879398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0810737609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5047397613525</t>
   </si>
   <si>
     <t xml:space="preserve">25.3352737426758</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">26.2673416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4368095397949</t>
+    <t xml:space="preserve">26.4368076324463</t>
   </si>
   <si>
     <t xml:space="preserve">26.521541595459</t>
@@ -2282,10 +2282,10 @@
     <t xml:space="preserve">27.8772773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5719413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.317741394043</t>
+    <t xml:space="preserve">29.5719451904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3177433013916</t>
   </si>
   <si>
     <t xml:space="preserve">28.9788112640381</t>
@@ -2303,13 +2303,13 @@
     <t xml:space="preserve">27.0299415588379</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4704055786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4536113739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3856754302979</t>
+    <t xml:space="preserve">28.4704093933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4536094665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3856773376465</t>
   </si>
   <si>
     <t xml:space="preserve">27.7078094482422</t>
@@ -2321,13 +2321,13 @@
     <t xml:space="preserve">27.2841415405273</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6742076873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0131416320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8436737060547</t>
+    <t xml:space="preserve">25.6742095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0131435394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8436756134033</t>
   </si>
   <si>
     <t xml:space="preserve">26.3520736694336</t>
@@ -2336,19 +2336,19 @@
     <t xml:space="preserve">26.6062755584717</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8268718719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1826095581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0978717803955</t>
+    <t xml:space="preserve">24.8268756866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1826076507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0978755950928</t>
   </si>
   <si>
     <t xml:space="preserve">25.9284076690674</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6910076141357</t>
+    <t xml:space="preserve">26.6910095214844</t>
   </si>
   <si>
     <t xml:space="preserve">22.5390739440918</t>
@@ -2360,10 +2360,10 @@
     <t xml:space="preserve">22.9627418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">24.318473815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8948078155518</t>
+    <t xml:space="preserve">24.3184757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8948097229004</t>
   </si>
   <si>
     <t xml:space="preserve">23.9795398712158</t>
@@ -2378,6 +2378,9 @@
     <t xml:space="preserve">23.2608528137207</t>
   </si>
   <si>
+    <t xml:space="preserve">24.2337398529053</t>
+  </si>
+  <si>
     <t xml:space="preserve">23.9684085845947</t>
   </si>
   <si>
@@ -2402,13 +2405,13 @@
     <t xml:space="preserve">25.295072555542</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2066287994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.587516784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3221836090088</t>
+    <t xml:space="preserve">25.2066268920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5875148773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3221855163574</t>
   </si>
   <si>
     <t xml:space="preserve">23.3492965698242</t>
@@ -2420,10 +2423,10 @@
     <t xml:space="preserve">22.4648532867432</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8457469940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7572994232178</t>
+    <t xml:space="preserve">21.8457450866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7573013305664</t>
   </si>
   <si>
     <t xml:space="preserve">21.4035224914551</t>
@@ -2441,43 +2444,43 @@
     <t xml:space="preserve">21.5804119110107</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1381874084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1110782623291</t>
+    <t xml:space="preserve">21.1381893157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1110763549805</t>
   </si>
   <si>
     <t xml:space="preserve">23.7915191650391</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1181831359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6759605407715</t>
+    <t xml:space="preserve">25.1181812286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6759624481201</t>
   </si>
   <si>
     <t xml:space="preserve">22.9955196380615</t>
   </si>
   <si>
-    <t xml:space="preserve">22.907075881958</t>
+    <t xml:space="preserve">22.9070777893066</t>
   </si>
   <si>
     <t xml:space="preserve">24.1452960968018</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4377422332764</t>
+    <t xml:space="preserve">23.437744140625</t>
   </si>
   <si>
     <t xml:space="preserve">23.614631652832</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6417446136475</t>
+    <t xml:space="preserve">22.6417427062988</t>
   </si>
   <si>
     <t xml:space="preserve">23.0839653015137</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1724109649658</t>
+    <t xml:space="preserve">23.1724090576172</t>
   </si>
   <si>
     <t xml:space="preserve">22.3764095306396</t>
@@ -2486,25 +2489,25 @@
     <t xml:space="preserve">22.1995220184326</t>
   </si>
   <si>
-    <t xml:space="preserve">22.022632598877</t>
+    <t xml:space="preserve">22.0226306915283</t>
   </si>
   <si>
     <t xml:space="preserve">21.0497455596924</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4919662475586</t>
+    <t xml:space="preserve">21.49196434021</t>
   </si>
   <si>
     <t xml:space="preserve">20.6959686279297</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3150806427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7644081115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7372951507568</t>
+    <t xml:space="preserve">21.3150787353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7644062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7372932434082</t>
   </si>
   <si>
     <t xml:space="preserve">25.0297393798828</t>
@@ -2516,19 +2519,19 @@
     <t xml:space="preserve">25.5604057312012</t>
   </si>
   <si>
-    <t xml:space="preserve">25.471960067749</t>
+    <t xml:space="preserve">25.4719619750977</t>
   </si>
   <si>
     <t xml:space="preserve">25.6488494873047</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9141807556152</t>
+    <t xml:space="preserve">25.9141826629639</t>
   </si>
   <si>
     <t xml:space="preserve">27.0639591217041</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2408447265625</t>
+    <t xml:space="preserve">27.2408466339111</t>
   </si>
   <si>
     <t xml:space="preserve">27.1524028778076</t>
@@ -2540,13 +2543,13 @@
     <t xml:space="preserve">27.5946254730225</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3292922973633</t>
+    <t xml:space="preserve">27.3292903900146</t>
   </si>
   <si>
     <t xml:space="preserve">26.7101821899414</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7986259460449</t>
+    <t xml:space="preserve">26.7986240386963</t>
   </si>
   <si>
     <t xml:space="preserve">26.8870697021484</t>
@@ -2567,19 +2570,19 @@
     <t xml:space="preserve">26.4448471069336</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3564052581787</t>
+    <t xml:space="preserve">26.3564033508301</t>
   </si>
   <si>
     <t xml:space="preserve">25.8257389068604</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0026264190674</t>
+    <t xml:space="preserve">26.002628326416</t>
   </si>
   <si>
     <t xml:space="preserve">26.179515838623</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6217365264893</t>
+    <t xml:space="preserve">26.6217384338379</t>
   </si>
   <si>
     <t xml:space="preserve">26.2679595947266</t>
@@ -2591,18 +2594,15 @@
     <t xml:space="preserve">28.7855377197266</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1557693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3227462768555</t>
+    <t xml:space="preserve">29.1557674407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3227481842041</t>
   </si>
   <si>
     <t xml:space="preserve">27.7673988342285</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8599586486816</t>
-  </si>
-  <si>
     <t xml:space="preserve">29.5259990692139</t>
   </si>
   <si>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">30.3590221405029</t>
   </si>
   <si>
-    <t xml:space="preserve">29.803674697876</t>
+    <t xml:space="preserve">29.8036766052246</t>
   </si>
   <si>
     <t xml:space="preserve">29.3408851623535</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">28.8780956268311</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1739044189453</t>
+    <t xml:space="preserve">30.1739063262939</t>
   </si>
   <si>
     <t xml:space="preserve">29.06321144104</t>
@@ -2654,25 +2654,25 @@
     <t xml:space="preserve">27.2120513916016</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3971672058105</t>
+    <t xml:space="preserve">27.3971691131592</t>
   </si>
   <si>
     <t xml:space="preserve">27.489725112915</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6748390197754</t>
+    <t xml:space="preserve">27.674840927124</t>
   </si>
   <si>
     <t xml:space="preserve">28.6004199981689</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6929779052734</t>
+    <t xml:space="preserve">28.6929798126221</t>
   </si>
   <si>
     <t xml:space="preserve">29.7111167907715</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5441398620605</t>
+    <t xml:space="preserve">30.5441379547119</t>
   </si>
   <si>
     <t xml:space="preserve">29.9887924194336</t>
@@ -2681,31 +2681,31 @@
     <t xml:space="preserve">30.2664661407471</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4515819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0994834899902</t>
+    <t xml:space="preserve">30.4515838623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0994873046875</t>
   </si>
   <si>
     <t xml:space="preserve">30.6366958618164</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9143733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7292537689209</t>
+    <t xml:space="preserve">30.9143714904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7292556762695</t>
   </si>
   <si>
     <t xml:space="preserve">30.821813583374</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1920471191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.006929397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.56227684021</t>
+    <t xml:space="preserve">31.192045211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0069274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5622749328613</t>
   </si>
   <si>
     <t xml:space="preserve">32.6729736328125</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">32.1176223754883</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9325103759766</t>
+    <t xml:space="preserve">31.9325084686279</t>
   </si>
   <si>
     <t xml:space="preserve">30.0813503265381</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">33.0432052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3208770751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5059967041016</t>
+    <t xml:space="preserve">33.3208808898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5059928894043</t>
   </si>
   <si>
     <t xml:space="preserve">33.6911125183105</t>
@@ -2771,25 +2771,25 @@
     <t xml:space="preserve">34.1539001464844</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7092475891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9687843322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8762283325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4134330749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2464599609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8943672180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5241355895996</t>
+    <t xml:space="preserve">34.7092514038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9687881469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8762245178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4134368896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2464561462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8943634033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5241317749023</t>
   </si>
   <si>
     <t xml:space="preserve">34.4315757751465</t>
@@ -2804,28 +2804,28 @@
     <t xml:space="preserve">34.3390159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1720352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5422744750977</t>
+    <t xml:space="preserve">35.1720390319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5422706604004</t>
   </si>
   <si>
     <t xml:space="preserve">35.0794830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9869232177734</t>
+    <t xml:space="preserve">34.9869194030762</t>
   </si>
   <si>
     <t xml:space="preserve">35.3571548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8199424743652</t>
+    <t xml:space="preserve">35.8199462890625</t>
   </si>
   <si>
     <t xml:space="preserve">35.7273864746094</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9306449890137</t>
+    <t xml:space="preserve">36.9306411743164</t>
   </si>
   <si>
     <t xml:space="preserve">37.7636604309082</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">38.8743591308594</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5966873168945</t>
+    <t xml:space="preserve">38.5966835021973</t>
   </si>
   <si>
     <t xml:space="preserve">38.6892433166504</t>
@@ -2867,13 +2867,13 @@
     <t xml:space="preserve">39.0594749450684</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2445945739746</t>
+    <t xml:space="preserve">39.2445907592773</t>
   </si>
   <si>
     <t xml:space="preserve">38.0413360595703</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8380813598633</t>
+    <t xml:space="preserve">36.8380851745605</t>
   </si>
   <si>
     <t xml:space="preserve">37.8562202453613</t>
@@ -2900,7 +2900,7 @@
     <t xml:space="preserve">41.3734245300293</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0957527160645</t>
+    <t xml:space="preserve">41.0957489013672</t>
   </si>
   <si>
     <t xml:space="preserve">41.0031929016113</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">40.9106369018555</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8180732727051</t>
+    <t xml:space="preserve">40.8180770874023</t>
   </si>
   <si>
     <t xml:space="preserve">40.2164497375488</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">40.5866813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6792373657227</t>
+    <t xml:space="preserve">40.6792411804199</t>
   </si>
   <si>
     <t xml:space="preserve">39.7999382019043</t>
@@ -2939,10 +2939,10 @@
     <t xml:space="preserve">40.6329612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0776100158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5222625732422</t>
+    <t xml:space="preserve">40.0776138305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5222663879395</t>
   </si>
   <si>
     <t xml:space="preserve">40.4478454589844</t>
@@ -3603,6 +3603,9 @@
   </si>
   <si>
     <t xml:space="preserve">62.4000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5</t>
   </si>
 </sst>
 </file>
@@ -20443,7 +20446,7 @@
         <v>25.5</v>
       </c>
       <c r="G635" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20469,7 +20472,7 @@
         <v>25.5</v>
       </c>
       <c r="G636" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20495,7 +20498,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G637" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20521,7 +20524,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G638" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20547,7 +20550,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G639" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20573,7 +20576,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G640" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20651,7 +20654,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G643" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20677,7 +20680,7 @@
         <v>25</v>
       </c>
       <c r="G644" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20703,7 +20706,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G645" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20729,7 +20732,7 @@
         <v>25</v>
       </c>
       <c r="G646" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20755,7 +20758,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G647" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20781,7 +20784,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G648" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20807,7 +20810,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G649" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20833,7 +20836,7 @@
         <v>24.75</v>
       </c>
       <c r="G650" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20859,7 +20862,7 @@
         <v>24.75</v>
       </c>
       <c r="G651" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20885,7 +20888,7 @@
         <v>24.75</v>
       </c>
       <c r="G652" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20963,7 +20966,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G655" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20989,7 +20992,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G656" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -21041,7 +21044,7 @@
         <v>25</v>
       </c>
       <c r="G658" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -21067,7 +21070,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G659" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -21119,7 +21122,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G661" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -21145,7 +21148,7 @@
         <v>25</v>
       </c>
       <c r="G662" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -21171,7 +21174,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G663" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -21197,7 +21200,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G664" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -21223,7 +21226,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G665" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21249,7 +21252,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G666" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21301,7 +21304,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G668" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21327,7 +21330,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G669" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21379,7 +21382,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G671" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21405,7 +21408,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G672" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21431,7 +21434,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G673" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21483,7 +21486,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21509,7 +21512,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G676" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21561,7 +21564,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G678" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21613,7 +21616,7 @@
         <v>25</v>
       </c>
       <c r="G680" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21639,7 +21642,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G681" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21665,7 +21668,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G682" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21691,7 +21694,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G683" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21717,7 +21720,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G684" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21743,7 +21746,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21873,7 +21876,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G690" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21899,7 +21902,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G691" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21925,7 +21928,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G692" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21951,7 +21954,7 @@
         <v>25</v>
       </c>
       <c r="G693" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21977,7 +21980,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G694" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -22029,7 +22032,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G696" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -22055,7 +22058,7 @@
         <v>24.75</v>
       </c>
       <c r="G697" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -22081,7 +22084,7 @@
         <v>24.75</v>
       </c>
       <c r="G698" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -22107,7 +22110,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G699" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -22133,7 +22136,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -22159,7 +22162,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G701" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -22185,7 +22188,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G702" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -22211,7 +22214,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G703" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22237,7 +22240,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G704" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -22263,7 +22266,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G705" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -22315,7 +22318,7 @@
         <v>23</v>
       </c>
       <c r="G707" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22341,7 +22344,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G708" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22367,7 +22370,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G709" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22393,7 +22396,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G710" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22419,7 +22422,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G711" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22445,7 +22448,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G712" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22471,7 +22474,7 @@
         <v>21.5</v>
       </c>
       <c r="G713" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22497,7 +22500,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22523,7 +22526,7 @@
         <v>21</v>
       </c>
       <c r="G715" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22549,7 +22552,7 @@
         <v>20.25</v>
       </c>
       <c r="G716" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22575,7 +22578,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22601,7 +22604,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G718" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22627,7 +22630,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G719" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22653,7 +22656,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G720" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22679,7 +22682,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G721" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22705,7 +22708,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G722" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22731,7 +22734,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G723" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22757,7 +22760,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G724" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22783,7 +22786,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G725" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22809,7 +22812,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G726" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22835,7 +22838,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G727" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22861,7 +22864,7 @@
         <v>21</v>
       </c>
       <c r="G728" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22887,7 +22890,7 @@
         <v>21.5</v>
       </c>
       <c r="G729" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22913,7 +22916,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G730" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22939,7 +22942,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G731" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22965,7 +22968,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G732" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22991,7 +22994,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G733" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -23017,7 +23020,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G734" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -23043,7 +23046,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -23069,7 +23072,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G736" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -23095,7 +23098,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G737" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -23121,7 +23124,7 @@
         <v>20.5</v>
       </c>
       <c r="G738" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -23147,7 +23150,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G739" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -23173,7 +23176,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G740" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -23199,7 +23202,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G741" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -23225,7 +23228,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G742" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23251,7 +23254,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23277,7 +23280,7 @@
         <v>21.25</v>
       </c>
       <c r="G744" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23303,7 +23306,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G745" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23329,7 +23332,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G746" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23355,7 +23358,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G747" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23381,7 +23384,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G748" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23407,7 +23410,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G749" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23433,7 +23436,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G750" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23459,7 +23462,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G751" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23485,7 +23488,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G752" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23511,7 +23514,7 @@
         <v>21</v>
       </c>
       <c r="G753" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23537,7 +23540,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G754" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23563,7 +23566,7 @@
         <v>21</v>
       </c>
       <c r="G755" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23589,7 +23592,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G756" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23615,7 +23618,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G757" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23641,7 +23644,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G758" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23667,7 +23670,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G759" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23693,7 +23696,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G760" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23719,7 +23722,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G761" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23745,7 +23748,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G762" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23771,7 +23774,7 @@
         <v>20.25</v>
       </c>
       <c r="G763" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23797,7 +23800,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G764" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23823,7 +23826,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G765" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23849,7 +23852,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G766" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23875,7 +23878,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G767" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23901,7 +23904,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G768" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23927,7 +23930,7 @@
         <v>21</v>
       </c>
       <c r="G769" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23953,7 +23956,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G770" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23979,7 +23982,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G771" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -24005,7 +24008,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G772" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -24031,7 +24034,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G773" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -24057,7 +24060,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G774" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -24083,7 +24086,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G775" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -24109,7 +24112,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G776" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -24135,7 +24138,7 @@
         <v>22.5</v>
       </c>
       <c r="G777" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -24161,7 +24164,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G778" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -24187,7 +24190,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G779" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -24213,7 +24216,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G780" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -24239,7 +24242,7 @@
         <v>21.5</v>
       </c>
       <c r="G781" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -24265,7 +24268,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G782" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -24291,7 +24294,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G783" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -24317,7 +24320,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G784" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -24343,7 +24346,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G785" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -24369,7 +24372,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G786" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -24395,7 +24398,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G787" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -24421,7 +24424,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G788" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -24447,7 +24450,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G789" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -24473,7 +24476,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G790" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -24499,7 +24502,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G791" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -24525,7 +24528,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G792" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -24551,7 +24554,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G793" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24577,7 +24580,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G794" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24603,7 +24606,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G795" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24629,7 +24632,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G796" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24655,7 +24658,7 @@
         <v>20.25</v>
       </c>
       <c r="G797" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24681,7 +24684,7 @@
         <v>20</v>
       </c>
       <c r="G798" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24707,7 +24710,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G799" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24733,7 +24736,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G800" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24759,7 +24762,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G801" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24785,7 +24788,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G802" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24811,7 +24814,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G803" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24837,7 +24840,7 @@
         <v>20.25</v>
       </c>
       <c r="G804" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24863,7 +24866,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G805" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24889,7 +24892,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G806" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24915,7 +24918,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G807" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24941,7 +24944,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G808" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24967,7 +24970,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G809" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24993,7 +24996,7 @@
         <v>20.5</v>
       </c>
       <c r="G810" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -25019,7 +25022,7 @@
         <v>20</v>
       </c>
       <c r="G811" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -25045,7 +25048,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G812" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -25071,7 +25074,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G813" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -25097,7 +25100,7 @@
         <v>20.25</v>
       </c>
       <c r="G814" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -25123,7 +25126,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G815" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -25149,7 +25152,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G816" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -25175,7 +25178,7 @@
         <v>20.25</v>
       </c>
       <c r="G817" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -25201,7 +25204,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -25227,7 +25230,7 @@
         <v>21</v>
       </c>
       <c r="G819" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -25253,7 +25256,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G820" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -25279,7 +25282,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G821" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -25305,7 +25308,7 @@
         <v>21.5</v>
       </c>
       <c r="G822" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -25331,7 +25334,7 @@
         <v>22</v>
       </c>
       <c r="G823" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -25357,7 +25360,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G824" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -25383,7 +25386,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G825" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -25409,7 +25412,7 @@
         <v>21.75</v>
       </c>
       <c r="G826" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -25435,7 +25438,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G827" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -25461,7 +25464,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G828" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -25487,7 +25490,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G829" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -25513,7 +25516,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -25539,7 +25542,7 @@
         <v>21.75</v>
       </c>
       <c r="G831" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25565,7 +25568,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G832" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25591,7 +25594,7 @@
         <v>22</v>
       </c>
       <c r="G833" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25617,7 +25620,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G834" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25643,7 +25646,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G835" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25669,7 +25672,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G836" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25695,7 +25698,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G837" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25721,7 +25724,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G838" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25747,7 +25750,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G839" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25773,7 +25776,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25799,7 +25802,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G841" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25825,7 +25828,7 @@
         <v>22.5</v>
       </c>
       <c r="G842" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25851,7 +25854,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G843" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25877,7 +25880,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G844" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25903,7 +25906,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G845" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25929,7 +25932,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G846" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25955,7 +25958,7 @@
         <v>23.5</v>
       </c>
       <c r="G847" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25981,7 +25984,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -26007,7 +26010,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G849" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -26033,7 +26036,7 @@
         <v>21.5</v>
       </c>
       <c r="G850" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -26059,7 +26062,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -26085,7 +26088,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -26111,7 +26114,7 @@
         <v>20.75</v>
       </c>
       <c r="G853" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -26137,7 +26140,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G854" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -26163,7 +26166,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G855" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -26189,7 +26192,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G856" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -26215,7 +26218,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G857" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26241,7 +26244,7 @@
         <v>20.25</v>
       </c>
       <c r="G858" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26267,7 +26270,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G859" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -26293,7 +26296,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G860" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -26319,7 +26322,7 @@
         <v>20</v>
       </c>
       <c r="G861" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -26345,7 +26348,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G862" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -26371,7 +26374,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G863" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -26397,7 +26400,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G864" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -26423,7 +26426,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G865" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26449,7 +26452,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G866" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -26475,7 +26478,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G867" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -26501,7 +26504,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G868" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -26527,7 +26530,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G869" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -26553,7 +26556,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -26579,7 +26582,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G871" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -26605,7 +26608,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G872" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26631,7 +26634,7 @@
         <v>20</v>
       </c>
       <c r="G873" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -26657,7 +26660,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G874" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26683,7 +26686,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G875" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26709,7 +26712,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G876" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26735,7 +26738,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G877" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26761,7 +26764,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G878" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26787,7 +26790,7 @@
         <v>20.25</v>
       </c>
       <c r="G879" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26813,7 +26816,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26839,7 +26842,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G881" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26865,7 +26868,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G882" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26891,7 +26894,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G883" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26917,7 +26920,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G884" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26943,7 +26946,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G885" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26969,7 +26972,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G886" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26995,7 +26998,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G887" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -27021,7 +27024,7 @@
         <v>20.25</v>
       </c>
       <c r="G888" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -27047,7 +27050,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G889" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -27073,7 +27076,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G890" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -27099,7 +27102,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G891" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -27125,7 +27128,7 @@
         <v>20.5</v>
       </c>
       <c r="G892" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -27151,7 +27154,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G893" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -27177,7 +27180,7 @@
         <v>20.25</v>
       </c>
       <c r="G894" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -27203,7 +27206,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -27229,7 +27232,7 @@
         <v>20.25</v>
       </c>
       <c r="G896" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -27255,7 +27258,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G897" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -27281,7 +27284,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G898" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -27307,7 +27310,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G899" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -27333,7 +27336,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G900" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -27359,7 +27362,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G901" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -27385,7 +27388,7 @@
         <v>20.25</v>
       </c>
       <c r="G902" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -27411,7 +27414,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G903" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -27437,7 +27440,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G904" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -27463,7 +27466,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G905" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -27489,7 +27492,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G906" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -27515,7 +27518,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G907" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -27541,7 +27544,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G908" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -27567,7 +27570,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G909" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -27593,7 +27596,7 @@
         <v>21.25</v>
       </c>
       <c r="G910" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27619,7 +27622,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G911" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27645,7 +27648,7 @@
         <v>21.5</v>
       </c>
       <c r="G912" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27671,7 +27674,7 @@
         <v>21.5</v>
       </c>
       <c r="G913" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27697,7 +27700,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G914" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27723,7 +27726,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G915" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27749,7 +27752,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G916" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27775,7 +27778,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G917" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -27801,7 +27804,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G918" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27827,7 +27830,7 @@
         <v>21</v>
       </c>
       <c r="G919" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27853,7 +27856,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G920" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27879,7 +27882,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G921" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27905,7 +27908,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G922" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27931,7 +27934,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G923" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27957,7 +27960,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G924" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27983,7 +27986,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G925" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -28009,7 +28012,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G926" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -28035,7 +28038,7 @@
         <v>20</v>
       </c>
       <c r="G927" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -28061,7 +28064,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G928" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -28087,7 +28090,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G929" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -28113,7 +28116,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G930" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -28139,7 +28142,7 @@
         <v>20</v>
       </c>
       <c r="G931" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -28165,7 +28168,7 @@
         <v>20</v>
       </c>
       <c r="G932" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -28191,7 +28194,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G933" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -28217,7 +28220,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G934" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -28243,7 +28246,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G935" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -28269,7 +28272,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G936" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -28295,7 +28298,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G937" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -28321,7 +28324,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G938" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -28347,7 +28350,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G939" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -28373,7 +28376,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G940" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -28399,7 +28402,7 @@
         <v>21.25</v>
       </c>
       <c r="G941" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -28425,7 +28428,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G942" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -28451,7 +28454,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G943" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -28477,7 +28480,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G944" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -28503,7 +28506,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G945" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -28529,7 +28532,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G946" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -28555,7 +28558,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G947" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -28581,7 +28584,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G948" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -28607,7 +28610,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G949" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -28633,7 +28636,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G950" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -28659,7 +28662,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G951" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28685,7 +28688,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G952" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -28711,7 +28714,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G953" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28737,7 +28740,7 @@
         <v>21.25</v>
       </c>
       <c r="G954" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -28763,7 +28766,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G955" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28789,7 +28792,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28815,7 +28818,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G957" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28841,7 +28844,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G958" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28867,7 +28870,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G959" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28893,7 +28896,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G960" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28919,7 +28922,7 @@
         <v>21.25</v>
       </c>
       <c r="G961" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28945,7 +28948,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G962" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28971,7 +28974,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G963" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28997,7 +29000,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G964" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -29023,7 +29026,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G965" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -29049,7 +29052,7 @@
         <v>21.5</v>
       </c>
       <c r="G966" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -29075,7 +29078,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G967" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -29101,7 +29104,7 @@
         <v>21.25</v>
       </c>
       <c r="G968" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -29127,7 +29130,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G969" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -29153,7 +29156,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G970" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -29179,7 +29182,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G971" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -29205,7 +29208,7 @@
         <v>21.5</v>
       </c>
       <c r="G972" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -29231,7 +29234,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G973" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -29257,7 +29260,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G974" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -29283,7 +29286,7 @@
         <v>21</v>
       </c>
       <c r="G975" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -29309,7 +29312,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G976" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -29335,7 +29338,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G977" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -29361,7 +29364,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G978" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -29387,7 +29390,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G979" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -29413,7 +29416,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G980" t="s">
-        <v>488</v>
+        <v>538</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -29543,7 +29546,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G985" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -30037,7 +30040,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1004" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -30245,7 +30248,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1012" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -31311,7 +31314,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1053" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -31441,7 +31444,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1058" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -31467,7 +31470,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1059" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -31493,7 +31496,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1060" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -31519,7 +31522,7 @@
         <v>20.75</v>
       </c>
       <c r="G1061" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -31545,7 +31548,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1062" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -31571,7 +31574,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1063" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -38461,7 +38464,7 @@
         <v>23</v>
       </c>
       <c r="G1328" t="s">
-        <v>695</v>
+        <v>548</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -38799,7 +38802,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1341" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -38825,7 +38828,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1342" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -38851,7 +38854,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1343" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -38877,7 +38880,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1344" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -38929,7 +38932,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1346" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -38955,7 +38958,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1347" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -38981,7 +38984,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1348" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -39033,7 +39036,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1350" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -39059,7 +39062,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1351" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -39085,7 +39088,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1352" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -39111,7 +39114,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1353" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -39163,7 +39166,7 @@
         <v>23</v>
       </c>
       <c r="G1355" t="s">
-        <v>695</v>
+        <v>548</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39189,7 +39192,7 @@
         <v>23</v>
       </c>
       <c r="G1356" t="s">
-        <v>695</v>
+        <v>548</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -39215,7 +39218,7 @@
         <v>23</v>
       </c>
       <c r="G1357" t="s">
-        <v>695</v>
+        <v>548</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39241,7 +39244,7 @@
         <v>23</v>
       </c>
       <c r="G1358" t="s">
-        <v>695</v>
+        <v>548</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39267,7 +39270,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -39293,7 +39296,7 @@
         <v>23</v>
       </c>
       <c r="G1360" t="s">
-        <v>695</v>
+        <v>548</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -39319,7 +39322,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1361" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -39345,7 +39348,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1362" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -39371,7 +39374,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -39397,7 +39400,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -39423,7 +39426,7 @@
         <v>23.5</v>
       </c>
       <c r="G1365" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -39553,7 +39556,7 @@
         <v>23.5</v>
       </c>
       <c r="G1370" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -39579,7 +39582,7 @@
         <v>23.5</v>
       </c>
       <c r="G1371" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -39605,7 +39608,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1372" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -39657,7 +39660,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1374" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -39683,7 +39686,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1375" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -39709,7 +39712,7 @@
         <v>23.5</v>
       </c>
       <c r="G1376" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -39735,7 +39738,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1377" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -39787,7 +39790,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1379" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -39813,7 +39816,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1380" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -39839,7 +39842,7 @@
         <v>23.5</v>
       </c>
       <c r="G1381" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -39865,7 +39868,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1382" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -39891,7 +39894,7 @@
         <v>23.5</v>
       </c>
       <c r="G1383" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -39917,7 +39920,7 @@
         <v>23.5</v>
       </c>
       <c r="G1384" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -40047,7 +40050,7 @@
         <v>23.5</v>
       </c>
       <c r="G1389" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -40073,7 +40076,7 @@
         <v>23.5</v>
       </c>
       <c r="G1390" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40177,7 +40180,7 @@
         <v>23.5</v>
       </c>
       <c r="G1394" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -40203,7 +40206,7 @@
         <v>23.5</v>
       </c>
       <c r="G1395" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -40749,7 +40752,7 @@
         <v>23.5</v>
       </c>
       <c r="G1416" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -40775,7 +40778,7 @@
         <v>23.5</v>
       </c>
       <c r="G1417" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -46027,7 +46030,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1619" t="s">
-        <v>741</v>
+        <v>788</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -46053,7 +46056,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1620" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46079,7 +46082,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1621" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46105,7 +46108,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1622" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46131,7 +46134,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1623" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46157,7 +46160,7 @@
         <v>27</v>
       </c>
       <c r="G1624" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46209,7 +46212,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1626" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46235,7 +46238,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1627" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46261,7 +46264,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1628" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46287,7 +46290,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1629" t="s">
-        <v>741</v>
+        <v>788</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -46313,7 +46316,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1630" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -46339,7 +46342,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1631" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -46365,7 +46368,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1632" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -46391,7 +46394,7 @@
         <v>28.5</v>
       </c>
       <c r="G1633" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -46417,7 +46420,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1634" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -46443,7 +46446,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1635" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -46469,7 +46472,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1636" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -46495,7 +46498,7 @@
         <v>27.5</v>
       </c>
       <c r="G1637" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -46521,7 +46524,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1638" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -46547,7 +46550,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1639" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -46573,7 +46576,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1640" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -46599,7 +46602,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1641" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -46625,7 +46628,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1642" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -46651,7 +46654,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1643" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -46677,7 +46680,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1644" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -46703,7 +46706,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1645" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -46729,7 +46732,7 @@
         <v>24.5</v>
       </c>
       <c r="G1646" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -46755,7 +46758,7 @@
         <v>24</v>
       </c>
       <c r="G1647" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -46781,7 +46784,7 @@
         <v>24</v>
       </c>
       <c r="G1648" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -46807,7 +46810,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1649" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -46833,7 +46836,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -46859,7 +46862,7 @@
         <v>24</v>
       </c>
       <c r="G1651" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -46885,7 +46888,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -46911,7 +46914,7 @@
         <v>25</v>
       </c>
       <c r="G1653" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -46937,7 +46940,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1654" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -46963,7 +46966,7 @@
         <v>27</v>
       </c>
       <c r="G1655" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -46989,7 +46992,7 @@
         <v>27.5</v>
       </c>
       <c r="G1656" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47015,7 +47018,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1657" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47041,7 +47044,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1658" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -47067,7 +47070,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1659" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47093,7 +47096,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1660" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47119,7 +47122,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1661" t="s">
-        <v>741</v>
+        <v>788</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47145,7 +47148,7 @@
         <v>27.5</v>
       </c>
       <c r="G1662" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47171,7 +47174,7 @@
         <v>26</v>
       </c>
       <c r="G1663" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -47197,7 +47200,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -47223,7 +47226,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1665" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47275,7 +47278,7 @@
         <v>26</v>
       </c>
       <c r="G1667" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47301,7 +47304,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1668" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -47353,7 +47356,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1670" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -47379,7 +47382,7 @@
         <v>27.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -47405,7 +47408,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1672" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -47431,7 +47434,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1673" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -47457,7 +47460,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1674" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -47483,7 +47486,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1675" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -47509,7 +47512,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>741</v>
+        <v>788</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -47535,7 +47538,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1677" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -47561,7 +47564,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1678" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -47587,7 +47590,7 @@
         <v>27</v>
       </c>
       <c r="G1679" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -47613,7 +47616,7 @@
         <v>27.5</v>
       </c>
       <c r="G1680" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -47639,7 +47642,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1681" t="s">
-        <v>741</v>
+        <v>788</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -47665,7 +47668,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1682" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -47691,7 +47694,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1683" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -47717,7 +47720,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1684" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -47743,7 +47746,7 @@
         <v>27</v>
       </c>
       <c r="G1685" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -47769,7 +47772,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1686" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -47795,7 +47798,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1687" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -47821,7 +47824,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1688" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -47847,7 +47850,7 @@
         <v>26.5</v>
       </c>
       <c r="G1689" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -47873,7 +47876,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1690" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -47899,7 +47902,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1691" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -47925,7 +47928,7 @@
         <v>26</v>
       </c>
       <c r="G1692" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -47951,7 +47954,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1693" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -47977,7 +47980,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1694" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48003,7 +48006,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1695" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48029,7 +48032,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1696" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -48055,7 +48058,7 @@
         <v>26.5</v>
       </c>
       <c r="G1697" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48081,7 +48084,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1698" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -48133,7 +48136,7 @@
         <v>26</v>
       </c>
       <c r="G1700" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -48159,7 +48162,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1701" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48237,7 +48240,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1704" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48263,7 +48266,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -48315,7 +48318,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1707" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -48341,7 +48344,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1708" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -48367,7 +48370,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -48393,7 +48396,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1710" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -48419,7 +48422,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -48445,7 +48448,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1712" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -48471,7 +48474,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1713" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -48497,7 +48500,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1714" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -48523,7 +48526,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1715" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -48549,7 +48552,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1716" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -48575,7 +48578,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1717" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -48601,7 +48604,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1718" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -48627,7 +48630,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1719" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -48653,7 +48656,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1720" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -48679,7 +48682,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1721" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -48705,7 +48708,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1722" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -48731,7 +48734,7 @@
         <v>24.5</v>
       </c>
       <c r="G1723" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -48757,7 +48760,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1724" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48783,7 +48786,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1725" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -48809,7 +48812,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1726" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -48835,7 +48838,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1727" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -48861,7 +48864,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1728" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -48887,7 +48890,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1729" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -48913,7 +48916,7 @@
         <v>25</v>
       </c>
       <c r="G1730" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -48965,7 +48968,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1732" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -48991,7 +48994,7 @@
         <v>26.5</v>
       </c>
       <c r="G1733" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -49017,7 +49020,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1734" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -49043,7 +49046,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1735" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49069,7 +49072,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1736" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -49095,7 +49098,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1737" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -49121,7 +49124,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1738" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -49147,7 +49150,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1739" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -49173,7 +49176,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1740" t="s">
-        <v>741</v>
+        <v>788</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -49199,7 +49202,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1741" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -49225,7 +49228,7 @@
         <v>27.5</v>
       </c>
       <c r="G1742" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -49251,7 +49254,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1743" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -49277,7 +49280,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1744" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -49303,7 +49306,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1745" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -49329,7 +49332,7 @@
         <v>27</v>
       </c>
       <c r="G1746" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -49355,7 +49358,7 @@
         <v>27.5</v>
       </c>
       <c r="G1747" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -49381,7 +49384,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1748" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -49407,7 +49410,7 @@
         <v>28</v>
       </c>
       <c r="G1749" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -49433,7 +49436,7 @@
         <v>28</v>
       </c>
       <c r="G1750" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -49459,7 +49462,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1751" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -49485,7 +49488,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1752" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -49511,7 +49514,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1753" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -49537,7 +49540,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1754" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -49563,7 +49566,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -49589,7 +49592,7 @@
         <v>28</v>
       </c>
       <c r="G1756" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -49615,7 +49618,7 @@
         <v>27.5</v>
       </c>
       <c r="G1757" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -49641,7 +49644,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1758" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -49667,7 +49670,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1759" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -49693,7 +49696,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1760" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -49719,7 +49722,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1761" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -49745,7 +49748,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1762" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -49771,7 +49774,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1763" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -49797,7 +49800,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1764" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -49823,7 +49826,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1765" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -49849,7 +49852,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1766" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -49875,7 +49878,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1767" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -49901,7 +49904,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1768" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -49927,7 +49930,7 @@
         <v>29</v>
       </c>
       <c r="G1769" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -49953,7 +49956,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1770" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -49979,7 +49982,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1771" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -50005,7 +50008,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1772" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -50031,7 +50034,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1773" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -50057,7 +50060,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1774" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -50083,7 +50086,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1775" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -50109,7 +50112,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1776" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50135,7 +50138,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1777" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -50161,7 +50164,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1778" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -50187,7 +50190,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1779" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -50213,7 +50216,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1780" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -50239,7 +50242,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1781" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -50265,7 +50268,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1782" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -50291,7 +50294,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1783" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -50317,7 +50320,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1784" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50343,7 +50346,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1785" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -50369,7 +50372,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1786" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -50395,7 +50398,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -50421,7 +50424,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1788" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -50447,7 +50450,7 @@
         <v>30.5</v>
       </c>
       <c r="G1789" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -50473,7 +50476,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1790" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -50499,7 +50502,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1791" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -50525,7 +50528,7 @@
         <v>30.5</v>
       </c>
       <c r="G1792" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -50551,7 +50554,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1793" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -50577,7 +50580,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1794" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -50603,7 +50606,7 @@
         <v>31</v>
       </c>
       <c r="G1795" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -50629,7 +50632,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1796" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -50655,7 +50658,7 @@
         <v>31</v>
       </c>
       <c r="G1797" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -50681,7 +50684,7 @@
         <v>31</v>
       </c>
       <c r="G1798" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -50707,7 +50710,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1799" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -50733,7 +50736,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1800" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -50759,7 +50762,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -50785,7 +50788,7 @@
         <v>31</v>
       </c>
       <c r="G1802" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -50811,7 +50814,7 @@
         <v>30.5</v>
       </c>
       <c r="G1803" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -50837,7 +50840,7 @@
         <v>30</v>
       </c>
       <c r="G1804" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -50863,7 +50866,7 @@
         <v>29.5</v>
       </c>
       <c r="G1805" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -50889,7 +50892,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1806" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -50915,7 +50918,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1807" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -50941,7 +50944,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1808" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -50967,7 +50970,7 @@
         <v>29.5</v>
       </c>
       <c r="G1809" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -50993,7 +50996,7 @@
         <v>30</v>
       </c>
       <c r="G1810" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -51019,7 +51022,7 @@
         <v>30</v>
       </c>
       <c r="G1811" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -51045,7 +51048,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1812" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -51071,7 +51074,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1813" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -51097,7 +51100,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1814" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -51123,7 +51126,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1815" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51149,7 +51152,7 @@
         <v>29.5</v>
       </c>
       <c r="G1816" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51175,7 +51178,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1817" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -51201,7 +51204,7 @@
         <v>29</v>
       </c>
       <c r="G1818" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -51227,7 +51230,7 @@
         <v>28.5</v>
       </c>
       <c r="G1819" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51253,7 +51256,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1820" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -51279,7 +51282,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1821" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -51305,7 +51308,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1822" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -51331,7 +51334,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1823" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51357,7 +51360,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51383,7 +51386,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -51409,7 +51412,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1826" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -51435,7 +51438,7 @@
         <v>29.5</v>
       </c>
       <c r="G1827" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -51461,7 +51464,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1828" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -51487,7 +51490,7 @@
         <v>30.5</v>
       </c>
       <c r="G1829" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -51513,7 +51516,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1830" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -51539,7 +51542,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -51565,7 +51568,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1832" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -51591,7 +51594,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1833" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -51617,7 +51620,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -51643,7 +51646,7 @@
         <v>30</v>
       </c>
       <c r="G1835" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -51669,7 +51672,7 @@
         <v>29.5</v>
       </c>
       <c r="G1836" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -51695,7 +51698,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -51721,7 +51724,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1838" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -51747,7 +51750,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1839" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -51773,7 +51776,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1840" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -51799,7 +51802,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1841" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -51825,7 +51828,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1842" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -51851,7 +51854,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1843" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -51877,7 +51880,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1844" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -51903,7 +51906,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1845" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -51929,7 +51932,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1846" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -51955,7 +51958,7 @@
         <v>30.5</v>
       </c>
       <c r="G1847" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -51981,7 +51984,7 @@
         <v>30.5</v>
       </c>
       <c r="G1848" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52007,7 +52010,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1849" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -52033,7 +52036,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1850" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -52059,7 +52062,7 @@
         <v>30</v>
       </c>
       <c r="G1851" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -52085,7 +52088,7 @@
         <v>30.5</v>
       </c>
       <c r="G1852" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52111,7 +52114,7 @@
         <v>30</v>
       </c>
       <c r="G1853" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52137,7 +52140,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1854" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52163,7 +52166,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1855" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -52189,7 +52192,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1856" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -52215,7 +52218,7 @@
         <v>30.5</v>
       </c>
       <c r="G1857" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -52241,7 +52244,7 @@
         <v>30</v>
       </c>
       <c r="G1858" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -52267,7 +52270,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1859" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -52293,7 +52296,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -52319,7 +52322,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1861" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -52345,7 +52348,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1862" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -52371,7 +52374,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1863" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -52397,7 +52400,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1864" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -52423,7 +52426,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1865" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -52449,7 +52452,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1866" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -52475,7 +52478,7 @@
         <v>31.5</v>
       </c>
       <c r="G1867" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52501,7 +52504,7 @@
         <v>31.5</v>
       </c>
       <c r="G1868" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -52527,7 +52530,7 @@
         <v>31.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -52553,7 +52556,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1870" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -52579,7 +52582,7 @@
         <v>31.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -52605,7 +52608,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1872" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52631,7 +52634,7 @@
         <v>30</v>
       </c>
       <c r="G1873" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52657,7 +52660,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1874" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -52683,7 +52686,7 @@
         <v>31.5</v>
       </c>
       <c r="G1875" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -53229,7 +53232,7 @@
         <v>31.5</v>
       </c>
       <c r="G1896" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -53333,7 +53336,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1900" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -53567,7 +53570,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -53593,7 +53596,7 @@
         <v>30</v>
       </c>
       <c r="G1910" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53879,7 +53882,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1921" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53905,7 +53908,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1922" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -55725,7 +55728,7 @@
         <v>31.5</v>
       </c>
       <c r="G1992" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -68993,7 +68996,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6909953704</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>12825</v>
@@ -69014,6 +69017,32 @@
         <v>1196</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6910300926</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>21046</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>62.2000007629395</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>60.7000007629395</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="1204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="1205">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,34 +44,34 @@
     <t xml:space="preserve">CMB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55656623840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31377506256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40145015716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40819263458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44191455841064</t>
+    <t xml:space="preserve">9.55656719207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3137731552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40144824981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40819358825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44191360473633</t>
   </si>
   <si>
     <t xml:space="preserve">9.36098384857178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13842391967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32051849365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26656532287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34075164794922</t>
+    <t xml:space="preserve">9.13842487335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32051753997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26656436920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34075260162354</t>
   </si>
   <si>
     <t xml:space="preserve">9.2733097076416</t>
@@ -80,16 +80,16 @@
     <t xml:space="preserve">9.19237804412842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19912338256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10470390319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84167671203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77423667907715</t>
+    <t xml:space="preserve">9.19912242889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10470199584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84167766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77423572540283</t>
   </si>
   <si>
     <t xml:space="preserve">8.84842300415039</t>
@@ -98,22 +98,22 @@
     <t xml:space="preserve">8.36283874511719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3291187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61912059783936</t>
+    <t xml:space="preserve">8.32911777496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61911869049072</t>
   </si>
   <si>
     <t xml:space="preserve">8.45051288604736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43028163909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63260746002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80121517181396</t>
+    <t xml:space="preserve">8.4302806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63260650634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80121421813965</t>
   </si>
   <si>
     <t xml:space="preserve">9.22609996795654</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">9.07098197937012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87539863586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96981811523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71353816986084</t>
+    <t xml:space="preserve">8.87539958953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96981906890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71354007720947</t>
   </si>
   <si>
     <t xml:space="preserve">8.6663293838501</t>
@@ -140,28 +140,28 @@
     <t xml:space="preserve">8.89563274383545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81470203399658</t>
+    <t xml:space="preserve">8.81470108032227</t>
   </si>
   <si>
     <t xml:space="preserve">8.99679565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01028347015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90237617492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97656345367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18563461303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17214488983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13168048858643</t>
+    <t xml:space="preserve">9.01028442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90237522125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18563365936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17214679718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13168144226074</t>
   </si>
   <si>
     <t xml:space="preserve">9.34749603271484</t>
@@ -170,19 +170,19 @@
     <t xml:space="preserve">9.25307750701904</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15865802764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08447170257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540145874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98330688476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7877254486084</t>
+    <t xml:space="preserve">9.15865707397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08447074890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540241241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98330783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78772449493408</t>
   </si>
   <si>
     <t xml:space="preserve">8.78098106384277</t>
@@ -191,136 +191,136 @@
     <t xml:space="preserve">9.1249361038208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03726196289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21261215209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04400634765625</t>
+    <t xml:space="preserve">9.03726100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21261024475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04400444030762</t>
   </si>
   <si>
     <t xml:space="preserve">9.09795951843262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20586681365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38121604919434</t>
+    <t xml:space="preserve">9.20586585998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38121700286865</t>
   </si>
   <si>
     <t xml:space="preserve">9.28679752349854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22100830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22798824310303</t>
+    <t xml:space="preserve">9.22100734710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22798919677734</t>
   </si>
   <si>
     <t xml:space="preserve">9.19308757781982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35363483428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4094762802124</t>
+    <t xml:space="preserve">9.35363388061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40947723388672</t>
   </si>
   <si>
     <t xml:space="preserve">9.52116203308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49324131011963</t>
+    <t xml:space="preserve">9.49324035644531</t>
   </si>
   <si>
     <t xml:space="preserve">9.38853549957275</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94696140289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76547241210938</t>
+    <t xml:space="preserve">9.94696235656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76547336578369</t>
   </si>
   <si>
     <t xml:space="preserve">9.77245330810547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66774940490723</t>
+    <t xml:space="preserve">9.66775035858154</t>
   </si>
   <si>
     <t xml:space="preserve">9.82829570770264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75151443481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57002353668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57700538635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55606365203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47928142547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42343807220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39551639556885</t>
+    <t xml:space="preserve">9.75151348114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57002449035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57700443267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55606269836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47928047180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42343711853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39551734924316</t>
   </si>
   <si>
     <t xml:space="preserve">9.41645812988281</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34665203094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6258659362793</t>
+    <t xml:space="preserve">9.34665584564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58398342132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62586688995361</t>
   </si>
   <si>
     <t xml:space="preserve">9.63284778594971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46531963348389</t>
+    <t xml:space="preserve">9.46531867980957</t>
   </si>
   <si>
     <t xml:space="preserve">9.48626041412354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59096622467041</t>
+    <t xml:space="preserve">9.59096717834473</t>
   </si>
   <si>
     <t xml:space="preserve">9.56304454803467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53512382507324</t>
+    <t xml:space="preserve">9.53512191772461</t>
   </si>
   <si>
     <t xml:space="preserve">9.12328338623047</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30477237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28382968902588</t>
+    <t xml:space="preserve">9.30477142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28383255004883</t>
   </si>
   <si>
     <t xml:space="preserve">9.20704746246338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27685165405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36061477661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29081153869629</t>
+    <t xml:space="preserve">9.27685070037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36061382293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29081058502197</t>
   </si>
   <si>
     <t xml:space="preserve">9.29779148101807</t>
@@ -329,46 +329,46 @@
     <t xml:space="preserve">9.31873321533203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36759567260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47229862213135</t>
+    <t xml:space="preserve">9.36759471893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47229957580566</t>
   </si>
   <si>
     <t xml:space="preserve">9.52814197540283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5072021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44437980651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50022125244141</t>
+    <t xml:space="preserve">9.50720024108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44437789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50022029876709</t>
   </si>
   <si>
     <t xml:space="preserve">9.33269309997559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32571220397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13724517822266</t>
+    <t xml:space="preserve">9.32571315765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13724422454834</t>
   </si>
   <si>
     <t xml:space="preserve">9.14422416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15120315551758</t>
+    <t xml:space="preserve">9.15120410919189</t>
   </si>
   <si>
     <t xml:space="preserve">9.10932445526123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03951835632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92783451080322</t>
+    <t xml:space="preserve">9.03952121734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92783355712891</t>
   </si>
   <si>
     <t xml:space="preserve">9.01159763336182</t>
@@ -380,22 +380,22 @@
     <t xml:space="preserve">8.97669696807861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86501121520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85105133056641</t>
+    <t xml:space="preserve">8.86501216888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85105037689209</t>
   </si>
   <si>
     <t xml:space="preserve">8.934814453125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92085456848145</t>
+    <t xml:space="preserve">8.92085361480713</t>
   </si>
   <si>
     <t xml:space="preserve">8.95575618743896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96971702575684</t>
+    <t xml:space="preserve">8.96971607208252</t>
   </si>
   <si>
     <t xml:space="preserve">9.00461769104004</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">8.91387462615967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87897300720215</t>
+    <t xml:space="preserve">8.87897205352783</t>
   </si>
   <si>
     <t xml:space="preserve">8.80916881561279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59976100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56485939025879</t>
+    <t xml:space="preserve">8.59975910186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56485652923584</t>
   </si>
   <si>
     <t xml:space="preserve">8.81614971160889</t>
@@ -422,16 +422,16 @@
     <t xml:space="preserve">8.83708953857422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8999137878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99763870239258</t>
+    <t xml:space="preserve">8.89991283416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99763774871826</t>
   </si>
   <si>
     <t xml:space="preserve">8.83010959625244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96273612976074</t>
+    <t xml:space="preserve">8.96273517608643</t>
   </si>
   <si>
     <t xml:space="preserve">9.08838176727295</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">9.09536266326904</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66076755523682</t>
+    <t xml:space="preserve">9.66076850891113</t>
   </si>
   <si>
     <t xml:space="preserve">9.64680767059326</t>
@@ -452,34 +452,34 @@
     <t xml:space="preserve">9.70265007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79339504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92602157592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98186302185059</t>
+    <t xml:space="preserve">9.79339408874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92602062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9818639755249</t>
   </si>
   <si>
     <t xml:space="preserve">10.0516662597656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.414644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1912727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2471151351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493921279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1354303359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2680587768555</t>
+    <t xml:space="preserve">10.4146432876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.19127368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2471160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493911743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1354312896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2680578231812</t>
   </si>
   <si>
     <t xml:space="preserve">10.393702507019</t>
@@ -491,25 +491,25 @@
     <t xml:space="preserve">10.5891513824463</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4844455718994</t>
+    <t xml:space="preserve">10.4844465255737</t>
   </si>
   <si>
     <t xml:space="preserve">10.6310338973999</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3588008880615</t>
+    <t xml:space="preserve">10.3588018417358</t>
   </si>
   <si>
     <t xml:space="preserve">9.988844871521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95394325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1005296707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4704875946045</t>
+    <t xml:space="preserve">9.95394229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.100528717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4704847335815</t>
   </si>
   <si>
     <t xml:space="preserve">10.3867235183716</t>
@@ -521,22 +521,22 @@
     <t xml:space="preserve">10.3448400497437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.477466583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4006814956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4355850219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3727607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3657808303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3378591537476</t>
+    <t xml:space="preserve">10.4774656295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4006824493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.435583114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3727617263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3657817840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3378620147705</t>
   </si>
   <si>
     <t xml:space="preserve">10.2820167541504</t>
@@ -548,70 +548,70 @@
     <t xml:space="preserve">10.6100931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5542507171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6938571929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0917367935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.042872428894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0358924865723</t>
+    <t xml:space="preserve">10.5542488098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6938552856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0917339324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0428733825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0358934402466</t>
   </si>
   <si>
     <t xml:space="preserve">11.0638151168823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.084755897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3569869995117</t>
+    <t xml:space="preserve">11.0847539901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.356987953186</t>
   </si>
   <si>
     <t xml:space="preserve">11.5175342559814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0899200439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9991779327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0689821243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1038827896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2853717803955</t>
+    <t xml:space="preserve">12.0899209976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9991788864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.06898021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1038808822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2853698730469</t>
   </si>
   <si>
     <t xml:space="preserve">12.8228569030762</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9764223098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.990385055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2486553192139</t>
+    <t xml:space="preserve">12.9764242172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.990382194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2486543655396</t>
   </si>
   <si>
     <t xml:space="preserve">13.1090488433838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1230087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8926591873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9135980606079</t>
+    <t xml:space="preserve">13.123010635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8926572799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9135999679565</t>
   </si>
   <si>
     <t xml:space="preserve">12.8437967300415</t>
@@ -620,133 +620,133 @@
     <t xml:space="preserve">12.9624624252319</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1928119659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3952398300171</t>
+    <t xml:space="preserve">13.1928129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3952436447144</t>
   </si>
   <si>
     <t xml:space="preserve">13.8978261947632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9815902709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9327259063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0234708786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0304498672485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1351547241211</t>
+    <t xml:space="preserve">13.9815893173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9327268600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0234718322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0304508209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1351556777954</t>
   </si>
   <si>
     <t xml:space="preserve">14.0723342895508</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0025281906128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.211254119873</t>
+    <t xml:space="preserve">14.0025291442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2112550735474</t>
   </si>
   <si>
     <t xml:space="preserve">14.3197383880615</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1461639404297</t>
+    <t xml:space="preserve">14.1461658477783</t>
   </si>
   <si>
     <t xml:space="preserve">14.0810747146606</t>
   </si>
   <si>
-    <t xml:space="preserve">13.994288444519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6688413619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.355899810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6833057403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0015239715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9870595932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2691144943237</t>
+    <t xml:space="preserve">13.9942922592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6688423156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3558988571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6833066940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0015230178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9870586395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2691135406494</t>
   </si>
   <si>
     <t xml:space="preserve">14.348669052124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3414325714111</t>
+    <t xml:space="preserve">14.3414354324341</t>
   </si>
   <si>
     <t xml:space="preserve">14.2763452529907</t>
   </si>
   <si>
-    <t xml:space="preserve">14.42822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5656337738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3322458267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8457317352295</t>
+    <t xml:space="preserve">14.4282236099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5656328201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3322477340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8457307815552</t>
   </si>
   <si>
     <t xml:space="preserve">15.7589454650879</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3611755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1876010894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9200096130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6307229995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636777877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3105497360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9272432327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0718860626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5492105484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4551973342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2671566009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1731395721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8332252502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1369762420654</t>
+    <t xml:space="preserve">15.3611745834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1876020431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9200115203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6307210922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636749267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3105487823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9272413253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0718870162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5492124557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4551944732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2671575546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1731376647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8332242965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1369781494141</t>
   </si>
   <si>
     <t xml:space="preserve">15.1152801513672</t>
@@ -755,46 +755,46 @@
     <t xml:space="preserve">14.9850997924805</t>
   </si>
   <si>
-    <t xml:space="preserve">15.151442527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0284957885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2092990875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6649255752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6938562393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7661771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9325189590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0409984588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9469795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6432304382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2816209793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.288854598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2599248886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3250131607056</t>
+    <t xml:space="preserve">15.1514415740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0284967422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2092971801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.664924621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6938552856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7661781311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9325199127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0410022735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9469804763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6432294845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2816200256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2888498306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2599239349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3250141143799</t>
   </si>
   <si>
     <t xml:space="preserve">15.238226890564</t>
@@ -803,28 +803,28 @@
     <t xml:space="preserve">15.1586723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0574245452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1803684234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2454595565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8983135223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.869384765625</t>
+    <t xml:space="preserve">15.0574235916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1803703308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2454605102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8983144760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8693857192993</t>
   </si>
   <si>
     <t xml:space="preserve">14.8259925842285</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9634056091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9706373214722</t>
+    <t xml:space="preserve">14.9634046554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9706354141235</t>
   </si>
   <si>
     <t xml:space="preserve">14.6813488006592</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">14.7536697387695</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6958122253418</t>
+    <t xml:space="preserve">14.6958131790161</t>
   </si>
   <si>
     <t xml:space="preserve">14.8910818099976</t>
@@ -842,31 +842,31 @@
     <t xml:space="preserve">14.493311882019</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8549194335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6524200439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6090269088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8476905822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1948347091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3394804000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.433497428894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2651958465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9956512451172</t>
+    <t xml:space="preserve">14.854923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.652419090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6090288162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8476877212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1948375701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3394765853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4334964752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2651977539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9956493377686</t>
   </si>
   <si>
     <t xml:space="preserve">17.5742244720459</t>
@@ -875,16 +875,16 @@
     <t xml:space="preserve">18.6879825592041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3986949920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4420871734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2178897857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0804805755615</t>
+    <t xml:space="preserve">18.3986930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4420890808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2178916931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0804786682129</t>
   </si>
   <si>
     <t xml:space="preserve">18.1889610290527</t>
@@ -899,34 +899,34 @@
     <t xml:space="preserve">17.8562812805176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9647636413574</t>
+    <t xml:space="preserve">17.9647655487061</t>
   </si>
   <si>
     <t xml:space="preserve">17.6393165588379</t>
   </si>
   <si>
-    <t xml:space="preserve">17.762264251709</t>
+    <t xml:space="preserve">17.7622585296631</t>
   </si>
   <si>
     <t xml:space="preserve">17.6031513214111</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5886878967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.538064956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5019073486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3861904144287</t>
+    <t xml:space="preserve">17.5886898040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5380630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5019054412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3861885070801</t>
   </si>
   <si>
     <t xml:space="preserve">17.3210983276367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2849349975586</t>
+    <t xml:space="preserve">17.2849369049072</t>
   </si>
   <si>
     <t xml:space="preserve">17.0462741851807</t>
@@ -935,64 +935,64 @@
     <t xml:space="preserve">17.263240814209</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0969009399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3283271789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3572616577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4006500244141</t>
+    <t xml:space="preserve">17.0968990325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3283290863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3572578430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4006519317627</t>
   </si>
   <si>
     <t xml:space="preserve">17.3789577484131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2921695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3427925109863</t>
+    <t xml:space="preserve">17.2921676635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3427963256836</t>
   </si>
   <si>
     <t xml:space="preserve">17.1692218780518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.590648651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6268081665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9233322143555</t>
+    <t xml:space="preserve">16.5906467437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6268062591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9233283996582</t>
   </si>
   <si>
     <t xml:space="preserve">16.3447532653809</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7083187103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1133213043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9180555343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6504602432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4749355316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3013591766357</t>
+    <t xml:space="preserve">15.7083196640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1133251190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9180517196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6504640579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4749336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3013610839844</t>
   </si>
   <si>
     <t xml:space="preserve">16.5761833190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5110950469971</t>
+    <t xml:space="preserve">16.5110931396484</t>
   </si>
   <si>
     <t xml:space="preserve">16.5617179870605</t>
@@ -1004,121 +1004,121 @@
     <t xml:space="preserve">16.5255565643311</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4098415374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2073383331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8746604919434</t>
+    <t xml:space="preserve">16.4098434448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2073421478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.874659538269</t>
   </si>
   <si>
     <t xml:space="preserve">16.243501663208</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4460048675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2001094818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8312664031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8601970672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8529644012451</t>
+    <t xml:space="preserve">16.4460029602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2001075744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8312683105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8601951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8529653549194</t>
   </si>
   <si>
     <t xml:space="preserve">15.6287651062012</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4696578979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4624223709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215362548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9976072311401</t>
+    <t xml:space="preserve">15.4696559906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4624252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215314865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9976081848145</t>
   </si>
   <si>
     <t xml:space="preserve">16.236270904541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1639499664307</t>
+    <t xml:space="preserve">16.163948059082</t>
   </si>
   <si>
     <t xml:space="preserve">16.2724323272705</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7786846160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6340370178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4532337188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7425212860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5978813171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7063636779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8510055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0318088531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2126140594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4295806884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9594917297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3809146881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9831428527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9108190536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.730016708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3684043884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4045677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4768886566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8023405075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6702003479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1402931213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1041297912598</t>
+    <t xml:space="preserve">16.7786865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6340389251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4532356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.742525100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.59787940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7063617706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8510036468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.031810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2126159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4295825958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9594898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3809127807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9831418991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9108209609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7300148010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3684091567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4045686721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4768896102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8023414611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6701984405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1402950286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.104133605957</t>
   </si>
   <si>
     <t xml:space="preserve">16.8148460388184</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">16.8871669769287</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8273487091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6827049255371</t>
+    <t xml:space="preserve">17.8273506164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6827087402344</t>
   </si>
   <si>
     <t xml:space="preserve">17.3934192657471</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2487773895264</t>
+    <t xml:space="preserve">17.248779296875</t>
   </si>
   <si>
     <t xml:space="preserve">17.7550296783447</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">17.8996753692627</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5867328643799</t>
+    <t xml:space="preserve">18.5867347717285</t>
   </si>
   <si>
     <t xml:space="preserve">18.6590557098389</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">19.5428009033203</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2444362640381</t>
+    <t xml:space="preserve">19.2444381713867</t>
   </si>
   <si>
     <t xml:space="preserve">19.9157524108887</t>
@@ -1172,61 +1172,61 @@
     <t xml:space="preserve">19.6546878814697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4682102203369</t>
+    <t xml:space="preserve">19.4682083129883</t>
   </si>
   <si>
     <t xml:space="preserve">19.6173915863037</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0952548980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8714790344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9460735321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7968921661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9018039703369</t>
+    <t xml:space="preserve">19.0952529907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8714809417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9460716247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7968940734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9018020629883</t>
   </si>
   <si>
     <t xml:space="preserve">17.3050746917725</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7899169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8341865539551</t>
+    <t xml:space="preserve">17.7899150848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8341884613037</t>
   </si>
   <si>
     <t xml:space="preserve">19.1698455810547</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3936157226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5055046081543</t>
+    <t xml:space="preserve">19.3936176300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5055065155029</t>
   </si>
   <si>
     <t xml:space="preserve">19.8038673400879</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8784561157227</t>
+    <t xml:space="preserve">19.8784580230713</t>
   </si>
   <si>
     <t xml:space="preserve">19.6919803619385</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3190269470215</t>
+    <t xml:space="preserve">19.3190288543701</t>
   </si>
   <si>
     <t xml:space="preserve">18.4239387512207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1325511932373</t>
+    <t xml:space="preserve">19.1325492858887</t>
   </si>
   <si>
     <t xml:space="preserve">19.3563232421875</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">19.7292766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7222995758057</t>
+    <t xml:space="preserve">18.7223014831543</t>
   </si>
   <si>
     <t xml:space="preserve">18.9087772369385</t>
@@ -1247,10 +1247,10 @@
     <t xml:space="preserve">18.5731182098389</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5358219146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9763927459717</t>
+    <t xml:space="preserve">18.5358257293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9763946533203</t>
   </si>
   <si>
     <t xml:space="preserve">18.1255722045898</t>
@@ -1259,16 +1259,16 @@
     <t xml:space="preserve">18.4612350463867</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7595977783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6104164123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3493461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6850032806396</t>
+    <t xml:space="preserve">18.7595958709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6104125976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3493480682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6850051879883</t>
   </si>
   <si>
     <t xml:space="preserve">18.3120498657227</t>
@@ -1277,52 +1277,52 @@
     <t xml:space="preserve">18.4985275268555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2817344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.057954788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1628704071045</t>
+    <t xml:space="preserve">19.2817325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0579586029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1628684997559</t>
   </si>
   <si>
     <t xml:space="preserve">18.0136871337891</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3866405487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.155891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1862144470215</t>
+    <t xml:space="preserve">18.3866424560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1558933258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1862125396729</t>
   </si>
   <si>
     <t xml:space="preserve">15.589485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1419401168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9554624557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0370311737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5218734741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6640777587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.104642868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9927606582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0300540924072</t>
+    <t xml:space="preserve">15.141939163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9554634094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0370292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5218677520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6640758514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1046447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9927587509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0300531387329</t>
   </si>
   <si>
     <t xml:space="preserve">14.768985748291</t>
@@ -1334,145 +1334,145 @@
     <t xml:space="preserve">14.5153770446777</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6198024749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8883323669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2538270950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2608013153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9251432418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7759609222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7013711929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.552188873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6267805099487</t>
+    <t xml:space="preserve">14.6198043823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.888331413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2538280487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2608032226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9251461029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7759637832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7013692855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5521898269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6267795562744</t>
   </si>
   <si>
     <t xml:space="preserve">15.5148935317993</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2911243438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2165307998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.179235458374</t>
+    <t xml:space="preserve">15.2911224365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.21653175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1792373657227</t>
   </si>
   <si>
     <t xml:space="preserve">15.8505544662476</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8132581710815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0743236541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8878479003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4030065536499</t>
+    <t xml:space="preserve">15.8132600784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0743255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8878498077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4030075073242</t>
   </si>
   <si>
     <t xml:space="preserve">14.9032506942749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7093143463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4403028488159</t>
+    <t xml:space="preserve">14.7093133926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4403038024902</t>
   </si>
   <si>
     <t xml:space="preserve">16.1116199493408</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9624376296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5591659545898</t>
+    <t xml:space="preserve">15.962438583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5591640472412</t>
   </si>
   <si>
     <t xml:space="preserve">16.3726902008057</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4845752716064</t>
+    <t xml:space="preserve">16.4845733642578</t>
   </si>
   <si>
     <t xml:space="preserve">16.7829399108887</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8948249816895</t>
+    <t xml:space="preserve">16.8948230743408</t>
   </si>
   <si>
     <t xml:space="preserve">15.7386674880981</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3657131195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.843578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8584966659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0673494338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8734159469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9181671142578</t>
+    <t xml:space="preserve">15.3657121658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8435754776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8584957122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0673522949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8734149932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9181680679321</t>
   </si>
   <si>
     <t xml:space="preserve">16.409984588623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2235088348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2980976104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6710529327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7083492279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7456455230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6337547302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9321212768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8575325012207</t>
+    <t xml:space="preserve">16.2235069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2980995178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6710548400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7083473205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7456436157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6337604522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9321231842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8575305938721</t>
   </si>
   <si>
     <t xml:space="preserve">17.0067100524902</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3796653747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2304859161377</t>
+    <t xml:space="preserve">17.3796634674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2304821014404</t>
   </si>
   <si>
     <t xml:space="preserve">17.5288467407227</t>
@@ -1481,13 +1481,13 @@
     <t xml:space="preserve">18.343240737915</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7227516174316</t>
+    <t xml:space="preserve">17.7227535247803</t>
   </si>
   <si>
     <t xml:space="preserve">16.6756744384766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7532329559326</t>
+    <t xml:space="preserve">16.7532348632812</t>
   </si>
   <si>
     <t xml:space="preserve">16.3654289245605</t>
@@ -1496,25 +1496,25 @@
     <t xml:space="preserve">16.0939636230469</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6673765182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6285972595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0468873977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2640571594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7061557769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5898170471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5122528076172</t>
+    <t xml:space="preserve">15.6673755645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6285943984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0468845367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2640590667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7061595916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5898151397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5122537612915</t>
   </si>
   <si>
     <t xml:space="preserve">15.7449388504028</t>
@@ -1523,46 +1523,46 @@
     <t xml:space="preserve">15.2950830459595</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0158634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1864986419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4191818237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4967432022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5510339736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3261079788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2795715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8612804412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0164012908936</t>
+    <t xml:space="preserve">15.0158624649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1864967346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4191808700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4967422485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5510349273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3261089324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2795724868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8612813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0164031982422</t>
   </si>
   <si>
     <t xml:space="preserve">15.9388408660889</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9000635147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7837181091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8224992752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3266468048096</t>
+    <t xml:space="preserve">15.9000597000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7837190628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8224983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3266487121582</t>
   </si>
   <si>
     <t xml:space="preserve">16.7920169830322</t>
@@ -1574,37 +1574,37 @@
     <t xml:space="preserve">16.9083576202393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4817714691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5593318939209</t>
+    <t xml:space="preserve">16.4817695617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5593338012695</t>
   </si>
   <si>
     <t xml:space="preserve">16.0551834106445</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4042091369629</t>
+    <t xml:space="preserve">16.4042072296143</t>
   </si>
   <si>
     <t xml:space="preserve">16.1327438354492</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2878684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1715240478516</t>
+    <t xml:space="preserve">16.2878665924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1715259552002</t>
   </si>
   <si>
     <t xml:space="preserve">15.9776220321655</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3881559371948</t>
+    <t xml:space="preserve">15.3881578445435</t>
   </si>
   <si>
     <t xml:space="preserve">15.4346942901611</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2103061676025</t>
+    <t xml:space="preserve">16.2103042602539</t>
   </si>
   <si>
     <t xml:space="preserve">16.4429893493652</t>
@@ -1613,516 +1613,519 @@
     <t xml:space="preserve">16.5981101989746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5205497741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6368961334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2490863800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8307971954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9859180450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5288486480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.83909034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5676288604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9942169189453</t>
+    <t xml:space="preserve">16.5205516815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6368942260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2490882873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8307952880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9859199523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8390941619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.567626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9942150115967</t>
   </si>
   <si>
     <t xml:space="preserve">18.6147060394287</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2656784057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8473873138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5371417999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0717754364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4595832824707</t>
+    <t xml:space="preserve">18.2656803131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8473892211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5371437072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.07177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4595813751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7698268890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9249515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1576347351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0025100708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0412940979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3044586181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1493358612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.032995223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.226900100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4207992553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4983654022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1105575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.683967590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8086109161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.382022857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1881198883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.916654586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.955436706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.606409072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6451892852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1410427093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1022624969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.29616355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1244487762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7676668167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5577096939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9610280990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0302925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1854162216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.138879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5732221603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.262978553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.169903755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.952733039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5649271011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7582883834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5566301345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8585786819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7810163497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3156490325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8197975158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1300439834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7893142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2546806335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9056558609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6341905593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0219964981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0607786178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8280944824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4790678024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7117528915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6729726791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5954103469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2851648330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4015064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7505321502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9749202728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5095539093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5871133804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6646747589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2463846206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2159013748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3710231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0773696899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1181735992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.036566734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8733501434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8325471878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.199782371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6078214645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2813901901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4245080947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5469198226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5061140060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7509393692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9549598693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5262145996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7710380554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6894292831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3221921920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4038038253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.587721824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4653120040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6285276412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.914155960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2405872344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9957637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1589794158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7917432785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3837032318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2204875946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0773706436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3428993225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7101345062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0572719573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1388788223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2612915039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0980749130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4860153198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8532514572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7308397293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.690034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9756631851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7716436386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8526487350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.260687828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4238996505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0767688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9135494232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5055103302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6687269210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5871171951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3014898300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3831005096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3422937393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7503356933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2198829650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1790781021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4647064208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3215885162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1583728790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8112373352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7089233398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1376705169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3824920654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.89284324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1991786956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4848041534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.648021697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5664138793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2399826049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4031963348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7296295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2192764282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4640998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5457096099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9537467956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0353584289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9744529724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8721408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.11696434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1985721588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3617877960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1778659820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8514366149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6882190704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0962600708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6066131591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9330444335938</t>
   </si>
   <si>
     <t xml:space="preserve">18.7698287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9249496459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1576366424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0025119781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0412902832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3044624328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1493377685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.032995223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.226900100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4208011627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4983654022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1105556488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6839694976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8086090087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3820209503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.188117980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.916654586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9554347991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.606409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6451892852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1410427093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1022605895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2961616516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1244497299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7676677703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5577087402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9610290527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0302934646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.185417175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.138879776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5732221603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.262978553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1699047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9527320861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5649271011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7582883834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5566301345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8585777282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7810163497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3156490325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8197975158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1300430297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7893133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2546815872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9056558609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6341915130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0219974517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0607786178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8280944824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4790687561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7117519378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6729717254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5954103469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2851657867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4015073776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7505321502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9749193191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5095529556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5871143341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6646757125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2463846206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2159004211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.371021270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0773706436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1181745529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0365676879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8733520507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8325471878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.199782371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6078224182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2813901901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4245090484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5469188690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5061140060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7509393692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9549589157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5262136459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7710371017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6894311904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3221950531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4038038253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5877237319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.465311050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6285276412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9141540527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2405872344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9957618713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1589775085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7917423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3837032318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2204885482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3429002761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7101345062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0572719573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1388807296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2612915039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0980758666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4860162734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.85325050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7308397293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6900358200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9756631851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7716426849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8526468276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2606859207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.423900604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0767669677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9135513305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5055103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6687269210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5871162414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3014907836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3830966949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3422937393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7503347396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2198820114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1790790557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4647064208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.321590423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1583728790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8112392425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7089252471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1376686096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3824939727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8928451538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1991767883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.484806060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6480178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5664138793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2399806976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4032001495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7296295166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2192764282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4641017913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5457077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9537467956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0353584289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9744510650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8721408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.11696434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1985702514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3617897033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1778678894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8514366149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6882209777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0962600708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6066112518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9330463409424</t>
-  </si>
-  <si>
     <t xml:space="preserve">19.2594757080078</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3410816192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4226913452148</t>
+    <t xml:space="preserve">19.3410835266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4226894378662</t>
   </si>
   <si>
     <t xml:space="preserve">19.0146503448486</t>
   </si>
   <si>
+    <t xml:space="preserve">19.9123401641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8276062011719</t>
+  </si>
+  <si>
     <t xml:space="preserve">19.9123382568359</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8276062011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9123401641846</t>
-  </si>
-  <si>
     <t xml:space="preserve">19.4886741638184</t>
   </si>
   <si>
@@ -2132,22 +2135,22 @@
     <t xml:space="preserve">19.5734062194824</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4039402008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9970741271973</t>
+    <t xml:space="preserve">19.403938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9970722198486</t>
   </si>
   <si>
     <t xml:space="preserve">20.3360061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">20.166540145874</t>
+    <t xml:space="preserve">20.1665382385254</t>
   </si>
   <si>
     <t xml:space="preserve">19.319206237793</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0650081634521</t>
+    <t xml:space="preserve">19.0650062561035</t>
   </si>
   <si>
     <t xml:space="preserve">18.6413383483887</t>
@@ -2156,16 +2159,16 @@
     <t xml:space="preserve">19.7428722381592</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0818042755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4207382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5054740905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6749382019043</t>
+    <t xml:space="preserve">20.0818061828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4207401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5054721832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6749401092529</t>
   </si>
   <si>
     <t xml:space="preserve">20.9291400909424</t>
@@ -2174,7 +2177,7 @@
     <t xml:space="preserve">21.1833400726318</t>
   </si>
   <si>
-    <t xml:space="preserve">20.759672164917</t>
+    <t xml:space="preserve">20.7596740722656</t>
   </si>
   <si>
     <t xml:space="preserve">21.4375381469727</t>
@@ -2183,31 +2186,31 @@
     <t xml:space="preserve">22.7085399627686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0306720733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4543399810791</t>
+    <t xml:space="preserve">22.0306739807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4543418884277</t>
   </si>
   <si>
     <t xml:space="preserve">22.2001419067383</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6238079071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7932739257812</t>
+    <t xml:space="preserve">22.6238098144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7932720184326</t>
   </si>
   <si>
     <t xml:space="preserve">23.0474739074707</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6406078338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.555871963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3016738891602</t>
+    <t xml:space="preserve">23.6406059265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5558738708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3016719818115</t>
   </si>
   <si>
     <t xml:space="preserve">23.4711418151855</t>
@@ -2216,16 +2219,16 @@
     <t xml:space="preserve">23.3864078521729</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7253398895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1322078704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2169380187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9459400177002</t>
+    <t xml:space="preserve">23.725341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1322059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2169399261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9459381103516</t>
   </si>
   <si>
     <t xml:space="preserve">22.8780059814453</t>
@@ -2234,37 +2237,37 @@
     <t xml:space="preserve">24.1490058898926</t>
   </si>
   <si>
-    <t xml:space="preserve">25.165807723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9116077423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2337398529053</t>
+    <t xml:space="preserve">25.1658096313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9116058349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2337417602539</t>
   </si>
   <si>
     <t xml:space="preserve">25.2505397796631</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8100757598877</t>
+    <t xml:space="preserve">23.8100738525391</t>
   </si>
   <si>
     <t xml:space="preserve">24.5726737976074</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4032077789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4879398345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0810775756836</t>
+    <t xml:space="preserve">24.403205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4879417419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0810737609863</t>
   </si>
   <si>
     <t xml:space="preserve">25.5047416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3352756500244</t>
+    <t xml:space="preserve">25.3352737426758</t>
   </si>
   <si>
     <t xml:space="preserve">25.4200077056885</t>
@@ -2273,13 +2276,13 @@
     <t xml:space="preserve">25.7589416503906</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2673416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4368095397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5215396881104</t>
+    <t xml:space="preserve">26.2673397064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4368076324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.521541595459</t>
   </si>
   <si>
     <t xml:space="preserve">27.8772773742676</t>
@@ -2288,43 +2291,43 @@
     <t xml:space="preserve">29.5719432830811</t>
   </si>
   <si>
-    <t xml:space="preserve">29.317741394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9788093566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1482772827148</t>
+    <t xml:space="preserve">29.3177394866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9788112640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1482753753662</t>
   </si>
   <si>
     <t xml:space="preserve">29.2330093383789</t>
   </si>
   <si>
-    <t xml:space="preserve">27.962007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0299396514893</t>
+    <t xml:space="preserve">27.9620094299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0299415588379</t>
   </si>
   <si>
     <t xml:space="preserve">28.4704074859619</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4536113739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3856735229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7078094482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1314754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.284143447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6742057800293</t>
+    <t xml:space="preserve">27.4536094665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3856754302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7078075408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.131477355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2841396331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6742076873779</t>
   </si>
   <si>
     <t xml:space="preserve">26.0131416320801</t>
@@ -2339,19 +2342,19 @@
     <t xml:space="preserve">26.6062755584717</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8268718719482</t>
+    <t xml:space="preserve">24.8268737792969</t>
   </si>
   <si>
     <t xml:space="preserve">26.1826076507568</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0978736877441</t>
+    <t xml:space="preserve">26.0978755950928</t>
   </si>
   <si>
     <t xml:space="preserve">25.9284076690674</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6910057067871</t>
+    <t xml:space="preserve">26.6910076141357</t>
   </si>
   <si>
     <t xml:space="preserve">22.5390739440918</t>
@@ -2363,10 +2366,10 @@
     <t xml:space="preserve">22.9627418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3184757232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8948059082031</t>
+    <t xml:space="preserve">24.318473815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8948078155518</t>
   </si>
   <si>
     <t xml:space="preserve">23.9795398712158</t>
@@ -2381,9 +2384,6 @@
     <t xml:space="preserve">23.2608528137207</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2337379455566</t>
-  </si>
-  <si>
     <t xml:space="preserve">23.9684085845947</t>
   </si>
   <si>
@@ -2405,37 +2405,37 @@
     <t xml:space="preserve">24.8528518676758</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2950706481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2066268920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5875148773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3221855163574</t>
+    <t xml:space="preserve">25.295072555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2066287994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.587516784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3221836090088</t>
   </si>
   <si>
     <t xml:space="preserve">23.3492965698242</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2879657745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4648551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8457450866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7573013305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4035243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6688537597656</t>
+    <t xml:space="preserve">22.2879676818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4648532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8457469940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7572994232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4035224914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6688556671143</t>
   </si>
   <si>
     <t xml:space="preserve">21.226634979248</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">21.9341869354248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5804100036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1381893157959</t>
+    <t xml:space="preserve">21.5804119110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1381874084473</t>
   </si>
   <si>
     <t xml:space="preserve">22.1110782623291</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">25.1181831359863</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6759624481201</t>
+    <t xml:space="preserve">24.6759605407715</t>
   </si>
   <si>
     <t xml:space="preserve">22.9955196380615</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">23.614631652832</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6417427062988</t>
+    <t xml:space="preserve">22.6417446136475</t>
   </si>
   <si>
     <t xml:space="preserve">23.0839653015137</t>
@@ -2486,13 +2486,13 @@
     <t xml:space="preserve">23.1724109649658</t>
   </si>
   <si>
-    <t xml:space="preserve">22.376407623291</t>
+    <t xml:space="preserve">22.3764095306396</t>
   </si>
   <si>
     <t xml:space="preserve">22.1995220184326</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0226306915283</t>
+    <t xml:space="preserve">22.022632598877</t>
   </si>
   <si>
     <t xml:space="preserve">21.0497455596924</t>
@@ -2504,10 +2504,10 @@
     <t xml:space="preserve">20.6959686279297</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3150768280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7644062042236</t>
+    <t xml:space="preserve">21.3150806427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7644081115723</t>
   </si>
   <si>
     <t xml:space="preserve">25.7372951507568</t>
@@ -2516,13 +2516,13 @@
     <t xml:space="preserve">25.0297393798828</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9412937164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5604038238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4719619750977</t>
+    <t xml:space="preserve">24.9412956237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5604057312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.471960067749</t>
   </si>
   <si>
     <t xml:space="preserve">25.6488494873047</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">27.0639591217041</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2408466339111</t>
+    <t xml:space="preserve">27.2408447265625</t>
   </si>
   <si>
     <t xml:space="preserve">27.1524028778076</t>
@@ -2546,13 +2546,13 @@
     <t xml:space="preserve">27.5946254730225</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3292903900146</t>
+    <t xml:space="preserve">27.3292922973633</t>
   </si>
   <si>
     <t xml:space="preserve">26.7101821899414</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7986240386963</t>
+    <t xml:space="preserve">26.7986259460449</t>
   </si>
   <si>
     <t xml:space="preserve">26.8870697021484</t>
@@ -2570,19 +2570,19 @@
     <t xml:space="preserve">26.0910720825195</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4448490142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3564033508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.825740814209</t>
+    <t xml:space="preserve">26.4448471069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3564052581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8257389068604</t>
   </si>
   <si>
     <t xml:space="preserve">26.0026264190674</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1795177459717</t>
+    <t xml:space="preserve">26.179515838623</t>
   </si>
   <si>
     <t xml:space="preserve">26.6217365264893</t>
@@ -2591,22 +2591,22 @@
     <t xml:space="preserve">26.2679595947266</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8599548339844</t>
+    <t xml:space="preserve">27.859956741333</t>
   </si>
   <si>
     <t xml:space="preserve">28.7855377197266</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1557674407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3227481842041</t>
+    <t xml:space="preserve">29.1557693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3227462768555</t>
   </si>
   <si>
     <t xml:space="preserve">27.7673988342285</t>
   </si>
   <si>
-    <t xml:space="preserve">27.859956741333</t>
+    <t xml:space="preserve">27.8599586486816</t>
   </si>
   <si>
     <t xml:space="preserve">29.5259990692139</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">30.3590221405029</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8036766052246</t>
+    <t xml:space="preserve">29.803674697876</t>
   </si>
   <si>
     <t xml:space="preserve">29.3408851623535</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">28.8780956268311</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1739063262939</t>
+    <t xml:space="preserve">30.1739044189453</t>
   </si>
   <si>
     <t xml:space="preserve">29.06321144104</t>
@@ -2660,25 +2660,25 @@
     <t xml:space="preserve">27.2120513916016</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3971691131592</t>
+    <t xml:space="preserve">27.3971672058105</t>
   </si>
   <si>
     <t xml:space="preserve">27.489725112915</t>
   </si>
   <si>
-    <t xml:space="preserve">27.674840927124</t>
+    <t xml:space="preserve">27.6748390197754</t>
   </si>
   <si>
     <t xml:space="preserve">28.6004199981689</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6929798126221</t>
+    <t xml:space="preserve">28.6929779052734</t>
   </si>
   <si>
     <t xml:space="preserve">29.7111167907715</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5441379547119</t>
+    <t xml:space="preserve">30.5441398620605</t>
   </si>
   <si>
     <t xml:space="preserve">29.9887924194336</t>
@@ -2687,31 +2687,31 @@
     <t xml:space="preserve">30.2664661407471</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4515838623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0994873046875</t>
+    <t xml:space="preserve">30.4515819549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0994834899902</t>
   </si>
   <si>
     <t xml:space="preserve">30.6366958618164</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9143714904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7292556762695</t>
+    <t xml:space="preserve">30.9143733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7292537689209</t>
   </si>
   <si>
     <t xml:space="preserve">30.821813583374</t>
   </si>
   <si>
-    <t xml:space="preserve">31.192045211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0069274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5622749328613</t>
+    <t xml:space="preserve">31.1920471191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.006929397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.56227684021</t>
   </si>
   <si>
     <t xml:space="preserve">32.6729736328125</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">32.1176223754883</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9325084686279</t>
+    <t xml:space="preserve">31.9325103759766</t>
   </si>
   <si>
     <t xml:space="preserve">30.0813503265381</t>
@@ -2759,10 +2759,10 @@
     <t xml:space="preserve">33.0432052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3208808898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5059928894043</t>
+    <t xml:space="preserve">33.3208770751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5059967041016</t>
   </si>
   <si>
     <t xml:space="preserve">33.6911125183105</t>
@@ -2777,25 +2777,25 @@
     <t xml:space="preserve">34.1539001464844</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7092514038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9687881469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8762245178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4134368896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2464561462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8943634033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5241317749023</t>
+    <t xml:space="preserve">34.7092475891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9687843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8762283325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4134330749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2464599609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8943672180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5241355895996</t>
   </si>
   <si>
     <t xml:space="preserve">34.4315757751465</t>
@@ -2810,28 +2810,28 @@
     <t xml:space="preserve">34.3390159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1720390319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5422706604004</t>
+    <t xml:space="preserve">35.1720352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5422744750977</t>
   </si>
   <si>
     <t xml:space="preserve">35.0794830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9869194030762</t>
+    <t xml:space="preserve">34.9869232177734</t>
   </si>
   <si>
     <t xml:space="preserve">35.3571548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8199462890625</t>
+    <t xml:space="preserve">35.8199424743652</t>
   </si>
   <si>
     <t xml:space="preserve">35.7273864746094</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9306411743164</t>
+    <t xml:space="preserve">36.9306449890137</t>
   </si>
   <si>
     <t xml:space="preserve">37.7636604309082</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">38.8743591308594</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5966835021973</t>
+    <t xml:space="preserve">38.5966873168945</t>
   </si>
   <si>
     <t xml:space="preserve">38.6892433166504</t>
@@ -2873,13 +2873,13 @@
     <t xml:space="preserve">39.0594749450684</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2445907592773</t>
+    <t xml:space="preserve">39.2445945739746</t>
   </si>
   <si>
     <t xml:space="preserve">38.0413360595703</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8380851745605</t>
+    <t xml:space="preserve">36.8380813598633</t>
   </si>
   <si>
     <t xml:space="preserve">37.8562202453613</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">41.3734245300293</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0957489013672</t>
+    <t xml:space="preserve">41.0957527160645</t>
   </si>
   <si>
     <t xml:space="preserve">41.0031929016113</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">40.9106369018555</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8180770874023</t>
+    <t xml:space="preserve">40.8180732727051</t>
   </si>
   <si>
     <t xml:space="preserve">40.2164497375488</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">40.5866813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6792411804199</t>
+    <t xml:space="preserve">40.6792373657227</t>
   </si>
   <si>
     <t xml:space="preserve">39.7999382019043</t>
@@ -2945,10 +2945,10 @@
     <t xml:space="preserve">40.6329612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0776138305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5222663879395</t>
+    <t xml:space="preserve">40.0776100158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5222625732422</t>
   </si>
   <si>
     <t xml:space="preserve">40.4478454589844</t>
@@ -3624,6 +3624,9 @@
   </si>
   <si>
     <t xml:space="preserve">66.3000030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.9000015258789</t>
   </si>
 </sst>
 </file>
@@ -29434,7 +29437,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G980" t="s">
-        <v>538</v>
+        <v>487</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -29460,7 +29463,7 @@
         <v>23</v>
       </c>
       <c r="G981" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -29486,7 +29489,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G982" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -29512,7 +29515,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G983" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -29538,7 +29541,7 @@
         <v>24</v>
       </c>
       <c r="G984" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -29590,7 +29593,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G986" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -29616,7 +29619,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G987" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29642,7 +29645,7 @@
         <v>24</v>
       </c>
       <c r="G988" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29668,7 +29671,7 @@
         <v>24</v>
       </c>
       <c r="G989" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29694,7 +29697,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G990" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29720,7 +29723,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G991" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29746,7 +29749,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G992" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29772,7 +29775,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G993" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29798,7 +29801,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G994" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29824,7 +29827,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G995" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29850,7 +29853,7 @@
         <v>24.5</v>
       </c>
       <c r="G996" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29876,7 +29879,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G997" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29902,7 +29905,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G998" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29928,7 +29931,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G999" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29954,7 +29957,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1000" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29980,7 +29983,7 @@
         <v>23.25</v>
       </c>
       <c r="G1001" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -30006,7 +30009,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1002" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -30032,7 +30035,7 @@
         <v>23.5</v>
       </c>
       <c r="G1003" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -30084,7 +30087,7 @@
         <v>23.75</v>
       </c>
       <c r="G1005" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -30110,7 +30113,7 @@
         <v>23.75</v>
       </c>
       <c r="G1006" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -30136,7 +30139,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1007" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -30162,7 +30165,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1008" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -30188,7 +30191,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1009" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -30214,7 +30217,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1010" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -30240,7 +30243,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1011" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -30292,7 +30295,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1013" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -30318,7 +30321,7 @@
         <v>24.25</v>
       </c>
       <c r="G1014" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -30344,7 +30347,7 @@
         <v>24</v>
       </c>
       <c r="G1015" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -30370,7 +30373,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1016" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -30396,7 +30399,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1017" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -30422,7 +30425,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1018" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -30448,7 +30451,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1019" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -30474,7 +30477,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1020" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -30500,7 +30503,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1021" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -30526,7 +30529,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G1022" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -30552,7 +30555,7 @@
         <v>23.5</v>
       </c>
       <c r="G1023" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -30578,7 +30581,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1024" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -30604,7 +30607,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1025" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -30630,7 +30633,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1026" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -30656,7 +30659,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1027" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -30682,7 +30685,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1028" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30708,7 +30711,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1029" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30734,7 +30737,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1030" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30760,7 +30763,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1031" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30786,7 +30789,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1032" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30812,7 +30815,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1033" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -30838,7 +30841,7 @@
         <v>22.75</v>
       </c>
       <c r="G1034" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -30864,7 +30867,7 @@
         <v>23.25</v>
       </c>
       <c r="G1035" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -30890,7 +30893,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1036" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -30916,7 +30919,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1037" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -30942,7 +30945,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1038" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -30968,7 +30971,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1039" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30994,7 +30997,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1040" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -31020,7 +31023,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1041" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -31046,7 +31049,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1042" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -31072,7 +31075,7 @@
         <v>23.75</v>
       </c>
       <c r="G1043" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -31098,7 +31101,7 @@
         <v>23.75</v>
       </c>
       <c r="G1044" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -31124,7 +31127,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1045" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -31150,7 +31153,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1046" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -31176,7 +31179,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1047" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -31202,7 +31205,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1048" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -31228,7 +31231,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1049" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -31254,7 +31257,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1050" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -31280,7 +31283,7 @@
         <v>23.25</v>
       </c>
       <c r="G1051" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -31306,7 +31309,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1052" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -31358,7 +31361,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1054" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -31384,7 +31387,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1055" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -31410,7 +31413,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1056" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -31436,7 +31439,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -31618,7 +31621,7 @@
         <v>19.5</v>
       </c>
       <c r="G1064" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -31644,7 +31647,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1065" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31670,7 +31673,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1066" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31696,7 +31699,7 @@
         <v>18</v>
       </c>
       <c r="G1067" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31722,7 +31725,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1068" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31748,7 +31751,7 @@
         <v>17</v>
       </c>
       <c r="G1069" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -31774,7 +31777,7 @@
         <v>17</v>
       </c>
       <c r="G1070" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -31800,7 +31803,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1071" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31826,7 +31829,7 @@
         <v>17.5</v>
       </c>
       <c r="G1072" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31852,7 +31855,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1073" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -31878,7 +31881,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1074" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -31904,7 +31907,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1075" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31930,7 +31933,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1076" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31956,7 +31959,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1077" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31982,7 +31985,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1078" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -32008,7 +32011,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1079" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -32034,7 +32037,7 @@
         <v>14</v>
       </c>
       <c r="G1080" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -32060,7 +32063,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1081" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -32086,7 +32089,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1082" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -32112,7 +32115,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1083" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -32138,7 +32141,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1084" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -32164,7 +32167,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1085" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32190,7 +32193,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1086" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -32216,7 +32219,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1087" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -32242,7 +32245,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1088" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -32268,7 +32271,7 @@
         <v>15</v>
       </c>
       <c r="G1089" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -32294,7 +32297,7 @@
         <v>15.5</v>
       </c>
       <c r="G1090" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -32320,7 +32323,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1091" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -32346,7 +32349,7 @@
         <v>15.25</v>
       </c>
       <c r="G1092" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -32372,7 +32375,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1093" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -32398,7 +32401,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1094" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -32424,7 +32427,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1095" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -32450,7 +32453,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1096" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -32476,7 +32479,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1097" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -32502,7 +32505,7 @@
         <v>15</v>
       </c>
       <c r="G1098" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -32528,7 +32531,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1099" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -32554,7 +32557,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1100" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -32580,7 +32583,7 @@
         <v>15</v>
       </c>
       <c r="G1101" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -32606,7 +32609,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1102" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -32632,7 +32635,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1103" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -32658,7 +32661,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1104" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32684,7 +32687,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1105" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -32710,7 +32713,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1106" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32736,7 +32739,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1107" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32762,7 +32765,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1108" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32788,7 +32791,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1109" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32814,7 +32817,7 @@
         <v>13.75</v>
       </c>
       <c r="G1110" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32840,7 +32843,7 @@
         <v>14</v>
       </c>
       <c r="G1111" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32866,7 +32869,7 @@
         <v>14</v>
       </c>
       <c r="G1112" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32892,7 +32895,7 @@
         <v>14.5</v>
       </c>
       <c r="G1113" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32918,7 +32921,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1114" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -32944,7 +32947,7 @@
         <v>15</v>
       </c>
       <c r="G1115" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -32970,7 +32973,7 @@
         <v>15.75</v>
       </c>
       <c r="G1116" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -32996,7 +32999,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1117" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -33022,7 +33025,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1118" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -33048,7 +33051,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1119" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -33074,7 +33077,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1120" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -33100,7 +33103,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1121" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -33126,7 +33129,7 @@
         <v>17</v>
       </c>
       <c r="G1122" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -33152,7 +33155,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1123" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -33178,7 +33181,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1124" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -33204,7 +33207,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1125" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -33230,7 +33233,7 @@
         <v>17.5</v>
       </c>
       <c r="G1126" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -33256,7 +33259,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1127" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -33282,7 +33285,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1128" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -33308,7 +33311,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1129" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -33334,7 +33337,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1130" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -33360,7 +33363,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1131" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -33386,7 +33389,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1132" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -33412,7 +33415,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1133" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -33438,7 +33441,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1134" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -33464,7 +33467,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1135" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -33490,7 +33493,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1136" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -33516,7 +33519,7 @@
         <v>18</v>
       </c>
       <c r="G1137" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -33542,7 +33545,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1138" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -33568,7 +33571,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1139" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -33594,7 +33597,7 @@
         <v>17.5</v>
       </c>
       <c r="G1140" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -33620,7 +33623,7 @@
         <v>17</v>
       </c>
       <c r="G1141" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33646,7 +33649,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1142" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33672,7 +33675,7 @@
         <v>16.5</v>
       </c>
       <c r="G1143" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33698,7 +33701,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1144" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33724,7 +33727,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1145" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33750,7 +33753,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1146" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33776,7 +33779,7 @@
         <v>17.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33802,7 +33805,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1148" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33828,7 +33831,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1149" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33854,7 +33857,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1150" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33880,7 +33883,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1151" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33906,7 +33909,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1152" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33932,7 +33935,7 @@
         <v>17.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33958,7 +33961,7 @@
         <v>17</v>
       </c>
       <c r="G1154" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33984,7 +33987,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1155" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -34010,7 +34013,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1156" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -34036,7 +34039,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1157" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -34062,7 +34065,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1158" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -34088,7 +34091,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1159" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -34114,7 +34117,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1160" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -34140,7 +34143,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1161" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -34166,7 +34169,7 @@
         <v>16.5</v>
       </c>
       <c r="G1162" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -34192,7 +34195,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1163" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -34218,7 +34221,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1164" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -34244,7 +34247,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1165" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -34270,7 +34273,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1166" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -34296,7 +34299,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1167" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -34322,7 +34325,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1168" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -34348,7 +34351,7 @@
         <v>17.25</v>
       </c>
       <c r="G1169" t="s">
-        <v>611</v>
+        <v>638</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34374,7 +34377,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1170" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -34400,7 +34403,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1171" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -34426,7 +34429,7 @@
         <v>17</v>
       </c>
       <c r="G1172" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -34452,7 +34455,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1173" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -34478,7 +34481,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1174" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -34504,7 +34507,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1175" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -34530,7 +34533,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -34556,7 +34559,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1177" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34608,7 +34611,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1179" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34634,7 +34637,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1180" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34660,7 +34663,7 @@
         <v>17</v>
       </c>
       <c r="G1181" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34686,7 +34689,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1182" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34712,7 +34715,7 @@
         <v>17</v>
       </c>
       <c r="G1183" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34738,7 +34741,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1184" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34764,7 +34767,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1185" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34816,7 +34819,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1187" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34842,7 +34845,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1188" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34868,7 +34871,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1189" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34894,7 +34897,7 @@
         <v>17.25</v>
       </c>
       <c r="G1190" t="s">
-        <v>611</v>
+        <v>638</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34920,7 +34923,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1191" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34946,7 +34949,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1192" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -34972,7 +34975,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1193" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -34998,7 +35001,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1194" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -35024,7 +35027,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1195" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -35050,7 +35053,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1196" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -35128,7 +35131,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1199" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35180,7 +35183,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1201" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -35206,7 +35209,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1202" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -35232,7 +35235,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1203" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -35284,7 +35287,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1205" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -35414,7 +35417,7 @@
         <v>16.5</v>
       </c>
       <c r="G1210" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -35440,7 +35443,7 @@
         <v>16.5</v>
       </c>
       <c r="G1211" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -35466,7 +35469,7 @@
         <v>17.25</v>
       </c>
       <c r="G1212" t="s">
-        <v>611</v>
+        <v>638</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -35492,7 +35495,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1213" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -35518,7 +35521,7 @@
         <v>17</v>
       </c>
       <c r="G1214" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -35544,7 +35547,7 @@
         <v>17.25</v>
       </c>
       <c r="G1215" t="s">
-        <v>611</v>
+        <v>638</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35570,7 +35573,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1216" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35596,7 +35599,7 @@
         <v>17</v>
       </c>
       <c r="G1217" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -35622,7 +35625,7 @@
         <v>17</v>
       </c>
       <c r="G1218" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35648,7 +35651,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1219" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35674,7 +35677,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1220" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35700,7 +35703,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1221" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35726,7 +35729,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1222" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -36012,7 +36015,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -36090,7 +36093,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1236" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -36116,7 +36119,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1237" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -38482,7 +38485,7 @@
         <v>23</v>
       </c>
       <c r="G1328" t="s">
-        <v>548</v>
+        <v>696</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -38820,7 +38823,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1341" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -38846,7 +38849,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1342" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -38872,7 +38875,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1343" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -38898,7 +38901,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1344" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -38950,7 +38953,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1346" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -38976,7 +38979,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1347" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -39002,7 +39005,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1348" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -39054,7 +39057,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1350" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -39080,7 +39083,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1351" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -39106,7 +39109,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1352" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -39132,7 +39135,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1353" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -39184,7 +39187,7 @@
         <v>23</v>
       </c>
       <c r="G1355" t="s">
-        <v>548</v>
+        <v>696</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39210,7 +39213,7 @@
         <v>23</v>
       </c>
       <c r="G1356" t="s">
-        <v>548</v>
+        <v>696</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -39236,7 +39239,7 @@
         <v>23</v>
       </c>
       <c r="G1357" t="s">
-        <v>548</v>
+        <v>696</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39262,7 +39265,7 @@
         <v>23</v>
       </c>
       <c r="G1358" t="s">
-        <v>548</v>
+        <v>696</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39288,7 +39291,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -39314,7 +39317,7 @@
         <v>23</v>
       </c>
       <c r="G1360" t="s">
-        <v>548</v>
+        <v>696</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -39340,7 +39343,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1361" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -39366,7 +39369,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1362" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -39392,7 +39395,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -39418,7 +39421,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -39444,7 +39447,7 @@
         <v>23.5</v>
       </c>
       <c r="G1365" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -39470,7 +39473,7 @@
         <v>23</v>
       </c>
       <c r="G1366" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -39496,7 +39499,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1367" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -39522,7 +39525,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1368" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -39548,7 +39551,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1369" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -39574,7 +39577,7 @@
         <v>23.5</v>
       </c>
       <c r="G1370" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -39600,7 +39603,7 @@
         <v>23.5</v>
       </c>
       <c r="G1371" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -39626,7 +39629,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1372" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -39652,7 +39655,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1373" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -39678,7 +39681,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1374" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -39704,7 +39707,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1375" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -39730,7 +39733,7 @@
         <v>23.5</v>
       </c>
       <c r="G1376" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -39756,7 +39759,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1377" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -39782,7 +39785,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1378" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -39808,7 +39811,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1379" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -39834,7 +39837,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1380" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -39860,7 +39863,7 @@
         <v>23.5</v>
       </c>
       <c r="G1381" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -39886,7 +39889,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1382" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -39912,7 +39915,7 @@
         <v>23.5</v>
       </c>
       <c r="G1383" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -39938,7 +39941,7 @@
         <v>23.5</v>
       </c>
       <c r="G1384" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -39964,7 +39967,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1385" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -39990,7 +39993,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -40016,7 +40019,7 @@
         <v>24</v>
       </c>
       <c r="G1387" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -40042,7 +40045,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1388" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -40068,7 +40071,7 @@
         <v>23.5</v>
       </c>
       <c r="G1389" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -40094,7 +40097,7 @@
         <v>23.5</v>
       </c>
       <c r="G1390" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40120,7 +40123,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1391" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -40146,7 +40149,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1392" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -40172,7 +40175,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1393" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -40198,7 +40201,7 @@
         <v>23.5</v>
       </c>
       <c r="G1394" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -40224,7 +40227,7 @@
         <v>23.5</v>
       </c>
       <c r="G1395" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -40250,7 +40253,7 @@
         <v>23</v>
       </c>
       <c r="G1396" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -40276,7 +40279,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1397" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -40302,7 +40305,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1398" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -40328,7 +40331,7 @@
         <v>23</v>
       </c>
       <c r="G1399" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -40354,7 +40357,7 @@
         <v>23</v>
       </c>
       <c r="G1400" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -40380,7 +40383,7 @@
         <v>23</v>
       </c>
       <c r="G1401" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -40406,7 +40409,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1402" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -40432,7 +40435,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1403" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -40458,7 +40461,7 @@
         <v>23</v>
       </c>
       <c r="G1404" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -40484,7 +40487,7 @@
         <v>23</v>
       </c>
       <c r="G1405" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -40510,7 +40513,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1406" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -40536,7 +40539,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1407" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -40562,7 +40565,7 @@
         <v>22.5</v>
       </c>
       <c r="G1408" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -40588,7 +40591,7 @@
         <v>22</v>
       </c>
       <c r="G1409" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -40614,7 +40617,7 @@
         <v>22.5</v>
       </c>
       <c r="G1410" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -40640,7 +40643,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1411" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -40666,7 +40669,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1412" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -40692,7 +40695,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1413" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -40718,7 +40721,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1414" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -40744,7 +40747,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1415" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -40770,7 +40773,7 @@
         <v>23.5</v>
       </c>
       <c r="G1416" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -40796,7 +40799,7 @@
         <v>23.5</v>
       </c>
       <c r="G1417" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -40822,7 +40825,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1418" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -40848,7 +40851,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -40874,7 +40877,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1420" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -40900,7 +40903,7 @@
         <v>24</v>
       </c>
       <c r="G1421" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -40926,7 +40929,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1422" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -40952,7 +40955,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1423" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -40978,7 +40981,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1424" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -41004,7 +41007,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1425" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -41030,7 +41033,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1426" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -41056,7 +41059,7 @@
         <v>25</v>
       </c>
       <c r="G1427" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -41082,7 +41085,7 @@
         <v>25</v>
       </c>
       <c r="G1428" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -41108,7 +41111,7 @@
         <v>25</v>
       </c>
       <c r="G1429" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -41134,7 +41137,7 @@
         <v>24.5</v>
       </c>
       <c r="G1430" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -41160,7 +41163,7 @@
         <v>24.5</v>
       </c>
       <c r="G1431" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -41186,7 +41189,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1432" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -41212,7 +41215,7 @@
         <v>24.5</v>
       </c>
       <c r="G1433" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -41238,7 +41241,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1434" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -41264,7 +41267,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1435" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -41290,7 +41293,7 @@
         <v>26</v>
       </c>
       <c r="G1436" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -41316,7 +41319,7 @@
         <v>26.5</v>
       </c>
       <c r="G1437" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -41342,7 +41345,7 @@
         <v>26</v>
       </c>
       <c r="G1438" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -41368,7 +41371,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1439" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -41394,7 +41397,7 @@
         <v>26</v>
       </c>
       <c r="G1440" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -41420,7 +41423,7 @@
         <v>26.5</v>
       </c>
       <c r="G1441" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -41446,7 +41449,7 @@
         <v>26.5</v>
       </c>
       <c r="G1442" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -41472,7 +41475,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1443" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -41498,7 +41501,7 @@
         <v>26.5</v>
       </c>
       <c r="G1444" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -41524,7 +41527,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1445" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -41550,7 +41553,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1446" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -41576,7 +41579,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1447" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -41602,7 +41605,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1448" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -41628,7 +41631,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1449" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -41654,7 +41657,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1450" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -41680,7 +41683,7 @@
         <v>27.5</v>
       </c>
       <c r="G1451" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -41706,7 +41709,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1452" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -41732,7 +41735,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -41758,7 +41761,7 @@
         <v>27.5</v>
       </c>
       <c r="G1454" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -41784,7 +41787,7 @@
         <v>27.5</v>
       </c>
       <c r="G1455" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -41810,7 +41813,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1456" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -41836,7 +41839,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1457" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -41862,7 +41865,7 @@
         <v>28</v>
       </c>
       <c r="G1458" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -41888,7 +41891,7 @@
         <v>28</v>
       </c>
       <c r="G1459" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -41914,7 +41917,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -41940,7 +41943,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1461" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -41966,7 +41969,7 @@
         <v>27.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -41992,7 +41995,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1463" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -42018,7 +42021,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1464" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -42044,7 +42047,7 @@
         <v>26.5</v>
       </c>
       <c r="G1465" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -42070,7 +42073,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1466" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -42096,7 +42099,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1467" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -42122,7 +42125,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1468" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -42148,7 +42151,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1469" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -42174,7 +42177,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1470" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -42200,7 +42203,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1471" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -42226,7 +42229,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1472" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -42252,7 +42255,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1473" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -42278,7 +42281,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1474" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -42304,7 +42307,7 @@
         <v>27.5</v>
       </c>
       <c r="G1475" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -42330,7 +42333,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1476" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -42356,7 +42359,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1477" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -42382,7 +42385,7 @@
         <v>27.5</v>
       </c>
       <c r="G1478" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -42408,7 +42411,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1479" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -42434,7 +42437,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1480" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -42460,7 +42463,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1481" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -42486,7 +42489,7 @@
         <v>27</v>
       </c>
       <c r="G1482" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -42512,7 +42515,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1483" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -42538,7 +42541,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1484" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -42564,7 +42567,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1485" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -42590,7 +42593,7 @@
         <v>27.5</v>
       </c>
       <c r="G1486" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -42616,7 +42619,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1487" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -42642,7 +42645,7 @@
         <v>27.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -42668,7 +42671,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1489" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -42694,7 +42697,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1490" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -42720,7 +42723,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1491" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -42746,7 +42749,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -42772,7 +42775,7 @@
         <v>28</v>
       </c>
       <c r="G1493" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -42798,7 +42801,7 @@
         <v>28</v>
       </c>
       <c r="G1494" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -42824,7 +42827,7 @@
         <v>28.5</v>
       </c>
       <c r="G1495" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -42850,7 +42853,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1496" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -42876,7 +42879,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1497" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -42902,7 +42905,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1498" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -42928,7 +42931,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1499" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -42954,7 +42957,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1500" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -42980,7 +42983,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1501" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -43006,7 +43009,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1502" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -43032,7 +43035,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1503" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -43058,7 +43061,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1504" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -43084,7 +43087,7 @@
         <v>29</v>
       </c>
       <c r="G1505" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -43110,7 +43113,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1506" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -43136,7 +43139,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1507" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43162,7 +43165,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1508" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43188,7 +43191,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1509" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -43214,7 +43217,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1510" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -43240,7 +43243,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1511" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -43266,7 +43269,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1512" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -43292,7 +43295,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1513" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43318,7 +43321,7 @@
         <v>30</v>
       </c>
       <c r="G1514" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -43344,7 +43347,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1515" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -43370,7 +43373,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1516" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -43396,7 +43399,7 @@
         <v>30</v>
       </c>
       <c r="G1517" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -43422,7 +43425,7 @@
         <v>31</v>
       </c>
       <c r="G1518" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -43448,7 +43451,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1519" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43474,7 +43477,7 @@
         <v>31</v>
       </c>
       <c r="G1520" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -43500,7 +43503,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1521" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -43526,7 +43529,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1522" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -43552,7 +43555,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1523" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -43578,7 +43581,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1524" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -43604,7 +43607,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1525" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43630,7 +43633,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1526" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -43656,7 +43659,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1527" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43682,7 +43685,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1528" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -43708,7 +43711,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1529" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -43734,7 +43737,7 @@
         <v>34.5</v>
       </c>
       <c r="G1530" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -43760,7 +43763,7 @@
         <v>33</v>
       </c>
       <c r="G1531" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -43786,7 +43789,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1532" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -43812,7 +43815,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1533" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -43838,7 +43841,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1534" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -43864,7 +43867,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1535" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -43890,7 +43893,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1536" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -43916,7 +43919,7 @@
         <v>33.5</v>
       </c>
       <c r="G1537" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -43942,7 +43945,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1538" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -43968,7 +43971,7 @@
         <v>33</v>
       </c>
       <c r="G1539" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -43994,7 +43997,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1540" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -44020,7 +44023,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1541" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -44046,7 +44049,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1542" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -44072,7 +44075,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1543" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -44098,7 +44101,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1544" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44124,7 +44127,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1545" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44150,7 +44153,7 @@
         <v>30.5</v>
       </c>
       <c r="G1546" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44176,7 +44179,7 @@
         <v>30.5</v>
       </c>
       <c r="G1547" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -44202,7 +44205,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1548" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -44228,7 +44231,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1549" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -44254,7 +44257,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1550" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -44280,7 +44283,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1551" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -44306,7 +44309,7 @@
         <v>30.5</v>
       </c>
       <c r="G1552" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -44332,7 +44335,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1553" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -44358,7 +44361,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1554" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -44384,7 +44387,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1555" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -44410,7 +44413,7 @@
         <v>30</v>
       </c>
       <c r="G1556" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44436,7 +44439,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1557" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -44462,7 +44465,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1558" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -44488,7 +44491,7 @@
         <v>31</v>
       </c>
       <c r="G1559" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -44514,7 +44517,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1560" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -44540,7 +44543,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1561" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -44566,7 +44569,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1562" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -44592,7 +44595,7 @@
         <v>30.5</v>
       </c>
       <c r="G1563" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -44618,7 +44621,7 @@
         <v>31.5</v>
       </c>
       <c r="G1564" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44644,7 +44647,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1565" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -44670,7 +44673,7 @@
         <v>30.5</v>
       </c>
       <c r="G1566" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -44696,7 +44699,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1567" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -44722,7 +44725,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1568" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44748,7 +44751,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1569" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -44774,7 +44777,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1570" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -44800,7 +44803,7 @@
         <v>27</v>
       </c>
       <c r="G1571" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -44826,7 +44829,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1572" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -44852,7 +44855,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1573" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -44878,7 +44881,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1574" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -44904,7 +44907,7 @@
         <v>27</v>
       </c>
       <c r="G1575" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -44930,7 +44933,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1576" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -44956,7 +44959,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1577" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -44982,7 +44985,7 @@
         <v>26</v>
       </c>
       <c r="G1578" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -45008,7 +45011,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1579" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -45034,7 +45037,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1580" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -45060,7 +45063,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1581" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -45086,7 +45089,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1582" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -45112,7 +45115,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1583" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45138,7 +45141,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1584" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45164,7 +45167,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1585" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45190,7 +45193,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1586" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -45216,7 +45219,7 @@
         <v>28.5</v>
       </c>
       <c r="G1587" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -45242,7 +45245,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1588" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -45268,7 +45271,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1589" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45294,7 +45297,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1590" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -45320,7 +45323,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1591" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45346,7 +45349,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1592" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -45372,7 +45375,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1593" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -45398,7 +45401,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1594" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -45424,7 +45427,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1595" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45450,7 +45453,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1596" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -45476,7 +45479,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1597" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -45502,7 +45505,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1598" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -45528,7 +45531,7 @@
         <v>27.5</v>
       </c>
       <c r="G1599" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -45554,7 +45557,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1600" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45580,7 +45583,7 @@
         <v>28</v>
       </c>
       <c r="G1601" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45606,7 +45609,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1602" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45632,7 +45635,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1603" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -45658,7 +45661,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1604" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -45684,7 +45687,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1605" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45710,7 +45713,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1606" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45736,7 +45739,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1607" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -45762,7 +45765,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1608" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -45788,7 +45791,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1609" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -45814,7 +45817,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1610" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -45840,7 +45843,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1611" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -45866,7 +45869,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1612" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -45892,7 +45895,7 @@
         <v>28</v>
       </c>
       <c r="G1613" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -45918,7 +45921,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1614" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -45944,7 +45947,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1615" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -45970,7 +45973,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1616" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -45996,7 +45999,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1617" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -46022,7 +46025,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1618" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -46048,7 +46051,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1619" t="s">
-        <v>789</v>
+        <v>743</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -46204,7 +46207,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1625" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46308,7 +46311,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1629" t="s">
-        <v>789</v>
+        <v>743</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -47140,7 +47143,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1661" t="s">
-        <v>789</v>
+        <v>743</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47270,7 +47273,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1666" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47348,7 +47351,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1669" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -47530,7 +47533,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>789</v>
+        <v>743</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -47660,7 +47663,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1681" t="s">
-        <v>789</v>
+        <v>743</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -48128,7 +48131,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1699" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -48206,7 +48209,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1702" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -48232,7 +48235,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1703" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -48310,7 +48313,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1706" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -48960,7 +48963,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1731" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -49194,7 +49197,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1740" t="s">
-        <v>789</v>
+        <v>743</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -69274,7 +69277,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6912037037</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>23380</v>
@@ -69295,6 +69298,32 @@
         <v>1203</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6910763889</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>17716</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>65.4000015258789</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>64.1999969482422</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>64.4000015258789</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>64.9000015258789</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>1204</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="1205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="1206">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23958778381348</t>
+    <t xml:space="preserve">9.23958587646484</t>
   </si>
   <si>
     <t xml:space="preserve">CMB.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">9.55656623840332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31377601623535</t>
+    <t xml:space="preserve">9.31377410888672</t>
   </si>
   <si>
     <t xml:space="preserve">9.40144920349121</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">9.40819358825684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44191455841064</t>
+    <t xml:space="preserve">9.44191551208496</t>
   </si>
   <si>
     <t xml:space="preserve">9.36098289489746</t>
@@ -65,16 +65,16 @@
     <t xml:space="preserve">9.13842487335205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32051849365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26656436920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34074974060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2733097076416</t>
+    <t xml:space="preserve">9.32051753997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26656532287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3407506942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27330875396729</t>
   </si>
   <si>
     <t xml:space="preserve">9.19237899780273</t>
@@ -86,25 +86,25 @@
     <t xml:space="preserve">9.10470294952393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84167861938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77423477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84842491149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36283683776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3291187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61911964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45051288604736</t>
+    <t xml:space="preserve">8.84167957305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77423763275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84842395782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36283874511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32911777496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61911869049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45051193237305</t>
   </si>
   <si>
     <t xml:space="preserve">8.43028163909912</t>
@@ -116,67 +116,67 @@
     <t xml:space="preserve">8.80121421813965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22610092163086</t>
+    <t xml:space="preserve">9.22609996795654</t>
   </si>
   <si>
     <t xml:space="preserve">9.25982093811035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07098388671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87539863586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96981811523438</t>
+    <t xml:space="preserve">9.0709810256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87539958953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96981906890869</t>
   </si>
   <si>
     <t xml:space="preserve">8.71353816986084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6663293838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89563369750977</t>
+    <t xml:space="preserve">8.66633033752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89563179016113</t>
   </si>
   <si>
     <t xml:space="preserve">8.81470203399658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99679660797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01028537750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90237617492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97656345367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18563365936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17214488983154</t>
+    <t xml:space="preserve">8.99679565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01028442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90237712860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18563556671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17214584350586</t>
   </si>
   <si>
     <t xml:space="preserve">9.13168048858643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34749507904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25307655334473</t>
+    <t xml:space="preserve">9.34749603271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25307750701904</t>
   </si>
   <si>
     <t xml:space="preserve">9.15865707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08447074890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540050506592</t>
+    <t xml:space="preserve">9.08447170257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540145874023</t>
   </si>
   <si>
     <t xml:space="preserve">8.98330688476562</t>
@@ -185,19 +185,19 @@
     <t xml:space="preserve">8.78772449493408</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78098106384277</t>
+    <t xml:space="preserve">8.78098011016846</t>
   </si>
   <si>
     <t xml:space="preserve">9.1249361038208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03726005554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21261119842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04400444030762</t>
+    <t xml:space="preserve">9.03726196289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21261024475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04400539398193</t>
   </si>
   <si>
     <t xml:space="preserve">9.0979585647583</t>
@@ -206,40 +206,40 @@
     <t xml:space="preserve">9.20586681365967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38121700286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28679656982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22100830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22798919677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19308757781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35363388061523</t>
+    <t xml:space="preserve">9.38121604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28679847717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22100734710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22798824310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19308662414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35363292694092</t>
   </si>
   <si>
     <t xml:space="preserve">9.4094762802124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52116203308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49324035644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38853645324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94696140289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76547241210938</t>
+    <t xml:space="preserve">9.52116394042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49324131011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38853549957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94696235656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76547336578369</t>
   </si>
   <si>
     <t xml:space="preserve">9.77245426177979</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">9.66774845123291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82829666137695</t>
+    <t xml:space="preserve">9.82829570770264</t>
   </si>
   <si>
     <t xml:space="preserve">9.75151252746582</t>
@@ -257,22 +257,22 @@
     <t xml:space="preserve">9.57002449035645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57700443267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55606365203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47928047180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42343807220459</t>
+    <t xml:space="preserve">9.57700538635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55606460571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47927951812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42343711853027</t>
   </si>
   <si>
     <t xml:space="preserve">9.39551639556885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4164571762085</t>
+    <t xml:space="preserve">9.41645526885986</t>
   </si>
   <si>
     <t xml:space="preserve">9.34665393829346</t>
@@ -281,52 +281,52 @@
     <t xml:space="preserve">9.583984375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6258659362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63284683227539</t>
+    <t xml:space="preserve">9.62586688995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63284778594971</t>
   </si>
   <si>
     <t xml:space="preserve">9.46531963348389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48625946044922</t>
+    <t xml:space="preserve">9.48626136779785</t>
   </si>
   <si>
     <t xml:space="preserve">9.59096527099609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56304359436035</t>
+    <t xml:space="preserve">9.56304264068604</t>
   </si>
   <si>
     <t xml:space="preserve">9.53512191772461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12328433990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30477333068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2838306427002</t>
+    <t xml:space="preserve">9.1232852935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30477237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28383159637451</t>
   </si>
   <si>
     <t xml:space="preserve">9.20704555511475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2768497467041</t>
+    <t xml:space="preserve">9.27685070037842</t>
   </si>
   <si>
     <t xml:space="preserve">9.36061477661133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29081058502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29779148101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31873321533203</t>
+    <t xml:space="preserve">9.29081153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29779243469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31873226165771</t>
   </si>
   <si>
     <t xml:space="preserve">9.36759567260742</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">9.47229957580566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52814197540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5072021484375</t>
+    <t xml:space="preserve">9.52814102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50720119476318</t>
   </si>
   <si>
     <t xml:space="preserve">9.44437789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50022125244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33269214630127</t>
+    <t xml:space="preserve">9.50022220611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33269309997559</t>
   </si>
   <si>
     <t xml:space="preserve">9.32571315765381</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">9.13724517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14422512054443</t>
+    <t xml:space="preserve">9.14422416687012</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120506286621</t>
@@ -374,25 +374,25 @@
     <t xml:space="preserve">9.01159858703613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07442092895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97669696807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86501026153564</t>
+    <t xml:space="preserve">9.07442188262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97669792175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86501312255859</t>
   </si>
   <si>
     <t xml:space="preserve">8.85105133056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.934814453125</t>
+    <t xml:space="preserve">8.93481349945068</t>
   </si>
   <si>
     <t xml:space="preserve">8.92085456848145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95575618743896</t>
+    <t xml:space="preserve">8.95575523376465</t>
   </si>
   <si>
     <t xml:space="preserve">8.96971702575684</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">8.91387462615967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87897205352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80916881561279</t>
+    <t xml:space="preserve">8.87897300720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80916690826416</t>
   </si>
   <si>
     <t xml:space="preserve">8.59975910186768</t>
@@ -422,25 +422,25 @@
     <t xml:space="preserve">8.83709049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8999137878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99763774871826</t>
+    <t xml:space="preserve">8.89991283416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99763679504395</t>
   </si>
   <si>
     <t xml:space="preserve">8.83010959625244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96273612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08838272094727</t>
+    <t xml:space="preserve">8.96273708343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08838176727295</t>
   </si>
   <si>
     <t xml:space="preserve">9.04650020599365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09536266326904</t>
+    <t xml:space="preserve">9.09536170959473</t>
   </si>
   <si>
     <t xml:space="preserve">9.66076850891113</t>
@@ -449,13 +449,13 @@
     <t xml:space="preserve">9.64680862426758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70264911651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79339504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92602157592773</t>
+    <t xml:space="preserve">9.70265102386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79339408874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9260196685791</t>
   </si>
   <si>
     <t xml:space="preserve">9.98186302185059</t>
@@ -464,37 +464,37 @@
     <t xml:space="preserve">10.0516662597656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4146432876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1912746429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2471170425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493902206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1354322433472</t>
+    <t xml:space="preserve">10.414644241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.19127368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2471151351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493911743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1354312896729</t>
   </si>
   <si>
     <t xml:space="preserve">10.2680568695068</t>
   </si>
   <si>
-    <t xml:space="preserve">10.393702507019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402898788452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5891523361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4844465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6310338973999</t>
+    <t xml:space="preserve">10.3937034606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402889251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5891513824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.484447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6310329437256</t>
   </si>
   <si>
     <t xml:space="preserve">10.3588008880615</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">9.95394325256348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1005296707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4704847335815</t>
+    <t xml:space="preserve">10.100528717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4704866409302</t>
   </si>
   <si>
     <t xml:space="preserve">10.3867225646973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.547269821167</t>
+    <t xml:space="preserve">10.5472707748413</t>
   </si>
   <si>
     <t xml:space="preserve">10.3448400497437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4774675369263</t>
+    <t xml:space="preserve">10.4774656295776</t>
   </si>
   <si>
     <t xml:space="preserve">10.4006824493408</t>
@@ -530,73 +530,73 @@
     <t xml:space="preserve">10.4355840682983</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3727617263794</t>
+    <t xml:space="preserve">10.3727607727051</t>
   </si>
   <si>
     <t xml:space="preserve">10.3657817840576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3378601074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2820158004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3797426223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6100921630859</t>
+    <t xml:space="preserve">10.3378610610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2820177078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3797407150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6100931167603</t>
   </si>
   <si>
     <t xml:space="preserve">10.5542507171631</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6938562393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0917358398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0428733825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0358915328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.063814163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0847549438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3569860458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5175342559814</t>
+    <t xml:space="preserve">10.6938543319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0917348861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.042872428894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0358934402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0638151168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0847539901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.356987953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5175361633301</t>
   </si>
   <si>
     <t xml:space="preserve">12.0899219512939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9991788864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0689811706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1038827896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2853708267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8228549957275</t>
+    <t xml:space="preserve">11.9991760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.06898021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1038818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2853698730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8228559494019</t>
   </si>
   <si>
     <t xml:space="preserve">12.9764223098755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.990382194519</t>
+    <t xml:space="preserve">12.9903841018677</t>
   </si>
   <si>
     <t xml:space="preserve">13.2486553192139</t>
@@ -605,46 +605,46 @@
     <t xml:space="preserve">13.1090488433838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1230068206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8926582336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9135999679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8437986373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9624624252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1928129196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3952445983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8978252410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9815902709961</t>
+    <t xml:space="preserve">13.123007774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8926572799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9136009216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8437976837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.962459564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1928119659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3952436447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8978261947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9815883636475</t>
   </si>
   <si>
     <t xml:space="preserve">13.9327268600464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0234708786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0304517745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1351566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0723342895508</t>
+    <t xml:space="preserve">14.023473739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0304527282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1351556777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0723352432251</t>
   </si>
   <si>
     <t xml:space="preserve">14.0025310516357</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">14.2112550735474</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3197374343872</t>
+    <t xml:space="preserve">14.3197402954102</t>
   </si>
   <si>
     <t xml:space="preserve">14.1461658477783</t>
@@ -665,16 +665,16 @@
     <t xml:space="preserve">13.9942903518677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6688413619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3558979034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6833057403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0015211105347</t>
+    <t xml:space="preserve">13.6688394546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.355899810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6833076477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0015239715576</t>
   </si>
   <si>
     <t xml:space="preserve">13.9870586395264</t>
@@ -683,97 +683,97 @@
     <t xml:space="preserve">14.2691125869751</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3486661911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3414344787598</t>
+    <t xml:space="preserve">14.3486680984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3414354324341</t>
   </si>
   <si>
     <t xml:space="preserve">14.276346206665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4282207489014</t>
+    <t xml:space="preserve">14.4282236099243</t>
   </si>
   <si>
     <t xml:space="preserve">14.5656337738037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3322477340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8457326889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7589483261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3611736297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1876010894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9200105667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6307210922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636768341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3105506896973</t>
+    <t xml:space="preserve">15.3322458267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8457298278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7589445114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3611745834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1876020431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9200124740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6307229995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636730194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3105487823486</t>
   </si>
   <si>
     <t xml:space="preserve">14.9272422790527</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0718870162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5492105484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4551916122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2671585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1731367111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8332252502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1369781494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1152782440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9851007461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1514415740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0284938812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2092981338501</t>
+    <t xml:space="preserve">15.0718879699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5492115020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4551935195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2671575546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1731376647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8332242965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1369771957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1152801513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9850997924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1514406204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0284957885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2093000411987</t>
   </si>
   <si>
     <t xml:space="preserve">15.6649265289307</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6938571929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7661771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9325189590454</t>
+    <t xml:space="preserve">15.6938543319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7661781311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9325199127197</t>
   </si>
   <si>
     <t xml:space="preserve">16.0410003662109</t>
@@ -782,100 +782,100 @@
     <t xml:space="preserve">15.9469814300537</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6432294845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2816219329834</t>
+    <t xml:space="preserve">15.6432304382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2816200256348</t>
   </si>
   <si>
     <t xml:space="preserve">15.2888517379761</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2599229812622</t>
+    <t xml:space="preserve">15.2599248886108</t>
   </si>
   <si>
     <t xml:space="preserve">15.3250122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2382278442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.158673286438</t>
+    <t xml:space="preserve">15.238226890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1586713790894</t>
   </si>
   <si>
     <t xml:space="preserve">15.0574226379395</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1803674697876</t>
+    <t xml:space="preserve">15.1803712844849</t>
   </si>
   <si>
     <t xml:space="preserve">15.2454595565796</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8983144760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8693828582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8259935379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9634056091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9706382751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6813478469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7536725997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6958093643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8910846710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.493311882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8549213409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6524200439453</t>
+    <t xml:space="preserve">14.8983135223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8693866729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8259916305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9634017944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9706363677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6813468933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7536687850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6958141326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8910818099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4933128356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.854923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6524181365967</t>
   </si>
   <si>
     <t xml:space="preserve">14.6090269088745</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8476915359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1948328018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3394765853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.433497428894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2651977539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9956474304199</t>
+    <t xml:space="preserve">14.8476905822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1948347091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3394784927368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4334936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2651958465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9956493377686</t>
   </si>
   <si>
     <t xml:space="preserve">17.5742244720459</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6879825592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3986930847168</t>
+    <t xml:space="preserve">18.6879806518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3986968994141</t>
   </si>
   <si>
     <t xml:space="preserve">18.4420871734619</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">18.2178897857666</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0804786682129</t>
+    <t xml:space="preserve">18.0804805755615</t>
   </si>
   <si>
     <t xml:space="preserve">18.1889629364014</t>
@@ -893,76 +893,76 @@
     <t xml:space="preserve">17.971996307373</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0081558227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8562812805176</t>
+    <t xml:space="preserve">18.0081539154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8562793731689</t>
   </si>
   <si>
     <t xml:space="preserve">17.9647636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6393146514893</t>
+    <t xml:space="preserve">17.6393165588379</t>
   </si>
   <si>
     <t xml:space="preserve">17.7622623443604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6031532287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5886878967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5380611419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5019035339355</t>
+    <t xml:space="preserve">17.6031551361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5886898040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5380630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5019054412842</t>
   </si>
   <si>
     <t xml:space="preserve">17.3861885070801</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3211002349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2849369049072</t>
+    <t xml:space="preserve">17.3210983276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2849349975586</t>
   </si>
   <si>
     <t xml:space="preserve">17.0462760925293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.263240814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0968990325928</t>
+    <t xml:space="preserve">17.2632389068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0969009399414</t>
   </si>
   <si>
     <t xml:space="preserve">17.3283309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3572578430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4006519317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3789577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2921676635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3427963256836</t>
+    <t xml:space="preserve">17.3572597503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4006538391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3789596557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2921695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.342794418335</t>
   </si>
   <si>
     <t xml:space="preserve">17.1692218780518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5906467437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6268081665039</t>
+    <t xml:space="preserve">16.590648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6268062591553</t>
   </si>
   <si>
     <t xml:space="preserve">16.9233264923096</t>
@@ -977,19 +977,19 @@
     <t xml:space="preserve">16.1133232116699</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9180526733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6504611968994</t>
+    <t xml:space="preserve">15.9180555343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6504650115967</t>
   </si>
   <si>
     <t xml:space="preserve">16.4749336242676</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3013610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5761795043945</t>
+    <t xml:space="preserve">16.3013572692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5761852264404</t>
   </si>
   <si>
     <t xml:space="preserve">16.5110931396484</t>
@@ -998,55 +998,55 @@
     <t xml:space="preserve">16.5617160797119</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0699272155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5255584716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4098434448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2073421478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8746604919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.243501663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4460029602051</t>
+    <t xml:space="preserve">16.0699310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5255565643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4098415374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2073402404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8746614456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2434997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4460067749023</t>
   </si>
   <si>
     <t xml:space="preserve">16.2001094818115</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8312683105469</t>
+    <t xml:space="preserve">15.831262588501</t>
   </si>
   <si>
     <t xml:space="preserve">15.8601980209351</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8529653549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6287641525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4696550369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4624223709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215324401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9976100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.236270904541</t>
+    <t xml:space="preserve">15.8529644012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6287670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4696559906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4624252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215333938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9976091384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2362689971924</t>
   </si>
   <si>
     <t xml:space="preserve">16.163948059082</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">16.6340408325195</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4532375335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7425212860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5978775024414</t>
+    <t xml:space="preserve">16.4532356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7425231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5978813171387</t>
   </si>
   <si>
     <t xml:space="preserve">16.7063636779785</t>
@@ -1076,28 +1076,28 @@
     <t xml:space="preserve">16.8510055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.031810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2126159667969</t>
+    <t xml:space="preserve">17.0318088531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2126140594482</t>
   </si>
   <si>
     <t xml:space="preserve">17.4295806884766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9594898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3809146881104</t>
+    <t xml:space="preserve">16.9594879150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3809127807617</t>
   </si>
   <si>
     <t xml:space="preserve">15.9831418991089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9108219146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7300157546997</t>
+    <t xml:space="preserve">15.9108238220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7300186157227</t>
   </si>
   <si>
     <t xml:space="preserve">15.3684062957764</t>
@@ -1106,49 +1106,49 @@
     <t xml:space="preserve">15.4045677185059</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4768886566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8023366928101</t>
+    <t xml:space="preserve">15.4768915176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.802339553833</t>
   </si>
   <si>
     <t xml:space="preserve">16.6702003479004</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1402950286865</t>
+    <t xml:space="preserve">17.1402969360352</t>
   </si>
   <si>
     <t xml:space="preserve">17.104133605957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8148460388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0679721832275</t>
+    <t xml:space="preserve">16.8148441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0679702758789</t>
   </si>
   <si>
     <t xml:space="preserve">16.8871669769287</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8273525238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6827068328857</t>
+    <t xml:space="preserve">17.8273506164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6827087402344</t>
   </si>
   <si>
     <t xml:space="preserve">17.3934211730957</t>
   </si>
   <si>
-    <t xml:space="preserve">17.248779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7550277709961</t>
+    <t xml:space="preserve">17.2487754821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7550296783447</t>
   </si>
   <si>
     <t xml:space="preserve">17.8996753692627</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5867347717285</t>
+    <t xml:space="preserve">18.5867328643799</t>
   </si>
   <si>
     <t xml:space="preserve">18.6590538024902</t>
@@ -1160,10 +1160,10 @@
     <t xml:space="preserve">19.5427989959717</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2444381713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9157524108887</t>
+    <t xml:space="preserve">19.2444362640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9157543182373</t>
   </si>
   <si>
     <t xml:space="preserve">20.4378890991211</t>
@@ -1172,19 +1172,19 @@
     <t xml:space="preserve">19.6546878814697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4682102203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6173896789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0952529907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8714809417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9460697174072</t>
+    <t xml:space="preserve">19.4682083129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6173877716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0952568054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8714828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9460754394531</t>
   </si>
   <si>
     <t xml:space="preserve">18.7968921661377</t>
@@ -1196,13 +1196,13 @@
     <t xml:space="preserve">17.3050746917725</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7899169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8341884613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1698455810547</t>
+    <t xml:space="preserve">17.7899150848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8341865539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.169849395752</t>
   </si>
   <si>
     <t xml:space="preserve">19.3936176300049</t>
@@ -1217,16 +1217,16 @@
     <t xml:space="preserve">19.8784599304199</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6919822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3190269470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4239387512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1325454711914</t>
+    <t xml:space="preserve">19.6919803619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3190288543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4239368438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1325492858887</t>
   </si>
   <si>
     <t xml:space="preserve">19.3563251495361</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">19.7292785644531</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7222995758057</t>
+    <t xml:space="preserve">18.7223033905029</t>
   </si>
   <si>
     <t xml:space="preserve">18.9087791442871</t>
@@ -1247,34 +1247,34 @@
     <t xml:space="preserve">18.6477108001709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5731182098389</t>
+    <t xml:space="preserve">18.5731163024902</t>
   </si>
   <si>
     <t xml:space="preserve">18.5358238220215</t>
   </si>
   <si>
-    <t xml:space="preserve">17.976390838623</t>
+    <t xml:space="preserve">17.9763927459717</t>
   </si>
   <si>
     <t xml:space="preserve">18.1255722045898</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4612350463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7595977783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6104145050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3493480682373</t>
+    <t xml:space="preserve">18.4612312316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7595958709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6104125976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3493461608887</t>
   </si>
   <si>
     <t xml:space="preserve">18.6850032806396</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3120498657227</t>
+    <t xml:space="preserve">18.3120517730713</t>
   </si>
   <si>
     <t xml:space="preserve">18.4985275268555</t>
@@ -1283,88 +1283,88 @@
     <t xml:space="preserve">19.2817325592041</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0579586029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1628665924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0136890411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3866424560547</t>
+    <t xml:space="preserve">19.0579566955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1628704071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0136852264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3866405487061</t>
   </si>
   <si>
     <t xml:space="preserve">17.1558933258057</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1862144470215</t>
+    <t xml:space="preserve">16.1862125396729</t>
   </si>
   <si>
     <t xml:space="preserve">15.589485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1419401168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9554634094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0370311737061</t>
+    <t xml:space="preserve">15.1419382095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9554615020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0370292663574</t>
   </si>
   <si>
     <t xml:space="preserve">16.5218696594238</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6640768051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1046457290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9927597045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0300550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7689847946167</t>
+    <t xml:space="preserve">15.6640777587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1046447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9927587509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0300540924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.768985748291</t>
   </si>
   <si>
     <t xml:space="preserve">14.3661956787109</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5153751373291</t>
+    <t xml:space="preserve">14.5153779983521</t>
   </si>
   <si>
     <t xml:space="preserve">14.6198043823242</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8883304595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2538270950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2608032226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9251461029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7759628295898</t>
+    <t xml:space="preserve">14.8883323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2538280487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2608013153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9251432418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7759618759155</t>
   </si>
   <si>
     <t xml:space="preserve">15.7013711929321</t>
   </si>
   <si>
-    <t xml:space="preserve">15.552188873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6267824172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.514892578125</t>
+    <t xml:space="preserve">15.5521898269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6267805099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5148944854736</t>
   </si>
   <si>
     <t xml:space="preserve">15.2911233901978</t>
@@ -1373,19 +1373,19 @@
     <t xml:space="preserve">15.2165327072144</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1792364120483</t>
+    <t xml:space="preserve">15.179235458374</t>
   </si>
   <si>
     <t xml:space="preserve">15.8505525588989</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8132581710815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0743274688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8878488540649</t>
+    <t xml:space="preserve">15.8132591247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0743236541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8878479003906</t>
   </si>
   <si>
     <t xml:space="preserve">15.4030075073242</t>
@@ -1394,13 +1394,13 @@
     <t xml:space="preserve">14.9032497406006</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7093124389648</t>
+    <t xml:space="preserve">14.7093133926392</t>
   </si>
   <si>
     <t xml:space="preserve">15.4403047561646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1116218566895</t>
+    <t xml:space="preserve">16.1116180419922</t>
   </si>
   <si>
     <t xml:space="preserve">15.962438583374</t>
@@ -1409,10 +1409,10 @@
     <t xml:space="preserve">16.5591659545898</t>
   </si>
   <si>
-    <t xml:space="preserve">16.372688293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4845752716064</t>
+    <t xml:space="preserve">16.3726902008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4845771789551</t>
   </si>
   <si>
     <t xml:space="preserve">16.7829399108887</t>
@@ -1421,49 +1421,49 @@
     <t xml:space="preserve">16.8948249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7386665344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657131195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8435754776001</t>
+    <t xml:space="preserve">15.7386684417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657121658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.843578338623</t>
   </si>
   <si>
     <t xml:space="preserve">14.8584966659546</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0673503875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8734149932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9181690216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.409984588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2235069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.298095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6710529327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7083473205566</t>
+    <t xml:space="preserve">15.0673513412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8734121322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9181671142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4099864959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2235088348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2980976104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6710548400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7083492279053</t>
   </si>
   <si>
     <t xml:space="preserve">16.7456436157227</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6337585449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9321193695068</t>
+    <t xml:space="preserve">16.6337566375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9321212768555</t>
   </si>
   <si>
     <t xml:space="preserve">16.8575305938721</t>
@@ -1487,40 +1487,40 @@
     <t xml:space="preserve">17.7227516174316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6756725311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7532348632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3654308319092</t>
+    <t xml:space="preserve">16.6756744384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7532329559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3654289245605</t>
   </si>
   <si>
     <t xml:space="preserve">16.0939636230469</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6673774719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6285972595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0468854904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2640581130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7061586380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5898170471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5122537612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7449369430542</t>
+    <t xml:space="preserve">15.6673784255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6285953521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0468873977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2640590667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7061567306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5898151397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5122547149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7449378967285</t>
   </si>
   <si>
     <t xml:space="preserve">15.2950820922852</t>
@@ -1529,55 +1529,55 @@
     <t xml:space="preserve">15.0158634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1864957809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4191808700562</t>
+    <t xml:space="preserve">15.1864967346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4191818237305</t>
   </si>
   <si>
     <t xml:space="preserve">15.4967432022095</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5510320663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3261060714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2795705795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8612785339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0164012908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9388418197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9000625610352</t>
+    <t xml:space="preserve">15.5510339736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3261079788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2795724868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8612823486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0164031982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9388399124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9000616073608</t>
   </si>
   <si>
     <t xml:space="preserve">15.7837190628052</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8225002288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3266468048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7920169830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0247020721436</t>
+    <t xml:space="preserve">15.8225011825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3266487121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7920150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0247001647949</t>
   </si>
   <si>
     <t xml:space="preserve">16.9083557128906</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4817695617676</t>
+    <t xml:space="preserve">16.4817714691162</t>
   </si>
   <si>
     <t xml:space="preserve">16.5593318939209</t>
@@ -1586,52 +1586,55 @@
     <t xml:space="preserve">16.0551853179932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4042091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1327419281006</t>
+    <t xml:space="preserve">16.4042072296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1327438354492</t>
   </si>
   <si>
     <t xml:space="preserve">16.2878684997559</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1715278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9776220321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3881568908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346942901611</t>
+    <t xml:space="preserve">16.1715240478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9776229858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3881559371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346933364868</t>
   </si>
   <si>
     <t xml:space="preserve">16.2103061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4429893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5981101989746</t>
+    <t xml:space="preserve">16.4429931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5981121063232</t>
   </si>
   <si>
     <t xml:space="preserve">16.5205497741699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6368942260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2490882873535</t>
+    <t xml:space="preserve">16.6368923187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2490863800049</t>
   </si>
   <si>
     <t xml:space="preserve">16.8307971954346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9859199523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8390960693359</t>
+    <t xml:space="preserve">16.9859180450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5288486480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8390922546387</t>
   </si>
   <si>
     <t xml:space="preserve">17.5676288604736</t>
@@ -1643,13 +1646,13 @@
     <t xml:space="preserve">18.6147041320801</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2656764984131</t>
+    <t xml:space="preserve">18.2656803131104</t>
   </si>
   <si>
     <t xml:space="preserve">18.8473873138428</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5371417999268</t>
+    <t xml:space="preserve">18.5371437072754</t>
   </si>
   <si>
     <t xml:space="preserve">18.0717754364014</t>
@@ -1667,10 +1670,10 @@
     <t xml:space="preserve">19.1576347351074</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0025100708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0412940979004</t>
+    <t xml:space="preserve">19.0025119781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0412921905518</t>
   </si>
   <si>
     <t xml:space="preserve">18.3044605255127</t>
@@ -1679,31 +1682,31 @@
     <t xml:space="preserve">18.1493377685547</t>
   </si>
   <si>
-    <t xml:space="preserve">18.032995223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.226900100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4208030700684</t>
+    <t xml:space="preserve">18.0329971313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2268981933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4208011627197</t>
   </si>
   <si>
     <t xml:space="preserve">18.498363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1105556488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6839714050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8086090087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3820209503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.188117980957</t>
+    <t xml:space="preserve">18.1105575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6839694976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8086071014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3820190429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1881198883057</t>
   </si>
   <si>
     <t xml:space="preserve">17.916654586792</t>
@@ -1712,13 +1715,13 @@
     <t xml:space="preserve">17.9554347991943</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6064109802246</t>
+    <t xml:space="preserve">17.6064071655273</t>
   </si>
   <si>
     <t xml:space="preserve">17.6451892852783</t>
   </si>
   <si>
-    <t xml:space="preserve">17.141040802002</t>
+    <t xml:space="preserve">17.1410388946533</t>
   </si>
   <si>
     <t xml:space="preserve">17.1022605895996</t>
@@ -1727,37 +1730,37 @@
     <t xml:space="preserve">17.29616355896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1244487762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7676668167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5577116012573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9610300064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0302934646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1854162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1388788223267</t>
+    <t xml:space="preserve">15.1244478225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7676677703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5577096939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9610290527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0302925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.185417175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.138879776001</t>
   </si>
   <si>
     <t xml:space="preserve">13.5732221603394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2629776000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.169903755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.952733039856</t>
+    <t xml:space="preserve">13.2629795074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1699028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9527339935303</t>
   </si>
   <si>
     <t xml:space="preserve">12.5649271011353</t>
@@ -1766,10 +1769,10 @@
     <t xml:space="preserve">11.7582883834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5566291809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8585777282715</t>
+    <t xml:space="preserve">11.5566301345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8585786819458</t>
   </si>
   <si>
     <t xml:space="preserve">10.7810163497925</t>
@@ -1781,34 +1784,34 @@
     <t xml:space="preserve">10.8197965621948</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1300439834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7893133163452</t>
+    <t xml:space="preserve">11.1300430297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7893142700195</t>
   </si>
   <si>
     <t xml:space="preserve">12.2546806335449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9056558609009</t>
+    <t xml:space="preserve">11.9056549072266</t>
   </si>
   <si>
     <t xml:space="preserve">11.6341905593872</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0219974517822</t>
+    <t xml:space="preserve">12.0219964981079</t>
   </si>
   <si>
     <t xml:space="preserve">12.0607776641846</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8280944824219</t>
+    <t xml:space="preserve">11.8280935287476</t>
   </si>
   <si>
     <t xml:space="preserve">11.4790687561035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7117528915405</t>
+    <t xml:space="preserve">11.7117519378662</t>
   </si>
   <si>
     <t xml:space="preserve">11.6729717254639</t>
@@ -1817,31 +1820,31 @@
     <t xml:space="preserve">11.5954103469849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2851657867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4015073776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7505311965942</t>
+    <t xml:space="preserve">11.2851648330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4015064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7505321502686</t>
   </si>
   <si>
     <t xml:space="preserve">10.9749193191528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5095529556274</t>
+    <t xml:space="preserve">10.5095520019531</t>
   </si>
   <si>
     <t xml:space="preserve">10.5871133804321</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6646757125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2463846206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2158994674683</t>
+    <t xml:space="preserve">10.6646738052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2463855743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2159004211426</t>
   </si>
   <si>
     <t xml:space="preserve">12.3710222244263</t>
@@ -1850,10 +1853,10 @@
     <t xml:space="preserve">14.0773706436157</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1181745529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0365686416626</t>
+    <t xml:space="preserve">14.1181755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0365676879883</t>
   </si>
   <si>
     <t xml:space="preserve">13.8733510971069</t>
@@ -1862,16 +1865,16 @@
     <t xml:space="preserve">13.8325462341309</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1997833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6078214645386</t>
+    <t xml:space="preserve">14.199782371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6078224182129</t>
   </si>
   <si>
     <t xml:space="preserve">14.2813901901245</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4245090484619</t>
+    <t xml:space="preserve">13.4245080947876</t>
   </si>
   <si>
     <t xml:space="preserve">13.5469198226929</t>
@@ -1880,67 +1883,67 @@
     <t xml:space="preserve">13.5061149597168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7509393692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9549589157104</t>
+    <t xml:space="preserve">13.7509384155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9549598693848</t>
   </si>
   <si>
     <t xml:space="preserve">14.5262136459351</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7710390090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6894311904907</t>
+    <t xml:space="preserve">14.7710380554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6894302368164</t>
   </si>
   <si>
     <t xml:space="preserve">14.3221940994263</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4038028717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5877237319946</t>
+    <t xml:space="preserve">14.4038019180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5877227783203</t>
   </si>
   <si>
     <t xml:space="preserve">13.4653120040894</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6285276412964</t>
+    <t xml:space="preserve">13.6285266876221</t>
   </si>
   <si>
     <t xml:space="preserve">13.9141550064087</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2405881881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9957618713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1589784622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7917423248291</t>
+    <t xml:space="preserve">14.2405872344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9957628250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1589794158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7917413711548</t>
   </si>
   <si>
     <t xml:space="preserve">13.3837032318115</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2204885482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3429002761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7101345062256</t>
+    <t xml:space="preserve">13.2204895019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3428993225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7101335525513</t>
   </si>
   <si>
     <t xml:space="preserve">13.0572710037231</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2612915039062</t>
+    <t xml:space="preserve">13.2612924575806</t>
   </si>
   <si>
     <t xml:space="preserve">13.0980749130249</t>
@@ -1955,7 +1958,7 @@
     <t xml:space="preserve">12.7308406829834</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6900358200073</t>
+    <t xml:space="preserve">12.6900367736816</t>
   </si>
   <si>
     <t xml:space="preserve">12.9756631851196</t>
@@ -1964,16 +1967,16 @@
     <t xml:space="preserve">12.7716436386108</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8526477813721</t>
+    <t xml:space="preserve">14.8526458740234</t>
   </si>
   <si>
     <t xml:space="preserve">15.2606868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4238996505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0767650604248</t>
+    <t xml:space="preserve">15.4239015579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0767669677734</t>
   </si>
   <si>
     <t xml:space="preserve">15.9135503768921</t>
@@ -1985,7 +1988,7 @@
     <t xml:space="preserve">15.6687250137329</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5871171951294</t>
+    <t xml:space="preserve">15.587119102478</t>
   </si>
   <si>
     <t xml:space="preserve">15.3014898300171</t>
@@ -1994,16 +1997,16 @@
     <t xml:space="preserve">15.3830976486206</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3422937393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7503347396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2198810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1790781021118</t>
+    <t xml:space="preserve">15.3422918319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7503328323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2198829650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1790790557861</t>
   </si>
   <si>
     <t xml:space="preserve">15.4647073745728</t>
@@ -2018,7 +2021,7 @@
     <t xml:space="preserve">16.8112373352051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7089252471924</t>
+    <t xml:space="preserve">17.7089233398438</t>
   </si>
   <si>
     <t xml:space="preserve">17.1376705169678</t>
@@ -2042,31 +2045,31 @@
     <t xml:space="preserve">16.5664119720459</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2399826049805</t>
+    <t xml:space="preserve">16.2399806976318</t>
   </si>
   <si>
     <t xml:space="preserve">16.4031982421875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7296314239502</t>
+    <t xml:space="preserve">16.7296295166016</t>
   </si>
   <si>
     <t xml:space="preserve">17.2192783355713</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4640979766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5457077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9537467956543</t>
+    <t xml:space="preserve">17.4640998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5457057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9537487030029</t>
   </si>
   <si>
     <t xml:space="preserve">18.0353565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9744510650635</t>
+    <t xml:space="preserve">16.9744529724121</t>
   </si>
   <si>
     <t xml:space="preserve">17.8721408843994</t>
@@ -2075,40 +2078,37 @@
     <t xml:space="preserve">18.11696434021</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1985721588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3617877960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1778678894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8514366149902</t>
+    <t xml:space="preserve">18.1985702514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3617897033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1778659820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8514385223389</t>
   </si>
   <si>
     <t xml:space="preserve">18.6882190704346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0962600708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6066131591797</t>
+    <t xml:space="preserve">19.0962581634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6066112518311</t>
   </si>
   <si>
     <t xml:space="preserve">18.9330444335938</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7698307037354</t>
-  </si>
-  <si>
     <t xml:space="preserve">19.2594757080078</t>
   </si>
   <si>
     <t xml:space="preserve">19.3410835266113</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4226913452148</t>
+    <t xml:space="preserve">19.4226894378662</t>
   </si>
   <si>
     <t xml:space="preserve">19.0146503448486</t>
@@ -3627,6 +3627,9 @@
   </si>
   <si>
     <t xml:space="preserve">65.6999969482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5</t>
   </si>
 </sst>
 </file>
@@ -29437,7 +29440,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G980" t="s">
-        <v>488</v>
+        <v>539</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -29463,7 +29466,7 @@
         <v>23</v>
       </c>
       <c r="G981" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -29489,7 +29492,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G982" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -29515,7 +29518,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G983" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -29541,7 +29544,7 @@
         <v>24</v>
       </c>
       <c r="G984" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -29593,7 +29596,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G986" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -29619,7 +29622,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G987" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29645,7 +29648,7 @@
         <v>24</v>
       </c>
       <c r="G988" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29671,7 +29674,7 @@
         <v>24</v>
       </c>
       <c r="G989" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29697,7 +29700,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G990" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29723,7 +29726,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G991" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29749,7 +29752,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G992" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29775,7 +29778,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G993" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29801,7 +29804,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G994" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29827,7 +29830,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G995" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29853,7 +29856,7 @@
         <v>24.5</v>
       </c>
       <c r="G996" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29879,7 +29882,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G997" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29905,7 +29908,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G998" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29931,7 +29934,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G999" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29957,7 +29960,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1000" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29983,7 +29986,7 @@
         <v>23.25</v>
       </c>
       <c r="G1001" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -30009,7 +30012,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1002" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -30035,7 +30038,7 @@
         <v>23.5</v>
       </c>
       <c r="G1003" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -30087,7 +30090,7 @@
         <v>23.75</v>
       </c>
       <c r="G1005" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -30113,7 +30116,7 @@
         <v>23.75</v>
       </c>
       <c r="G1006" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -30139,7 +30142,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1007" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -30165,7 +30168,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1008" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -30191,7 +30194,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1009" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -30217,7 +30220,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1010" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -30243,7 +30246,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1011" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -30295,7 +30298,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1013" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -30321,7 +30324,7 @@
         <v>24.25</v>
       </c>
       <c r="G1014" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -30347,7 +30350,7 @@
         <v>24</v>
       </c>
       <c r="G1015" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -30373,7 +30376,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1016" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -30399,7 +30402,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1017" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -30425,7 +30428,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1018" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -30451,7 +30454,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1019" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -30477,7 +30480,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1020" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -30503,7 +30506,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1021" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -30529,7 +30532,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G1022" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -30555,7 +30558,7 @@
         <v>23.5</v>
       </c>
       <c r="G1023" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -30581,7 +30584,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1024" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -30607,7 +30610,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1025" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -30633,7 +30636,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1026" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -30659,7 +30662,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1027" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -30685,7 +30688,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1028" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30711,7 +30714,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1029" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30737,7 +30740,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1030" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30763,7 +30766,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1031" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30789,7 +30792,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1032" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30815,7 +30818,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1033" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -30841,7 +30844,7 @@
         <v>22.75</v>
       </c>
       <c r="G1034" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -30867,7 +30870,7 @@
         <v>23.25</v>
       </c>
       <c r="G1035" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -30893,7 +30896,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1036" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -30919,7 +30922,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1037" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -30945,7 +30948,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1038" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -30971,7 +30974,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1039" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30997,7 +31000,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1040" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -31023,7 +31026,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1041" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -31049,7 +31052,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1042" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -31075,7 +31078,7 @@
         <v>23.75</v>
       </c>
       <c r="G1043" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -31101,7 +31104,7 @@
         <v>23.75</v>
       </c>
       <c r="G1044" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -31127,7 +31130,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1045" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -31153,7 +31156,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1046" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -31179,7 +31182,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1047" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -31205,7 +31208,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1048" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -31231,7 +31234,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1049" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -31257,7 +31260,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1050" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -31283,7 +31286,7 @@
         <v>23.25</v>
       </c>
       <c r="G1051" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -31309,7 +31312,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1052" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -31361,7 +31364,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1054" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -31387,7 +31390,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1055" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -31413,7 +31416,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1056" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -31439,7 +31442,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -31621,7 +31624,7 @@
         <v>19.5</v>
       </c>
       <c r="G1064" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -31647,7 +31650,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1065" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31673,7 +31676,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1066" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31699,7 +31702,7 @@
         <v>18</v>
       </c>
       <c r="G1067" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31725,7 +31728,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1068" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31751,7 +31754,7 @@
         <v>17</v>
       </c>
       <c r="G1069" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -31777,7 +31780,7 @@
         <v>17</v>
       </c>
       <c r="G1070" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -31803,7 +31806,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1071" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31829,7 +31832,7 @@
         <v>17.5</v>
       </c>
       <c r="G1072" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31855,7 +31858,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1073" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -31881,7 +31884,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1074" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -31907,7 +31910,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1075" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31933,7 +31936,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1076" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31959,7 +31962,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1077" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31985,7 +31988,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1078" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -32011,7 +32014,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1079" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -32037,7 +32040,7 @@
         <v>14</v>
       </c>
       <c r="G1080" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -32063,7 +32066,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1081" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -32089,7 +32092,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1082" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -32115,7 +32118,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1083" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -32141,7 +32144,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1084" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -32167,7 +32170,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1085" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32193,7 +32196,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1086" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -32219,7 +32222,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1087" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -32245,7 +32248,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1088" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -32271,7 +32274,7 @@
         <v>15</v>
       </c>
       <c r="G1089" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -32297,7 +32300,7 @@
         <v>15.5</v>
       </c>
       <c r="G1090" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -32323,7 +32326,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1091" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -32349,7 +32352,7 @@
         <v>15.25</v>
       </c>
       <c r="G1092" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -32375,7 +32378,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1093" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -32401,7 +32404,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1094" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -32427,7 +32430,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1095" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -32453,7 +32456,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1096" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -32479,7 +32482,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1097" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -32505,7 +32508,7 @@
         <v>15</v>
       </c>
       <c r="G1098" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -32531,7 +32534,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1099" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -32557,7 +32560,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1100" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -32583,7 +32586,7 @@
         <v>15</v>
       </c>
       <c r="G1101" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -32609,7 +32612,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1102" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -32635,7 +32638,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1103" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -32661,7 +32664,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1104" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32687,7 +32690,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1105" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -32713,7 +32716,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1106" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32739,7 +32742,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1107" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32765,7 +32768,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1108" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32791,7 +32794,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1109" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32817,7 +32820,7 @@
         <v>13.75</v>
       </c>
       <c r="G1110" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32843,7 +32846,7 @@
         <v>14</v>
       </c>
       <c r="G1111" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32869,7 +32872,7 @@
         <v>14</v>
       </c>
       <c r="G1112" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32895,7 +32898,7 @@
         <v>14.5</v>
       </c>
       <c r="G1113" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32921,7 +32924,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1114" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -32947,7 +32950,7 @@
         <v>15</v>
       </c>
       <c r="G1115" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -32973,7 +32976,7 @@
         <v>15.75</v>
       </c>
       <c r="G1116" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -32999,7 +33002,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1117" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -33025,7 +33028,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1118" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -33051,7 +33054,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1119" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -33077,7 +33080,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1120" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -33103,7 +33106,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1121" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -33129,7 +33132,7 @@
         <v>17</v>
       </c>
       <c r="G1122" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -33155,7 +33158,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1123" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -33181,7 +33184,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1124" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -33207,7 +33210,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1125" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -33233,7 +33236,7 @@
         <v>17.5</v>
       </c>
       <c r="G1126" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -33259,7 +33262,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1127" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -33285,7 +33288,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1128" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -33311,7 +33314,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1129" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -33337,7 +33340,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1130" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -33363,7 +33366,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1131" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -33389,7 +33392,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1132" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -33415,7 +33418,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1133" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -33441,7 +33444,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1134" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -33467,7 +33470,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1135" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -33493,7 +33496,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1136" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -33519,7 +33522,7 @@
         <v>18</v>
       </c>
       <c r="G1137" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -33545,7 +33548,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1138" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -33571,7 +33574,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1139" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -33597,7 +33600,7 @@
         <v>17.5</v>
       </c>
       <c r="G1140" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -33623,7 +33626,7 @@
         <v>17</v>
       </c>
       <c r="G1141" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33649,7 +33652,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1142" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33675,7 +33678,7 @@
         <v>16.5</v>
       </c>
       <c r="G1143" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33701,7 +33704,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1144" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33727,7 +33730,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1145" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33753,7 +33756,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1146" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33779,7 +33782,7 @@
         <v>17.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33805,7 +33808,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1148" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33831,7 +33834,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1149" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33857,7 +33860,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1150" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33883,7 +33886,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1151" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33909,7 +33912,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1152" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33935,7 +33938,7 @@
         <v>17.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33961,7 +33964,7 @@
         <v>17</v>
       </c>
       <c r="G1154" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33987,7 +33990,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1155" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -34013,7 +34016,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1156" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -34039,7 +34042,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1157" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -34065,7 +34068,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1158" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -34091,7 +34094,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1159" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -34117,7 +34120,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1160" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -34143,7 +34146,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1161" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -34169,7 +34172,7 @@
         <v>16.5</v>
       </c>
       <c r="G1162" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -34195,7 +34198,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1163" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -34221,7 +34224,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1164" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -34247,7 +34250,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1165" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -34273,7 +34276,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1166" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -34299,7 +34302,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1167" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -34325,7 +34328,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1168" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -34351,7 +34354,7 @@
         <v>17.25</v>
       </c>
       <c r="G1169" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34377,7 +34380,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1170" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -34403,7 +34406,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1171" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -34429,7 +34432,7 @@
         <v>17</v>
       </c>
       <c r="G1172" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -34455,7 +34458,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1173" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -34481,7 +34484,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1174" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -34507,7 +34510,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1175" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -34533,7 +34536,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -34559,7 +34562,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1177" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34585,7 +34588,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1178" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -34611,7 +34614,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1179" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34637,7 +34640,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1180" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34663,7 +34666,7 @@
         <v>17</v>
       </c>
       <c r="G1181" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34689,7 +34692,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1182" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34715,7 +34718,7 @@
         <v>17</v>
       </c>
       <c r="G1183" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34741,7 +34744,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1184" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34767,7 +34770,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1185" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34793,7 +34796,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1186" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34819,7 +34822,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1187" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34845,7 +34848,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1188" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34871,7 +34874,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1189" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34897,7 +34900,7 @@
         <v>17.25</v>
       </c>
       <c r="G1190" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34923,7 +34926,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1191" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34949,7 +34952,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1192" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -34975,7 +34978,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1193" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -35001,7 +35004,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1194" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -35027,7 +35030,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1195" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -35053,7 +35056,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1196" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -35079,7 +35082,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1197" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35105,7 +35108,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -35131,7 +35134,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1199" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35157,7 +35160,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1200" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -35183,7 +35186,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1201" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -35209,7 +35212,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1202" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -35235,7 +35238,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1203" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -35261,7 +35264,7 @@
         <v>16</v>
       </c>
       <c r="G1204" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -35287,7 +35290,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1205" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -35313,7 +35316,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1206" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35339,7 +35342,7 @@
         <v>16</v>
       </c>
       <c r="G1207" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -35365,7 +35368,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1208" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -35391,7 +35394,7 @@
         <v>16.25</v>
       </c>
       <c r="G1209" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -35417,7 +35420,7 @@
         <v>16.5</v>
       </c>
       <c r="G1210" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -35443,7 +35446,7 @@
         <v>16.5</v>
       </c>
       <c r="G1211" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -35469,7 +35472,7 @@
         <v>17.25</v>
       </c>
       <c r="G1212" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -35495,7 +35498,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1213" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -35521,7 +35524,7 @@
         <v>17</v>
       </c>
       <c r="G1214" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -35547,7 +35550,7 @@
         <v>17.25</v>
       </c>
       <c r="G1215" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35573,7 +35576,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1216" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35599,7 +35602,7 @@
         <v>17</v>
       </c>
       <c r="G1217" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -35625,7 +35628,7 @@
         <v>17</v>
       </c>
       <c r="G1218" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35651,7 +35654,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1219" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35677,7 +35680,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1220" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35703,7 +35706,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1221" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35729,7 +35732,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1222" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35755,7 +35758,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1223" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35781,7 +35784,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1224" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35807,7 +35810,7 @@
         <v>16</v>
       </c>
       <c r="G1225" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35833,7 +35836,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1226" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35859,7 +35862,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35885,7 +35888,7 @@
         <v>15.75</v>
       </c>
       <c r="G1228" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35911,7 +35914,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1229" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35937,7 +35940,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1230" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35963,7 +35966,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1231" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -35989,7 +35992,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -36015,7 +36018,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -36041,7 +36044,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1234" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -36067,7 +36070,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1235" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -36093,7 +36096,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1236" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -36119,7 +36122,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1237" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -36145,7 +36148,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1238" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -36171,7 +36174,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1239" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -36197,7 +36200,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -36223,7 +36226,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1241" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -36249,7 +36252,7 @@
         <v>19.5</v>
       </c>
       <c r="G1242" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -36275,7 +36278,7 @@
         <v>19</v>
       </c>
       <c r="G1243" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -36301,7 +36304,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1244" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -36327,7 +36330,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1245" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -36353,7 +36356,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1246" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -36379,7 +36382,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1247" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -36405,7 +36408,7 @@
         <v>18.75</v>
       </c>
       <c r="G1248" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -36431,7 +36434,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1249" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -36457,7 +36460,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1250" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -36483,7 +36486,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1251" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -36509,7 +36512,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -36535,7 +36538,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1253" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -36561,7 +36564,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -36587,7 +36590,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1255" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -36613,7 +36616,7 @@
         <v>19</v>
       </c>
       <c r="G1256" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36639,7 +36642,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36665,7 +36668,7 @@
         <v>19</v>
       </c>
       <c r="G1258" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36691,7 +36694,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1259" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36717,7 +36720,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1260" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36743,7 +36746,7 @@
         <v>19</v>
       </c>
       <c r="G1261" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36769,7 +36772,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1262" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36795,7 +36798,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36821,7 +36824,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1264" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36847,7 +36850,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1265" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36873,7 +36876,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1266" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36899,7 +36902,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1267" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36925,7 +36928,7 @@
         <v>18.75</v>
       </c>
       <c r="G1268" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36951,7 +36954,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1269" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -36977,7 +36980,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1270" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -37003,7 +37006,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1271" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -37029,7 +37032,7 @@
         <v>19</v>
       </c>
       <c r="G1272" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -37055,7 +37058,7 @@
         <v>20</v>
       </c>
       <c r="G1273" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -37081,7 +37084,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1274" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -37107,7 +37110,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1275" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -37133,7 +37136,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1276" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -37159,7 +37162,7 @@
         <v>21</v>
       </c>
       <c r="G1277" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -37185,7 +37188,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1278" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -37211,7 +37214,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1279" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -37237,7 +37240,7 @@
         <v>20</v>
       </c>
       <c r="G1280" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -37263,7 +37266,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1281" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -37289,7 +37292,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1282" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -37315,7 +37318,7 @@
         <v>20</v>
       </c>
       <c r="G1283" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -37341,7 +37344,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1284" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -37367,7 +37370,7 @@
         <v>20</v>
       </c>
       <c r="G1285" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -37393,7 +37396,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1286" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -37419,7 +37422,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1287" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -37445,7 +37448,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -37471,7 +37474,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1289" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -37497,7 +37500,7 @@
         <v>20</v>
       </c>
       <c r="G1290" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -37523,7 +37526,7 @@
         <v>20</v>
       </c>
       <c r="G1291" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -37549,7 +37552,7 @@
         <v>20.5</v>
       </c>
       <c r="G1292" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -37575,7 +37578,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1293" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -37601,7 +37604,7 @@
         <v>21</v>
       </c>
       <c r="G1294" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -37627,7 +37630,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1295" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -37653,7 +37656,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1296" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -37679,7 +37682,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1297" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37705,7 +37708,7 @@
         <v>21.5</v>
       </c>
       <c r="G1298" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -37731,7 +37734,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1299" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37757,7 +37760,7 @@
         <v>22</v>
       </c>
       <c r="G1300" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -37783,7 +37786,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1301" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37809,7 +37812,7 @@
         <v>22</v>
       </c>
       <c r="G1302" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37835,7 +37838,7 @@
         <v>21.5</v>
       </c>
       <c r="G1303" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37861,7 +37864,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1304" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37887,7 +37890,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1305" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37913,7 +37916,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -37939,7 +37942,7 @@
         <v>21</v>
       </c>
       <c r="G1307" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -37965,7 +37968,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1308" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -37991,7 +37994,7 @@
         <v>21</v>
       </c>
       <c r="G1309" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -38017,7 +38020,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1310" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -38043,7 +38046,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -38069,7 +38072,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1312" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -38095,7 +38098,7 @@
         <v>21.5</v>
       </c>
       <c r="G1313" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -38121,7 +38124,7 @@
         <v>21.5</v>
       </c>
       <c r="G1314" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -38147,7 +38150,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1315" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -38173,7 +38176,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1316" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -38199,7 +38202,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1317" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -38225,7 +38228,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1318" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -38251,7 +38254,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1319" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -38277,7 +38280,7 @@
         <v>22.5</v>
       </c>
       <c r="G1320" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38303,7 +38306,7 @@
         <v>23.5</v>
       </c>
       <c r="G1321" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -38329,7 +38332,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1322" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -38355,7 +38358,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1323" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -38381,7 +38384,7 @@
         <v>23.5</v>
       </c>
       <c r="G1324" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -38407,7 +38410,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1325" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -38433,7 +38436,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1326" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -38459,7 +38462,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -38485,7 +38488,7 @@
         <v>23</v>
       </c>
       <c r="G1328" t="s">
-        <v>695</v>
+        <v>549</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -38511,7 +38514,7 @@
         <v>23.5</v>
       </c>
       <c r="G1329" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -38537,7 +38540,7 @@
         <v>23.5</v>
       </c>
       <c r="G1330" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38563,7 +38566,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1331" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -38589,7 +38592,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1332" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -38615,7 +38618,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1333" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -38641,7 +38644,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -38667,7 +38670,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1335" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -38693,7 +38696,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -38719,7 +38722,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1337" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -38745,7 +38748,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1338" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -38771,7 +38774,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1339" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -38797,7 +38800,7 @@
         <v>23.5</v>
       </c>
       <c r="G1340" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -38927,7 +38930,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1345" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -39031,7 +39034,7 @@
         <v>23.5</v>
       </c>
       <c r="G1349" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -39161,7 +39164,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -39187,7 +39190,7 @@
         <v>23</v>
       </c>
       <c r="G1355" t="s">
-        <v>695</v>
+        <v>549</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39213,7 +39216,7 @@
         <v>23</v>
       </c>
       <c r="G1356" t="s">
-        <v>695</v>
+        <v>549</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -39239,7 +39242,7 @@
         <v>23</v>
       </c>
       <c r="G1357" t="s">
-        <v>695</v>
+        <v>549</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39265,7 +39268,7 @@
         <v>23</v>
       </c>
       <c r="G1358" t="s">
-        <v>695</v>
+        <v>549</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39317,7 +39320,7 @@
         <v>23</v>
       </c>
       <c r="G1360" t="s">
-        <v>695</v>
+        <v>549</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -69433,7 +69436,7 @@
     </row>
     <row r="2519">
       <c r="A2519" s="1" t="n">
-        <v>45986.6909953704</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2519" t="n">
         <v>7596</v>
@@ -69454,6 +69457,32 @@
         <v>1201</v>
       </c>
       <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.6910300926</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>6195</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>66.3000030517578</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>65.3000030517578</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>66.1999969482422</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H2520" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="1212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="1213">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23958683013916</t>
+    <t xml:space="preserve">9.23958778381348</t>
   </si>
   <si>
     <t xml:space="preserve">CMB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55656814575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31377410888672</t>
+    <t xml:space="preserve">9.556565284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31377506256104</t>
   </si>
   <si>
     <t xml:space="preserve">9.40144920349121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40819454193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44191455841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36098480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13842391967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32051753997803</t>
+    <t xml:space="preserve">9.40819358825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44191551208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36098575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13842487335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32051944732666</t>
   </si>
   <si>
     <t xml:space="preserve">9.26656532287598</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34075164794922</t>
+    <t xml:space="preserve">9.34075260162354</t>
   </si>
   <si>
     <t xml:space="preserve">9.2733097076416</t>
@@ -80,49 +80,49 @@
     <t xml:space="preserve">9.19237899780273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19912433624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10470294952393</t>
+    <t xml:space="preserve">9.19912338256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10470390319824</t>
   </si>
   <si>
     <t xml:space="preserve">8.84167861938477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77423667907715</t>
+    <t xml:space="preserve">8.77423572540283</t>
   </si>
   <si>
     <t xml:space="preserve">8.84842300415039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3628396987915</t>
+    <t xml:space="preserve">8.36283779144287</t>
   </si>
   <si>
     <t xml:space="preserve">8.32911777496338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61911869049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45051288604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4302806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63260841369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80121421813965</t>
+    <t xml:space="preserve">8.61911964416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45051383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43028259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63260936737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80121326446533</t>
   </si>
   <si>
     <t xml:space="preserve">9.22610092163086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25982093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07098197937012</t>
+    <t xml:space="preserve">9.25981998443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07098293304443</t>
   </si>
   <si>
     <t xml:space="preserve">8.87540054321289</t>
@@ -134,22 +134,22 @@
     <t xml:space="preserve">8.71353816986084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66632843017578</t>
+    <t xml:space="preserve">8.6663293838501</t>
   </si>
   <si>
     <t xml:space="preserve">8.89563179016113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81470108032227</t>
+    <t xml:space="preserve">8.81470203399658</t>
   </si>
   <si>
     <t xml:space="preserve">8.99679660797119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01028347015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90237712860107</t>
+    <t xml:space="preserve">9.01028442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90237617492676</t>
   </si>
   <si>
     <t xml:space="preserve">8.9765625</t>
@@ -158,58 +158,58 @@
     <t xml:space="preserve">9.18563365936279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17214584350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13168144226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34749507904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25307655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15865707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08447074890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540050506592</t>
+    <t xml:space="preserve">9.17214488983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13168048858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34749412536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25307750701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15865612030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08447170257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540145874023</t>
   </si>
   <si>
     <t xml:space="preserve">8.98330593109131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78772354125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78098011016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12493515014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03726100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21261024475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04400539398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09796047210693</t>
+    <t xml:space="preserve">8.7877254486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78098106384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1249361038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03726291656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21261119842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04400634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0979585647583</t>
   </si>
   <si>
     <t xml:space="preserve">9.20586681365967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38121604919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28679752349854</t>
+    <t xml:space="preserve">9.38121700286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28679656982422</t>
   </si>
   <si>
     <t xml:space="preserve">9.22100734710693</t>
@@ -221,34 +221,34 @@
     <t xml:space="preserve">9.19308662414551</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35363292694092</t>
+    <t xml:space="preserve">9.35363483428955</t>
   </si>
   <si>
     <t xml:space="preserve">9.4094762802124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.521164894104</t>
+    <t xml:space="preserve">9.52116203308105</t>
   </si>
   <si>
     <t xml:space="preserve">9.49324035644531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38853549957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9469633102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76547241210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77245330810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66774940490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82829570770264</t>
+    <t xml:space="preserve">9.38853645324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94696140289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76547336578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77245426177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66775035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82829666137695</t>
   </si>
   <si>
     <t xml:space="preserve">9.75151252746582</t>
@@ -263,31 +263,31 @@
     <t xml:space="preserve">9.55606365203857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47927951812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42343711853027</t>
+    <t xml:space="preserve">9.47928047180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42343902587891</t>
   </si>
   <si>
     <t xml:space="preserve">9.39551639556885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41645812988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34665489196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58398532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62586688995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63284873962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4653205871582</t>
+    <t xml:space="preserve">9.4164571762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34665393829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.583984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6258659362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63284683227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46531963348389</t>
   </si>
   <si>
     <t xml:space="preserve">9.48626041412354</t>
@@ -296,19 +296,19 @@
     <t xml:space="preserve">9.59096527099609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56304264068604</t>
+    <t xml:space="preserve">9.56304359436035</t>
   </si>
   <si>
     <t xml:space="preserve">9.53512287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12328338623047</t>
+    <t xml:space="preserve">9.12328433990479</t>
   </si>
   <si>
     <t xml:space="preserve">9.30477237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28383159637451</t>
+    <t xml:space="preserve">9.2838306427002</t>
   </si>
   <si>
     <t xml:space="preserve">9.20704746246338</t>
@@ -317,70 +317,70 @@
     <t xml:space="preserve">9.2768497467041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36061477661133</t>
+    <t xml:space="preserve">9.36061668395996</t>
   </si>
   <si>
     <t xml:space="preserve">9.29081058502197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29779148101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31873416900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36759471893311</t>
+    <t xml:space="preserve">9.29779052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31873321533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36759567260742</t>
   </si>
   <si>
     <t xml:space="preserve">9.47229957580566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52814197540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5072021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44437789916992</t>
+    <t xml:space="preserve">9.52814102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50720119476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44437885284424</t>
   </si>
   <si>
     <t xml:space="preserve">9.50022125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33269309997559</t>
+    <t xml:space="preserve">9.3326940536499</t>
   </si>
   <si>
     <t xml:space="preserve">9.32571220397949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13724422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14422416687012</t>
+    <t xml:space="preserve">9.13724517822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14422607421875</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120506286621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10932350158691</t>
+    <t xml:space="preserve">9.1093225479126</t>
   </si>
   <si>
     <t xml:space="preserve">9.03952026367188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92783451080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01159858703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07442092895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97669792175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86501216888428</t>
+    <t xml:space="preserve">8.92783546447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0115966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07442188262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9766960144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86501121520996</t>
   </si>
   <si>
     <t xml:space="preserve">8.85105133056641</t>
@@ -389,16 +389,16 @@
     <t xml:space="preserve">8.93481540679932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92085456848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95575523376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96971607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00461864471436</t>
+    <t xml:space="preserve">8.92085361480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95575714111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96971702575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00461673736572</t>
   </si>
   <si>
     <t xml:space="preserve">8.91387367248535</t>
@@ -407,22 +407,22 @@
     <t xml:space="preserve">8.87897205352783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80916786193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59976005554199</t>
+    <t xml:space="preserve">8.80916881561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59975910186768</t>
   </si>
   <si>
     <t xml:space="preserve">8.56485843658447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8161506652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83709144592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89991474151611</t>
+    <t xml:space="preserve">8.81614971160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83709049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8999137878418</t>
   </si>
   <si>
     <t xml:space="preserve">8.99763774871826</t>
@@ -434,13 +434,13 @@
     <t xml:space="preserve">8.96273612976074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08838176727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04649925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09536075592041</t>
+    <t xml:space="preserve">9.08838367462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04650115966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09536266326904</t>
   </si>
   <si>
     <t xml:space="preserve">9.66076850891113</t>
@@ -455,28 +455,28 @@
     <t xml:space="preserve">9.79339504241943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92602062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98186302185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0516672134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.414644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1912746429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2471160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493911743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1354312896729</t>
+    <t xml:space="preserve">9.9260196685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9818639755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0516662597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4146432876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1912727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2471151351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493921279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1354303359985</t>
   </si>
   <si>
     <t xml:space="preserve">10.2680568695068</t>
@@ -488,13 +488,13 @@
     <t xml:space="preserve">10.5402898788452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5891513824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4844465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6310329437256</t>
+    <t xml:space="preserve">10.5891523361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4844484329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6310338973999</t>
   </si>
   <si>
     <t xml:space="preserve">10.3588008880615</t>
@@ -512,55 +512,55 @@
     <t xml:space="preserve">10.4704856872559</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3867216110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.547269821167</t>
+    <t xml:space="preserve">10.3867235183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5472688674927</t>
   </si>
   <si>
     <t xml:space="preserve">10.344841003418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.477466583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4006834030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.435583114624</t>
+    <t xml:space="preserve">10.4774675369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4006814956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4355850219727</t>
   </si>
   <si>
     <t xml:space="preserve">10.3727617263794</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3657817840576</t>
+    <t xml:space="preserve">10.3657827377319</t>
   </si>
   <si>
     <t xml:space="preserve">10.3378610610962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2820177078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3797407150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6100931167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5542507171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6938562393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0917348861694</t>
+    <t xml:space="preserve">10.2820167541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3797416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6100940704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5542497634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6938552856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0917339324951</t>
   </si>
   <si>
     <t xml:space="preserve">11.0428733825684</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0358924865723</t>
+    <t xml:space="preserve">11.0358934402466</t>
   </si>
   <si>
     <t xml:space="preserve">11.0638132095337</t>
@@ -569,49 +569,49 @@
     <t xml:space="preserve">11.0847549438477</t>
   </si>
   <si>
-    <t xml:space="preserve">11.356987953186</t>
+    <t xml:space="preserve">11.3569869995117</t>
   </si>
   <si>
     <t xml:space="preserve">11.5175342559814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0899219512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9991788864136</t>
+    <t xml:space="preserve">12.0899209976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9991769790649</t>
   </si>
   <si>
     <t xml:space="preserve">12.0689811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1038818359375</t>
+    <t xml:space="preserve">12.1038827896118</t>
   </si>
   <si>
     <t xml:space="preserve">12.2853708267212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8228569030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9764223098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9903831481934</t>
+    <t xml:space="preserve">12.8228549957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9764232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9903841018677</t>
   </si>
   <si>
     <t xml:space="preserve">13.2486553192139</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1090469360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1230087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8926572799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9135980606079</t>
+    <t xml:space="preserve">13.1090478897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1230068206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8926591873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9135999679565</t>
   </si>
   <si>
     <t xml:space="preserve">12.8437957763672</t>
@@ -620,220 +620,220 @@
     <t xml:space="preserve">12.9624624252319</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1928119659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3952445983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8978261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9815893173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9327268600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0234727859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0304517745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1351566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0723323822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0025300979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2112550735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197383880615</t>
+    <t xml:space="preserve">13.1928129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.39524269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8978242874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9815902709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9327259063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0234718322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0304508209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1351585388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0723333358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0025310516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.211254119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197393417358</t>
   </si>
   <si>
     <t xml:space="preserve">14.1461658477783</t>
   </si>
   <si>
-    <t xml:space="preserve">14.081072807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9942922592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6688404083252</t>
+    <t xml:space="preserve">14.0810747146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9942893981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6688423156738</t>
   </si>
   <si>
     <t xml:space="preserve">14.3558988571167</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6833066940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0015239715576</t>
+    <t xml:space="preserve">13.6833057403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.001522064209</t>
   </si>
   <si>
     <t xml:space="preserve">13.9870586395264</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2691144943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3486680984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3414335250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2763471603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4282217025757</t>
+    <t xml:space="preserve">14.2691135406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3486661911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3414373397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.276346206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.42822265625</t>
   </si>
   <si>
     <t xml:space="preserve">14.5656337738037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3322448730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8457336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7589445114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3611745834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1876010894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9200115203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6307210922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636768341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3105506896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9272441864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0718870162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5492134094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4551935195923</t>
+    <t xml:space="preserve">15.3322477340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8457307815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7589464187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3611736297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1876049041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9200096130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6307249069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636777877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3105487823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9272432327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0718879699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5492105484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4551944732666</t>
   </si>
   <si>
     <t xml:space="preserve">15.2671566009521</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1731386184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8332233428955</t>
+    <t xml:space="preserve">15.1731376647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8332242965698</t>
   </si>
   <si>
     <t xml:space="preserve">15.1369781494141</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1152811050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9851016998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1514387130737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.028491973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2092990875244</t>
+    <t xml:space="preserve">15.1152801513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9851007461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1514415740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0284938812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2092962265015</t>
   </si>
   <si>
     <t xml:space="preserve">15.6649265289307</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6938581466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7661762237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9325199127197</t>
+    <t xml:space="preserve">15.6938552856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7661790847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9325170516968</t>
   </si>
   <si>
     <t xml:space="preserve">16.0410003662109</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9469833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6432285308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2816190719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2888517379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2599258422852</t>
+    <t xml:space="preserve">15.9469814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6432294845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2816181182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2888536453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2599229812622</t>
   </si>
   <si>
     <t xml:space="preserve">15.3250141143799</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2382307052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1586713790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0574235916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1803684234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2454595565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8983163833618</t>
+    <t xml:space="preserve">15.2382278442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1586742401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0574216842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1803712844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.245457649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8983125686646</t>
   </si>
   <si>
     <t xml:space="preserve">14.8693866729736</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8259935379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9634065628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9706373214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6813478469849</t>
+    <t xml:space="preserve">14.8259906768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9634037017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9706363677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6813488006592</t>
   </si>
   <si>
     <t xml:space="preserve">14.7536687850952</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6958131790161</t>
+    <t xml:space="preserve">14.6958141326904</t>
   </si>
   <si>
     <t xml:space="preserve">14.8910827636719</t>
@@ -842,31 +842,31 @@
     <t xml:space="preserve">14.4933128356934</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8549222946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6524181365967</t>
+    <t xml:space="preserve">14.8549194335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.652419090271</t>
   </si>
   <si>
     <t xml:space="preserve">14.6090278625488</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8476896286011</t>
+    <t xml:space="preserve">14.8476886749268</t>
   </si>
   <si>
     <t xml:space="preserve">15.1948337554932</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3394765853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4334955215454</t>
+    <t xml:space="preserve">15.3394746780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4334964752197</t>
   </si>
   <si>
     <t xml:space="preserve">16.2651977539062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9956512451172</t>
+    <t xml:space="preserve">16.9956493377686</t>
   </si>
   <si>
     <t xml:space="preserve">17.5742244720459</t>
@@ -875,34 +875,34 @@
     <t xml:space="preserve">18.6879806518555</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3986949920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4420909881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2178897857666</t>
+    <t xml:space="preserve">18.3986930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4420871734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2178916931152</t>
   </si>
   <si>
     <t xml:space="preserve">18.0804786682129</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1889610290527</t>
+    <t xml:space="preserve">18.1889629364014</t>
   </si>
   <si>
     <t xml:space="preserve">17.971996307373</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0081539154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8562793731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9647636413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6393165588379</t>
+    <t xml:space="preserve">18.0081577301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8562812805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9647655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6393127441406</t>
   </si>
   <si>
     <t xml:space="preserve">17.7622623443604</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">17.6031551361084</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5886878967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.538064956665</t>
+    <t xml:space="preserve">17.5886898040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5380630493164</t>
   </si>
   <si>
     <t xml:space="preserve">17.5019035339355</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">17.3211002349854</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2849349975586</t>
+    <t xml:space="preserve">17.2849388122559</t>
   </si>
   <si>
     <t xml:space="preserve">17.0462760925293</t>
@@ -935,91 +935,91 @@
     <t xml:space="preserve">17.2632427215576</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0968990325928</t>
+    <t xml:space="preserve">17.0969009399414</t>
   </si>
   <si>
     <t xml:space="preserve">17.3283309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3572597503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4006519317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3789577484131</t>
+    <t xml:space="preserve">17.3572616577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4006500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3789539337158</t>
   </si>
   <si>
     <t xml:space="preserve">17.2921714782715</t>
   </si>
   <si>
-    <t xml:space="preserve">17.342794418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1692218780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5906467437744</t>
+    <t xml:space="preserve">17.3427925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1692199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.590648651123</t>
   </si>
   <si>
     <t xml:space="preserve">16.6268081665039</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9233264923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3447532653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7083206176758</t>
+    <t xml:space="preserve">16.9233283996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3447513580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7083187103271</t>
   </si>
   <si>
     <t xml:space="preserve">16.1133251190186</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9180517196655</t>
+    <t xml:space="preserve">15.9180545806885</t>
   </si>
   <si>
     <t xml:space="preserve">15.6504611968994</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4749336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3013591766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5761833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5110950469971</t>
+    <t xml:space="preserve">16.4749317169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.301362991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5761814117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5110912322998</t>
   </si>
   <si>
     <t xml:space="preserve">16.5617160797119</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0699272155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5255565643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4098415374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2073421478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8746614456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.243501663208</t>
+    <t xml:space="preserve">16.0699310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5255584716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4098434448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2073402404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8746585845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2434997558594</t>
   </si>
   <si>
     <t xml:space="preserve">16.4460029602051</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2001094818115</t>
+    <t xml:space="preserve">16.2001075744629</t>
   </si>
   <si>
     <t xml:space="preserve">15.8312664031982</t>
@@ -1028,31 +1028,31 @@
     <t xml:space="preserve">15.8601961135864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8529605865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6287651062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4696578979492</t>
+    <t xml:space="preserve">15.8529634475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6287679672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4696588516235</t>
   </si>
   <si>
     <t xml:space="preserve">15.4624242782593</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6215353012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9976072311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.236270904541</t>
+    <t xml:space="preserve">15.6215343475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9976100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2362728118896</t>
   </si>
   <si>
     <t xml:space="preserve">16.163948059082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2724323272705</t>
+    <t xml:space="preserve">16.2724285125732</t>
   </si>
   <si>
     <t xml:space="preserve">16.7786846160889</t>
@@ -1064,55 +1064,55 @@
     <t xml:space="preserve">16.4532356262207</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7425212860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.59787940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7063598632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8510055541992</t>
+    <t xml:space="preserve">16.7425231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5978832244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7063617706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8510074615479</t>
   </si>
   <si>
     <t xml:space="preserve">17.0318088531494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2126159667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4295787811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9594898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3809108734131</t>
+    <t xml:space="preserve">17.2126140594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4295825958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9594879150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3809127807617</t>
   </si>
   <si>
     <t xml:space="preserve">15.9831438064575</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9108200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.730016708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3684062957764</t>
+    <t xml:space="preserve">15.9108219146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7300157546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.368408203125</t>
   </si>
   <si>
     <t xml:space="preserve">15.4045677185059</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4768896102905</t>
+    <t xml:space="preserve">15.4768905639648</t>
   </si>
   <si>
     <t xml:space="preserve">15.8023386001587</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6702003479004</t>
+    <t xml:space="preserve">16.670202255249</t>
   </si>
   <si>
     <t xml:space="preserve">17.1402950286865</t>
@@ -1121,25 +1121,25 @@
     <t xml:space="preserve">17.1041297912598</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8148460388184</t>
+    <t xml:space="preserve">16.8148441314697</t>
   </si>
   <si>
     <t xml:space="preserve">17.0679721832275</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8871650695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8273487091064</t>
+    <t xml:space="preserve">16.8871688842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8273525238037</t>
   </si>
   <si>
     <t xml:space="preserve">17.6827087402344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3934211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2487754821777</t>
+    <t xml:space="preserve">17.3934192657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2487773895264</t>
   </si>
   <si>
     <t xml:space="preserve">17.7550296783447</t>
@@ -1148,112 +1148,112 @@
     <t xml:space="preserve">17.8996753692627</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5867309570312</t>
+    <t xml:space="preserve">18.5867328643799</t>
   </si>
   <si>
     <t xml:space="preserve">18.6590557098389</t>
   </si>
   <si>
+    <t xml:space="preserve">19.0206623077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5428009033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2444381713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9157524108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4378910064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6546897888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4682102203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6173896789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0952548980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8714828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9460716247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7968921661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9018020629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3050746917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7899169921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8341865539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1698474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3936195373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5055046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8038654327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8784580230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6919803619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3190250396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4239368438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1325492858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3563213348389</t>
+  </si>
+  <si>
     <t xml:space="preserve">19.0206642150879</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5427989959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2444381713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9157581329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4378871917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6546878814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4682121276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6173896789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0952568054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8714809417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9460735321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7968921661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9018020629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3050746917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7899131774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8341865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1698455810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3936176300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5055065155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8038673400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8784580230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6919822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3190288543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4239368438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1325492858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3563232421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0206661224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7292785644531</t>
+    <t xml:space="preserve">19.7292766571045</t>
   </si>
   <si>
     <t xml:space="preserve">18.7223014831543</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9087791442871</t>
+    <t xml:space="preserve">18.9087753295898</t>
   </si>
   <si>
     <t xml:space="preserve">18.6477108001709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5731163024902</t>
+    <t xml:space="preserve">18.5731201171875</t>
   </si>
   <si>
     <t xml:space="preserve">18.5358238220215</t>
   </si>
   <si>
-    <t xml:space="preserve">17.976390838623</t>
+    <t xml:space="preserve">17.9763927459717</t>
   </si>
   <si>
     <t xml:space="preserve">18.1255722045898</t>
@@ -1262,13 +1262,13 @@
     <t xml:space="preserve">18.4612331390381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7595958709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6104145050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3493480682373</t>
+    <t xml:space="preserve">18.7595977783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6104164123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.34934425354</t>
   </si>
   <si>
     <t xml:space="preserve">18.6850051879883</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">18.3120517730713</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4985275268555</t>
+    <t xml:space="preserve">18.4985256195068</t>
   </si>
   <si>
     <t xml:space="preserve">19.2817325592041</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">19.0579586029053</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1628704071045</t>
+    <t xml:space="preserve">18.1628684997559</t>
   </si>
   <si>
     <t xml:space="preserve">18.0136871337891</t>
@@ -1298,16 +1298,16 @@
     <t xml:space="preserve">17.1558933258057</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1862144470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5894870758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1419401168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9554634094238</t>
+    <t xml:space="preserve">16.1862125396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.589485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1419410705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9554624557495</t>
   </si>
   <si>
     <t xml:space="preserve">16.0370311737061</t>
@@ -1316,10 +1316,10 @@
     <t xml:space="preserve">16.5218715667725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6640758514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1046447753906</t>
+    <t xml:space="preserve">15.6640787124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1046438217163</t>
   </si>
   <si>
     <t xml:space="preserve">14.9927597045898</t>
@@ -1328,76 +1328,76 @@
     <t xml:space="preserve">15.0300550460815</t>
   </si>
   <si>
-    <t xml:space="preserve">14.768985748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3661947250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5153770446777</t>
+    <t xml:space="preserve">14.7689876556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3661937713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5153751373291</t>
   </si>
   <si>
     <t xml:space="preserve">14.6198053359985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8883323669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2538270950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2608013153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.925145149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7759637832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7013731002808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5521898269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6267786026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5148944854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2911233901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2165298461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1792345046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8505525588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8132572174072</t>
+    <t xml:space="preserve">14.8883304595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2538251876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2608032226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.925142288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7759628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7013711929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5521907806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6267824172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.514892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2911214828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2165288925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1792364120483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8505544662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8132581710815</t>
   </si>
   <si>
     <t xml:space="preserve">16.0743236541748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8878479003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4030075073242</t>
+    <t xml:space="preserve">15.8878488540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4030084609985</t>
   </si>
   <si>
     <t xml:space="preserve">14.9032487869263</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7093124389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4403047561646</t>
+    <t xml:space="preserve">14.7093143463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4403028488159</t>
   </si>
   <si>
     <t xml:space="preserve">16.1116218566895</t>
@@ -1415,79 +1415,79 @@
     <t xml:space="preserve">16.4845771789551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7829399108887</t>
+    <t xml:space="preserve">16.7829360961914</t>
   </si>
   <si>
     <t xml:space="preserve">16.8948230743408</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7386684417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657140731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8435773849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8584966659546</t>
+    <t xml:space="preserve">15.7386665344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657112121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8435764312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8584957122803</t>
   </si>
   <si>
     <t xml:space="preserve">15.0673503875732</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8734149932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9181671142578</t>
+    <t xml:space="preserve">14.8734140396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9181680679321</t>
   </si>
   <si>
     <t xml:space="preserve">16.409984588623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2235069274902</t>
+    <t xml:space="preserve">16.2235088348389</t>
   </si>
   <si>
     <t xml:space="preserve">16.2980976104736</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6710529327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7083492279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7456436157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6337566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9321212768555</t>
+    <t xml:space="preserve">16.6710510253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.708345413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7456455230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6337585449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9321193695068</t>
   </si>
   <si>
     <t xml:space="preserve">16.8575305938721</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0067100524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3796634674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2304821014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5288486480713</t>
+    <t xml:space="preserve">17.0067119598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3796653747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2304840087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5288467407227</t>
   </si>
   <si>
     <t xml:space="preserve">18.3432388305664</t>
   </si>
   <si>
-    <t xml:space="preserve">17.722749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6756744384766</t>
+    <t xml:space="preserve">17.7227516174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6756725311279</t>
   </si>
   <si>
     <t xml:space="preserve">16.7532348632812</t>
@@ -1496,49 +1496,49 @@
     <t xml:space="preserve">16.3654289245605</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0939636230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6673765182495</t>
+    <t xml:space="preserve">16.0939655303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6673774719238</t>
   </si>
   <si>
     <t xml:space="preserve">15.6285972595215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0468854904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2640571594238</t>
+    <t xml:space="preserve">15.0468864440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2640600204468</t>
   </si>
   <si>
     <t xml:space="preserve">15.7061567306519</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5898180007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5122528076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7449359893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950820922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0158643722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1864967346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4191818237305</t>
+    <t xml:space="preserve">15.5898170471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5122556686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7449388504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950839996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0158624649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1864957809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4191808700562</t>
   </si>
   <si>
     <t xml:space="preserve">15.4967412948608</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5510358810425</t>
+    <t xml:space="preserve">15.5510339736938</t>
   </si>
   <si>
     <t xml:space="preserve">15.3261079788208</t>
@@ -1547,94 +1547,94 @@
     <t xml:space="preserve">15.2795705795288</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8612804412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0164012908936</t>
+    <t xml:space="preserve">15.8612785339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0164031982422</t>
   </si>
   <si>
     <t xml:space="preserve">15.9388399124146</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9000625610352</t>
+    <t xml:space="preserve">15.9000597000122</t>
   </si>
   <si>
     <t xml:space="preserve">15.7837190628052</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8224973678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3266487121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7920150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0246982574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9083557128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4817695617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5593338012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0551853179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4042072296143</t>
+    <t xml:space="preserve">15.8224983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3266468048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.792013168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0247001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9083576202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4817714691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5593318939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0551834106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4042091369629</t>
   </si>
   <si>
     <t xml:space="preserve">16.1327419281006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2878665924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1715240478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9776229858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3881559371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346933364868</t>
+    <t xml:space="preserve">16.2878684997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1715278625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9776201248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3881549835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346923828125</t>
   </si>
   <si>
     <t xml:space="preserve">16.2103061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4429893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5981101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5205516815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6368942260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2490863800049</t>
+    <t xml:space="preserve">16.4429912567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5981121063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5205497741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6368923187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2490882873535</t>
   </si>
   <si>
     <t xml:space="preserve">16.8307971954346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9859180450439</t>
+    <t xml:space="preserve">16.9859199523926</t>
   </si>
   <si>
     <t xml:space="preserve">17.8390941619873</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5676288604736</t>
+    <t xml:space="preserve">17.567626953125</t>
   </si>
   <si>
     <t xml:space="preserve">17.9942150115967</t>
@@ -1646,13 +1646,13 @@
     <t xml:space="preserve">18.2656784057617</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8473873138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5371437072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0717735290527</t>
+    <t xml:space="preserve">18.8473892211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.537145614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.07177734375</t>
   </si>
   <si>
     <t xml:space="preserve">18.4595832824707</t>
@@ -1664,19 +1664,19 @@
     <t xml:space="preserve">18.9249496459961</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1576366424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0025119781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0412902832031</t>
+    <t xml:space="preserve">19.1576328277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0025100708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0412940979004</t>
   </si>
   <si>
     <t xml:space="preserve">18.3044605255127</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1493396759033</t>
+    <t xml:space="preserve">18.1493377685547</t>
   </si>
   <si>
     <t xml:space="preserve">18.0329971313477</t>
@@ -1685,28 +1685,28 @@
     <t xml:space="preserve">18.226900100708</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4208030700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.498363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1105556488037</t>
+    <t xml:space="preserve">18.4208011627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4983654022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1105575561523</t>
   </si>
   <si>
     <t xml:space="preserve">17.6839714050293</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8086090087891</t>
+    <t xml:space="preserve">18.8086071014404</t>
   </si>
   <si>
     <t xml:space="preserve">18.3820209503174</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1881198883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.916654586792</t>
+    <t xml:space="preserve">18.1881160736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9166526794434</t>
   </si>
   <si>
     <t xml:space="preserve">17.9554347991943</t>
@@ -1715,37 +1715,37 @@
     <t xml:space="preserve">17.606409072876</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6451873779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.141040802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1022605895996</t>
+    <t xml:space="preserve">17.6451892852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1410427093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.102258682251</t>
   </si>
   <si>
     <t xml:space="preserve">17.29616355896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1244506835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7676668167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5577087402344</t>
+    <t xml:space="preserve">15.1244478225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7676687240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5577116012573</t>
   </si>
   <si>
     <t xml:space="preserve">13.9610300064087</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0302934646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1854162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1388807296753</t>
+    <t xml:space="preserve">13.030294418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1854152679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1388788223267</t>
   </si>
   <si>
     <t xml:space="preserve">13.5732221603394</t>
@@ -1754,31 +1754,31 @@
     <t xml:space="preserve">13.2629776000977</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1699047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.952733039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5649251937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7582893371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5566301345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8585786819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7810153961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3156490325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8197984695435</t>
+    <t xml:space="preserve">13.1699028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9527339935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5649261474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7582883834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5566291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8585796356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7810173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3156480789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8197975158691</t>
   </si>
   <si>
     <t xml:space="preserve">11.1300430297852</t>
@@ -1790,37 +1790,37 @@
     <t xml:space="preserve">12.2546806335449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9056558609009</t>
+    <t xml:space="preserve">11.9056549072266</t>
   </si>
   <si>
     <t xml:space="preserve">11.6341905593872</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0219974517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0607767105103</t>
+    <t xml:space="preserve">12.0219984054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0607786178589</t>
   </si>
   <si>
     <t xml:space="preserve">11.8280935287476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4790697097778</t>
+    <t xml:space="preserve">11.4790687561035</t>
   </si>
   <si>
     <t xml:space="preserve">11.7117519378662</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6729717254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5954093933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2851648330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4015054702759</t>
+    <t xml:space="preserve">11.6729707717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5954113006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2851657867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4015064239502</t>
   </si>
   <si>
     <t xml:space="preserve">11.7505321502686</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">10.9749193191528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5095529556274</t>
+    <t xml:space="preserve">10.5095520019531</t>
   </si>
   <si>
     <t xml:space="preserve">10.5871133804321</t>
@@ -1841,118 +1841,124 @@
     <t xml:space="preserve">11.2463846206665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2159004211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3710222244263</t>
+    <t xml:space="preserve">12.2159013748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3710231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0773696899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1181735992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0365676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8733501434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8325471878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.199782371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6078233718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2813901901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4245080947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5469198226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5061149597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.750940322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9549589157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5262145996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7710371017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6894311904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3221921920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4038009643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5877227783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.465311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6285285949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9141540527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2405881881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9957628250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1589794158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7917423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3837022781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2204875946045</t>
   </si>
   <si>
     <t xml:space="preserve">14.0773706436157</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1181745529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0365686416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8733520507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8325471878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.199782371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6078214645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2813911437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4245090484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5469198226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5061149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7509393692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9549589157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5262136459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7710371017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6894311904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3221960067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4038028717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5877237319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.465311050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6285266876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9141540527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2405872344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9957618713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1589775085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7917423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3837032318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2204885482788</t>
-  </si>
-  <si>
     <t xml:space="preserve">13.3429002761841</t>
   </si>
   <si>
     <t xml:space="preserve">13.7101354598999</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0572710037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2612924575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0980758666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4860172271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.85325050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7308406829834</t>
+    <t xml:space="preserve">13.0572719573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.138879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2612905502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0980749130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4860153198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8532524108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7308397293091</t>
   </si>
   <si>
     <t xml:space="preserve">12.6900367736816</t>
@@ -1964,43 +1970,43 @@
     <t xml:space="preserve">12.7716436386108</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8526468276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2606868743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4239015579224</t>
+    <t xml:space="preserve">14.8526458740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.260684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4239025115967</t>
   </si>
   <si>
     <t xml:space="preserve">16.0767650604248</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9135503768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5055093765259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6687250137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5871171951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3014917373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3830976486206</t>
+    <t xml:space="preserve">15.9135494232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5055103302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6687259674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5871181488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3014907836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3830995559692</t>
   </si>
   <si>
     <t xml:space="preserve">15.3422937393188</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7503328323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2198829650879</t>
+    <t xml:space="preserve">15.7503318786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2198820114136</t>
   </si>
   <si>
     <t xml:space="preserve">15.1790781021118</t>
@@ -2009,16 +2015,16 @@
     <t xml:space="preserve">15.4647073745728</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3215885162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1583728790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8112392425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.708927154541</t>
+    <t xml:space="preserve">16.321590423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.158374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8112354278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7089252471924</t>
   </si>
   <si>
     <t xml:space="preserve">17.1376705169678</t>
@@ -2027,7 +2033,7 @@
     <t xml:space="preserve">17.3824920654297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8928470611572</t>
+    <t xml:space="preserve">16.8928451538086</t>
   </si>
   <si>
     <t xml:space="preserve">16.1991767883301</t>
@@ -2036,22 +2042,22 @@
     <t xml:space="preserve">16.484806060791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.648021697998</t>
+    <t xml:space="preserve">16.6480197906494</t>
   </si>
   <si>
     <t xml:space="preserve">16.5664138793945</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2399826049805</t>
+    <t xml:space="preserve">16.2399806976318</t>
   </si>
   <si>
     <t xml:space="preserve">16.4031982421875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7296314239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2192783355713</t>
+    <t xml:space="preserve">16.7296276092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2192764282227</t>
   </si>
   <si>
     <t xml:space="preserve">17.4640998840332</t>
@@ -2066,28 +2072,28 @@
     <t xml:space="preserve">18.0353584289551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9744529724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8721408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.11696434021</t>
+    <t xml:space="preserve">16.9744510650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.872142791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1169662475586</t>
   </si>
   <si>
     <t xml:space="preserve">18.1985721588135</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3617897033691</t>
+    <t xml:space="preserve">18.3617858886719</t>
   </si>
   <si>
     <t xml:space="preserve">19.1778678894043</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8514385223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6882209777832</t>
+    <t xml:space="preserve">18.8514347076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6882190704346</t>
   </si>
   <si>
     <t xml:space="preserve">19.0962600708008</t>
@@ -2096,10 +2102,10 @@
     <t xml:space="preserve">18.6066131591797</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9330463409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2594776153564</t>
+    <t xml:space="preserve">18.9330444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2594757080078</t>
   </si>
   <si>
     <t xml:space="preserve">19.3410835266113</t>
@@ -2108,7 +2114,7 @@
     <t xml:space="preserve">19.4226913452148</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0146503448486</t>
+    <t xml:space="preserve">19.0146522521973</t>
   </si>
   <si>
     <t xml:space="preserve">19.9123382568359</t>
@@ -2117,13 +2123,10 @@
     <t xml:space="preserve">19.8276062011719</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9123401641846</t>
-  </si>
-  <si>
     <t xml:space="preserve">19.4886722564697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6581420898438</t>
+    <t xml:space="preserve">19.6581401824951</t>
   </si>
   <si>
     <t xml:space="preserve">19.5734062194824</t>
@@ -2132,31 +2135,31 @@
     <t xml:space="preserve">19.403938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9970741271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3360080718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1665382385254</t>
+    <t xml:space="preserve">19.9970722198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3360061645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.166540145874</t>
   </si>
   <si>
     <t xml:space="preserve">19.319206237793</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0650081634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6413383483887</t>
+    <t xml:space="preserve">19.0650062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6413402557373</t>
   </si>
   <si>
     <t xml:space="preserve">19.7428703308105</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0818042755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4207382202148</t>
+    <t xml:space="preserve">20.08180809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4207401275635</t>
   </si>
   <si>
     <t xml:space="preserve">20.5054740905762</t>
@@ -2168,7 +2171,7 @@
     <t xml:space="preserve">20.9291400909424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1833400726318</t>
+    <t xml:space="preserve">21.1833419799805</t>
   </si>
   <si>
     <t xml:space="preserve">20.759672164917</t>
@@ -2180,40 +2183,40 @@
     <t xml:space="preserve">22.7085380554199</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0306720733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4543418884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2001419067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6238059997559</t>
+    <t xml:space="preserve">22.0306739807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4543399810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2001399993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6238079071045</t>
   </si>
   <si>
     <t xml:space="preserve">22.7932739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0474739074707</t>
+    <t xml:space="preserve">23.0474758148193</t>
   </si>
   <si>
     <t xml:space="preserve">23.6406059265137</t>
   </si>
   <si>
-    <t xml:space="preserve">23.555871963501</t>
+    <t xml:space="preserve">23.5558738708496</t>
   </si>
   <si>
     <t xml:space="preserve">23.3016738891602</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4711418151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3864078521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7253398895264</t>
+    <t xml:space="preserve">23.4711399078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3864059448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.725341796875</t>
   </si>
   <si>
     <t xml:space="preserve">23.1322078704834</t>
@@ -2225,7 +2228,7 @@
     <t xml:space="preserve">21.9459400177002</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8780078887939</t>
+    <t xml:space="preserve">22.8780059814453</t>
   </si>
   <si>
     <t xml:space="preserve">24.1490077972412</t>
@@ -2237,150 +2240,150 @@
     <t xml:space="preserve">24.9116077423096</t>
   </si>
   <si>
+    <t xml:space="preserve">24.2337417602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2505397796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8100757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5726737976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.403205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4879398345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.081075668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5047416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3352737426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4200077056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7589416503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2673416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4368076324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.521541595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8772754669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5719470977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3177433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9788074493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1482753753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2330093383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9620094299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0299415588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4704093933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4536094665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3856773376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7078094482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1314754486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2841415405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6742076873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0131416320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8436756134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3520755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.606273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8268756866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1826076507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0978736877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9284076690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6910095214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5390739440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0642738342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9627418518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3184757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8948078155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9795398712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5261859893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.730188369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2608528137207</t>
+  </si>
+  <si>
     <t xml:space="preserve">24.2337398529053</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2505397796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8100757598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5726737976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4032077789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4879398345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0810775756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5047397613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3352737426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4200077056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7589416503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2673416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4368095397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5215396881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8772773742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5719432830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3177433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9788093566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1482791900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2330093383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.962007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0299396514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4704093933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4536094665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3856754302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7078094482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1314754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.284143447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6742076873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0131416320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8436737060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3520755767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6062755584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8268737792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1826057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0978736877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.928409576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6910076141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5390758514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0642738342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.962739944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.318473815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8948078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9795398712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5261859893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7301864624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2608528137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2337379455566</t>
-  </si>
-  <si>
     <t xml:space="preserve">23.9684085845947</t>
   </si>
   <si>
@@ -2402,13 +2405,13 @@
     <t xml:space="preserve">24.8528518676758</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2950706481934</t>
+    <t xml:space="preserve">25.295072555542</t>
   </si>
   <si>
     <t xml:space="preserve">25.2066268920898</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5875148773193</t>
+    <t xml:space="preserve">24.587516784668</t>
   </si>
   <si>
     <t xml:space="preserve">24.3221855163574</t>
@@ -2420,19 +2423,19 @@
     <t xml:space="preserve">22.2879657745361</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4648551940918</t>
+    <t xml:space="preserve">22.4648532867432</t>
   </si>
   <si>
     <t xml:space="preserve">21.8457450866699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7573013305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4035243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6688537597656</t>
+    <t xml:space="preserve">21.7572994232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4035224914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6688556671143</t>
   </si>
   <si>
     <t xml:space="preserve">21.226634979248</t>
@@ -2441,7 +2444,7 @@
     <t xml:space="preserve">21.9341869354248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5804100036621</t>
+    <t xml:space="preserve">21.5804119110107</t>
   </si>
   <si>
     <t xml:space="preserve">21.1381893157959</t>
@@ -2456,7 +2459,7 @@
     <t xml:space="preserve">25.1181831359863</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6759624481201</t>
+    <t xml:space="preserve">24.6759605407715</t>
   </si>
   <si>
     <t xml:space="preserve">22.9955196380615</t>
@@ -2480,16 +2483,16 @@
     <t xml:space="preserve">23.0839653015137</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1724109649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.376407623291</t>
+    <t xml:space="preserve">23.1724090576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3764095306396</t>
   </si>
   <si>
     <t xml:space="preserve">22.1995220184326</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0226306915283</t>
+    <t xml:space="preserve">22.022632598877</t>
   </si>
   <si>
     <t xml:space="preserve">21.0497455596924</t>
@@ -2501,43 +2504,43 @@
     <t xml:space="preserve">20.6959686279297</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3150768280029</t>
+    <t xml:space="preserve">21.3150787353516</t>
   </si>
   <si>
     <t xml:space="preserve">24.7644062042236</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7372951507568</t>
+    <t xml:space="preserve">25.7372932434082</t>
   </si>
   <si>
     <t xml:space="preserve">25.0297393798828</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9412937164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5604038238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4719619750977</t>
+    <t xml:space="preserve">24.9412956237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5604057312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.471960067749</t>
   </si>
   <si>
     <t xml:space="preserve">25.6488494873047</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9141807556152</t>
+    <t xml:space="preserve">25.9141826629639</t>
   </si>
   <si>
     <t xml:space="preserve">27.0639591217041</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2408466339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1524028778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5061798095703</t>
+    <t xml:space="preserve">27.2408447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1524047851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5061817169189</t>
   </si>
   <si>
     <t xml:space="preserve">27.5946254730225</t>
@@ -2546,7 +2549,7 @@
     <t xml:space="preserve">27.3292903900146</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7101821899414</t>
+    <t xml:space="preserve">26.7101802825928</t>
   </si>
   <si>
     <t xml:space="preserve">26.7986240386963</t>
@@ -2555,7 +2558,7 @@
     <t xml:space="preserve">26.8870697021484</t>
   </si>
   <si>
-    <t xml:space="preserve">26.975513458252</t>
+    <t xml:space="preserve">26.9755153656006</t>
   </si>
   <si>
     <t xml:space="preserve">27.4177360534668</t>
@@ -2573,22 +2576,22 @@
     <t xml:space="preserve">26.3564033508301</t>
   </si>
   <si>
-    <t xml:space="preserve">25.825740814209</t>
+    <t xml:space="preserve">25.8257389068604</t>
   </si>
   <si>
     <t xml:space="preserve">26.0026264190674</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1795177459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6217365264893</t>
+    <t xml:space="preserve">26.179515838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6217384338379</t>
   </si>
   <si>
     <t xml:space="preserve">26.2679595947266</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8599548339844</t>
+    <t xml:space="preserve">27.859956741333</t>
   </si>
   <si>
     <t xml:space="preserve">28.7855377197266</t>
@@ -2603,9 +2606,6 @@
     <t xml:space="preserve">27.7673988342285</t>
   </si>
   <si>
-    <t xml:space="preserve">27.859956741333</t>
-  </si>
-  <si>
     <t xml:space="preserve">29.5259990692139</t>
   </si>
   <si>
@@ -3648,6 +3648,9 @@
   </si>
   <si>
     <t xml:space="preserve">68.4000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3000030517578</t>
   </si>
 </sst>
 </file>
@@ -34372,7 +34375,7 @@
         <v>17.25</v>
       </c>
       <c r="G1169" t="s">
-        <v>611</v>
+        <v>639</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34606,7 +34609,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1178" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -34814,7 +34817,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1186" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34918,7 +34921,7 @@
         <v>17.25</v>
       </c>
       <c r="G1190" t="s">
-        <v>611</v>
+        <v>639</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -35100,7 +35103,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1197" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35126,7 +35129,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -35178,7 +35181,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1200" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -35282,7 +35285,7 @@
         <v>16</v>
       </c>
       <c r="G1204" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -35334,7 +35337,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1206" t="s">
-        <v>577</v>
+        <v>643</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35360,7 +35363,7 @@
         <v>16</v>
       </c>
       <c r="G1207" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -35386,7 +35389,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1208" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -35412,7 +35415,7 @@
         <v>16.25</v>
       </c>
       <c r="G1209" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -35490,7 +35493,7 @@
         <v>17.25</v>
       </c>
       <c r="G1212" t="s">
-        <v>611</v>
+        <v>639</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -35568,7 +35571,7 @@
         <v>17.25</v>
       </c>
       <c r="G1215" t="s">
-        <v>611</v>
+        <v>639</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35776,7 +35779,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1223" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35802,7 +35805,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1224" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35828,7 +35831,7 @@
         <v>16</v>
       </c>
       <c r="G1225" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35854,7 +35857,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1226" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35880,7 +35883,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35906,7 +35909,7 @@
         <v>15.75</v>
       </c>
       <c r="G1228" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35932,7 +35935,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1229" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35958,7 +35961,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1230" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35984,7 +35987,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1231" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -36010,7 +36013,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -36062,7 +36065,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1234" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -36088,7 +36091,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1235" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -36166,7 +36169,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1238" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -36192,7 +36195,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1239" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -36218,7 +36221,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -36244,7 +36247,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1241" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -36270,7 +36273,7 @@
         <v>19.5</v>
       </c>
       <c r="G1242" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -36296,7 +36299,7 @@
         <v>19</v>
       </c>
       <c r="G1243" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -36322,7 +36325,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1244" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -36348,7 +36351,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1245" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -36374,7 +36377,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1246" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -36400,7 +36403,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1247" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -36426,7 +36429,7 @@
         <v>18.75</v>
       </c>
       <c r="G1248" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -36452,7 +36455,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1249" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -36478,7 +36481,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1250" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -36504,7 +36507,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1251" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -36530,7 +36533,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -36556,7 +36559,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1253" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -36582,7 +36585,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -36608,7 +36611,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1255" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -36634,7 +36637,7 @@
         <v>19</v>
       </c>
       <c r="G1256" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36660,7 +36663,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36686,7 +36689,7 @@
         <v>19</v>
       </c>
       <c r="G1258" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36712,7 +36715,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1259" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36738,7 +36741,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1260" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36764,7 +36767,7 @@
         <v>19</v>
       </c>
       <c r="G1261" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36790,7 +36793,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1262" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36816,7 +36819,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36842,7 +36845,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1264" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36868,7 +36871,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1265" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36894,7 +36897,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1266" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36920,7 +36923,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1267" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36946,7 +36949,7 @@
         <v>18.75</v>
       </c>
       <c r="G1268" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36972,7 +36975,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1269" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -36998,7 +37001,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1270" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -37024,7 +37027,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1271" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -37050,7 +37053,7 @@
         <v>19</v>
       </c>
       <c r="G1272" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -37076,7 +37079,7 @@
         <v>20</v>
       </c>
       <c r="G1273" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -37102,7 +37105,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1274" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -37128,7 +37131,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1275" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -37154,7 +37157,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1276" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -37180,7 +37183,7 @@
         <v>21</v>
       </c>
       <c r="G1277" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -37206,7 +37209,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1278" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -37232,7 +37235,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1279" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -37258,7 +37261,7 @@
         <v>20</v>
       </c>
       <c r="G1280" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -37284,7 +37287,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1281" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -37310,7 +37313,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1282" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -37336,7 +37339,7 @@
         <v>20</v>
       </c>
       <c r="G1283" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -37362,7 +37365,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1284" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -37388,7 +37391,7 @@
         <v>20</v>
       </c>
       <c r="G1285" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -37414,7 +37417,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1286" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -37440,7 +37443,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1287" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -37466,7 +37469,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -37492,7 +37495,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1289" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -37518,7 +37521,7 @@
         <v>20</v>
       </c>
       <c r="G1290" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -37544,7 +37547,7 @@
         <v>20</v>
       </c>
       <c r="G1291" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -37570,7 +37573,7 @@
         <v>20.5</v>
       </c>
       <c r="G1292" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -37596,7 +37599,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1293" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -37622,7 +37625,7 @@
         <v>21</v>
       </c>
       <c r="G1294" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -37648,7 +37651,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1295" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -37674,7 +37677,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1296" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -37700,7 +37703,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1297" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37726,7 +37729,7 @@
         <v>21.5</v>
       </c>
       <c r="G1298" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -37752,7 +37755,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1299" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37778,7 +37781,7 @@
         <v>22</v>
       </c>
       <c r="G1300" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -37804,7 +37807,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1301" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37830,7 +37833,7 @@
         <v>22</v>
       </c>
       <c r="G1302" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37856,7 +37859,7 @@
         <v>21.5</v>
       </c>
       <c r="G1303" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37882,7 +37885,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1304" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37908,7 +37911,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1305" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37934,7 +37937,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -37960,7 +37963,7 @@
         <v>21</v>
       </c>
       <c r="G1307" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -37986,7 +37989,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1308" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -38012,7 +38015,7 @@
         <v>21</v>
       </c>
       <c r="G1309" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -38038,7 +38041,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1310" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -38064,7 +38067,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -38090,7 +38093,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1312" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -38116,7 +38119,7 @@
         <v>21.5</v>
       </c>
       <c r="G1313" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -38142,7 +38145,7 @@
         <v>21.5</v>
       </c>
       <c r="G1314" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -38168,7 +38171,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1315" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -38194,7 +38197,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1316" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -38220,7 +38223,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1317" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -38246,7 +38249,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1318" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -38272,7 +38275,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1319" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -38298,7 +38301,7 @@
         <v>22.5</v>
       </c>
       <c r="G1320" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38324,7 +38327,7 @@
         <v>23.5</v>
       </c>
       <c r="G1321" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -38350,7 +38353,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1322" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -38376,7 +38379,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1323" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -38402,7 +38405,7 @@
         <v>23.5</v>
       </c>
       <c r="G1324" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -38428,7 +38431,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1325" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -38454,7 +38457,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1326" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -38480,7 +38483,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -38532,7 +38535,7 @@
         <v>23.5</v>
       </c>
       <c r="G1329" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -38558,7 +38561,7 @@
         <v>23.5</v>
       </c>
       <c r="G1330" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38584,7 +38587,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1331" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -38610,7 +38613,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1332" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -38636,7 +38639,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1333" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -38662,7 +38665,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -38688,7 +38691,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1335" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -38714,7 +38717,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -38740,7 +38743,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1337" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -38766,7 +38769,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1338" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -38792,7 +38795,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1339" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -38818,7 +38821,7 @@
         <v>23.5</v>
       </c>
       <c r="G1340" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -38844,7 +38847,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1341" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -38870,7 +38873,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1342" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -38896,7 +38899,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1343" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -38922,7 +38925,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1344" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -38948,7 +38951,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1345" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -38974,7 +38977,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1346" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -39000,7 +39003,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1347" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -39026,7 +39029,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1348" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -39052,7 +39055,7 @@
         <v>23.5</v>
       </c>
       <c r="G1349" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -39078,7 +39081,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1350" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -39104,7 +39107,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1351" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -39130,7 +39133,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1352" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -39156,7 +39159,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1353" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -39182,7 +39185,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -39312,7 +39315,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -39364,7 +39367,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1361" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -39390,7 +39393,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1362" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -39416,7 +39419,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -39442,7 +39445,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -39494,7 +39497,7 @@
         <v>23</v>
       </c>
       <c r="G1366" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -39520,7 +39523,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1367" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -39546,7 +39549,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1368" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -39572,7 +39575,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1369" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -39650,7 +39653,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1372" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -39676,7 +39679,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1373" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -39702,7 +39705,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1374" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -39728,7 +39731,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1375" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -39780,7 +39783,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1377" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -39806,7 +39809,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1378" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -39832,7 +39835,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1379" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -39858,7 +39861,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1380" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -39910,7 +39913,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1382" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -39988,7 +39991,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1385" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -40014,7 +40017,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -40040,7 +40043,7 @@
         <v>24</v>
       </c>
       <c r="G1387" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -40066,7 +40069,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1388" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -40144,7 +40147,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1391" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -40170,7 +40173,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1392" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -40196,7 +40199,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1393" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -40274,7 +40277,7 @@
         <v>23</v>
       </c>
       <c r="G1396" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -40300,7 +40303,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1397" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -40326,7 +40329,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1398" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -40352,7 +40355,7 @@
         <v>23</v>
       </c>
       <c r="G1399" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -40378,7 +40381,7 @@
         <v>23</v>
       </c>
       <c r="G1400" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -40404,7 +40407,7 @@
         <v>23</v>
       </c>
       <c r="G1401" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -40430,7 +40433,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1402" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -40456,7 +40459,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1403" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -40482,7 +40485,7 @@
         <v>23</v>
       </c>
       <c r="G1404" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -40508,7 +40511,7 @@
         <v>23</v>
       </c>
       <c r="G1405" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -40534,7 +40537,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1406" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -40560,7 +40563,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1407" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -40586,7 +40589,7 @@
         <v>22.5</v>
       </c>
       <c r="G1408" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -40612,7 +40615,7 @@
         <v>22</v>
       </c>
       <c r="G1409" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -40638,7 +40641,7 @@
         <v>22.5</v>
       </c>
       <c r="G1410" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -40664,7 +40667,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1411" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -40690,7 +40693,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1412" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -40716,7 +40719,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1413" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -40742,7 +40745,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1414" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -40768,7 +40771,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1415" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -40846,7 +40849,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1418" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -40872,7 +40875,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -40898,7 +40901,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1420" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -40924,7 +40927,7 @@
         <v>24</v>
       </c>
       <c r="G1421" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -40950,7 +40953,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1422" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -40976,7 +40979,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1423" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -41002,7 +41005,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1424" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -41028,7 +41031,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1425" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -41054,7 +41057,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1426" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -41080,7 +41083,7 @@
         <v>25</v>
       </c>
       <c r="G1427" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -41106,7 +41109,7 @@
         <v>25</v>
       </c>
       <c r="G1428" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -41132,7 +41135,7 @@
         <v>25</v>
       </c>
       <c r="G1429" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -41158,7 +41161,7 @@
         <v>24.5</v>
       </c>
       <c r="G1430" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -41184,7 +41187,7 @@
         <v>24.5</v>
       </c>
       <c r="G1431" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -41210,7 +41213,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1432" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -41236,7 +41239,7 @@
         <v>24.5</v>
       </c>
       <c r="G1433" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -41262,7 +41265,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1434" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -41288,7 +41291,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1435" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -41314,7 +41317,7 @@
         <v>26</v>
       </c>
       <c r="G1436" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -41340,7 +41343,7 @@
         <v>26.5</v>
       </c>
       <c r="G1437" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -41366,7 +41369,7 @@
         <v>26</v>
       </c>
       <c r="G1438" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -41392,7 +41395,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1439" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -41418,7 +41421,7 @@
         <v>26</v>
       </c>
       <c r="G1440" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -41444,7 +41447,7 @@
         <v>26.5</v>
       </c>
       <c r="G1441" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -41470,7 +41473,7 @@
         <v>26.5</v>
       </c>
       <c r="G1442" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -41496,7 +41499,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1443" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -41522,7 +41525,7 @@
         <v>26.5</v>
       </c>
       <c r="G1444" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -41548,7 +41551,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1445" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -41574,7 +41577,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1446" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -41600,7 +41603,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1447" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -41626,7 +41629,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1448" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -41652,7 +41655,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1449" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -41678,7 +41681,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1450" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -41704,7 +41707,7 @@
         <v>27.5</v>
       </c>
       <c r="G1451" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -41730,7 +41733,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1452" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -41756,7 +41759,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -41782,7 +41785,7 @@
         <v>27.5</v>
       </c>
       <c r="G1454" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -41808,7 +41811,7 @@
         <v>27.5</v>
       </c>
       <c r="G1455" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -41834,7 +41837,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1456" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -41860,7 +41863,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1457" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -41886,7 +41889,7 @@
         <v>28</v>
       </c>
       <c r="G1458" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -41912,7 +41915,7 @@
         <v>28</v>
       </c>
       <c r="G1459" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -41938,7 +41941,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -41964,7 +41967,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1461" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -41990,7 +41993,7 @@
         <v>27.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -42016,7 +42019,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1463" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -42042,7 +42045,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1464" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -42068,7 +42071,7 @@
         <v>26.5</v>
       </c>
       <c r="G1465" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -42094,7 +42097,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1466" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -42120,7 +42123,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1467" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -42146,7 +42149,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1468" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -42172,7 +42175,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1469" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -42198,7 +42201,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1470" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -42224,7 +42227,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1471" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -42250,7 +42253,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1472" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -42276,7 +42279,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1473" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -42302,7 +42305,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1474" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -42328,7 +42331,7 @@
         <v>27.5</v>
       </c>
       <c r="G1475" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -42354,7 +42357,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1476" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -42380,7 +42383,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1477" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -42406,7 +42409,7 @@
         <v>27.5</v>
       </c>
       <c r="G1478" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -42432,7 +42435,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1479" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -42458,7 +42461,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1480" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -42484,7 +42487,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1481" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -42510,7 +42513,7 @@
         <v>27</v>
       </c>
       <c r="G1482" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -42536,7 +42539,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1483" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -42562,7 +42565,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1484" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -42588,7 +42591,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1485" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -42614,7 +42617,7 @@
         <v>27.5</v>
       </c>
       <c r="G1486" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -42640,7 +42643,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1487" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -42666,7 +42669,7 @@
         <v>27.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -42692,7 +42695,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1489" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -42718,7 +42721,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1490" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -42744,7 +42747,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1491" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -42770,7 +42773,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -42796,7 +42799,7 @@
         <v>28</v>
       </c>
       <c r="G1493" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -42822,7 +42825,7 @@
         <v>28</v>
       </c>
       <c r="G1494" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -42848,7 +42851,7 @@
         <v>28.5</v>
       </c>
       <c r="G1495" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -42874,7 +42877,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1496" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -42900,7 +42903,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1497" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -42926,7 +42929,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1498" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -42952,7 +42955,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1499" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -42978,7 +42981,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1500" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -43004,7 +43007,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1501" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -43030,7 +43033,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1502" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -43056,7 +43059,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1503" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -43082,7 +43085,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1504" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -43108,7 +43111,7 @@
         <v>29</v>
       </c>
       <c r="G1505" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -43134,7 +43137,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1506" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -43160,7 +43163,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1507" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -43186,7 +43189,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1508" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -43212,7 +43215,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1509" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -43238,7 +43241,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1510" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -43264,7 +43267,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1511" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -43290,7 +43293,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1512" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -43316,7 +43319,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1513" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43342,7 +43345,7 @@
         <v>30</v>
       </c>
       <c r="G1514" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -43368,7 +43371,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1515" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -43394,7 +43397,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1516" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -43420,7 +43423,7 @@
         <v>30</v>
       </c>
       <c r="G1517" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -43446,7 +43449,7 @@
         <v>31</v>
       </c>
       <c r="G1518" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -43472,7 +43475,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1519" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43498,7 +43501,7 @@
         <v>31</v>
       </c>
       <c r="G1520" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -43524,7 +43527,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1521" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -43550,7 +43553,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G1522" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -43576,7 +43579,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1523" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -43602,7 +43605,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1524" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -43628,7 +43631,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1525" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43654,7 +43657,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1526" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -43680,7 +43683,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1527" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43706,7 +43709,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1528" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -43732,7 +43735,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1529" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -43758,7 +43761,7 @@
         <v>34.5</v>
       </c>
       <c r="G1530" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -43784,7 +43787,7 @@
         <v>33</v>
       </c>
       <c r="G1531" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -43810,7 +43813,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1532" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -43836,7 +43839,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1533" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -43862,7 +43865,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1534" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -43888,7 +43891,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1535" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -43914,7 +43917,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1536" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -43940,7 +43943,7 @@
         <v>33.5</v>
       </c>
       <c r="G1537" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -43966,7 +43969,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G1538" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -43992,7 +43995,7 @@
         <v>33</v>
       </c>
       <c r="G1539" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -44018,7 +44021,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1540" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -44044,7 +44047,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1541" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -44070,7 +44073,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1542" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -44096,7 +44099,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1543" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -44122,7 +44125,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1544" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -44148,7 +44151,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1545" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -44174,7 +44177,7 @@
         <v>30.5</v>
       </c>
       <c r="G1546" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -44200,7 +44203,7 @@
         <v>30.5</v>
       </c>
       <c r="G1547" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -44226,7 +44229,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1548" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -44252,7 +44255,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1549" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -44278,7 +44281,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1550" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -44304,7 +44307,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1551" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -44330,7 +44333,7 @@
         <v>30.5</v>
       </c>
       <c r="G1552" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -44356,7 +44359,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1553" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -44382,7 +44385,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1554" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -44408,7 +44411,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1555" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -44434,7 +44437,7 @@
         <v>30</v>
       </c>
       <c r="G1556" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44460,7 +44463,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1557" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -44486,7 +44489,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1558" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -44512,7 +44515,7 @@
         <v>31</v>
       </c>
       <c r="G1559" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -44538,7 +44541,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1560" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -44564,7 +44567,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1561" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -44590,7 +44593,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1562" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -44616,7 +44619,7 @@
         <v>30.5</v>
       </c>
       <c r="G1563" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -44642,7 +44645,7 @@
         <v>31.5</v>
       </c>
       <c r="G1564" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44668,7 +44671,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1565" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -44694,7 +44697,7 @@
         <v>30.5</v>
       </c>
       <c r="G1566" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -44720,7 +44723,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1567" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -44746,7 +44749,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1568" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44772,7 +44775,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1569" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -44798,7 +44801,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1570" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -44824,7 +44827,7 @@
         <v>27</v>
       </c>
       <c r="G1571" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -44850,7 +44853,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1572" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -44876,7 +44879,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1573" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -44902,7 +44905,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1574" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -44928,7 +44931,7 @@
         <v>27</v>
       </c>
       <c r="G1575" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -44954,7 +44957,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1576" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -44980,7 +44983,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1577" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -45006,7 +45009,7 @@
         <v>26</v>
       </c>
       <c r="G1578" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -45032,7 +45035,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1579" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -45058,7 +45061,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1580" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -45084,7 +45087,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1581" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -45110,7 +45113,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1582" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -45136,7 +45139,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1583" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -45162,7 +45165,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1584" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -45188,7 +45191,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1585" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -45214,7 +45217,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1586" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -45240,7 +45243,7 @@
         <v>28.5</v>
       </c>
       <c r="G1587" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -45266,7 +45269,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1588" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -45292,7 +45295,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1589" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45318,7 +45321,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1590" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -45344,7 +45347,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1591" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45370,7 +45373,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1592" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -45396,7 +45399,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1593" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -45422,7 +45425,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1594" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -45448,7 +45451,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1595" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -45474,7 +45477,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1596" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -45500,7 +45503,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1597" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -45526,7 +45529,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1598" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -45552,7 +45555,7 @@
         <v>27.5</v>
       </c>
       <c r="G1599" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -45578,7 +45581,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1600" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45604,7 +45607,7 @@
         <v>28</v>
       </c>
       <c r="G1601" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45630,7 +45633,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1602" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45656,7 +45659,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1603" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -45682,7 +45685,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1604" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -45708,7 +45711,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1605" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45734,7 +45737,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1606" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45760,7 +45763,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1607" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -45786,7 +45789,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1608" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -45812,7 +45815,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1609" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -45838,7 +45841,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1610" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -45864,7 +45867,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1611" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -45890,7 +45893,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1612" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -45916,7 +45919,7 @@
         <v>28</v>
       </c>
       <c r="G1613" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -45942,7 +45945,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1614" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -45968,7 +45971,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1615" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -45994,7 +45997,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1616" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -46020,7 +46023,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1617" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -46046,7 +46049,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1618" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -46072,7 +46075,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1619" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -46098,7 +46101,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1620" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46124,7 +46127,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1621" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46150,7 +46153,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1622" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46176,7 +46179,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1623" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46202,7 +46205,7 @@
         <v>27</v>
       </c>
       <c r="G1624" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46228,7 +46231,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1625" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46254,7 +46257,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1626" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46280,7 +46283,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1627" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46306,7 +46309,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1628" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46332,7 +46335,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1629" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -46358,7 +46361,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1630" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -46384,7 +46387,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1631" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -46410,7 +46413,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1632" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -46436,7 +46439,7 @@
         <v>28.5</v>
       </c>
       <c r="G1633" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -46462,7 +46465,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1634" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -46488,7 +46491,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1635" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -46514,7 +46517,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1636" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -46540,7 +46543,7 @@
         <v>27.5</v>
       </c>
       <c r="G1637" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -46566,7 +46569,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1638" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -46592,7 +46595,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1639" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -46618,7 +46621,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1640" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -46644,7 +46647,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1641" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -46670,7 +46673,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1642" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -46696,7 +46699,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1643" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -46722,7 +46725,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1644" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -46748,7 +46751,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1645" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -46774,7 +46777,7 @@
         <v>24.5</v>
       </c>
       <c r="G1646" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -46800,7 +46803,7 @@
         <v>24</v>
       </c>
       <c r="G1647" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -46826,7 +46829,7 @@
         <v>24</v>
       </c>
       <c r="G1648" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -46852,7 +46855,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1649" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -46878,7 +46881,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -46904,7 +46907,7 @@
         <v>24</v>
       </c>
       <c r="G1651" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -46930,7 +46933,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -46956,7 +46959,7 @@
         <v>25</v>
       </c>
       <c r="G1653" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -46982,7 +46985,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1654" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -47008,7 +47011,7 @@
         <v>27</v>
       </c>
       <c r="G1655" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -47034,7 +47037,7 @@
         <v>27.5</v>
       </c>
       <c r="G1656" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47060,7 +47063,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1657" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47086,7 +47089,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1658" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -47112,7 +47115,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1659" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47138,7 +47141,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1660" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47164,7 +47167,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1661" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47190,7 +47193,7 @@
         <v>27.5</v>
       </c>
       <c r="G1662" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47216,7 +47219,7 @@
         <v>26</v>
       </c>
       <c r="G1663" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -47242,7 +47245,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1664" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -47268,7 +47271,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1665" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47294,7 +47297,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1666" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47320,7 +47323,7 @@
         <v>26</v>
       </c>
       <c r="G1667" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47346,7 +47349,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1668" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -47372,7 +47375,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1669" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -47398,7 +47401,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1670" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -47424,7 +47427,7 @@
         <v>27.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -47450,7 +47453,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1672" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -47476,7 +47479,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1673" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -47502,7 +47505,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1674" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -47528,7 +47531,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1675" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -47554,7 +47557,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1676" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -47580,7 +47583,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1677" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -47606,7 +47609,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1678" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -47632,7 +47635,7 @@
         <v>27</v>
       </c>
       <c r="G1679" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -47658,7 +47661,7 @@
         <v>27.5</v>
       </c>
       <c r="G1680" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -47684,7 +47687,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1681" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -47710,7 +47713,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1682" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -47736,7 +47739,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1683" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -47762,7 +47765,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1684" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -47788,7 +47791,7 @@
         <v>27</v>
       </c>
       <c r="G1685" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -47814,7 +47817,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1686" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -47840,7 +47843,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1687" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -47866,7 +47869,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1688" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -47892,7 +47895,7 @@
         <v>26.5</v>
       </c>
       <c r="G1689" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -47918,7 +47921,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1690" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -47944,7 +47947,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1691" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -47970,7 +47973,7 @@
         <v>26</v>
       </c>
       <c r="G1692" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -47996,7 +47999,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1693" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -48022,7 +48025,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1694" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48048,7 +48051,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1695" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48074,7 +48077,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1696" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -48100,7 +48103,7 @@
         <v>26.5</v>
       </c>
       <c r="G1697" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48126,7 +48129,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1698" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -48152,7 +48155,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1699" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -48178,7 +48181,7 @@
         <v>26</v>
       </c>
       <c r="G1700" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -48204,7 +48207,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1701" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48230,7 +48233,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1702" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -48256,7 +48259,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1703" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -48282,7 +48285,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1704" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48308,7 +48311,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -48334,7 +48337,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1706" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -48360,7 +48363,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1707" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -48386,7 +48389,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1708" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -48412,7 +48415,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -48438,7 +48441,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1710" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -48464,7 +48467,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -48490,7 +48493,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1712" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -48516,7 +48519,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1713" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -48542,7 +48545,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1714" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -48568,7 +48571,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1715" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -48594,7 +48597,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1716" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -48620,7 +48623,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1717" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -48646,7 +48649,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1718" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -48672,7 +48675,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1719" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -48698,7 +48701,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1720" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -48724,7 +48727,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1721" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -48750,7 +48753,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1722" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -48776,7 +48779,7 @@
         <v>24.5</v>
       </c>
       <c r="G1723" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -48802,7 +48805,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1724" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48828,7 +48831,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1725" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -48854,7 +48857,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1726" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -48880,7 +48883,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1727" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -48906,7 +48909,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1728" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -48932,7 +48935,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1729" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -48958,7 +48961,7 @@
         <v>25</v>
       </c>
       <c r="G1730" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -48984,7 +48987,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1731" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -49010,7 +49013,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1732" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -49036,7 +49039,7 @@
         <v>26.5</v>
       </c>
       <c r="G1733" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -49062,7 +49065,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1734" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -49088,7 +49091,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1735" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49114,7 +49117,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1736" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -49140,7 +49143,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1737" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -49166,7 +49169,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1738" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -49192,7 +49195,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1739" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -49218,7 +49221,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1740" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -49244,7 +49247,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1741" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -49270,7 +49273,7 @@
         <v>27.5</v>
       </c>
       <c r="G1742" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -49296,7 +49299,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1743" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -49322,7 +49325,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1744" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -49348,7 +49351,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1745" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -49374,7 +49377,7 @@
         <v>27</v>
       </c>
       <c r="G1746" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -49400,7 +49403,7 @@
         <v>27.5</v>
       </c>
       <c r="G1747" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -49426,7 +49429,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1748" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -49452,7 +49455,7 @@
         <v>28</v>
       </c>
       <c r="G1749" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -49478,7 +49481,7 @@
         <v>28</v>
       </c>
       <c r="G1750" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -49504,7 +49507,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1751" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -49530,7 +49533,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1752" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -49556,7 +49559,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1753" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -49582,7 +49585,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1754" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -49608,7 +49611,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -49634,7 +49637,7 @@
         <v>28</v>
       </c>
       <c r="G1756" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -49660,7 +49663,7 @@
         <v>27.5</v>
       </c>
       <c r="G1757" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -49686,7 +49689,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1758" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -49712,7 +49715,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1759" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -49738,7 +49741,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1760" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -49764,7 +49767,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1761" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -49790,7 +49793,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1762" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -49816,7 +49819,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1763" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -49842,7 +49845,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1764" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -49868,7 +49871,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1765" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -49894,7 +49897,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1766" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -49920,7 +49923,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1767" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -49946,7 +49949,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1768" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -49972,7 +49975,7 @@
         <v>29</v>
       </c>
       <c r="G1769" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -49998,7 +50001,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1770" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -50024,7 +50027,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1771" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -50050,7 +50053,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1772" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -50076,7 +50079,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1773" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -50102,7 +50105,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1774" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -50128,7 +50131,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1775" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -50154,7 +50157,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1776" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50180,7 +50183,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1777" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -50206,7 +50209,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1778" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -50232,7 +50235,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1779" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -50258,7 +50261,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1780" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -50284,7 +50287,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1781" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -50310,7 +50313,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1782" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -50336,7 +50339,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1783" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -50362,7 +50365,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1784" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50388,7 +50391,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1785" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -50414,7 +50417,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1786" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -50440,7 +50443,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -50466,7 +50469,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1788" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -50492,7 +50495,7 @@
         <v>30.5</v>
       </c>
       <c r="G1789" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -50518,7 +50521,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1790" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -50544,7 +50547,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1791" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -50570,7 +50573,7 @@
         <v>30.5</v>
       </c>
       <c r="G1792" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -50596,7 +50599,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1793" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -50622,7 +50625,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1794" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -50648,7 +50651,7 @@
         <v>31</v>
       </c>
       <c r="G1795" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -50674,7 +50677,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1796" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -50700,7 +50703,7 @@
         <v>31</v>
       </c>
       <c r="G1797" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -50726,7 +50729,7 @@
         <v>31</v>
       </c>
       <c r="G1798" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -50752,7 +50755,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1799" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -50778,7 +50781,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1800" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -50804,7 +50807,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -50830,7 +50833,7 @@
         <v>31</v>
       </c>
       <c r="G1802" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -50856,7 +50859,7 @@
         <v>30.5</v>
       </c>
       <c r="G1803" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -50882,7 +50885,7 @@
         <v>30</v>
       </c>
       <c r="G1804" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -50908,7 +50911,7 @@
         <v>29.5</v>
       </c>
       <c r="G1805" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -50934,7 +50937,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1806" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -50960,7 +50963,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1807" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -50986,7 +50989,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1808" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -51012,7 +51015,7 @@
         <v>29.5</v>
       </c>
       <c r="G1809" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -51038,7 +51041,7 @@
         <v>30</v>
       </c>
       <c r="G1810" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -51064,7 +51067,7 @@
         <v>30</v>
       </c>
       <c r="G1811" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -51090,7 +51093,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1812" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -51116,7 +51119,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1813" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -51142,7 +51145,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1814" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -51168,7 +51171,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1815" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51194,7 +51197,7 @@
         <v>29.5</v>
       </c>
       <c r="G1816" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51220,7 +51223,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1817" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -51246,7 +51249,7 @@
         <v>29</v>
       </c>
       <c r="G1818" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -51272,7 +51275,7 @@
         <v>28.5</v>
       </c>
       <c r="G1819" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51298,7 +51301,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1820" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -51324,7 +51327,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1821" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -51350,7 +51353,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1822" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -51376,7 +51379,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1823" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51402,7 +51405,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51428,7 +51431,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -51454,7 +51457,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1826" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -51480,7 +51483,7 @@
         <v>29.5</v>
       </c>
       <c r="G1827" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -51506,7 +51509,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1828" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -51532,7 +51535,7 @@
         <v>30.5</v>
       </c>
       <c r="G1829" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -51558,7 +51561,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1830" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -51584,7 +51587,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1831" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -51610,7 +51613,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1832" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -51636,7 +51639,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1833" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -51662,7 +51665,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -51688,7 +51691,7 @@
         <v>30</v>
       </c>
       <c r="G1835" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -51714,7 +51717,7 @@
         <v>29.5</v>
       </c>
       <c r="G1836" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -51740,7 +51743,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1837" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -51766,7 +51769,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1838" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -51792,7 +51795,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1839" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -51818,7 +51821,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1840" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -51844,7 +51847,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1841" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -51870,7 +51873,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1842" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -51896,7 +51899,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1843" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -51922,7 +51925,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1844" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -51948,7 +51951,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1845" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -51974,7 +51977,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1846" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -52000,7 +52003,7 @@
         <v>30.5</v>
       </c>
       <c r="G1847" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -52026,7 +52029,7 @@
         <v>30.5</v>
       </c>
       <c r="G1848" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52052,7 +52055,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1849" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -52078,7 +52081,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1850" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -52104,7 +52107,7 @@
         <v>30</v>
       </c>
       <c r="G1851" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -52130,7 +52133,7 @@
         <v>30.5</v>
       </c>
       <c r="G1852" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52156,7 +52159,7 @@
         <v>30</v>
       </c>
       <c r="G1853" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52182,7 +52185,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1854" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52208,7 +52211,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1855" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -52234,7 +52237,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1856" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -52260,7 +52263,7 @@
         <v>30.5</v>
       </c>
       <c r="G1857" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -52286,7 +52289,7 @@
         <v>30</v>
       </c>
       <c r="G1858" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -52312,7 +52315,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1859" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -52338,7 +52341,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -52364,7 +52367,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1861" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -52390,7 +52393,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1862" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -52416,7 +52419,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1863" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -52442,7 +52445,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1864" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -52468,7 +52471,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1865" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -52494,7 +52497,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1866" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -52520,7 +52523,7 @@
         <v>31.5</v>
       </c>
       <c r="G1867" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52546,7 +52549,7 @@
         <v>31.5</v>
       </c>
       <c r="G1868" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -52572,7 +52575,7 @@
         <v>31.5</v>
       </c>
       <c r="G1869" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -52598,7 +52601,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1870" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -52624,7 +52627,7 @@
         <v>31.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -52650,7 +52653,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1872" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52676,7 +52679,7 @@
         <v>30</v>
       </c>
       <c r="G1873" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52702,7 +52705,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1874" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -52728,7 +52731,7 @@
         <v>31.5</v>
       </c>
       <c r="G1875" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -53274,7 +53277,7 @@
         <v>31.5</v>
       </c>
       <c r="G1896" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -53378,7 +53381,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1900" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -53612,7 +53615,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -53638,7 +53641,7 @@
         <v>30</v>
       </c>
       <c r="G1910" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53924,7 +53927,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1921" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53950,7 +53953,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1922" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -55770,7 +55773,7 @@
         <v>31.5</v>
       </c>
       <c r="G1992" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -69662,7 +69665,7 @@
     </row>
     <row r="2527">
       <c r="A2527" s="1" t="n">
-        <v>45996.6910300926</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B2527" t="n">
         <v>12261</v>
@@ -69683,6 +69686,32 @@
         <v>1211</v>
       </c>
       <c r="H2527" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" s="1" t="n">
+        <v>45999.6915740741</v>
+      </c>
+      <c r="B2528" t="n">
+        <v>4851</v>
+      </c>
+      <c r="C2528" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="D2528" t="n">
+        <v>67.4000015258789</v>
+      </c>
+      <c r="E2528" t="n">
+        <v>68</v>
+      </c>
+      <c r="F2528" t="n">
+        <v>68.3000030517578</v>
+      </c>
+      <c r="G2528" t="s">
+        <v>1212</v>
+      </c>
+      <c r="H2528" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="1213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="1214">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23958778381348</t>
+    <t xml:space="preserve">9.23958873748779</t>
   </si>
   <si>
     <t xml:space="preserve">CMB.MI</t>
@@ -47,28 +47,28 @@
     <t xml:space="preserve">9.55656719207764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31377506256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40144824981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4081916809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44191360473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36098384857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13842391967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32051753997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26656436920166</t>
+    <t xml:space="preserve">9.31377410888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40144920349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40819358825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44191551208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36098480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13842582702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32051944732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26656532287598</t>
   </si>
   <si>
     <t xml:space="preserve">9.34075164794922</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">9.2733097076416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19237804412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19912147521973</t>
+    <t xml:space="preserve">9.1923770904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19912242889404</t>
   </si>
   <si>
     <t xml:space="preserve">9.10470294952393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84167861938477</t>
+    <t xml:space="preserve">8.84167671203613</t>
   </si>
   <si>
     <t xml:space="preserve">8.77423667907715</t>
@@ -95,73 +95,73 @@
     <t xml:space="preserve">8.84842300415039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36283874511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32911682128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61911869049072</t>
+    <t xml:space="preserve">8.36283779144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32911777496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61911964416504</t>
   </si>
   <si>
     <t xml:space="preserve">8.45051383972168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43028163909912</t>
+    <t xml:space="preserve">8.43027973175049</t>
   </si>
   <si>
     <t xml:space="preserve">8.63260841369629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80121326446533</t>
+    <t xml:space="preserve">8.80121421813965</t>
   </si>
   <si>
     <t xml:space="preserve">9.22610092163086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25982093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07098197937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87539863586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96981906890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71353912353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66632843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89563369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81470108032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99679565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01028347015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90237522125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97656440734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18563461303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17214679718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13168144226074</t>
+    <t xml:space="preserve">9.25982189178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07098293304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87539958953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96982002258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71353721618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6663293838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89563179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81470203399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99679660797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01028442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90237617492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97656345367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18563365936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17214584350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13167953491211</t>
   </si>
   <si>
     <t xml:space="preserve">9.34749507904053</t>
@@ -170,10 +170,10 @@
     <t xml:space="preserve">9.25307655334473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15865707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08447074890137</t>
+    <t xml:space="preserve">9.15865802764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08447170257568</t>
   </si>
   <si>
     <t xml:space="preserve">9.16540145874023</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">8.98330688476562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78772354125977</t>
+    <t xml:space="preserve">8.7877254486084</t>
   </si>
   <si>
     <t xml:space="preserve">8.78098106384277</t>
@@ -191,79 +191,79 @@
     <t xml:space="preserve">9.1249361038208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03726005554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21261119842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04400634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0979585647583</t>
+    <t xml:space="preserve">9.03726100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21260929107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04400444030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09795951843262</t>
   </si>
   <si>
     <t xml:space="preserve">9.20586681365967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38121604919434</t>
+    <t xml:space="preserve">9.38121700286865</t>
   </si>
   <si>
     <t xml:space="preserve">9.28679752349854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22100830078125</t>
+    <t xml:space="preserve">9.22100639343262</t>
   </si>
   <si>
     <t xml:space="preserve">9.22798824310303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19308757781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35363292694092</t>
+    <t xml:space="preserve">9.19308662414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35363388061523</t>
   </si>
   <si>
     <t xml:space="preserve">9.4094762802124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52116298675537</t>
+    <t xml:space="preserve">9.52116107940674</t>
   </si>
   <si>
     <t xml:space="preserve">9.49324226379395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38853549957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94696235656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76547241210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77245330810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66774940490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82829666137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75151348114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57002353668213</t>
+    <t xml:space="preserve">9.38853645324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94696044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76547336578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77245235443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66774845123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82829570770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75151443481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57002449035645</t>
   </si>
   <si>
     <t xml:space="preserve">9.57700538635254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55606269836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47928142547607</t>
+    <t xml:space="preserve">9.55606365203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47928047180176</t>
   </si>
   <si>
     <t xml:space="preserve">9.42343711853027</t>
@@ -272,22 +272,22 @@
     <t xml:space="preserve">9.39551639556885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41645622253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34665489196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58398532867432</t>
+    <t xml:space="preserve">9.4164571762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34665298461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.583984375</t>
   </si>
   <si>
     <t xml:space="preserve">9.6258659362793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63284778594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4653205871582</t>
+    <t xml:space="preserve">9.63284683227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46531963348389</t>
   </si>
   <si>
     <t xml:space="preserve">9.48625946044922</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">9.53512287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1232852935791</t>
+    <t xml:space="preserve">9.12328338623047</t>
   </si>
   <si>
     <t xml:space="preserve">9.30477237701416</t>
@@ -314,52 +314,52 @@
     <t xml:space="preserve">9.20704746246338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27685165405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36061477661133</t>
+    <t xml:space="preserve">9.27685070037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36061382293701</t>
   </si>
   <si>
     <t xml:space="preserve">9.29081058502197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29779052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31873321533203</t>
+    <t xml:space="preserve">9.29779148101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31873416900635</t>
   </si>
   <si>
     <t xml:space="preserve">9.36759567260742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47229957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52814197540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50720119476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44437789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50022125244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3326940536499</t>
+    <t xml:space="preserve">9.47230052947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52814292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5072021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44437885284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50022029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33269309997559</t>
   </si>
   <si>
     <t xml:space="preserve">9.32571220397949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13724517822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1442232131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15120601654053</t>
+    <t xml:space="preserve">9.13724422454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14422512054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15120506286621</t>
   </si>
   <si>
     <t xml:space="preserve">9.1093225479126</t>
@@ -368,16 +368,16 @@
     <t xml:space="preserve">9.03952026367188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92783451080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01159763336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07442188262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97669696807861</t>
+    <t xml:space="preserve">8.92783355712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01159858703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07441997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97669792175293</t>
   </si>
   <si>
     <t xml:space="preserve">8.86501121520996</t>
@@ -386,25 +386,25 @@
     <t xml:space="preserve">8.85105037689209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93481540679932</t>
+    <t xml:space="preserve">8.934814453125</t>
   </si>
   <si>
     <t xml:space="preserve">8.92085456848145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95575618743896</t>
+    <t xml:space="preserve">8.95575714111328</t>
   </si>
   <si>
     <t xml:space="preserve">8.96971607208252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00461769104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91387462615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87897205352783</t>
+    <t xml:space="preserve">9.00461864471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91387367248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87897300720215</t>
   </si>
   <si>
     <t xml:space="preserve">8.80916786193848</t>
@@ -413,25 +413,25 @@
     <t xml:space="preserve">8.59975910186768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56485748291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81614971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8370885848999</t>
+    <t xml:space="preserve">8.56485939025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81614875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83709049224854</t>
   </si>
   <si>
     <t xml:space="preserve">8.89991283416748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99763679504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83010959625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96273708343506</t>
+    <t xml:space="preserve">8.99763774871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83011054992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96273612976074</t>
   </si>
   <si>
     <t xml:space="preserve">9.08838176727295</t>
@@ -446,13 +446,13 @@
     <t xml:space="preserve">9.66076850891113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64680671691895</t>
+    <t xml:space="preserve">9.64680767059326</t>
   </si>
   <si>
     <t xml:space="preserve">9.70265007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79339408874512</t>
+    <t xml:space="preserve">9.79339504241943</t>
   </si>
   <si>
     <t xml:space="preserve">9.92602062225342</t>
@@ -464,25 +464,25 @@
     <t xml:space="preserve">10.0516662597656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.414644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1912727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2471151351929</t>
+    <t xml:space="preserve">10.4146432876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.19127368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2471160888672</t>
   </si>
   <si>
     <t xml:space="preserve">10.1493921279907</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1354312896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2680568695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3937015533447</t>
+    <t xml:space="preserve">10.1354303359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2680578231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.393702507019</t>
   </si>
   <si>
     <t xml:space="preserve">10.5402898788452</t>
@@ -491,10 +491,10 @@
     <t xml:space="preserve">10.5891513824463</t>
   </si>
   <si>
-    <t xml:space="preserve">10.484447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6310329437256</t>
+    <t xml:space="preserve">10.4844465255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6310348510742</t>
   </si>
   <si>
     <t xml:space="preserve">10.3588008880615</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">9.988844871521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95394134521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.100528717041</t>
+    <t xml:space="preserve">9.95394229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1005277633667</t>
   </si>
   <si>
     <t xml:space="preserve">10.4704875946045</t>
@@ -515,16 +515,16 @@
     <t xml:space="preserve">10.3867216110229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.547269821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3448400497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4774675369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4006824493408</t>
+    <t xml:space="preserve">10.5472688674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.344841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.477466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4006834030151</t>
   </si>
   <si>
     <t xml:space="preserve">10.4355840682983</t>
@@ -533,37 +533,37 @@
     <t xml:space="preserve">10.3727617263794</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3657808303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3378601074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2820167541504</t>
+    <t xml:space="preserve">10.3657817840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3378620147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2820177078247</t>
   </si>
   <si>
     <t xml:space="preserve">10.3797416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6100921630859</t>
+    <t xml:space="preserve">10.6100931167603</t>
   </si>
   <si>
     <t xml:space="preserve">10.5542497634888</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6938562393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0917348861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.042872428894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0358934402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.063814163208</t>
+    <t xml:space="preserve">10.6938571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0917358398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0428733825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0358915328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0638132095337</t>
   </si>
   <si>
     <t xml:space="preserve">11.0847549438477</t>
@@ -572,145 +572,145 @@
     <t xml:space="preserve">11.3569869995117</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5175352096558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0899219512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9991769790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0689821243286</t>
+    <t xml:space="preserve">11.5175342559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0899209976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9991779327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0689811706543</t>
   </si>
   <si>
     <t xml:space="preserve">12.1038818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2853708267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8228559494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9764242172241</t>
+    <t xml:space="preserve">12.2853717803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8228549957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9764223098755</t>
   </si>
   <si>
     <t xml:space="preserve">12.9903831481934</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2486534118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1090497970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1230096817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8926572799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9135999679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8437967300415</t>
+    <t xml:space="preserve">13.2486553192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1090488433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1230087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8926591873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9136009216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8437948226929</t>
   </si>
   <si>
     <t xml:space="preserve">12.9624624252319</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1928129196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3952436447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8978271484375</t>
+    <t xml:space="preserve">13.1928119659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.39524269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8978261947632</t>
   </si>
   <si>
     <t xml:space="preserve">13.9815902709961</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9327249526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0234718322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0304536819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1351566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0723342895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0025310516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.211256980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197393417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.146164894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0810747146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9942893981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6688413619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.355899810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6833047866821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0015230178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9870586395264</t>
+    <t xml:space="preserve">13.9327268600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0234699249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0304517745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.135157585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0723314285278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0025281906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2112550735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197383880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1461658477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.081075668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9942922592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6688394546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3559017181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6833076477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0015239715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9870576858521</t>
   </si>
   <si>
     <t xml:space="preserve">14.2691125869751</t>
   </si>
   <si>
-    <t xml:space="preserve">14.348669052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3414363861084</t>
+    <t xml:space="preserve">14.3486671447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3414373397827</t>
   </si>
   <si>
     <t xml:space="preserve">14.2763452529907</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4282236099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5656337738037</t>
+    <t xml:space="preserve">14.4282217025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5656328201294</t>
   </si>
   <si>
     <t xml:space="preserve">15.3322477340698</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8457326889038</t>
+    <t xml:space="preserve">15.8457317352295</t>
   </si>
   <si>
     <t xml:space="preserve">15.7589454650879</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3611745834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1876020431519</t>
+    <t xml:space="preserve">15.3611755371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1876029968262</t>
   </si>
   <si>
     <t xml:space="preserve">14.9200096130371</t>
@@ -719,13 +719,13 @@
     <t xml:space="preserve">14.6307239532471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5636768341064</t>
+    <t xml:space="preserve">15.5636777877808</t>
   </si>
   <si>
     <t xml:space="preserve">15.3105497360229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9272403717041</t>
+    <t xml:space="preserve">14.9272432327271</t>
   </si>
   <si>
     <t xml:space="preserve">15.0718870162964</t>
@@ -734,58 +734,58 @@
     <t xml:space="preserve">15.5492105484009</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4551944732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2671566009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1731357574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8332242965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1369781494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1152811050415</t>
+    <t xml:space="preserve">15.4551935195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2671556472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1731395721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8332223892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1369771957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1152801513672</t>
   </si>
   <si>
     <t xml:space="preserve">14.9851007461548</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1514415740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0284948348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2092990875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.664924621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6938571929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7661781311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9325199127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0410003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9469804763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6432294845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2816181182861</t>
+    <t xml:space="preserve">15.151442527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0284957885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2092981338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.664927482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6938543319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7661790847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9325189590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0410022735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9469814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6432304382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2816200256348</t>
   </si>
   <si>
     <t xml:space="preserve">15.2888517379761</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">15.3250141143799</t>
   </si>
   <si>
-    <t xml:space="preserve">15.238226890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1586713790894</t>
+    <t xml:space="preserve">15.2382259368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1586723327637</t>
   </si>
   <si>
     <t xml:space="preserve">15.0574226379395</t>
@@ -809,58 +809,58 @@
     <t xml:space="preserve">15.1803674697876</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2454595565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8983144760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8693828582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8259935379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9634046554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9706363677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6813478469849</t>
+    <t xml:space="preserve">15.2454586029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8983125686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8693838119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8259944915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9634056091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9706392288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6813488006592</t>
   </si>
   <si>
     <t xml:space="preserve">14.7536697387695</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6958141326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8910837173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4933137893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8549203872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6524200439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6090278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8476905822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1948337554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3394775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4334964752197</t>
+    <t xml:space="preserve">14.6958131790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8910808563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4933128356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8549222946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6524209976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6090250015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8476886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1948347091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3394804000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4334955215454</t>
   </si>
   <si>
     <t xml:space="preserve">16.2651977539062</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">17.5742244720459</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6879825592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3986949920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4420852661133</t>
+    <t xml:space="preserve">18.6879844665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3986968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4420871734619</t>
   </si>
   <si>
     <t xml:space="preserve">18.2178897857666</t>
@@ -887,82 +887,82 @@
     <t xml:space="preserve">18.0804786682129</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1889591217041</t>
+    <t xml:space="preserve">18.1889610290527</t>
   </si>
   <si>
     <t xml:space="preserve">17.971996307373</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0081558227539</t>
+    <t xml:space="preserve">18.0081577301025</t>
   </si>
   <si>
     <t xml:space="preserve">17.8562812805176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9647617340088</t>
+    <t xml:space="preserve">17.9647636413574</t>
   </si>
   <si>
     <t xml:space="preserve">17.6393146514893</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7622604370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.603157043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5886898040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5380668640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5019035339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3861885070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3211002349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2849369049072</t>
+    <t xml:space="preserve">17.7622623443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6031532287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5886878967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5380630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5019016265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3861904144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3210983276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2849388122559</t>
   </si>
   <si>
     <t xml:space="preserve">17.0462760925293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.263240814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0969009399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3283290863037</t>
+    <t xml:space="preserve">17.2632389068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0968990325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3283309936523</t>
   </si>
   <si>
     <t xml:space="preserve">17.3572597503662</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4006538391113</t>
+    <t xml:space="preserve">17.4006519317627</t>
   </si>
   <si>
     <t xml:space="preserve">17.3789577484131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2921695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.342794418335</t>
+    <t xml:space="preserve">17.2921714782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3427925109863</t>
   </si>
   <si>
     <t xml:space="preserve">17.1692218780518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5906467437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6268062591553</t>
+    <t xml:space="preserve">16.5906505584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6268081665039</t>
   </si>
   <si>
     <t xml:space="preserve">16.9233283996582</t>
@@ -971,91 +971,91 @@
     <t xml:space="preserve">16.3447532653809</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7083215713501</t>
+    <t xml:space="preserve">15.7083187103271</t>
   </si>
   <si>
     <t xml:space="preserve">16.1133251190186</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9180517196655</t>
+    <t xml:space="preserve">15.9180536270142</t>
   </si>
   <si>
     <t xml:space="preserve">15.6504621505737</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4749336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3013591766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5761795043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5110950469971</t>
+    <t xml:space="preserve">16.4749317169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3013610839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5761833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5110912322998</t>
   </si>
   <si>
     <t xml:space="preserve">16.5617179870605</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0699310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5255584716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4098434448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2073421478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8746614456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.243501663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4460048675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2001094818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8312664031982</t>
+    <t xml:space="preserve">16.0699291229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5255565643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4098415374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2073383331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8746604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2435054779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4460029602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2001075744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8312644958496</t>
   </si>
   <si>
     <t xml:space="preserve">15.8601932525635</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8529634475708</t>
+    <t xml:space="preserve">15.8529644012451</t>
   </si>
   <si>
     <t xml:space="preserve">15.6287651062012</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4696559906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.462423324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215353012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9976081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2362689971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1639499664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2724323272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7786865234375</t>
+    <t xml:space="preserve">15.4696569442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4624242782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215362548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9976072311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.236270904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.163948059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2724285125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7786846160889</t>
   </si>
   <si>
     <t xml:space="preserve">16.6340389251709</t>
@@ -1067,22 +1067,22 @@
     <t xml:space="preserve">16.7425212860107</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5978813171387</t>
+    <t xml:space="preserve">16.59787940979</t>
   </si>
   <si>
     <t xml:space="preserve">16.7063636779785</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8510074615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0318126678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2126178741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4295825958252</t>
+    <t xml:space="preserve">16.8510036468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.031810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2126159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4295806884766</t>
   </si>
   <si>
     <t xml:space="preserve">16.9594898223877</t>
@@ -1091,40 +1091,40 @@
     <t xml:space="preserve">16.3809146881104</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9831438064575</t>
+    <t xml:space="preserve">15.9831428527832</t>
   </si>
   <si>
     <t xml:space="preserve">15.9108228683472</t>
   </si>
   <si>
-    <t xml:space="preserve">15.730016708374</t>
+    <t xml:space="preserve">15.7300148010254</t>
   </si>
   <si>
     <t xml:space="preserve">15.3684062957764</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4045686721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4768877029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.802339553833</t>
+    <t xml:space="preserve">15.4045658111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4768905639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8023386001587</t>
   </si>
   <si>
     <t xml:space="preserve">16.670202255249</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1402950286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.104133605957</t>
+    <t xml:space="preserve">17.1402912139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1041316986084</t>
   </si>
   <si>
     <t xml:space="preserve">16.814847946167</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0679721832275</t>
+    <t xml:space="preserve">17.0679740905762</t>
   </si>
   <si>
     <t xml:space="preserve">16.8871669769287</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">17.8273506164551</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6827068328857</t>
+    <t xml:space="preserve">17.682710647583</t>
   </si>
   <si>
     <t xml:space="preserve">17.3934192657471</t>
@@ -1145,34 +1145,34 @@
     <t xml:space="preserve">17.7550296783447</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8996734619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5867309570312</t>
+    <t xml:space="preserve">17.8996753692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5867328643799</t>
   </si>
   <si>
     <t xml:space="preserve">18.6590538024902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0206642150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5427989959717</t>
+    <t xml:space="preserve">19.0206623077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5428009033203</t>
   </si>
   <si>
     <t xml:space="preserve">19.2444362640381</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9157524108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4378910064697</t>
+    <t xml:space="preserve">19.9157543182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4378890991211</t>
   </si>
   <si>
     <t xml:space="preserve">19.6546859741211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4682102203369</t>
+    <t xml:space="preserve">19.4682083129883</t>
   </si>
   <si>
     <t xml:space="preserve">19.6173896789551</t>
@@ -1181,16 +1181,16 @@
     <t xml:space="preserve">19.0952548980713</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8714809417725</t>
+    <t xml:space="preserve">18.8714828491211</t>
   </si>
   <si>
     <t xml:space="preserve">18.9460716247559</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7968902587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9018020629883</t>
+    <t xml:space="preserve">18.7968921661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9018001556396</t>
   </si>
   <si>
     <t xml:space="preserve">17.3050765991211</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">17.7899169921875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8341865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1698436737061</t>
+    <t xml:space="preserve">18.8341884613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1698455810547</t>
   </si>
   <si>
     <t xml:space="preserve">19.3936176300049</t>
@@ -1220,22 +1220,22 @@
     <t xml:space="preserve">19.6919803619385</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3190269470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4239368438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.13254737854</t>
+    <t xml:space="preserve">19.3190288543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4239387512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1325492858887</t>
   </si>
   <si>
     <t xml:space="preserve">19.3563232421875</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7292766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7223014831543</t>
+    <t xml:space="preserve">19.7292785644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7222995758057</t>
   </si>
   <si>
     <t xml:space="preserve">18.9087772369385</t>
@@ -1247,22 +1247,22 @@
     <t xml:space="preserve">18.5731182098389</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5358257293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9763946533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1255741119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4612331390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.759593963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6104125976562</t>
+    <t xml:space="preserve">18.5358238220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9763927459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1255722045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4612350463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7595958709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6104164123535</t>
   </si>
   <si>
     <t xml:space="preserve">18.3493461608887</t>
@@ -1274,52 +1274,52 @@
     <t xml:space="preserve">18.3120498657227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4985275268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2817306518555</t>
+    <t xml:space="preserve">18.4985294342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2817325592041</t>
   </si>
   <si>
     <t xml:space="preserve">19.0579586029053</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1628704071045</t>
+    <t xml:space="preserve">18.1628684997559</t>
   </si>
   <si>
     <t xml:space="preserve">18.0136871337891</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3866405487061</t>
+    <t xml:space="preserve">18.3866424560547</t>
   </si>
   <si>
     <t xml:space="preserve">17.1558933258057</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1862144470215</t>
+    <t xml:space="preserve">16.1862106323242</t>
   </si>
   <si>
     <t xml:space="preserve">15.5894870758057</t>
   </si>
   <si>
-    <t xml:space="preserve">15.141939163208</t>
+    <t xml:space="preserve">15.1419382095337</t>
   </si>
   <si>
     <t xml:space="preserve">14.9554615020752</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0370292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5218696594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6640777587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1046457290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9927597045898</t>
+    <t xml:space="preserve">16.0370311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5218715667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6640758514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1046447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9927577972412</t>
   </si>
   <si>
     <t xml:space="preserve">15.0300531387329</t>
@@ -1331,85 +1331,85 @@
     <t xml:space="preserve">14.3661947250366</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5153751373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6198043823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8883304595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2538261413574</t>
+    <t xml:space="preserve">14.5153770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6198053359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.888331413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2538270950317</t>
   </si>
   <si>
     <t xml:space="preserve">16.2608013153076</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9251441955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7759599685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7013721466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.552191734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6267795562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5148935317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2911214828491</t>
+    <t xml:space="preserve">15.925145149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7759609222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7013711929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.552188873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6267824172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5148954391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2911233901978</t>
   </si>
   <si>
     <t xml:space="preserve">15.21653175354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1792373657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8505535125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8132600784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0743274688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8878479003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4030075073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9032487869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7093152999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4403057098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1116199493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9624404907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5591659545898</t>
+    <t xml:space="preserve">15.179235458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8505525588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8132581710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0743255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8878498077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4030065536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9032497406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7093124389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4403038024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1116237640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.962438583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5591678619385</t>
   </si>
   <si>
     <t xml:space="preserve">16.3726902008057</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4845752716064</t>
+    <t xml:space="preserve">16.4845771789551</t>
   </si>
   <si>
     <t xml:space="preserve">16.7829399108887</t>
@@ -1421,67 +1421,67 @@
     <t xml:space="preserve">15.7386655807495</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3657121658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8435754776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8584966659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0673513412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8734149932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9181680679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.409984588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2235088348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2980995178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6710548400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7083473205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.745641708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6337585449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9321231842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8575286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0067100524902</t>
+    <t xml:space="preserve">15.3657131195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.843578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.858494758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0673503875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8734140396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9181671142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4099864959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2235069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2980976104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6710510253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.708345413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7456436157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6337547302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9321212768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8575305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0067081451416</t>
   </si>
   <si>
     <t xml:space="preserve">17.3796653747559</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2304840087891</t>
+    <t xml:space="preserve">17.2304859161377</t>
   </si>
   <si>
     <t xml:space="preserve">17.5288467407227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.343240737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7227535247803</t>
+    <t xml:space="preserve">18.3432388305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.722749710083</t>
   </si>
   <si>
     <t xml:space="preserve">16.6756725311279</t>
@@ -1490,91 +1490,91 @@
     <t xml:space="preserve">16.7532348632812</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3654308319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0939636230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6673774719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6285943984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0468854904175</t>
+    <t xml:space="preserve">16.3654270172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0939655303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6673765182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6285953521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0468873977661</t>
   </si>
   <si>
     <t xml:space="preserve">15.2640571594238</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7061576843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5898170471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5122537612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7449388504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950830459595</t>
+    <t xml:space="preserve">15.7061557769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5898151397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5122528076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7449369430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950820922852</t>
   </si>
   <si>
     <t xml:space="preserve">15.0158634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1864957809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4191808700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4967422485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5510330200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3261070251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2795715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8612813949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0164031982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9388389587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9000616073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7837190628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8224983215332</t>
+    <t xml:space="preserve">15.1864986419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4191818237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4967432022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5510339736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3261079788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2795696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8612804412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0164012908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9388408660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9000635147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7837181091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8224992752075</t>
   </si>
   <si>
     <t xml:space="preserve">16.3266468048096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7920150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0247020721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9083557128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4817695617676</t>
+    <t xml:space="preserve">16.7920169830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0247001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9083576202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4817714691162</t>
   </si>
   <si>
     <t xml:space="preserve">16.5593318939209</t>
@@ -1583,52 +1583,55 @@
     <t xml:space="preserve">16.0551853179932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4042072296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1327438354492</t>
+    <t xml:space="preserve">16.4042091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1327457427979</t>
   </si>
   <si>
     <t xml:space="preserve">16.2878684997559</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1715278625488</t>
+    <t xml:space="preserve">16.1715240478516</t>
   </si>
   <si>
     <t xml:space="preserve">15.9776220321655</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3881578445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346923828125</t>
+    <t xml:space="preserve">15.3881559371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346942901611</t>
   </si>
   <si>
     <t xml:space="preserve">16.2103061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4429893493652</t>
+    <t xml:space="preserve">16.4429912567139</t>
   </si>
   <si>
     <t xml:space="preserve">16.5981101989746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5205516815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6368961334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2490882873535</t>
+    <t xml:space="preserve">16.5205497741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6368942260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2490863800049</t>
   </si>
   <si>
     <t xml:space="preserve">16.8307952880859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9859180450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8390922546387</t>
+    <t xml:space="preserve">16.9859199523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5288486480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.83909034729</t>
   </si>
   <si>
     <t xml:space="preserve">17.5676288604736</t>
@@ -1637,10 +1640,10 @@
     <t xml:space="preserve">17.9942169189453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6147060394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2656784057617</t>
+    <t xml:space="preserve">18.6147041320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2656803131104</t>
   </si>
   <si>
     <t xml:space="preserve">18.8473873138428</t>
@@ -1649,10 +1652,10 @@
     <t xml:space="preserve">18.5371437072754</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0717754364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4595813751221</t>
+    <t xml:space="preserve">18.07177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4595832824707</t>
   </si>
   <si>
     <t xml:space="preserve">18.7698268890381</t>
@@ -1661,16 +1664,16 @@
     <t xml:space="preserve">18.9249496459961</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1576347351074</t>
+    <t xml:space="preserve">19.1576385498047</t>
   </si>
   <si>
     <t xml:space="preserve">19.0025119781494</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0412921905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3044605255127</t>
+    <t xml:space="preserve">19.0412902832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3044624328613</t>
   </si>
   <si>
     <t xml:space="preserve">18.1493377685547</t>
@@ -1697,22 +1700,22 @@
     <t xml:space="preserve">18.8086090087891</t>
   </si>
   <si>
-    <t xml:space="preserve">18.382022857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1881198883057</t>
+    <t xml:space="preserve">18.3820209503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.188117980957</t>
   </si>
   <si>
     <t xml:space="preserve">17.916654586792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9554328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6064109802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6451873779297</t>
+    <t xml:space="preserve">17.9554347991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.606409072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6451892852783</t>
   </si>
   <si>
     <t xml:space="preserve">17.1410427093506</t>
@@ -1721,40 +1724,40 @@
     <t xml:space="preserve">17.1022605895996</t>
   </si>
   <si>
-    <t xml:space="preserve">17.29616355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1244478225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7676687240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.557710647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9610300064087</t>
+    <t xml:space="preserve">17.2961616516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1244487762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7676677703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5577087402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9610271453857</t>
   </si>
   <si>
     <t xml:space="preserve">13.0302925109863</t>
   </si>
   <si>
-    <t xml:space="preserve">13.185417175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1388807296753</t>
+    <t xml:space="preserve">13.1854162216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.138879776001</t>
   </si>
   <si>
     <t xml:space="preserve">13.5732221603394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.262978553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.169903755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.952733039856</t>
+    <t xml:space="preserve">13.2629776000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1699028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9527320861816</t>
   </si>
   <si>
     <t xml:space="preserve">12.5649271011353</t>
@@ -1763,34 +1766,34 @@
     <t xml:space="preserve">11.7582883834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5566291809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8585786819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7810153961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3156499862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8197965621948</t>
+    <t xml:space="preserve">11.5566301345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8585777282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7810173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3156490325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8197975158691</t>
   </si>
   <si>
     <t xml:space="preserve">11.1300439834595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7893123626709</t>
+    <t xml:space="preserve">11.7893133163452</t>
   </si>
   <si>
     <t xml:space="preserve">12.2546815872192</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9056568145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6341905593872</t>
+    <t xml:space="preserve">11.9056558609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6341924667358</t>
   </si>
   <si>
     <t xml:space="preserve">12.0219974517822</t>
@@ -1802,19 +1805,19 @@
     <t xml:space="preserve">11.8280944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4790697097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7117528915405</t>
+    <t xml:space="preserve">11.4790678024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7117519378662</t>
   </si>
   <si>
     <t xml:space="preserve">11.6729726791382</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5954093933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2851667404175</t>
+    <t xml:space="preserve">11.5954103469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2851648330688</t>
   </si>
   <si>
     <t xml:space="preserve">11.4015064239502</t>
@@ -1829,28 +1832,28 @@
     <t xml:space="preserve">10.5095529556274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871124267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6646747589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2463855743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2159004211426</t>
+    <t xml:space="preserve">10.5871143341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6646757125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2463846206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2159013748169</t>
   </si>
   <si>
     <t xml:space="preserve">12.3710222244263</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0773696899414</t>
+    <t xml:space="preserve">14.07737159729</t>
   </si>
   <si>
     <t xml:space="preserve">14.1181745529175</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0365686416626</t>
+    <t xml:space="preserve">14.0365676879883</t>
   </si>
   <si>
     <t xml:space="preserve">13.8733520507812</t>
@@ -1859,52 +1862,52 @@
     <t xml:space="preserve">13.8325471878052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1997833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6078214645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2813911437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4245071411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5469179153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5061149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7509393692017</t>
+    <t xml:space="preserve">14.199782371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6078224182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2813901901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4245080947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5469188690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5061140060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.750940322876</t>
   </si>
   <si>
     <t xml:space="preserve">13.9549589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5262145996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7710409164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6894311904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3221940994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4038019180298</t>
+    <t xml:space="preserve">14.5262136459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7710390090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6894292831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3221950531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4038038253784</t>
   </si>
   <si>
     <t xml:space="preserve">13.5877237319946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4653120040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6285276412964</t>
+    <t xml:space="preserve">13.465311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6285285949707</t>
   </si>
   <si>
     <t xml:space="preserve">13.9141550064087</t>
@@ -1919,16 +1922,13 @@
     <t xml:space="preserve">14.1589775085449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7917432785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3837022781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2204875946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0773706436157</t>
+    <t xml:space="preserve">13.7917423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3837032318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2204885482788</t>
   </si>
   <si>
     <t xml:space="preserve">13.3429002761841</t>
@@ -1940,10 +1940,10 @@
     <t xml:space="preserve">13.0572719573975</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2612924575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0980749130249</t>
+    <t xml:space="preserve">13.2612915039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0980758666992</t>
   </si>
   <si>
     <t xml:space="preserve">12.4860153198242</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">12.8532514572144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7308406829834</t>
+    <t xml:space="preserve">12.7308397293091</t>
   </si>
   <si>
     <t xml:space="preserve">12.6900358200073</t>
@@ -1964,16 +1964,16 @@
     <t xml:space="preserve">12.7716426849365</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8526477813721</t>
+    <t xml:space="preserve">14.8526468276978</t>
   </si>
   <si>
     <t xml:space="preserve">15.2606859207153</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4239015579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0767669677734</t>
+    <t xml:space="preserve">15.4239025115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0767650604248</t>
   </si>
   <si>
     <t xml:space="preserve">15.9135494232178</t>
@@ -1982,28 +1982,28 @@
     <t xml:space="preserve">15.5055084228516</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6687250137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.587119102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3014907836914</t>
+    <t xml:space="preserve">15.6687288284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5871162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3014888763428</t>
   </si>
   <si>
     <t xml:space="preserve">15.3830986022949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3422918319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7503318786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2198820114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1790781021118</t>
+    <t xml:space="preserve">15.3422937393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7503347396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2198839187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1790790557861</t>
   </si>
   <si>
     <t xml:space="preserve">15.4647064208984</t>
@@ -2015,13 +2015,13 @@
     <t xml:space="preserve">16.1583728790283</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8112373352051</t>
+    <t xml:space="preserve">16.8112392425537</t>
   </si>
   <si>
     <t xml:space="preserve">17.7089233398438</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1376705169678</t>
+    <t xml:space="preserve">17.1376686096191</t>
   </si>
   <si>
     <t xml:space="preserve">17.3824939727783</t>
@@ -2030,31 +2030,31 @@
     <t xml:space="preserve">16.8928451538086</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1991786956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4848079681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6480197906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5664119720459</t>
+    <t xml:space="preserve">16.1991767883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.484806060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6480178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5664138793945</t>
   </si>
   <si>
     <t xml:space="preserve">16.2399787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4031982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7296314239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2192783355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4640979766846</t>
+    <t xml:space="preserve">16.4032001495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7296295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2192764282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4641017913818</t>
   </si>
   <si>
     <t xml:space="preserve">17.5457077026367</t>
@@ -2066,19 +2066,19 @@
     <t xml:space="preserve">18.0353584289551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9744529724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8721389770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.11696434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1985721588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3617877960205</t>
+    <t xml:space="preserve">16.9744510650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8721408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1169662475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1985702514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3617897033691</t>
   </si>
   <si>
     <t xml:space="preserve">19.1778678894043</t>
@@ -2087,22 +2087,22 @@
     <t xml:space="preserve">18.8514366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6882190704346</t>
+    <t xml:space="preserve">18.6882209777832</t>
   </si>
   <si>
     <t xml:space="preserve">19.0962600708008</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6066112518311</t>
+    <t xml:space="preserve">18.6066093444824</t>
   </si>
   <si>
     <t xml:space="preserve">18.9330463409424</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2594776153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3410835266113</t>
+    <t xml:space="preserve">19.2594757080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3410816192627</t>
   </si>
   <si>
     <t xml:space="preserve">19.4226913452148</t>
@@ -2123,19 +2123,19 @@
     <t xml:space="preserve">19.4886722564697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6581420898438</t>
+    <t xml:space="preserve">19.6581401824951</t>
   </si>
   <si>
     <t xml:space="preserve">19.5734062194824</t>
   </si>
   <si>
-    <t xml:space="preserve">19.403938293457</t>
+    <t xml:space="preserve">19.4039402008057</t>
   </si>
   <si>
     <t xml:space="preserve">19.9970741271973</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3360080718994</t>
+    <t xml:space="preserve">20.3360061645508</t>
   </si>
   <si>
     <t xml:space="preserve">20.166540145874</t>
@@ -2144,22 +2144,22 @@
     <t xml:space="preserve">19.3192043304443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0650062561035</t>
+    <t xml:space="preserve">19.0650081634521</t>
   </si>
   <si>
     <t xml:space="preserve">18.6413383483887</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7428703308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0818061828613</t>
+    <t xml:space="preserve">19.7428722381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0818042755127</t>
   </si>
   <si>
     <t xml:space="preserve">20.4207401275635</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5054721832275</t>
+    <t xml:space="preserve">20.5054740905762</t>
   </si>
   <si>
     <t xml:space="preserve">20.6749382019043</t>
@@ -2180,10 +2180,10 @@
     <t xml:space="preserve">22.7085399627686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0306739807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4543418884277</t>
+    <t xml:space="preserve">22.0306720733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4543399810791</t>
   </si>
   <si>
     <t xml:space="preserve">22.2001419067383</t>
@@ -2195,16 +2195,16 @@
     <t xml:space="preserve">22.7932739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0474739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6406059265137</t>
+    <t xml:space="preserve">23.0474758148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6406078338623</t>
   </si>
   <si>
     <t xml:space="preserve">23.5558738708496</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3016719818115</t>
+    <t xml:space="preserve">23.3016738891602</t>
   </si>
   <si>
     <t xml:space="preserve">23.4711399078369</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">24.1490077972412</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1658096313477</t>
+    <t xml:space="preserve">25.165807723999</t>
   </si>
   <si>
     <t xml:space="preserve">24.9116077423096</t>
@@ -2240,34 +2240,34 @@
     <t xml:space="preserve">24.2337398529053</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2505416870117</t>
+    <t xml:space="preserve">25.2505397796631</t>
   </si>
   <si>
     <t xml:space="preserve">23.8100757598877</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5726757049561</t>
+    <t xml:space="preserve">24.5726737976074</t>
   </si>
   <si>
     <t xml:space="preserve">24.403205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4879417419434</t>
+    <t xml:space="preserve">24.4879398345947</t>
   </si>
   <si>
     <t xml:space="preserve">25.081075668335</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5047397613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3352718353271</t>
+    <t xml:space="preserve">25.5047435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3352737426758</t>
   </si>
   <si>
     <t xml:space="preserve">25.4200077056885</t>
   </si>
   <si>
-    <t xml:space="preserve">25.758939743042</t>
+    <t xml:space="preserve">25.7589416503906</t>
   </si>
   <si>
     <t xml:space="preserve">26.2673397064209</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">26.5215396881104</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8772754669189</t>
+    <t xml:space="preserve">27.8772773742676</t>
   </si>
   <si>
     <t xml:space="preserve">29.5719432830811</t>
@@ -2291,22 +2291,22 @@
     <t xml:space="preserve">28.9788093566895</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1482791900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2330093383789</t>
+    <t xml:space="preserve">29.1482772827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2330112457275</t>
   </si>
   <si>
     <t xml:space="preserve">27.9620094299316</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0299415588379</t>
+    <t xml:space="preserve">27.0299396514893</t>
   </si>
   <si>
     <t xml:space="preserve">28.4704055786133</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4536094665527</t>
+    <t xml:space="preserve">27.4536113739014</t>
   </si>
   <si>
     <t xml:space="preserve">28.3856754302979</t>
@@ -2315,28 +2315,28 @@
     <t xml:space="preserve">27.7078094482422</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1314735412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.284143447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6742076873779</t>
+    <t xml:space="preserve">28.1314754486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2841415405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6742057800293</t>
   </si>
   <si>
     <t xml:space="preserve">26.0131416320801</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8436737060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3520755767822</t>
+    <t xml:space="preserve">25.8436756134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3520736694336</t>
   </si>
   <si>
     <t xml:space="preserve">26.6062755584717</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8268737792969</t>
+    <t xml:space="preserve">24.8268718719482</t>
   </si>
   <si>
     <t xml:space="preserve">26.1826076507568</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">24.0642738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">22.962739944458</t>
+    <t xml:space="preserve">22.9627418518066</t>
   </si>
   <si>
     <t xml:space="preserve">24.3184757232666</t>
@@ -3651,6 +3651,9 @@
   </si>
   <si>
     <t xml:space="preserve">67.8000030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.4000015258789</t>
   </si>
 </sst>
 </file>
@@ -29461,7 +29464,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G980" t="s">
-        <v>487</v>
+        <v>538</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -29487,7 +29490,7 @@
         <v>23</v>
       </c>
       <c r="G981" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -29513,7 +29516,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G982" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -29539,7 +29542,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G983" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -29565,7 +29568,7 @@
         <v>24</v>
       </c>
       <c r="G984" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -29617,7 +29620,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G986" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -29643,7 +29646,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G987" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29669,7 +29672,7 @@
         <v>24</v>
       </c>
       <c r="G988" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29695,7 +29698,7 @@
         <v>24</v>
       </c>
       <c r="G989" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29721,7 +29724,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G990" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29747,7 +29750,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G991" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29773,7 +29776,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G992" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29799,7 +29802,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G993" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29825,7 +29828,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G994" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29851,7 +29854,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G995" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29877,7 +29880,7 @@
         <v>24.5</v>
       </c>
       <c r="G996" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29903,7 +29906,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G997" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29929,7 +29932,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G998" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29955,7 +29958,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G999" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29981,7 +29984,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1000" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -30007,7 +30010,7 @@
         <v>23.25</v>
       </c>
       <c r="G1001" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -30033,7 +30036,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1002" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -30059,7 +30062,7 @@
         <v>23.5</v>
       </c>
       <c r="G1003" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -30111,7 +30114,7 @@
         <v>23.75</v>
       </c>
       <c r="G1005" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -30137,7 +30140,7 @@
         <v>23.75</v>
       </c>
       <c r="G1006" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -30163,7 +30166,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1007" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -30189,7 +30192,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1008" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -30215,7 +30218,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1009" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -30241,7 +30244,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1010" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -30267,7 +30270,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1011" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -30319,7 +30322,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1013" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -30345,7 +30348,7 @@
         <v>24.25</v>
       </c>
       <c r="G1014" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -30371,7 +30374,7 @@
         <v>24</v>
       </c>
       <c r="G1015" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -30397,7 +30400,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1016" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -30423,7 +30426,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1017" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -30449,7 +30452,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1018" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -30475,7 +30478,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1019" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -30501,7 +30504,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1020" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -30527,7 +30530,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1021" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -30553,7 +30556,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G1022" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -30579,7 +30582,7 @@
         <v>23.5</v>
       </c>
       <c r="G1023" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -30605,7 +30608,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1024" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -30631,7 +30634,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1025" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -30657,7 +30660,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1026" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -30683,7 +30686,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1027" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -30709,7 +30712,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1028" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30735,7 +30738,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1029" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30761,7 +30764,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1030" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30787,7 +30790,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1031" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30813,7 +30816,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1032" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30839,7 +30842,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1033" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -30865,7 +30868,7 @@
         <v>22.75</v>
       </c>
       <c r="G1034" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -30891,7 +30894,7 @@
         <v>23.25</v>
       </c>
       <c r="G1035" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -30917,7 +30920,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1036" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -30943,7 +30946,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1037" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -30969,7 +30972,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1038" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -30995,7 +30998,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1039" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -31021,7 +31024,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1040" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -31047,7 +31050,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1041" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -31073,7 +31076,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1042" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -31099,7 +31102,7 @@
         <v>23.75</v>
       </c>
       <c r="G1043" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -31125,7 +31128,7 @@
         <v>23.75</v>
       </c>
       <c r="G1044" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -31151,7 +31154,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1045" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -31177,7 +31180,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1046" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -31203,7 +31206,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1047" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -31229,7 +31232,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1048" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -31255,7 +31258,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1049" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -31281,7 +31284,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1050" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -31307,7 +31310,7 @@
         <v>23.25</v>
       </c>
       <c r="G1051" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -31333,7 +31336,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1052" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -31385,7 +31388,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1054" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -31411,7 +31414,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1055" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -31437,7 +31440,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1056" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -31463,7 +31466,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -31645,7 +31648,7 @@
         <v>19.5</v>
       </c>
       <c r="G1064" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -31671,7 +31674,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1065" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31697,7 +31700,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1066" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31723,7 +31726,7 @@
         <v>18</v>
       </c>
       <c r="G1067" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31749,7 +31752,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1068" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31775,7 +31778,7 @@
         <v>17</v>
       </c>
       <c r="G1069" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -31801,7 +31804,7 @@
         <v>17</v>
       </c>
       <c r="G1070" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -31827,7 +31830,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1071" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31853,7 +31856,7 @@
         <v>17.5</v>
       </c>
       <c r="G1072" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31879,7 +31882,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1073" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -31905,7 +31908,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1074" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -31931,7 +31934,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1075" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31957,7 +31960,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1076" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31983,7 +31986,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1077" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -32009,7 +32012,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1078" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -32035,7 +32038,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1079" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -32061,7 +32064,7 @@
         <v>14</v>
       </c>
       <c r="G1080" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -32087,7 +32090,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1081" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -32113,7 +32116,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1082" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -32139,7 +32142,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1083" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -32165,7 +32168,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1084" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -32191,7 +32194,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1085" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32217,7 +32220,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1086" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -32243,7 +32246,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1087" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -32269,7 +32272,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1088" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -32295,7 +32298,7 @@
         <v>15</v>
       </c>
       <c r="G1089" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -32321,7 +32324,7 @@
         <v>15.5</v>
       </c>
       <c r="G1090" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -32347,7 +32350,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1091" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -32373,7 +32376,7 @@
         <v>15.25</v>
       </c>
       <c r="G1092" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -32399,7 +32402,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1093" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -32425,7 +32428,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1094" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -32451,7 +32454,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1095" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -32477,7 +32480,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1096" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -32503,7 +32506,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1097" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -32529,7 +32532,7 @@
         <v>15</v>
       </c>
       <c r="G1098" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -32555,7 +32558,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1099" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -32581,7 +32584,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1100" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -32607,7 +32610,7 @@
         <v>15</v>
       </c>
       <c r="G1101" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -32633,7 +32636,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1102" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -32659,7 +32662,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1103" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -32685,7 +32688,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1104" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32711,7 +32714,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1105" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -32737,7 +32740,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1106" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32763,7 +32766,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1107" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32789,7 +32792,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1108" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32815,7 +32818,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1109" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32841,7 +32844,7 @@
         <v>13.75</v>
       </c>
       <c r="G1110" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32867,7 +32870,7 @@
         <v>14</v>
       </c>
       <c r="G1111" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32893,7 +32896,7 @@
         <v>14</v>
       </c>
       <c r="G1112" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32919,7 +32922,7 @@
         <v>14.5</v>
       </c>
       <c r="G1113" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32945,7 +32948,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1114" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -32971,7 +32974,7 @@
         <v>15</v>
       </c>
       <c r="G1115" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -32997,7 +33000,7 @@
         <v>15.75</v>
       </c>
       <c r="G1116" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -33023,7 +33026,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1117" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -33049,7 +33052,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1118" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -33075,7 +33078,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1119" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -33101,7 +33104,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1120" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -33127,7 +33130,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1121" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -33153,7 +33156,7 @@
         <v>17</v>
       </c>
       <c r="G1122" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -33179,7 +33182,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1123" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -33205,7 +33208,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1124" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -33231,7 +33234,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1125" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -33257,7 +33260,7 @@
         <v>17.5</v>
       </c>
       <c r="G1126" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -33283,7 +33286,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1127" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -33309,7 +33312,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1128" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -33335,7 +33338,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1129" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -33361,7 +33364,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1130" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -33387,7 +33390,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1131" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -33413,7 +33416,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1132" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -33439,7 +33442,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1133" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -33465,7 +33468,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1134" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -33491,7 +33494,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1135" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -33517,7 +33520,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1136" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -33543,7 +33546,7 @@
         <v>18</v>
       </c>
       <c r="G1137" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -33569,7 +33572,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1138" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -33595,7 +33598,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1139" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -33621,7 +33624,7 @@
         <v>17.5</v>
       </c>
       <c r="G1140" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -33647,7 +33650,7 @@
         <v>17</v>
       </c>
       <c r="G1141" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33673,7 +33676,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1142" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33699,7 +33702,7 @@
         <v>16.5</v>
       </c>
       <c r="G1143" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33725,7 +33728,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1144" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33751,7 +33754,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1145" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33777,7 +33780,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1146" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33803,7 +33806,7 @@
         <v>17.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33829,7 +33832,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1148" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33855,7 +33858,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1149" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33881,7 +33884,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1150" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33907,7 +33910,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1151" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33933,7 +33936,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1152" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33959,7 +33962,7 @@
         <v>17.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33985,7 +33988,7 @@
         <v>17</v>
       </c>
       <c r="G1154" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -34011,7 +34014,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1155" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -34037,7 +34040,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1156" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -34063,7 +34066,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1157" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -34089,7 +34092,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1158" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -34115,7 +34118,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1159" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -34141,7 +34144,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1160" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -34167,7 +34170,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1161" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -34193,7 +34196,7 @@
         <v>16.5</v>
       </c>
       <c r="G1162" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -34219,7 +34222,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1163" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -34245,7 +34248,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1164" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -34271,7 +34274,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1165" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -34297,7 +34300,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1166" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -34323,7 +34326,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1167" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -34349,7 +34352,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1168" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -34375,7 +34378,7 @@
         <v>17.25</v>
       </c>
       <c r="G1169" t="s">
-        <v>638</v>
+        <v>611</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34401,7 +34404,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1170" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -34427,7 +34430,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1171" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -34453,7 +34456,7 @@
         <v>17</v>
       </c>
       <c r="G1172" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -34479,7 +34482,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1173" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -34505,7 +34508,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1174" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -34531,7 +34534,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1175" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -34557,7 +34560,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -34583,7 +34586,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1177" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34635,7 +34638,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1179" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34661,7 +34664,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1180" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34687,7 +34690,7 @@
         <v>17</v>
       </c>
       <c r="G1181" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34713,7 +34716,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1182" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34739,7 +34742,7 @@
         <v>17</v>
       </c>
       <c r="G1183" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34765,7 +34768,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1184" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34791,7 +34794,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1185" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34843,7 +34846,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1187" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34869,7 +34872,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1188" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34895,7 +34898,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1189" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34921,7 +34924,7 @@
         <v>17.25</v>
       </c>
       <c r="G1190" t="s">
-        <v>638</v>
+        <v>611</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34947,7 +34950,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1191" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34973,7 +34976,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1192" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -34999,7 +35002,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1193" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -35025,7 +35028,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1194" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -35051,7 +35054,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1195" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -35077,7 +35080,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1196" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -35155,7 +35158,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1199" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35207,7 +35210,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1201" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -35233,7 +35236,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1202" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -35259,7 +35262,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1203" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -35311,7 +35314,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1205" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -35337,7 +35340,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1206" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35441,7 +35444,7 @@
         <v>16.5</v>
       </c>
       <c r="G1210" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -35467,7 +35470,7 @@
         <v>16.5</v>
       </c>
       <c r="G1211" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -35493,7 +35496,7 @@
         <v>17.25</v>
       </c>
       <c r="G1212" t="s">
-        <v>638</v>
+        <v>611</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -35519,7 +35522,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1213" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -35545,7 +35548,7 @@
         <v>17</v>
       </c>
       <c r="G1214" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -35571,7 +35574,7 @@
         <v>17.25</v>
       </c>
       <c r="G1215" t="s">
-        <v>638</v>
+        <v>611</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35597,7 +35600,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1216" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35623,7 +35626,7 @@
         <v>17</v>
       </c>
       <c r="G1217" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -35649,7 +35652,7 @@
         <v>17</v>
       </c>
       <c r="G1218" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35675,7 +35678,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1219" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35701,7 +35704,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1220" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35727,7 +35730,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1221" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35753,7 +35756,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1222" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -36039,7 +36042,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -36117,7 +36120,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1236" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -36143,7 +36146,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1237" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -38509,7 +38512,7 @@
         <v>23</v>
       </c>
       <c r="G1328" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -39211,7 +39214,7 @@
         <v>23</v>
       </c>
       <c r="G1355" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39237,7 +39240,7 @@
         <v>23</v>
       </c>
       <c r="G1356" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -39263,7 +39266,7 @@
         <v>23</v>
       </c>
       <c r="G1357" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39289,7 +39292,7 @@
         <v>23</v>
       </c>
       <c r="G1358" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39341,7 +39344,7 @@
         <v>23</v>
       </c>
       <c r="G1360" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -69743,7 +69746,7 @@
     </row>
     <row r="2530">
       <c r="A2530" s="1" t="n">
-        <v>46001.6924884259</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B2530" t="n">
         <v>6629</v>
@@ -69764,6 +69767,32 @@
         <v>1212</v>
       </c>
       <c r="H2530" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" s="1" t="n">
+        <v>46002.6910069444</v>
+      </c>
+      <c r="B2531" t="n">
+        <v>27250</v>
+      </c>
+      <c r="C2531" t="n">
+        <v>70</v>
+      </c>
+      <c r="D2531" t="n">
+        <v>67.3000030517578</v>
+      </c>
+      <c r="E2531" t="n">
+        <v>67.4000015258789</v>
+      </c>
+      <c r="F2531" t="n">
+        <v>69.4000015258789</v>
+      </c>
+      <c r="G2531" t="s">
+        <v>1213</v>
+      </c>
+      <c r="H2531" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="1215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="1216">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23958683013916</t>
+    <t xml:space="preserve">9.23958778381348</t>
   </si>
   <si>
     <t xml:space="preserve">CMB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55656623840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31377601623535</t>
+    <t xml:space="preserve">9.55656719207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31377506256104</t>
   </si>
   <si>
     <t xml:space="preserve">9.40144920349121</t>
@@ -56,34 +56,34 @@
     <t xml:space="preserve">9.40819263458252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44191360473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36098384857178</t>
+    <t xml:space="preserve">9.44191455841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36098289489746</t>
   </si>
   <si>
     <t xml:space="preserve">9.13842487335205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32051753997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26656532287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34075164794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27330875396729</t>
+    <t xml:space="preserve">9.32051849365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26656341552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3407506942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2733097076416</t>
   </si>
   <si>
     <t xml:space="preserve">9.19237804412842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19912242889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10470390319824</t>
+    <t xml:space="preserve">9.19912338256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10470294952393</t>
   </si>
   <si>
     <t xml:space="preserve">8.84167957305908</t>
@@ -92,25 +92,25 @@
     <t xml:space="preserve">8.77423763275146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84842205047607</t>
+    <t xml:space="preserve">8.84842395782471</t>
   </si>
   <si>
     <t xml:space="preserve">8.36283874511719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3291187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61911964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.450514793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43028163909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63260746002197</t>
+    <t xml:space="preserve">8.32911682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61911869049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45051288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4302806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63260936737061</t>
   </si>
   <si>
     <t xml:space="preserve">8.80121326446533</t>
@@ -119,28 +119,28 @@
     <t xml:space="preserve">9.22609996795654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25982093811035</t>
+    <t xml:space="preserve">9.25981998443604</t>
   </si>
   <si>
     <t xml:space="preserve">9.07098197937012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87539958953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96981906890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71353912353516</t>
+    <t xml:space="preserve">8.87540054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96981811523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71353816986084</t>
   </si>
   <si>
     <t xml:space="preserve">8.6663293838501</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89563179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81470203399658</t>
+    <t xml:space="preserve">8.89563274383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81470108032227</t>
   </si>
   <si>
     <t xml:space="preserve">8.99679565429688</t>
@@ -149,31 +149,31 @@
     <t xml:space="preserve">9.01028442382812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90237617492676</t>
+    <t xml:space="preserve">8.90237712860107</t>
   </si>
   <si>
     <t xml:space="preserve">8.9765625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18563365936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17214679718018</t>
+    <t xml:space="preserve">9.18563270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17214488983154</t>
   </si>
   <si>
     <t xml:space="preserve">9.13168048858643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34749412536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25307655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15865802764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08447074890137</t>
+    <t xml:space="preserve">9.34749698638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25307750701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15865707397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08447170257568</t>
   </si>
   <si>
     <t xml:space="preserve">9.16540241241455</t>
@@ -191,37 +191,37 @@
     <t xml:space="preserve">9.1249361038208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03726100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21261119842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04400444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09795951843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20586585998535</t>
+    <t xml:space="preserve">9.03726196289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21261024475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04400634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0979585647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20586776733398</t>
   </si>
   <si>
     <t xml:space="preserve">9.38121604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28679752349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22100830078125</t>
+    <t xml:space="preserve">9.28679943084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22100734710693</t>
   </si>
   <si>
     <t xml:space="preserve">9.22798824310303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19308757781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35363388061523</t>
+    <t xml:space="preserve">9.19308853149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35363483428955</t>
   </si>
   <si>
     <t xml:space="preserve">9.4094762802124</t>
@@ -230,40 +230,40 @@
     <t xml:space="preserve">9.52116298675537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49324131011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38853359222412</t>
+    <t xml:space="preserve">9.49324035644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38853549957275</t>
   </si>
   <si>
     <t xml:space="preserve">9.94696235656738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76547431945801</t>
+    <t xml:space="preserve">9.76547336578369</t>
   </si>
   <si>
     <t xml:space="preserve">9.77245330810547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66774940490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82829666137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75151252746582</t>
+    <t xml:space="preserve">9.66774845123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82829570770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75151348114014</t>
   </si>
   <si>
     <t xml:space="preserve">9.57002449035645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57700443267822</t>
+    <t xml:space="preserve">9.57700538635254</t>
   </si>
   <si>
     <t xml:space="preserve">9.55606365203857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47927856445312</t>
+    <t xml:space="preserve">9.47927951812744</t>
   </si>
   <si>
     <t xml:space="preserve">9.42343711853027</t>
@@ -272,76 +272,76 @@
     <t xml:space="preserve">9.39551639556885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4164571762085</t>
+    <t xml:space="preserve">9.41645622253418</t>
   </si>
   <si>
     <t xml:space="preserve">9.34665393829346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58398532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62586688995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63284683227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4653205871582</t>
+    <t xml:space="preserve">9.583984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62586498260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63284778594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46531963348389</t>
   </si>
   <si>
     <t xml:space="preserve">9.48626136779785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59096527099609</t>
+    <t xml:space="preserve">9.59096431732178</t>
   </si>
   <si>
     <t xml:space="preserve">9.56304359436035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53512287139893</t>
+    <t xml:space="preserve">9.53512191772461</t>
   </si>
   <si>
     <t xml:space="preserve">9.12328338623047</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30477237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28383159637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20704555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27685070037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36061382293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29081153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29778957366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31873226165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36759567260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47229957580566</t>
+    <t xml:space="preserve">9.30477333068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2838306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20704746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27685165405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36061573028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29081058502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29779148101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31873321533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36759471893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47229862213135</t>
   </si>
   <si>
     <t xml:space="preserve">9.52814292907715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50720119476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44437789916992</t>
+    <t xml:space="preserve">9.50720024108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44437885284424</t>
   </si>
   <si>
     <t xml:space="preserve">9.50022125244141</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">9.13724422454834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14422416687012</t>
+    <t xml:space="preserve">9.1442232131958</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120601654053</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">9.1093225479126</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03951930999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92783355712891</t>
+    <t xml:space="preserve">9.03952026367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92783546447754</t>
   </si>
   <si>
     <t xml:space="preserve">9.01159763336182</t>
@@ -377,52 +377,52 @@
     <t xml:space="preserve">9.07442188262939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97669792175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86501216888428</t>
+    <t xml:space="preserve">8.97669696807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86501121520996</t>
   </si>
   <si>
     <t xml:space="preserve">8.85105133056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.934814453125</t>
+    <t xml:space="preserve">8.93481636047363</t>
   </si>
   <si>
     <t xml:space="preserve">8.92085361480713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95575523376465</t>
+    <t xml:space="preserve">8.95575714111328</t>
   </si>
   <si>
     <t xml:space="preserve">8.96971702575684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00461864471436</t>
+    <t xml:space="preserve">9.00461769104004</t>
   </si>
   <si>
     <t xml:space="preserve">8.91387462615967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87897300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80916976928711</t>
+    <t xml:space="preserve">8.87897205352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80916881561279</t>
   </si>
   <si>
     <t xml:space="preserve">8.59975910186768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56485748291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81614875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83708953857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8999137878418</t>
+    <t xml:space="preserve">8.56485939025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81614971160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83709049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89991188049316</t>
   </si>
   <si>
     <t xml:space="preserve">8.99763774871826</t>
@@ -431,16 +431,16 @@
     <t xml:space="preserve">8.83010959625244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96273708343506</t>
+    <t xml:space="preserve">8.96273612976074</t>
   </si>
   <si>
     <t xml:space="preserve">9.08838176727295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04649925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09536266326904</t>
+    <t xml:space="preserve">9.04650020599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09536170959473</t>
   </si>
   <si>
     <t xml:space="preserve">9.66076850891113</t>
@@ -449,37 +449,37 @@
     <t xml:space="preserve">9.64680767059326</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70265007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79339504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92602157592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9818639755249</t>
+    <t xml:space="preserve">9.70265102386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79339408874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92602062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98186302185059</t>
   </si>
   <si>
     <t xml:space="preserve">10.0516662597656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4146432876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1912746429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2471160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1493902206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1354303359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2680549621582</t>
+    <t xml:space="preserve">10.414644241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.19127368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2471151351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1493921279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1354293823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2680568695068</t>
   </si>
   <si>
     <t xml:space="preserve">10.393702507019</t>
@@ -500,13 +500,13 @@
     <t xml:space="preserve">10.3588008880615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98884391784668</t>
+    <t xml:space="preserve">9.98884296417236</t>
   </si>
   <si>
     <t xml:space="preserve">9.95394229888916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1005296707153</t>
+    <t xml:space="preserve">10.100528717041</t>
   </si>
   <si>
     <t xml:space="preserve">10.4704856872559</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">10.3867225646973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5472707748413</t>
+    <t xml:space="preserve">10.5472688674927</t>
   </si>
   <si>
     <t xml:space="preserve">10.3448400497437</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">10.4006824493408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4355840682983</t>
+    <t xml:space="preserve">10.4355850219727</t>
   </si>
   <si>
     <t xml:space="preserve">10.3727617263794</t>
@@ -536,43 +536,43 @@
     <t xml:space="preserve">10.3657817840576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3378601074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2820177078247</t>
+    <t xml:space="preserve">10.3378620147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2820158004761</t>
   </si>
   <si>
     <t xml:space="preserve">10.3797426223755</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6100921630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5542507171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6938552856445</t>
+    <t xml:space="preserve">10.6100931167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5542488098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6938562393188</t>
   </si>
   <si>
     <t xml:space="preserve">11.0917348861694</t>
   </si>
   <si>
-    <t xml:space="preserve">11.042872428894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0358924865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.063814163208</t>
+    <t xml:space="preserve">11.0428733825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0358915328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0638132095337</t>
   </si>
   <si>
     <t xml:space="preserve">11.0847549438477</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3569869995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5175352096558</t>
+    <t xml:space="preserve">11.356987953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5175342559814</t>
   </si>
   <si>
     <t xml:space="preserve">12.0899219512939</t>
@@ -581,58 +581,58 @@
     <t xml:space="preserve">11.9991779327393</t>
   </si>
   <si>
-    <t xml:space="preserve">12.06898021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1038808822632</t>
+    <t xml:space="preserve">12.0689811706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1038827896118</t>
   </si>
   <si>
     <t xml:space="preserve">12.2853698730469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8228559494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9764223098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9903831481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2486534118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1090478897095</t>
+    <t xml:space="preserve">12.8228549957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9764242172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9903841018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2486543655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1090488433838</t>
   </si>
   <si>
     <t xml:space="preserve">13.1230087280273</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8926601409912</t>
+    <t xml:space="preserve">12.8926582336426</t>
   </si>
   <si>
     <t xml:space="preserve">12.9135999679565</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8437976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9624624252319</t>
+    <t xml:space="preserve">12.8437957763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9624614715576</t>
   </si>
   <si>
     <t xml:space="preserve">13.1928110122681</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3952407836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8978223800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9815902709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9327278137207</t>
+    <t xml:space="preserve">13.3952436447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8978252410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9815893173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9327268600464</t>
   </si>
   <si>
     <t xml:space="preserve">14.0234708786011</t>
@@ -641,121 +641,121 @@
     <t xml:space="preserve">14.0304517745972</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1351537704468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0723333358765</t>
+    <t xml:space="preserve">14.1351556777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0723342895508</t>
   </si>
   <si>
     <t xml:space="preserve">14.0025300979614</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2112531661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197393417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1461658477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0810766220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.994291305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6688413619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3559007644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6833076477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0015258789062</t>
+    <t xml:space="preserve">14.2112550735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197383880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1461668014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.081075668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9942893981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6688394546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.355899810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6833066940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0015230178833</t>
   </si>
   <si>
     <t xml:space="preserve">13.9870567321777</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2691125869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3486671447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3414363861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.276346206665</t>
+    <t xml:space="preserve">14.2691135406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.348669052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3414354324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2763442993164</t>
   </si>
   <si>
     <t xml:space="preserve">14.4282217025757</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5656337738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3322486877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8457288742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7589483261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3611726760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1876020431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9200115203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6307220458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636739730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3105487823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9272422790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0718879699707</t>
+    <t xml:space="preserve">14.5656328201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3322448730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8457307815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7589464187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3611755371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1876049041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9200096130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6307210922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636758804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3105506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9272432327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0718860626221</t>
   </si>
   <si>
     <t xml:space="preserve">15.5492115020752</t>
   </si>
   <si>
-    <t xml:space="preserve">15.455192565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2671556472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1731357574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8332242965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1369752883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1152791976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9850978851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.151439666748</t>
+    <t xml:space="preserve">15.4551963806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2671575546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1731386184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8332233428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1369781494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1152811050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9850988388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1514415740967</t>
   </si>
   <si>
     <t xml:space="preserve">15.0284929275513</t>
@@ -764,10 +764,10 @@
     <t xml:space="preserve">15.2093000411987</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6649284362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6938552856445</t>
+    <t xml:space="preserve">15.6649265289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6938562393188</t>
   </si>
   <si>
     <t xml:space="preserve">15.7661771774292</t>
@@ -779,112 +779,112 @@
     <t xml:space="preserve">16.0410022735596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9469814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6432294845581</t>
+    <t xml:space="preserve">15.946982383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6432313919067</t>
   </si>
   <si>
     <t xml:space="preserve">15.2816190719604</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2888536453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2599239349365</t>
+    <t xml:space="preserve">15.2888517379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2599248886108</t>
   </si>
   <si>
     <t xml:space="preserve">15.3250141143799</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2382278442383</t>
+    <t xml:space="preserve">15.2382259368896</t>
   </si>
   <si>
     <t xml:space="preserve">15.1586723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0574207305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1803703308105</t>
+    <t xml:space="preserve">15.0574226379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1803712844849</t>
   </si>
   <si>
     <t xml:space="preserve">15.2454586029053</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8983135223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8693819046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8259944915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9634027481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9706373214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6813459396362</t>
+    <t xml:space="preserve">14.8983144760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8693838119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8259906768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9634037017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9706363677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6813468933105</t>
   </si>
   <si>
     <t xml:space="preserve">14.7536706924438</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6958131790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8910799026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4933099746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8549222946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6524209976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6090288162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8476905822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1948328018188</t>
+    <t xml:space="preserve">14.6958112716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8910818099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.493311882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8549194335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6524200439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6090269088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8476886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1948347091675</t>
   </si>
   <si>
     <t xml:space="preserve">15.3394756317139</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4334936141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2651996612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9956493377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5742244720459</t>
+    <t xml:space="preserve">15.433497428894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2651977539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9956474304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5742225646973</t>
   </si>
   <si>
     <t xml:space="preserve">18.6879825592041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3986988067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4420871734619</t>
+    <t xml:space="preserve">18.3986968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4420890808105</t>
   </si>
   <si>
     <t xml:space="preserve">18.2178897857666</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0804786682129</t>
+    <t xml:space="preserve">18.0804805755615</t>
   </si>
   <si>
     <t xml:space="preserve">18.1889629364014</t>
@@ -896,49 +896,49 @@
     <t xml:space="preserve">18.0081558227539</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8562793731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9647617340088</t>
+    <t xml:space="preserve">17.8562812805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9647636413574</t>
   </si>
   <si>
     <t xml:space="preserve">17.6393127441406</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7622604370117</t>
+    <t xml:space="preserve">17.7622623443604</t>
   </si>
   <si>
     <t xml:space="preserve">17.6031532287598</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5886898040771</t>
+    <t xml:space="preserve">17.5886878967285</t>
   </si>
   <si>
     <t xml:space="preserve">17.5380630493164</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5019054412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3861885070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3210983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2849407196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0462779998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2632427215576</t>
+    <t xml:space="preserve">17.5019016265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3861904144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3210964202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2849388122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0462741851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.263240814209</t>
   </si>
   <si>
     <t xml:space="preserve">17.0969009399414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.328332901001</t>
+    <t xml:space="preserve">17.3283309936523</t>
   </si>
   <si>
     <t xml:space="preserve">17.3572597503662</t>
@@ -947,64 +947,64 @@
     <t xml:space="preserve">17.4006500244141</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3789596557617</t>
+    <t xml:space="preserve">17.3789558410645</t>
   </si>
   <si>
     <t xml:space="preserve">17.2921695709229</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3427963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1692237854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.590648651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6268081665039</t>
+    <t xml:space="preserve">17.342794418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1692218780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5906505584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6268062591553</t>
   </si>
   <si>
     <t xml:space="preserve">16.9233303070068</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3447513580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7083206176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1133232116699</t>
+    <t xml:space="preserve">16.3447532653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7083187103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1133213043213</t>
   </si>
   <si>
     <t xml:space="preserve">15.9180545806885</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6504621505737</t>
+    <t xml:space="preserve">15.6504602432251</t>
   </si>
   <si>
     <t xml:space="preserve">16.4749336242676</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3013610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5761833190918</t>
+    <t xml:space="preserve">16.3013591766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5761814117432</t>
   </si>
   <si>
     <t xml:space="preserve">16.5110931396484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5617160797119</t>
+    <t xml:space="preserve">16.5617179870605</t>
   </si>
   <si>
     <t xml:space="preserve">16.0699291229248</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5255565643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.409839630127</t>
+    <t xml:space="preserve">16.5255546569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4098453521729</t>
   </si>
   <si>
     <t xml:space="preserve">16.2073402404785</t>
@@ -1013,34 +1013,34 @@
     <t xml:space="preserve">15.8746604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2434997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4460048675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2001113891602</t>
+    <t xml:space="preserve">16.243501663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4460010528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2001075744629</t>
   </si>
   <si>
     <t xml:space="preserve">15.8312644958496</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8601970672607</t>
+    <t xml:space="preserve">15.8601980209351</t>
   </si>
   <si>
     <t xml:space="preserve">15.8529634475708</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6287670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4696550369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.462423324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215305328369</t>
+    <t xml:space="preserve">15.6287689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4696588516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4624252319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215362548828</t>
   </si>
   <si>
     <t xml:space="preserve">15.9976081848145</t>
@@ -1052,10 +1052,10 @@
     <t xml:space="preserve">16.163948059082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2724323272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7786865234375</t>
+    <t xml:space="preserve">16.2724304199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7786846160889</t>
   </si>
   <si>
     <t xml:space="preserve">16.6340408325195</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">16.4532375335693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7425212860107</t>
+    <t xml:space="preserve">16.7425231933594</t>
   </si>
   <si>
     <t xml:space="preserve">16.5978813171387</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">16.7063617706299</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8510055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0318069458008</t>
+    <t xml:space="preserve">16.8510074615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0318088531494</t>
   </si>
   <si>
     <t xml:space="preserve">17.2126140594482</t>
@@ -1088,97 +1088,97 @@
     <t xml:space="preserve">16.9594898223877</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3809146881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9831428527832</t>
+    <t xml:space="preserve">16.3809127807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9831438064575</t>
   </si>
   <si>
     <t xml:space="preserve">15.9108200073242</t>
   </si>
   <si>
-    <t xml:space="preserve">15.730019569397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3684091567993</t>
+    <t xml:space="preserve">15.7300157546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.368408203125</t>
   </si>
   <si>
     <t xml:space="preserve">15.4045658111572</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4768915176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8023405075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.670202255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1402950286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1041316986084</t>
+    <t xml:space="preserve">15.4768877029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8023386001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6702003479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1402912139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1041355133057</t>
   </si>
   <si>
     <t xml:space="preserve">16.8148441314697</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0679702758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8871669769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8273525238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6827087402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3934173583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.248779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7550315856934</t>
+    <t xml:space="preserve">17.0679721832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8871688842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8273506164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6827068328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3934192657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2487754821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7550296783447</t>
   </si>
   <si>
     <t xml:space="preserve">17.8996753692627</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5867328643799</t>
+    <t xml:space="preserve">18.5867347717285</t>
   </si>
   <si>
     <t xml:space="preserve">18.6590538024902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0206604003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5428009033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2444362640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9157562255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4378871917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6546859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4682083129883</t>
+    <t xml:space="preserve">19.0206642150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.542797088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2444343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9157543182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4378910064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6546840667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4682102203369</t>
   </si>
   <si>
     <t xml:space="preserve">19.6173896789551</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0952529907227</t>
+    <t xml:space="preserve">19.0952548980713</t>
   </si>
   <si>
     <t xml:space="preserve">18.8714828491211</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">18.9460716247559</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7968921661377</t>
+    <t xml:space="preserve">18.7968902587891</t>
   </si>
   <si>
     <t xml:space="preserve">17.9018020629883</t>
@@ -1196,49 +1196,49 @@
     <t xml:space="preserve">17.3050765991211</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7899188995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8341884613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1698474884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3936195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5055027008057</t>
+    <t xml:space="preserve">17.7899150848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8341865539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1698455810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3936176300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5055046081543</t>
   </si>
   <si>
     <t xml:space="preserve">19.8038673400879</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8784580230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6919822692871</t>
+    <t xml:space="preserve">19.8784561157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6919803619385</t>
   </si>
   <si>
     <t xml:space="preserve">19.3190269470215</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4239368438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1325492858887</t>
+    <t xml:space="preserve">18.4239387512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1325531005859</t>
   </si>
   <si>
     <t xml:space="preserve">19.3563232421875</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0206642150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7292785644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7223014831543</t>
+    <t xml:space="preserve">19.0206661224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7292766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7223033905029</t>
   </si>
   <si>
     <t xml:space="preserve">18.9087791442871</t>
@@ -1247,10 +1247,10 @@
     <t xml:space="preserve">18.6477108001709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5731163024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5358238220215</t>
+    <t xml:space="preserve">18.5731182098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5358219146729</t>
   </si>
   <si>
     <t xml:space="preserve">17.9763927459717</t>
@@ -1259,19 +1259,19 @@
     <t xml:space="preserve">18.1255722045898</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4612312316895</t>
+    <t xml:space="preserve">18.4612331390381</t>
   </si>
   <si>
     <t xml:space="preserve">18.7595958709717</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6104125976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3493480682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6850090026855</t>
+    <t xml:space="preserve">18.6104145050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.34934425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6850051879883</t>
   </si>
   <si>
     <t xml:space="preserve">18.3120517730713</t>
@@ -1286,37 +1286,37 @@
     <t xml:space="preserve">19.0579586029053</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1628704071045</t>
+    <t xml:space="preserve">18.1628684997559</t>
   </si>
   <si>
     <t xml:space="preserve">18.0136871337891</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3866405487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.155891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1862125396729</t>
+    <t xml:space="preserve">18.3866386413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1558952331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1862106323242</t>
   </si>
   <si>
     <t xml:space="preserve">15.589485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1419382095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9554624557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0370292663574</t>
+    <t xml:space="preserve">15.1419410705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9554634094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0370311737061</t>
   </si>
   <si>
     <t xml:space="preserve">16.5218696594238</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6640748977661</t>
+    <t xml:space="preserve">15.6640768051147</t>
   </si>
   <si>
     <t xml:space="preserve">15.1046447753906</t>
@@ -1325,100 +1325,100 @@
     <t xml:space="preserve">14.9927587509155</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0300512313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.768985748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.366192817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5153770446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6198043823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8883323669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2538280487061</t>
+    <t xml:space="preserve">15.0300540924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7689876556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3661947250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5153760910034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6198062896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8883304595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2538270950317</t>
   </si>
   <si>
     <t xml:space="preserve">16.2608032226562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9251461029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7759628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7013711929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5521879196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6267795562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5148935317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2911233901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2165327072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.179235458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8505544662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8132591247559</t>
+    <t xml:space="preserve">15.925142288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7759618759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7013721466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.552191734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.626781463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5148954391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2911214828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.21653175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1792364120483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8505535125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8132572174072</t>
   </si>
   <si>
     <t xml:space="preserve">16.0743255615234</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8878469467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4030075073242</t>
+    <t xml:space="preserve">15.8878488540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4030084609985</t>
   </si>
   <si>
     <t xml:space="preserve">14.9032497406006</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7093133926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4403057098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1116199493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9624404907227</t>
+    <t xml:space="preserve">14.7093152999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4403047561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1116218566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.962438583374</t>
   </si>
   <si>
     <t xml:space="preserve">16.5591678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3726902008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4845752716064</t>
+    <t xml:space="preserve">16.372688293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4845771789551</t>
   </si>
   <si>
     <t xml:space="preserve">16.7829399108887</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8948230743408</t>
+    <t xml:space="preserve">16.8948249816895</t>
   </si>
   <si>
     <t xml:space="preserve">15.7386665344238</t>
@@ -1427,34 +1427,34 @@
     <t xml:space="preserve">15.3657131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8435764312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8584957122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0673513412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8734130859375</t>
+    <t xml:space="preserve">14.8435754776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.858494758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0673503875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8734121322632</t>
   </si>
   <si>
     <t xml:space="preserve">14.9181680679321</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4099826812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2235088348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2980995178223</t>
+    <t xml:space="preserve">16.409984588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2235069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2980976104736</t>
   </si>
   <si>
     <t xml:space="preserve">16.6710529327393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7083511352539</t>
+    <t xml:space="preserve">16.7083473205566</t>
   </si>
   <si>
     <t xml:space="preserve">16.7456436157227</t>
@@ -1469,34 +1469,34 @@
     <t xml:space="preserve">16.8575305938721</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0067100524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3796634674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2304840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.528844833374</t>
+    <t xml:space="preserve">17.0067119598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3796672821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2304821014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5288467407227</t>
   </si>
   <si>
     <t xml:space="preserve">18.343240737915</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7227516174316</t>
+    <t xml:space="preserve">17.722749710083</t>
   </si>
   <si>
     <t xml:space="preserve">16.6756725311279</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7532329559326</t>
+    <t xml:space="preserve">16.7532348632812</t>
   </si>
   <si>
     <t xml:space="preserve">16.3654289245605</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0939636230469</t>
+    <t xml:space="preserve">16.0939674377441</t>
   </si>
   <si>
     <t xml:space="preserve">15.6673784255981</t>
@@ -1505,10 +1505,10 @@
     <t xml:space="preserve">15.6285963058472</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0468873977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2640590667725</t>
+    <t xml:space="preserve">15.0468854904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2640581130981</t>
   </si>
   <si>
     <t xml:space="preserve">15.7061567306519</t>
@@ -1520,49 +1520,49 @@
     <t xml:space="preserve">15.5122547149658</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7449359893799</t>
+    <t xml:space="preserve">15.7449378967285</t>
   </si>
   <si>
     <t xml:space="preserve">15.2950830459595</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0158634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1864967346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4191799163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4967441558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5510330200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3261079788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2795724868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8612813949585</t>
+    <t xml:space="preserve">15.0158615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1864976882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4191789627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4967412948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5510349273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3261089324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2795715332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8612794876099</t>
   </si>
   <si>
     <t xml:space="preserve">16.0164031982422</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9388399124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9000616073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7837200164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8225021362305</t>
+    <t xml:space="preserve">15.9388418197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9000597000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7837181091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8225002288818</t>
   </si>
   <si>
     <t xml:space="preserve">16.3266468048096</t>
@@ -1571,16 +1571,16 @@
     <t xml:space="preserve">16.7920150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0247020721436</t>
+    <t xml:space="preserve">17.0247001647949</t>
   </si>
   <si>
     <t xml:space="preserve">16.9083557128906</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4817714691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5593299865723</t>
+    <t xml:space="preserve">16.4817695617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5593318939209</t>
   </si>
   <si>
     <t xml:space="preserve">16.0551853179932</t>
@@ -1589,82 +1589,82 @@
     <t xml:space="preserve">16.4042091369629</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1327438354492</t>
+    <t xml:space="preserve">16.1327457427979</t>
   </si>
   <si>
     <t xml:space="preserve">16.2878684997559</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1715259552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9776239395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3881559371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346942901611</t>
+    <t xml:space="preserve">16.1715278625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9776229858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3881568908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346933364868</t>
   </si>
   <si>
     <t xml:space="preserve">16.2103061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4429931640625</t>
+    <t xml:space="preserve">16.4429874420166</t>
   </si>
   <si>
     <t xml:space="preserve">16.5981121063232</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5205516815186</t>
+    <t xml:space="preserve">16.5205497741699</t>
   </si>
   <si>
     <t xml:space="preserve">16.6368923187256</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2490863800049</t>
+    <t xml:space="preserve">16.2490882873535</t>
   </si>
   <si>
     <t xml:space="preserve">16.8307971954346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9859180450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5288467407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8390922546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.567626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9942169189453</t>
+    <t xml:space="preserve">16.9859161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5288486480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8390941619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5676288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9942188262939</t>
   </si>
   <si>
     <t xml:space="preserve">18.6147060394287</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2656803131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8473892211914</t>
+    <t xml:space="preserve">18.2656784057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8473873138428</t>
   </si>
   <si>
     <t xml:space="preserve">18.5371437072754</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0717754364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4595832824707</t>
+    <t xml:space="preserve">18.0717792510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4595813751221</t>
   </si>
   <si>
     <t xml:space="preserve">18.7698268890381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9249515533447</t>
+    <t xml:space="preserve">18.9249496459961</t>
   </si>
   <si>
     <t xml:space="preserve">19.1576347351074</t>
@@ -1673,13 +1673,13 @@
     <t xml:space="preserve">19.0025119781494</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0412921905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3044605255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1493358612061</t>
+    <t xml:space="preserve">19.0412940979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3044624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1493377685547</t>
   </si>
   <si>
     <t xml:space="preserve">18.0329971313477</t>
@@ -1694,19 +1694,19 @@
     <t xml:space="preserve">18.498363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1105575561523</t>
+    <t xml:space="preserve">18.1105556488037</t>
   </si>
   <si>
     <t xml:space="preserve">17.6839694976807</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8086071014404</t>
+    <t xml:space="preserve">18.8086090087891</t>
   </si>
   <si>
     <t xml:space="preserve">18.3820209503174</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1881198883057</t>
+    <t xml:space="preserve">18.188117980957</t>
   </si>
   <si>
     <t xml:space="preserve">17.916654586792</t>
@@ -1715,10 +1715,10 @@
     <t xml:space="preserve">17.9554347991943</t>
   </si>
   <si>
-    <t xml:space="preserve">17.606409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.645191192627</t>
+    <t xml:space="preserve">17.6064109802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6451892852783</t>
   </si>
   <si>
     <t xml:space="preserve">17.141040802002</t>
@@ -1727,52 +1727,52 @@
     <t xml:space="preserve">17.1022605895996</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2961616516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1244478225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7676677703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.557710647583</t>
+    <t xml:space="preserve">17.29616355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1244487762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7676687240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5577096939087</t>
   </si>
   <si>
     <t xml:space="preserve">13.9610290527344</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0302925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.185417175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1388788223267</t>
+    <t xml:space="preserve">13.030294418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1854152679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.138879776001</t>
   </si>
   <si>
     <t xml:space="preserve">13.5732221603394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2629795074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1699028015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9527339935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5649271011353</t>
+    <t xml:space="preserve">13.2629776000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.169903755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9527349472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5649261474609</t>
   </si>
   <si>
     <t xml:space="preserve">11.7582883834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5566301345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8585777282715</t>
+    <t xml:space="preserve">11.5566291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8585786819458</t>
   </si>
   <si>
     <t xml:space="preserve">10.7810163497925</t>
@@ -1784,31 +1784,31 @@
     <t xml:space="preserve">10.8197975158691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1300439834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7893133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2546806335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9056558609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6341905593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0219964981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0607776641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8280935287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4790678024292</t>
+    <t xml:space="preserve">11.1300430297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7893142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2546815872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9056549072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6341915130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0219974517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0607786178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8280944824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4790697097778</t>
   </si>
   <si>
     <t xml:space="preserve">11.7117528915405</t>
@@ -1820,10 +1820,10 @@
     <t xml:space="preserve">11.5954103469849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2851657867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4015073776245</t>
+    <t xml:space="preserve">11.2851638793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4015064239502</t>
   </si>
   <si>
     <t xml:space="preserve">11.7505331039429</t>
@@ -1835,22 +1835,22 @@
     <t xml:space="preserve">10.5095529556274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871124267578</t>
+    <t xml:space="preserve">10.5871133804321</t>
   </si>
   <si>
     <t xml:space="preserve">10.6646747589111</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2463855743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2158994674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3710222244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0773696899414</t>
+    <t xml:space="preserve">11.2463836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2159004211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3710231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.07737159729</t>
   </si>
   <si>
     <t xml:space="preserve">14.1181745529175</t>
@@ -1859,19 +1859,19 @@
     <t xml:space="preserve">14.0365676879883</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8733510971069</t>
+    <t xml:space="preserve">13.8733501434326</t>
   </si>
   <si>
     <t xml:space="preserve">13.8325471878052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1997814178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6078233718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2813892364502</t>
+    <t xml:space="preserve">14.199782371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6078224182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2813901901245</t>
   </si>
   <si>
     <t xml:space="preserve">13.4245080947876</t>
@@ -1886,13 +1886,13 @@
     <t xml:space="preserve">13.7509393692017</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9549598693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5262145996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7710380554199</t>
+    <t xml:space="preserve">13.9549589157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5262136459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7710390090942</t>
   </si>
   <si>
     <t xml:space="preserve">14.6894302368164</t>
@@ -1904,49 +1904,46 @@
     <t xml:space="preserve">14.4038019180298</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5877227783203</t>
+    <t xml:space="preserve">13.5877237319946</t>
   </si>
   <si>
     <t xml:space="preserve">13.4653120040894</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6285276412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9141550064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2405862808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9957628250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1589784622192</t>
+    <t xml:space="preserve">13.628529548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9141540527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2405881881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9957618713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1589794158936</t>
   </si>
   <si>
     <t xml:space="preserve">13.7917423248291</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3837032318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2204885482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0773706436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3428983688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7101345062256</t>
+    <t xml:space="preserve">13.3837041854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2204875946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3429002761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7101354598999</t>
   </si>
   <si>
     <t xml:space="preserve">13.0572710037231</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2612915039062</t>
+    <t xml:space="preserve">13.2612905502319</t>
   </si>
   <si>
     <t xml:space="preserve">13.0980739593506</t>
@@ -1958,40 +1955,40 @@
     <t xml:space="preserve">12.8532514572144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7308406829834</t>
+    <t xml:space="preserve">12.7308397293091</t>
   </si>
   <si>
     <t xml:space="preserve">12.6900367736816</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9756641387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7716436386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8526458740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2606868743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4239025115967</t>
+    <t xml:space="preserve">12.9756622314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7716426849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8526468276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.260687828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4239015579224</t>
   </si>
   <si>
     <t xml:space="preserve">16.0767669677734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9135494232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5055103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6687259674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5871200561523</t>
+    <t xml:space="preserve">15.9135503768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5055093765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6687278747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.587119102478</t>
   </si>
   <si>
     <t xml:space="preserve">15.3014898300171</t>
@@ -2000,52 +1997,52 @@
     <t xml:space="preserve">15.3830986022949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3422937393188</t>
+    <t xml:space="preserve">15.3422918319702</t>
   </si>
   <si>
     <t xml:space="preserve">15.7503318786621</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2198820114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1790790557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4647073745728</t>
+    <t xml:space="preserve">15.2198839187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1790800094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4647064208984</t>
   </si>
   <si>
     <t xml:space="preserve">16.3215885162354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1583728790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8112354278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7089252471924</t>
+    <t xml:space="preserve">16.158374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8112373352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7089233398438</t>
   </si>
   <si>
     <t xml:space="preserve">17.1376705169678</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3824939727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8928451538086</t>
+    <t xml:space="preserve">17.3824920654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8928470611572</t>
   </si>
   <si>
     <t xml:space="preserve">16.1991767883301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.484806060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6480197906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5664119720459</t>
+    <t xml:space="preserve">16.4848079681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.648021697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5664138793945</t>
   </si>
   <si>
     <t xml:space="preserve">16.2399806976318</t>
@@ -2057,16 +2054,16 @@
     <t xml:space="preserve">16.7296276092529</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2192783355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4641017913818</t>
+    <t xml:space="preserve">17.2192764282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4640998840332</t>
   </si>
   <si>
     <t xml:space="preserve">17.5457077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9537487030029</t>
+    <t xml:space="preserve">17.9537467956543</t>
   </si>
   <si>
     <t xml:space="preserve">18.0353565216064</t>
@@ -2075,16 +2072,16 @@
     <t xml:space="preserve">16.9744529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8721408843994</t>
+    <t xml:space="preserve">17.8721389770508</t>
   </si>
   <si>
     <t xml:space="preserve">18.11696434021</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1985702514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3617877960205</t>
+    <t xml:space="preserve">18.1985721588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3617897033691</t>
   </si>
   <si>
     <t xml:space="preserve">19.1778678894043</t>
@@ -2093,25 +2090,28 @@
     <t xml:space="preserve">18.8514366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6882171630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0962600708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6066093444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9330444335938</t>
+    <t xml:space="preserve">18.6882209777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0962619781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6066112518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9330463409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7698287963867</t>
   </si>
   <si>
     <t xml:space="preserve">19.2594776153564</t>
   </si>
   <si>
-    <t xml:space="preserve">19.34108543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4226913452148</t>
+    <t xml:space="preserve">19.3410835266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4226894378662</t>
   </si>
   <si>
     <t xml:space="preserve">19.0146522521973</t>
@@ -2123,10 +2123,10 @@
     <t xml:space="preserve">19.8276062011719</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4886741638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6581401824951</t>
+    <t xml:space="preserve">19.4886722564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6581420898438</t>
   </si>
   <si>
     <t xml:space="preserve">19.5734062194824</t>
@@ -2135,13 +2135,13 @@
     <t xml:space="preserve">19.403938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9970722198486</t>
+    <t xml:space="preserve">19.9970741271973</t>
   </si>
   <si>
     <t xml:space="preserve">20.3360061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">20.166540145874</t>
+    <t xml:space="preserve">20.1665382385254</t>
   </si>
   <si>
     <t xml:space="preserve">19.319206237793</t>
@@ -2153,16 +2153,16 @@
     <t xml:space="preserve">18.6413383483887</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7428703308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.08180809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4207401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5054740905762</t>
+    <t xml:space="preserve">19.7428741455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0818061828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4207382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5054721832275</t>
   </si>
   <si>
     <t xml:space="preserve">20.6749401092529</t>
@@ -2174,76 +2174,76 @@
     <t xml:space="preserve">21.1833400726318</t>
   </si>
   <si>
-    <t xml:space="preserve">20.759672164917</t>
+    <t xml:space="preserve">20.7596740722656</t>
   </si>
   <si>
     <t xml:space="preserve">21.4375381469727</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7085380554199</t>
+    <t xml:space="preserve">22.7085399627686</t>
   </si>
   <si>
     <t xml:space="preserve">22.0306739807129</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4543399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2001419067383</t>
+    <t xml:space="preserve">22.4543380737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2001399993896</t>
   </si>
   <si>
     <t xml:space="preserve">22.6238079071045</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7932739257812</t>
+    <t xml:space="preserve">22.7932720184326</t>
   </si>
   <si>
     <t xml:space="preserve">23.0474739074707</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6406059265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.555871963501</t>
+    <t xml:space="preserve">23.6406078338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5558738708496</t>
   </si>
   <si>
     <t xml:space="preserve">23.3016738891602</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4711418151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3864078521729</t>
+    <t xml:space="preserve">23.4711399078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3864059448242</t>
   </si>
   <si>
     <t xml:space="preserve">23.725341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1322078704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2169399261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9459419250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8780078887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1490077972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.165807723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9116096496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2337398529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2505416870117</t>
+    <t xml:space="preserve">23.1322059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2169418334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9459400177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8780059814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1490097045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1658096313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9116058349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2337417602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2505397796631</t>
   </si>
   <si>
     <t xml:space="preserve">23.8100757598877</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">24.5726737976074</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4032077789307</t>
+    <t xml:space="preserve">24.4032039642334</t>
   </si>
   <si>
     <t xml:space="preserve">24.4879398345947</t>
@@ -2276,16 +2276,16 @@
     <t xml:space="preserve">26.2673416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4368095397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.521541595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8772773742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5719451904297</t>
+    <t xml:space="preserve">26.4368076324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5215396881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8772754669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5719470977783</t>
   </si>
   <si>
     <t xml:space="preserve">29.317741394043</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">28.9788093566895</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1482772827148</t>
+    <t xml:space="preserve">29.1482753753662</t>
   </si>
   <si>
     <t xml:space="preserve">29.2330093383789</t>
@@ -2312,13 +2312,13 @@
     <t xml:space="preserve">27.4536094665527</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3856754302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7078113555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1314754486084</t>
+    <t xml:space="preserve">28.3856773376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7078094482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.131477355957</t>
   </si>
   <si>
     <t xml:space="preserve">27.2841415405273</t>
@@ -2333,22 +2333,22 @@
     <t xml:space="preserve">25.8436756134033</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3520736694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6062755584717</t>
+    <t xml:space="preserve">26.3520755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.606273651123</t>
   </si>
   <si>
     <t xml:space="preserve">24.8268737792969</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1826076507568</t>
+    <t xml:space="preserve">26.1826095581055</t>
   </si>
   <si>
     <t xml:space="preserve">26.0978755950928</t>
   </si>
   <si>
-    <t xml:space="preserve">25.928409576416</t>
+    <t xml:space="preserve">25.9284076690674</t>
   </si>
   <si>
     <t xml:space="preserve">26.6910076141357</t>
@@ -2360,10 +2360,10 @@
     <t xml:space="preserve">24.0642738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9627418518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3184757232666</t>
+    <t xml:space="preserve">22.962739944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.318473815918</t>
   </si>
   <si>
     <t xml:space="preserve">23.8948078155518</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">23.5261859893799</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7301864624023</t>
+    <t xml:space="preserve">22.730188369751</t>
   </si>
   <si>
     <t xml:space="preserve">23.2608528137207</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">23.9684085845947</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7030735015869</t>
+    <t xml:space="preserve">23.7030754089355</t>
   </si>
   <si>
     <t xml:space="preserve">24.0568523406982</t>
@@ -2405,10 +2405,10 @@
     <t xml:space="preserve">25.295072555542</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2066268920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5875148773193</t>
+    <t xml:space="preserve">25.2066287994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.587516784668</t>
   </si>
   <si>
     <t xml:space="preserve">24.3221855163574</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">23.3492965698242</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2879676818848</t>
+    <t xml:space="preserve">22.2879657745361</t>
   </si>
   <si>
     <t xml:space="preserve">22.4648532867432</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">21.8457450866699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7573013305664</t>
+    <t xml:space="preserve">21.7572994232178</t>
   </si>
   <si>
     <t xml:space="preserve">21.4035224914551</t>
@@ -2447,13 +2447,13 @@
     <t xml:space="preserve">21.1381893157959</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1110763549805</t>
+    <t xml:space="preserve">22.1110782623291</t>
   </si>
   <si>
     <t xml:space="preserve">23.7915191650391</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1181812286377</t>
+    <t xml:space="preserve">25.1181831359863</t>
   </si>
   <si>
     <t xml:space="preserve">24.6759624481201</t>
@@ -2462,25 +2462,25 @@
     <t xml:space="preserve">22.9955196380615</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9070777893066</t>
+    <t xml:space="preserve">22.907075881958</t>
   </si>
   <si>
     <t xml:space="preserve">24.1452960968018</t>
   </si>
   <si>
-    <t xml:space="preserve">23.437744140625</t>
+    <t xml:space="preserve">23.4377422332764</t>
   </si>
   <si>
     <t xml:space="preserve">23.614631652832</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6417427062988</t>
+    <t xml:space="preserve">22.6417446136475</t>
   </si>
   <si>
     <t xml:space="preserve">23.0839653015137</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1724090576172</t>
+    <t xml:space="preserve">23.1724109649658</t>
   </si>
   <si>
     <t xml:space="preserve">22.3764095306396</t>
@@ -2489,13 +2489,13 @@
     <t xml:space="preserve">22.1995220184326</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0226306915283</t>
+    <t xml:space="preserve">22.022632598877</t>
   </si>
   <si>
     <t xml:space="preserve">21.0497455596924</t>
   </si>
   <si>
-    <t xml:space="preserve">21.49196434021</t>
+    <t xml:space="preserve">21.4919662475586</t>
   </si>
   <si>
     <t xml:space="preserve">20.6959686279297</t>
@@ -2504,10 +2504,10 @@
     <t xml:space="preserve">21.3150787353516</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7644062042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7372932434082</t>
+    <t xml:space="preserve">24.7644081115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7372951507568</t>
   </si>
   <si>
     <t xml:space="preserve">25.0297393798828</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">25.5604057312012</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4719619750977</t>
+    <t xml:space="preserve">25.471960067749</t>
   </si>
   <si>
     <t xml:space="preserve">25.6488494873047</t>
@@ -2537,25 +2537,25 @@
     <t xml:space="preserve">27.1524028778076</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5061798095703</t>
+    <t xml:space="preserve">27.5061817169189</t>
   </si>
   <si>
     <t xml:space="preserve">27.5946254730225</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3292903900146</t>
+    <t xml:space="preserve">27.3292922973633</t>
   </si>
   <si>
     <t xml:space="preserve">26.7101821899414</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7986240386963</t>
+    <t xml:space="preserve">26.7986259460449</t>
   </si>
   <si>
     <t xml:space="preserve">26.8870697021484</t>
   </si>
   <si>
-    <t xml:space="preserve">26.975513458252</t>
+    <t xml:space="preserve">26.9755153656006</t>
   </si>
   <si>
     <t xml:space="preserve">27.4177360534668</t>
@@ -2567,37 +2567,37 @@
     <t xml:space="preserve">26.0910720825195</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4448471069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3564033508301</t>
+    <t xml:space="preserve">26.4448490142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3564052581787</t>
   </si>
   <si>
     <t xml:space="preserve">25.8257389068604</t>
   </si>
   <si>
-    <t xml:space="preserve">26.002628326416</t>
+    <t xml:space="preserve">26.0026264190674</t>
   </si>
   <si>
     <t xml:space="preserve">26.179515838623</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6217384338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2679595947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.859956741333</t>
+    <t xml:space="preserve">26.6217365264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2679615020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8599586486816</t>
   </si>
   <si>
     <t xml:space="preserve">28.7855377197266</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1557674407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3227481842041</t>
+    <t xml:space="preserve">29.1557693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3227462768555</t>
   </si>
   <si>
     <t xml:space="preserve">27.7673988342285</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">30.3590221405029</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8036766052246</t>
+    <t xml:space="preserve">29.803674697876</t>
   </si>
   <si>
     <t xml:space="preserve">29.3408851623535</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">28.8780956268311</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1739063262939</t>
+    <t xml:space="preserve">30.1739044189453</t>
   </si>
   <si>
     <t xml:space="preserve">29.06321144104</t>
@@ -2654,25 +2654,25 @@
     <t xml:space="preserve">27.2120513916016</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3971691131592</t>
+    <t xml:space="preserve">27.3971672058105</t>
   </si>
   <si>
     <t xml:space="preserve">27.489725112915</t>
   </si>
   <si>
-    <t xml:space="preserve">27.674840927124</t>
+    <t xml:space="preserve">27.6748390197754</t>
   </si>
   <si>
     <t xml:space="preserve">28.6004199981689</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6929798126221</t>
+    <t xml:space="preserve">28.6929779052734</t>
   </si>
   <si>
     <t xml:space="preserve">29.7111167907715</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5441379547119</t>
+    <t xml:space="preserve">30.5441398620605</t>
   </si>
   <si>
     <t xml:space="preserve">29.9887924194336</t>
@@ -2681,31 +2681,31 @@
     <t xml:space="preserve">30.2664661407471</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4515838623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0994873046875</t>
+    <t xml:space="preserve">30.4515819549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0994834899902</t>
   </si>
   <si>
     <t xml:space="preserve">30.6366958618164</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9143714904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7292556762695</t>
+    <t xml:space="preserve">30.9143733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7292537689209</t>
   </si>
   <si>
     <t xml:space="preserve">30.821813583374</t>
   </si>
   <si>
-    <t xml:space="preserve">31.192045211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0069274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5622749328613</t>
+    <t xml:space="preserve">31.1920471191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.006929397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.56227684021</t>
   </si>
   <si>
     <t xml:space="preserve">32.6729736328125</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">32.1176223754883</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9325084686279</t>
+    <t xml:space="preserve">31.9325103759766</t>
   </si>
   <si>
     <t xml:space="preserve">30.0813503265381</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">33.0432052612305</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3208808898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5059928894043</t>
+    <t xml:space="preserve">33.3208770751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5059967041016</t>
   </si>
   <si>
     <t xml:space="preserve">33.6911125183105</t>
@@ -2771,25 +2771,25 @@
     <t xml:space="preserve">34.1539001464844</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7092514038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9687881469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8762245178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4134368896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2464561462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8943634033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5241317749023</t>
+    <t xml:space="preserve">34.7092475891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9687843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8762283325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4134330749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2464599609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8943672180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5241355895996</t>
   </si>
   <si>
     <t xml:space="preserve">34.4315757751465</t>
@@ -2804,28 +2804,28 @@
     <t xml:space="preserve">34.3390159606934</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1720390319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5422706604004</t>
+    <t xml:space="preserve">35.1720352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5422744750977</t>
   </si>
   <si>
     <t xml:space="preserve">35.0794830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9869194030762</t>
+    <t xml:space="preserve">34.9869232177734</t>
   </si>
   <si>
     <t xml:space="preserve">35.3571548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8199462890625</t>
+    <t xml:space="preserve">35.8199424743652</t>
   </si>
   <si>
     <t xml:space="preserve">35.7273864746094</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9306411743164</t>
+    <t xml:space="preserve">36.9306449890137</t>
   </si>
   <si>
     <t xml:space="preserve">37.7636604309082</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">38.8743591308594</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5966835021973</t>
+    <t xml:space="preserve">38.5966873168945</t>
   </si>
   <si>
     <t xml:space="preserve">38.6892433166504</t>
@@ -2867,13 +2867,13 @@
     <t xml:space="preserve">39.0594749450684</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2445907592773</t>
+    <t xml:space="preserve">39.2445945739746</t>
   </si>
   <si>
     <t xml:space="preserve">38.0413360595703</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8380851745605</t>
+    <t xml:space="preserve">36.8380813598633</t>
   </si>
   <si>
     <t xml:space="preserve">37.8562202453613</t>
@@ -2900,7 +2900,7 @@
     <t xml:space="preserve">41.3734245300293</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0957489013672</t>
+    <t xml:space="preserve">41.0957527160645</t>
   </si>
   <si>
     <t xml:space="preserve">41.0031929016113</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">40.9106369018555</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8180770874023</t>
+    <t xml:space="preserve">40.8180732727051</t>
   </si>
   <si>
     <t xml:space="preserve">40.2164497375488</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">40.5866813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6792411804199</t>
+    <t xml:space="preserve">40.6792373657227</t>
   </si>
   <si>
     <t xml:space="preserve">39.7999382019043</t>
@@ -2939,10 +2939,10 @@
     <t xml:space="preserve">40.6329612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0776138305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5222663879395</t>
+    <t xml:space="preserve">40.0776100158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5222625732422</t>
   </si>
   <si>
     <t xml:space="preserve">40.4478454589844</t>
@@ -3657,6 +3657,9 @@
   </si>
   <si>
     <t xml:space="preserve">68.5999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0999984741211</t>
   </si>
 </sst>
 </file>
@@ -34381,7 +34384,7 @@
         <v>17.25</v>
       </c>
       <c r="G1169" t="s">
-        <v>640</v>
+        <v>612</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34615,7 +34618,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1178" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -34823,7 +34826,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1186" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34927,7 +34930,7 @@
         <v>17.25</v>
       </c>
       <c r="G1190" t="s">
-        <v>640</v>
+        <v>612</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -35109,7 +35112,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1197" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35135,7 +35138,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -35187,7 +35190,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1200" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -35291,7 +35294,7 @@
         <v>16</v>
       </c>
       <c r="G1204" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -35369,7 +35372,7 @@
         <v>16</v>
       </c>
       <c r="G1207" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -35395,7 +35398,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1208" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -35421,7 +35424,7 @@
         <v>16.25</v>
       </c>
       <c r="G1209" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -35499,7 +35502,7 @@
         <v>17.25</v>
       </c>
       <c r="G1212" t="s">
-        <v>640</v>
+        <v>612</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -35577,7 +35580,7 @@
         <v>17.25</v>
       </c>
       <c r="G1215" t="s">
-        <v>640</v>
+        <v>612</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35785,7 +35788,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1223" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35811,7 +35814,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1224" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35837,7 +35840,7 @@
         <v>16</v>
       </c>
       <c r="G1225" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35863,7 +35866,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1226" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35889,7 +35892,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35915,7 +35918,7 @@
         <v>15.75</v>
       </c>
       <c r="G1228" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35941,7 +35944,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1229" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35967,7 +35970,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1230" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35993,7 +35996,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1231" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -36019,7 +36022,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -36071,7 +36074,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1234" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -36097,7 +36100,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1235" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -36175,7 +36178,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1238" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -36201,7 +36204,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1239" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -36227,7 +36230,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -36253,7 +36256,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1241" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -36279,7 +36282,7 @@
         <v>19.5</v>
       </c>
       <c r="G1242" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -36305,7 +36308,7 @@
         <v>19</v>
       </c>
       <c r="G1243" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -36331,7 +36334,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1244" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -36357,7 +36360,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1245" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -36383,7 +36386,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1246" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -36409,7 +36412,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1247" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -36435,7 +36438,7 @@
         <v>18.75</v>
       </c>
       <c r="G1248" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -36461,7 +36464,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1249" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -36487,7 +36490,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1250" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -36513,7 +36516,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1251" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -36539,7 +36542,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -36565,7 +36568,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1253" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -36591,7 +36594,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -36617,7 +36620,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1255" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -36643,7 +36646,7 @@
         <v>19</v>
       </c>
       <c r="G1256" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36669,7 +36672,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36695,7 +36698,7 @@
         <v>19</v>
       </c>
       <c r="G1258" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36721,7 +36724,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1259" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36747,7 +36750,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1260" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36773,7 +36776,7 @@
         <v>19</v>
       </c>
       <c r="G1261" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36799,7 +36802,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1262" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36825,7 +36828,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36851,7 +36854,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1264" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36877,7 +36880,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1265" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36903,7 +36906,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1266" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36929,7 +36932,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1267" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36955,7 +36958,7 @@
         <v>18.75</v>
       </c>
       <c r="G1268" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36981,7 +36984,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1269" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -37007,7 +37010,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1270" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -37033,7 +37036,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1271" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -37059,7 +37062,7 @@
         <v>19</v>
       </c>
       <c r="G1272" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -37085,7 +37088,7 @@
         <v>20</v>
       </c>
       <c r="G1273" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -37111,7 +37114,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1274" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -37137,7 +37140,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1275" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -37163,7 +37166,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1276" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -37189,7 +37192,7 @@
         <v>21</v>
       </c>
       <c r="G1277" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -37215,7 +37218,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1278" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -37241,7 +37244,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1279" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -37267,7 +37270,7 @@
         <v>20</v>
       </c>
       <c r="G1280" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -37293,7 +37296,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1281" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -37319,7 +37322,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1282" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -37345,7 +37348,7 @@
         <v>20</v>
       </c>
       <c r="G1283" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -37371,7 +37374,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1284" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -37397,7 +37400,7 @@
         <v>20</v>
       </c>
       <c r="G1285" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -37423,7 +37426,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1286" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -37449,7 +37452,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1287" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -37475,7 +37478,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -37501,7 +37504,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1289" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -37527,7 +37530,7 @@
         <v>20</v>
       </c>
       <c r="G1290" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -37553,7 +37556,7 @@
         <v>20</v>
       </c>
       <c r="G1291" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -37579,7 +37582,7 @@
         <v>20.5</v>
       </c>
       <c r="G1292" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -37605,7 +37608,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1293" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -37631,7 +37634,7 @@
         <v>21</v>
       </c>
       <c r="G1294" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -37657,7 +37660,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1295" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -37683,7 +37686,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1296" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -37709,7 +37712,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1297" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37735,7 +37738,7 @@
         <v>21.5</v>
       </c>
       <c r="G1298" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -37761,7 +37764,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1299" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37787,7 +37790,7 @@
         <v>22</v>
       </c>
       <c r="G1300" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -37813,7 +37816,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1301" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37839,7 +37842,7 @@
         <v>22</v>
       </c>
       <c r="G1302" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37865,7 +37868,7 @@
         <v>21.5</v>
       </c>
       <c r="G1303" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37891,7 +37894,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1304" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37917,7 +37920,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1305" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37943,7 +37946,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -37969,7 +37972,7 @@
         <v>21</v>
       </c>
       <c r="G1307" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -37995,7 +37998,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1308" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -38021,7 +38024,7 @@
         <v>21</v>
       </c>
       <c r="G1309" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -38047,7 +38050,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1310" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -38073,7 +38076,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -38099,7 +38102,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1312" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -38125,7 +38128,7 @@
         <v>21.5</v>
       </c>
       <c r="G1313" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -38151,7 +38154,7 @@
         <v>21.5</v>
       </c>
       <c r="G1314" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -38177,7 +38180,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1315" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -38203,7 +38206,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1316" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -38229,7 +38232,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1317" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -38255,7 +38258,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1318" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -38281,7 +38284,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1319" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -38307,7 +38310,7 @@
         <v>22.5</v>
       </c>
       <c r="G1320" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38333,7 +38336,7 @@
         <v>23.5</v>
       </c>
       <c r="G1321" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -38359,7 +38362,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1322" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -38385,7 +38388,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1323" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -38411,7 +38414,7 @@
         <v>23.5</v>
       </c>
       <c r="G1324" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -38437,7 +38440,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1325" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -38463,7 +38466,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1326" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -38489,7 +38492,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -38515,7 +38518,7 @@
         <v>23</v>
       </c>
       <c r="G1328" t="s">
-        <v>549</v>
+        <v>696</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -38541,7 +38544,7 @@
         <v>23.5</v>
       </c>
       <c r="G1329" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -38567,7 +38570,7 @@
         <v>23.5</v>
       </c>
       <c r="G1330" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38593,7 +38596,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1331" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -38619,7 +38622,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1332" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -38645,7 +38648,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1333" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -38671,7 +38674,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -38697,7 +38700,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1335" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -38723,7 +38726,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -38749,7 +38752,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1337" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -38775,7 +38778,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1338" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -38801,7 +38804,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1339" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -38827,7 +38830,7 @@
         <v>23.5</v>
       </c>
       <c r="G1340" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -38957,7 +38960,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1345" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -39061,7 +39064,7 @@
         <v>23.5</v>
       </c>
       <c r="G1349" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -39191,7 +39194,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -39217,7 +39220,7 @@
         <v>23</v>
       </c>
       <c r="G1355" t="s">
-        <v>549</v>
+        <v>696</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39243,7 +39246,7 @@
         <v>23</v>
       </c>
       <c r="G1356" t="s">
-        <v>549</v>
+        <v>696</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -39269,7 +39272,7 @@
         <v>23</v>
       </c>
       <c r="G1357" t="s">
-        <v>549</v>
+        <v>696</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39295,7 +39298,7 @@
         <v>23</v>
       </c>
       <c r="G1358" t="s">
-        <v>549</v>
+        <v>696</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39347,7 +39350,7 @@
         <v>23</v>
       </c>
       <c r="G1360" t="s">
-        <v>549</v>
+        <v>696</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -69905,7 +69908,7 @@
     </row>
     <row r="2536">
       <c r="A2536" s="1" t="n">
-        <v>46009.6912847222</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B2536" t="n">
         <v>11284</v>
@@ -69926,6 +69929,32 @@
         <v>1214</v>
       </c>
       <c r="H2536" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" s="1" t="n">
+        <v>46010.6912152778</v>
+      </c>
+      <c r="B2537" t="n">
+        <v>20055</v>
+      </c>
+      <c r="C2537" t="n">
+        <v>70.3000030517578</v>
+      </c>
+      <c r="D2537" t="n">
+        <v>68.4000015258789</v>
+      </c>
+      <c r="E2537" t="n">
+        <v>68.6999969482422</v>
+      </c>
+      <c r="F2537" t="n">
+        <v>69.0999984741211</v>
+      </c>
+      <c r="G2537" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H2537" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="1222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="1223">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23958683013916</t>
+    <t xml:space="preserve">9.23958778381348</t>
   </si>
   <si>
     <t xml:space="preserve">CMB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55656719207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31377410888672</t>
+    <t xml:space="preserve">9.55656623840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31377506256104</t>
   </si>
   <si>
     <t xml:space="preserve">9.40144920349121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40819358825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44191455841064</t>
+    <t xml:space="preserve">9.40819263458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44191551208496</t>
   </si>
   <si>
     <t xml:space="preserve">9.36098384857178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13842391967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32051753997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26656627655029</t>
+    <t xml:space="preserve">9.13842487335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32051849365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26656436920166</t>
   </si>
   <si>
     <t xml:space="preserve">9.34075164794922</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">9.2733097076416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19237899780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19912242889404</t>
+    <t xml:space="preserve">9.19237804412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19912338256836</t>
   </si>
   <si>
     <t xml:space="preserve">9.10470294952393</t>
@@ -92,25 +92,25 @@
     <t xml:space="preserve">8.77423667907715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84842300415039</t>
+    <t xml:space="preserve">8.84842395782471</t>
   </si>
   <si>
     <t xml:space="preserve">8.36283779144287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32911682128906</t>
+    <t xml:space="preserve">8.3291187286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.61911869049072</t>
   </si>
   <si>
-    <t xml:space="preserve">8.450514793396</t>
+    <t xml:space="preserve">8.45051383972168</t>
   </si>
   <si>
     <t xml:space="preserve">8.43028163909912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63260746002197</t>
+    <t xml:space="preserve">8.63260841369629</t>
   </si>
   <si>
     <t xml:space="preserve">8.80121421813965</t>
@@ -119,16 +119,16 @@
     <t xml:space="preserve">9.22609996795654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25981903076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07098293304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87539958953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96982002258301</t>
+    <t xml:space="preserve">9.25982093811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07098197937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87540054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96981906890869</t>
   </si>
   <si>
     <t xml:space="preserve">8.71353816986084</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">8.6663293838501</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89563179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81470108032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99679660797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01028442382812</t>
+    <t xml:space="preserve">8.89563274383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81470203399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99679470062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01028347015381</t>
   </si>
   <si>
     <t xml:space="preserve">8.90237617492676</t>
@@ -155,28 +155,28 @@
     <t xml:space="preserve">8.97656345367432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18563365936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17214488983154</t>
+    <t xml:space="preserve">9.18563461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17214584350586</t>
   </si>
   <si>
     <t xml:space="preserve">9.13168048858643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34749507904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25307655334473</t>
+    <t xml:space="preserve">9.34749603271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25307750701904</t>
   </si>
   <si>
     <t xml:space="preserve">9.15865707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08446979522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540050506592</t>
+    <t xml:space="preserve">9.08447170257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540241241455</t>
   </si>
   <si>
     <t xml:space="preserve">8.98330688476562</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">8.7877254486084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78098011016846</t>
+    <t xml:space="preserve">8.78098106384277</t>
   </si>
   <si>
     <t xml:space="preserve">9.1249361038208</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">9.03726100921631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21261119842529</t>
+    <t xml:space="preserve">9.21261024475098</t>
   </si>
   <si>
     <t xml:space="preserve">9.04400444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09795951843262</t>
+    <t xml:space="preserve">9.0979585647583</t>
   </si>
   <si>
     <t xml:space="preserve">9.20586681365967</t>
@@ -215,22 +215,22 @@
     <t xml:space="preserve">9.22100830078125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22798919677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19308853149414</t>
+    <t xml:space="preserve">9.22798824310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19308757781982</t>
   </si>
   <si>
     <t xml:space="preserve">9.35363483428955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4094762802124</t>
+    <t xml:space="preserve">9.40947532653809</t>
   </si>
   <si>
     <t xml:space="preserve">9.52116203308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49324131011963</t>
+    <t xml:space="preserve">9.49324226379395</t>
   </si>
   <si>
     <t xml:space="preserve">9.38853549957275</t>
@@ -239,19 +239,19 @@
     <t xml:space="preserve">9.94696140289307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76547336578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77245426177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66774845123291</t>
+    <t xml:space="preserve">9.76547431945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77245330810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66775035858154</t>
   </si>
   <si>
     <t xml:space="preserve">9.82829666137695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75151252746582</t>
+    <t xml:space="preserve">9.75151348114014</t>
   </si>
   <si>
     <t xml:space="preserve">9.57002353668213</t>
@@ -260,28 +260,28 @@
     <t xml:space="preserve">9.57700443267822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55606365203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47927951812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42343902587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39551734924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41645812988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34665298461914</t>
+    <t xml:space="preserve">9.55606460571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47928047180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42343711853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39551639556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41645622253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34665489196777</t>
   </si>
   <si>
     <t xml:space="preserve">9.58398532867432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62586688995361</t>
+    <t xml:space="preserve">9.6258659362793</t>
   </si>
   <si>
     <t xml:space="preserve">9.63284683227539</t>
@@ -293,19 +293,19 @@
     <t xml:space="preserve">9.48626041412354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59096622467041</t>
+    <t xml:space="preserve">9.59096527099609</t>
   </si>
   <si>
     <t xml:space="preserve">9.56304454803467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53512287139893</t>
+    <t xml:space="preserve">9.53512191772461</t>
   </si>
   <si>
     <t xml:space="preserve">9.12328433990479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30477142333984</t>
+    <t xml:space="preserve">9.30477237701416</t>
   </si>
   <si>
     <t xml:space="preserve">9.2838306427002</t>
@@ -314,16 +314,16 @@
     <t xml:space="preserve">9.20704746246338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27685070037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36061573028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29081153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29779243469238</t>
+    <t xml:space="preserve">9.27685165405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36061382293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29081344604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29779052734375</t>
   </si>
   <si>
     <t xml:space="preserve">9.31873321533203</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">9.36759567260742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47229957580566</t>
+    <t xml:space="preserve">9.47229862213135</t>
   </si>
   <si>
     <t xml:space="preserve">9.52814292907715</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">9.50022125244141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33269309997559</t>
+    <t xml:space="preserve">9.33269214630127</t>
   </si>
   <si>
     <t xml:space="preserve">9.32571315765381</t>
@@ -356,19 +356,19 @@
     <t xml:space="preserve">9.13724517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14422416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15120410919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10932350158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03951930999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92783546447754</t>
+    <t xml:space="preserve">9.14422512054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15120506286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1093225479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03952121734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92783451080322</t>
   </si>
   <si>
     <t xml:space="preserve">9.01159858703613</t>
@@ -380,37 +380,37 @@
     <t xml:space="preserve">8.9766960144043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86501216888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85105037689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.934814453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92085456848145</t>
+    <t xml:space="preserve">8.86501121520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85105133056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93481540679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92085266113281</t>
   </si>
   <si>
     <t xml:space="preserve">8.95575523376465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96971797943115</t>
+    <t xml:space="preserve">8.96971702575684</t>
   </si>
   <si>
     <t xml:space="preserve">9.00461769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91387462615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87897300720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80916786193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59976005554199</t>
+    <t xml:space="preserve">8.91387557983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87897396087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80916881561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59975814819336</t>
   </si>
   <si>
     <t xml:space="preserve">8.56485748291016</t>
@@ -419,28 +419,28 @@
     <t xml:space="preserve">8.81614971160889</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83708953857422</t>
+    <t xml:space="preserve">8.83709049224854</t>
   </si>
   <si>
     <t xml:space="preserve">8.89991283416748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99763774871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83010959625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96273708343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08838272094727</t>
+    <t xml:space="preserve">8.99763679504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83011054992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96273612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08838176727295</t>
   </si>
   <si>
     <t xml:space="preserve">9.04650020599365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09536170959473</t>
+    <t xml:space="preserve">9.09536266326904</t>
   </si>
   <si>
     <t xml:space="preserve">9.66076850891113</t>
@@ -449,16 +449,16 @@
     <t xml:space="preserve">9.64680767059326</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70265102386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79339599609375</t>
+    <t xml:space="preserve">9.70265007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79339504241943</t>
   </si>
   <si>
     <t xml:space="preserve">9.92602062225342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9818639755249</t>
+    <t xml:space="preserve">9.98186302185059</t>
   </si>
   <si>
     <t xml:space="preserve">10.0516662597656</t>
@@ -473,49 +473,49 @@
     <t xml:space="preserve">10.2471160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1493902206421</t>
+    <t xml:space="preserve">10.1493911743164</t>
   </si>
   <si>
     <t xml:space="preserve">10.1354303359985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2680578231812</t>
+    <t xml:space="preserve">10.2680568695068</t>
   </si>
   <si>
     <t xml:space="preserve">10.3937015533447</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5402889251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5891523361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4844465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6310338973999</t>
+    <t xml:space="preserve">10.5402898788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5891513824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.484447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6310319900513</t>
   </si>
   <si>
     <t xml:space="preserve">10.3588008880615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98884391784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95394325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.100528717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4704856872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3867235183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5472707748413</t>
+    <t xml:space="preserve">9.98884296417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95394229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1005296707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4704866409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3867216110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.547269821167</t>
   </si>
   <si>
     <t xml:space="preserve">10.3448400497437</t>
@@ -536,34 +536,34 @@
     <t xml:space="preserve">10.3657817840576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3378591537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2820167541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3797407150269</t>
+    <t xml:space="preserve">10.3378601074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2820177078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3797426223755</t>
   </si>
   <si>
     <t xml:space="preserve">10.6100931167603</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5542497634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6938562393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0917358398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0428733825684</t>
+    <t xml:space="preserve">10.5542507171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6938552856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0917339324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0428714752197</t>
   </si>
   <si>
     <t xml:space="preserve">11.0358934402466</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0638132095337</t>
+    <t xml:space="preserve">11.0638151168823</t>
   </si>
   <si>
     <t xml:space="preserve">11.0847549438477</t>
@@ -572,19 +572,19 @@
     <t xml:space="preserve">11.356987953186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5175361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0899200439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9991779327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.06898021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1038818359375</t>
+    <t xml:space="preserve">11.5175352096558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0899209976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9991760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0689811706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1038808822632</t>
   </si>
   <si>
     <t xml:space="preserve">12.2853708267212</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">12.8228559494019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9764242172241</t>
+    <t xml:space="preserve">12.9764223098755</t>
   </si>
   <si>
     <t xml:space="preserve">12.9903841018677</t>
@@ -602,28 +602,28 @@
     <t xml:space="preserve">13.2486553192139</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1090488433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1230068206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8926591873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9136018753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8437957763672</t>
+    <t xml:space="preserve">13.1090507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1230087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8926572799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9135990142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8437976837158</t>
   </si>
   <si>
     <t xml:space="preserve">12.9624624252319</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1928129196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.39524269104</t>
+    <t xml:space="preserve">13.1928119659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3952417373657</t>
   </si>
   <si>
     <t xml:space="preserve">13.8978252410889</t>
@@ -635,91 +635,91 @@
     <t xml:space="preserve">13.9327268600464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0234708786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0304508209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.135157585144</t>
+    <t xml:space="preserve">14.0234727859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0304517745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1351566314697</t>
   </si>
   <si>
     <t xml:space="preserve">14.0723323822021</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0025300979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.211256980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197402954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.146167755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0810775756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9942903518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6688423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.355899810791</t>
+    <t xml:space="preserve">14.0025291442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2112550735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197374343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.146164894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0810737609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.994291305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6688413619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3558988571167</t>
   </si>
   <si>
     <t xml:space="preserve">13.6833066940308</t>
   </si>
   <si>
-    <t xml:space="preserve">14.001522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9870567321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2691144943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.348669052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3414363861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2763471603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4282207489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5656337738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3322458267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8457298278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7589435577393</t>
+    <t xml:space="preserve">14.0015239715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9870586395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2691125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3486671447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.341438293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2763442993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4282236099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5656318664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3322477340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8457317352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7589454650879</t>
   </si>
   <si>
     <t xml:space="preserve">15.3611755371094</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1876049041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9200077056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6307210922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636768341064</t>
+    <t xml:space="preserve">15.1876029968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9200105667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6307220458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636758804321</t>
   </si>
   <si>
     <t xml:space="preserve">15.3105497360229</t>
@@ -731,46 +731,46 @@
     <t xml:space="preserve">15.0718879699707</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5492134094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.455192565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2671556472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1731405258179</t>
+    <t xml:space="preserve">15.5492105484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4551935195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2671566009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1731376647949</t>
   </si>
   <si>
     <t xml:space="preserve">14.8332252502441</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1369781494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1152820587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9851016998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1514444351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0284938812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2092971801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.664924621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6938552856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7661781311035</t>
+    <t xml:space="preserve">15.1369752883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1152782440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9850978851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1514406204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0284948348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2092981338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6649255752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6938562393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7661771774292</t>
   </si>
   <si>
     <t xml:space="preserve">15.9325199127197</t>
@@ -779,19 +779,19 @@
     <t xml:space="preserve">16.0410003662109</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9469795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6432304382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2816190719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2888517379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2599229812622</t>
+    <t xml:space="preserve">15.9469814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6432285308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2816219329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.288854598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2599239349365</t>
   </si>
   <si>
     <t xml:space="preserve">15.3250131607056</t>
@@ -800,10 +800,10 @@
     <t xml:space="preserve">15.238226890564</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1586742401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0574216842651</t>
+    <t xml:space="preserve">15.1586723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0574197769165</t>
   </si>
   <si>
     <t xml:space="preserve">15.1803703308105</t>
@@ -812,31 +812,31 @@
     <t xml:space="preserve">15.2454586029053</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8983135223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.869384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8259906768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9634056091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9706354141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6813468933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7536687850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6958141326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8910827636719</t>
+    <t xml:space="preserve">14.8983144760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8693866729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8259944915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9634037017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9706382751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6813449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7536725997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6958131790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8910808563232</t>
   </si>
   <si>
     <t xml:space="preserve">14.493311882019</t>
@@ -845,43 +845,43 @@
     <t xml:space="preserve">14.8549213409424</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6524200439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6090269088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8476886749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1948366165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3394775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4334945678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2651977539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9956493377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5742225646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6879825592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3986949920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4420871734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2178897857666</t>
+    <t xml:space="preserve">14.6524219512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6090278625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8476905822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1948347091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3394746780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4334955215454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2651958465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9956474304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5742244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6879844665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3986968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4420890808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2178916931152</t>
   </si>
   <si>
     <t xml:space="preserve">18.0804786682129</t>
@@ -890,16 +890,16 @@
     <t xml:space="preserve">18.1889610290527</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9719944000244</t>
+    <t xml:space="preserve">17.971996307373</t>
   </si>
   <si>
     <t xml:space="preserve">18.0081558227539</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8562812805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9647617340088</t>
+    <t xml:space="preserve">17.8562793731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9647636413574</t>
   </si>
   <si>
     <t xml:space="preserve">17.6393127441406</t>
@@ -911,58 +911,58 @@
     <t xml:space="preserve">17.6031551361084</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5886878967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.538064956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5019016265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3861885070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3211002349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2849349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0462741851807</t>
+    <t xml:space="preserve">17.5886917114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5380630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5019054412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3861904144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3210964202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2849388122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0462760925293</t>
   </si>
   <si>
     <t xml:space="preserve">17.263240814209</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0968971252441</t>
+    <t xml:space="preserve">17.0968990325928</t>
   </si>
   <si>
     <t xml:space="preserve">17.3283290863037</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3572597503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4006500244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3789558410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2921676635742</t>
+    <t xml:space="preserve">17.3572578430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4006538391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3789577484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2921695709229</t>
   </si>
   <si>
     <t xml:space="preserve">17.342794418335</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1692218780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5906467437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6268100738525</t>
+    <t xml:space="preserve">17.1692237854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.590648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6268081665039</t>
   </si>
   <si>
     <t xml:space="preserve">16.9233283996582</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">15.7083187103271</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1133232116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9180545806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6504592895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4749317169189</t>
+    <t xml:space="preserve">16.1133270263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9180555343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6504621505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4749336242676</t>
   </si>
   <si>
     <t xml:space="preserve">16.3013591766357</t>
@@ -992,28 +992,28 @@
     <t xml:space="preserve">16.5761833190918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5110931396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5617160797119</t>
+    <t xml:space="preserve">16.5110912322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5617179870605</t>
   </si>
   <si>
     <t xml:space="preserve">16.0699291229248</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5255546569824</t>
+    <t xml:space="preserve">16.5255565643311</t>
   </si>
   <si>
     <t xml:space="preserve">16.4098415374756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2073402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8746604919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2434997558594</t>
+    <t xml:space="preserve">16.2073421478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8746614456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.243501663208</t>
   </si>
   <si>
     <t xml:space="preserve">16.4460029602051</t>
@@ -1022,31 +1022,31 @@
     <t xml:space="preserve">16.2001094818115</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8312644958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8601951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8529624938965</t>
+    <t xml:space="preserve">15.8312683105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8601970672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8529644012451</t>
   </si>
   <si>
     <t xml:space="preserve">15.6287651062012</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4696559906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4624252319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215343475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9976081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2362689971924</t>
+    <t xml:space="preserve">15.4696578979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4624261856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215305328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9976072311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.236270904541</t>
   </si>
   <si>
     <t xml:space="preserve">16.163948059082</t>
@@ -1055,22 +1055,22 @@
     <t xml:space="preserve">16.2724304199219</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7786865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6340389251709</t>
+    <t xml:space="preserve">16.7786846160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6340408325195</t>
   </si>
   <si>
     <t xml:space="preserve">16.4532337188721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7425212860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.59787940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7063617706299</t>
+    <t xml:space="preserve">16.742525100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5978813171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7063636779785</t>
   </si>
   <si>
     <t xml:space="preserve">16.8510074615479</t>
@@ -1082,25 +1082,25 @@
     <t xml:space="preserve">17.2126140594482</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4295825958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9594879150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3809146881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9831447601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9108219146729</t>
+    <t xml:space="preserve">17.4295806884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9594898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3809127807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9831428527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9108228683472</t>
   </si>
   <si>
     <t xml:space="preserve">15.730016708374</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3684053421021</t>
+    <t xml:space="preserve">15.368408203125</t>
   </si>
   <si>
     <t xml:space="preserve">15.4045677185059</t>
@@ -1109,22 +1109,22 @@
     <t xml:space="preserve">15.4768886566162</t>
   </si>
   <si>
-    <t xml:space="preserve">15.802339553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6701984405518</t>
+    <t xml:space="preserve">15.8023386001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.670202255249</t>
   </si>
   <si>
     <t xml:space="preserve">17.1402931213379</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1041297912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8148460388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0679702758789</t>
+    <t xml:space="preserve">17.1041316986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8148441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0679740905762</t>
   </si>
   <si>
     <t xml:space="preserve">16.8871669769287</t>
@@ -1133,16 +1133,16 @@
     <t xml:space="preserve">17.8273506164551</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6827068328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3934192657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2487773895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7550296783447</t>
+    <t xml:space="preserve">17.6827087402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3934211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2487754821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7550315856934</t>
   </si>
   <si>
     <t xml:space="preserve">17.8996715545654</t>
@@ -1166,64 +1166,64 @@
     <t xml:space="preserve">19.9157543182373</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4378910064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6546878814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4682102203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6173915863037</t>
+    <t xml:space="preserve">20.4378890991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6546859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4682083129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6173877716064</t>
   </si>
   <si>
     <t xml:space="preserve">19.0952548980713</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8714790344238</t>
+    <t xml:space="preserve">18.8714828491211</t>
   </si>
   <si>
     <t xml:space="preserve">18.9460735321045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7968921661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9018020629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3050765991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7899150848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8341865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1698474884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3936195373535</t>
+    <t xml:space="preserve">18.7968940734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9018001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3050746917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7899169921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8341884613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1698455810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3936157226562</t>
   </si>
   <si>
     <t xml:space="preserve">19.5055027008057</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8038673400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8784599304199</t>
+    <t xml:space="preserve">19.8038654327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8784580230713</t>
   </si>
   <si>
     <t xml:space="preserve">19.6919803619385</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3190269470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4239387512207</t>
+    <t xml:space="preserve">19.3190288543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4239368438721</t>
   </si>
   <si>
     <t xml:space="preserve">19.1325511932373</t>
@@ -1232,22 +1232,25 @@
     <t xml:space="preserve">19.3563213348389</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7292766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7222995758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9087791442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6477088928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5731201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5358200073242</t>
+    <t xml:space="preserve">19.0206642150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7292785644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7223033905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9087810516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6477108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5731182098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5358238220215</t>
   </si>
   <si>
     <t xml:space="preserve">17.9763927459717</t>
@@ -1256,7 +1259,7 @@
     <t xml:space="preserve">18.1255722045898</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4612312316895</t>
+    <t xml:space="preserve">18.4612331390381</t>
   </si>
   <si>
     <t xml:space="preserve">18.7595958709717</t>
@@ -1274,37 +1277,37 @@
     <t xml:space="preserve">18.3120517730713</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4985275268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2817344665527</t>
+    <t xml:space="preserve">18.4985294342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2817325592041</t>
   </si>
   <si>
     <t xml:space="preserve">19.0579586029053</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1628684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0136871337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3866405487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.155891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1862106323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.589485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1419410705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9554624557495</t>
+    <t xml:space="preserve">18.1628704071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0136852264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3866424560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1558933258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1862125396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5894832611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.141939163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9554634094238</t>
   </si>
   <si>
     <t xml:space="preserve">16.0370311737061</t>
@@ -1316,127 +1319,127 @@
     <t xml:space="preserve">15.6640777587891</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1046447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9927577972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0300550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7689876556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3661947250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5153751373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6198053359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8883323669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2538251876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2608032226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9251441955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7759609222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7013702392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.552188873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6267805099487</t>
+    <t xml:space="preserve">15.1046457290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9927568435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0300540924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7689847946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3661956787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5153770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6198024749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8883304595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2538280487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.260799407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.925145149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7759647369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7013731002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5521907806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6267824172974</t>
   </si>
   <si>
     <t xml:space="preserve">15.5148954391479</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2911224365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2165307998657</t>
+    <t xml:space="preserve">15.2911233901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2165327072144</t>
   </si>
   <si>
     <t xml:space="preserve">15.1792364120483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8505525588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8132591247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0743255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8878479003906</t>
+    <t xml:space="preserve">15.8505554199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8132600784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0743236541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8878498077393</t>
   </si>
   <si>
     <t xml:space="preserve">15.4030084609985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9032506942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7093133926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4403018951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1116199493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9624376296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5591678619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3726921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4845771789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.78293800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8948249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7386655807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657131195068</t>
+    <t xml:space="preserve">14.9032516479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7093143463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4403057098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1116218566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9624404907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5591659545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3726902008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4845733642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7829399108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8948230743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7386693954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657150268555</t>
   </si>
   <si>
     <t xml:space="preserve">14.8435764312744</t>
   </si>
   <si>
-    <t xml:space="preserve">14.858494758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0673513412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8734140396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9181661605835</t>
+    <t xml:space="preserve">14.8584957122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0673503875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8734121322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9181680679321</t>
   </si>
   <si>
     <t xml:space="preserve">16.409984588623</t>
@@ -1448,7 +1451,7 @@
     <t xml:space="preserve">16.2980976104736</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6710529327393</t>
+    <t xml:space="preserve">16.6710510253906</t>
   </si>
   <si>
     <t xml:space="preserve">16.7083473205566</t>
@@ -1460,7 +1463,7 @@
     <t xml:space="preserve">16.6337547302246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9321212768555</t>
+    <t xml:space="preserve">16.9321193695068</t>
   </si>
   <si>
     <t xml:space="preserve">16.8575305938721</t>
@@ -1472,162 +1475,165 @@
     <t xml:space="preserve">17.3796672821045</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2304840087891</t>
+    <t xml:space="preserve">17.2304859161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5288467407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.343240737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7227516174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6756706237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7532329559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3654289245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0939636230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6673784255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6285972595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0468854904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2640590667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7061557769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5898151397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5122528076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7449369430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950830459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0158624649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1864967346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4191808700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4967451095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5510330200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3261070251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2795724868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8612823486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0164031982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9388408660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9000616073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7837200164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8225011825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3266468048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.792013168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0247001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9083576202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4817714691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5593338012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0551872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4042110443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1327438354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2878684997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1715240478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9776220321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3881559371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346942901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2103061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4429931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5981121063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5205497741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6368942260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2490882873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8307971954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9859180450439</t>
   </si>
   <si>
     <t xml:space="preserve">17.5288486480713</t>
   </si>
   <si>
-    <t xml:space="preserve">18.343240737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7227516174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6756744384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7532329559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3654270172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0939636230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6673784255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6285972595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0468854904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2640590667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7061576843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5898151397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5122528076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7449388504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950830459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0158615112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1864967346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4191789627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4967432022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5510339736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3261079788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2795715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8612785339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0164031982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9388408660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9000616073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7837200164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8224992752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3266468048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7920150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0247020721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9083576202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4817695617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5593318939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0551815032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4042072296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1327457427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2878684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1715240478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9776220321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3881578445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346923828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2103061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4429912567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5981101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5205497741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6368961334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2490863800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8307952880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9859199523926</t>
-  </si>
-  <si>
     <t xml:space="preserve">17.83909034729</t>
   </si>
   <si>
@@ -1637,7 +1643,7 @@
     <t xml:space="preserve">17.9942169189453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6147060394287</t>
+    <t xml:space="preserve">18.6147022247314</t>
   </si>
   <si>
     <t xml:space="preserve">18.2656784057617</t>
@@ -1652,7 +1658,7 @@
     <t xml:space="preserve">18.07177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4595832824707</t>
+    <t xml:space="preserve">18.4595813751221</t>
   </si>
   <si>
     <t xml:space="preserve">18.7698268890381</t>
@@ -1664,28 +1670,28 @@
     <t xml:space="preserve">19.1576366424561</t>
   </si>
   <si>
-    <t xml:space="preserve">19.002513885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0412940979004</t>
+    <t xml:space="preserve">19.0025119781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0412921905518</t>
   </si>
   <si>
     <t xml:space="preserve">18.3044605255127</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1493396759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0329971313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.226900100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4208030700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.498363494873</t>
+    <t xml:space="preserve">18.1493377685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.032995223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2268981933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4208011627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4983654022217</t>
   </si>
   <si>
     <t xml:space="preserve">18.1105575561523</t>
@@ -1694,13 +1700,13 @@
     <t xml:space="preserve">17.6839694976807</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8086090087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3820209503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1881160736084</t>
+    <t xml:space="preserve">18.8086051940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.382022857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1881198883057</t>
   </si>
   <si>
     <t xml:space="preserve">17.916654586792</t>
@@ -1712,10 +1718,10 @@
     <t xml:space="preserve">17.606409072876</t>
   </si>
   <si>
-    <t xml:space="preserve">17.645191192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1410427093506</t>
+    <t xml:space="preserve">17.6451892852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.141040802002</t>
   </si>
   <si>
     <t xml:space="preserve">17.102258682251</t>
@@ -1724,7 +1730,7 @@
     <t xml:space="preserve">17.2961616516113</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1244487762451</t>
+    <t xml:space="preserve">15.1244478225708</t>
   </si>
   <si>
     <t xml:space="preserve">14.7676677703857</t>
@@ -1736,25 +1742,25 @@
     <t xml:space="preserve">13.9610290527344</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0302934646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1854162216187</t>
+    <t xml:space="preserve">13.0302925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1854181289673</t>
   </si>
   <si>
     <t xml:space="preserve">13.138879776001</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5732221603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.262978553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.169903755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9527320861816</t>
+    <t xml:space="preserve">13.5732231140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2629795074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1699028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.952733039856</t>
   </si>
   <si>
     <t xml:space="preserve">12.5649271011353</t>
@@ -1766,7 +1772,7 @@
     <t xml:space="preserve">11.5566301345825</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8585786819458</t>
+    <t xml:space="preserve">10.8585777282715</t>
   </si>
   <si>
     <t xml:space="preserve">10.7810163497925</t>
@@ -1781,13 +1787,13 @@
     <t xml:space="preserve">11.1300439834595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7893133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2546815872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9056558609009</t>
+    <t xml:space="preserve">11.7893142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2546806335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9056549072266</t>
   </si>
   <si>
     <t xml:space="preserve">11.6341915130615</t>
@@ -1799,13 +1805,13 @@
     <t xml:space="preserve">12.0607786178589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8280944824219</t>
+    <t xml:space="preserve">11.8280935287476</t>
   </si>
   <si>
     <t xml:space="preserve">11.4790678024292</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7117519378662</t>
+    <t xml:space="preserve">11.7117528915405</t>
   </si>
   <si>
     <t xml:space="preserve">11.6729717254639</t>
@@ -1832,10 +1838,10 @@
     <t xml:space="preserve">10.5871133804321</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6646757125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2463836669922</t>
+    <t xml:space="preserve">10.6646747589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2463846206665</t>
   </si>
   <si>
     <t xml:space="preserve">12.2159004211426</t>
@@ -1844,58 +1850,58 @@
     <t xml:space="preserve">12.3710231781006</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0773696899414</t>
+    <t xml:space="preserve">14.0773706436157</t>
   </si>
   <si>
     <t xml:space="preserve">14.1181745529175</t>
   </si>
   <si>
-    <t xml:space="preserve">14.036566734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8733510971069</t>
+    <t xml:space="preserve">14.0365676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8733530044556</t>
   </si>
   <si>
     <t xml:space="preserve">13.8325471878052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1997833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6078233718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2813901901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4245080947876</t>
+    <t xml:space="preserve">14.199782371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6078224182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2813892364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4245071411133</t>
   </si>
   <si>
     <t xml:space="preserve">13.5469188690186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5061140060425</t>
+    <t xml:space="preserve">13.5061149597168</t>
   </si>
   <si>
     <t xml:space="preserve">13.7509393692017</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9549589157104</t>
+    <t xml:space="preserve">13.9549598693848</t>
   </si>
   <si>
     <t xml:space="preserve">14.5262136459351</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7710390090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.689432144165</t>
+    <t xml:space="preserve">14.7710380554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6894311904907</t>
   </si>
   <si>
     <t xml:space="preserve">14.3221940994263</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4038019180298</t>
+    <t xml:space="preserve">14.4038009643555</t>
   </si>
   <si>
     <t xml:space="preserve">13.5877227783203</t>
@@ -1907,43 +1913,37 @@
     <t xml:space="preserve">13.6285285949707</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9141540527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2405881881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9957628250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1589803695679</t>
+    <t xml:space="preserve">13.9141550064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2405862808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9957637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1589784622192</t>
   </si>
   <si>
     <t xml:space="preserve">13.7917413711548</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3837032318115</t>
+    <t xml:space="preserve">13.3837022781372</t>
   </si>
   <si>
     <t xml:space="preserve">13.2204885482788</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0773706436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3429002761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7101354598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0572710037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1388807296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2612905502319</t>
+    <t xml:space="preserve">13.3428993225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7101335525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0572729110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2612915039062</t>
   </si>
   <si>
     <t xml:space="preserve">13.0980749130249</t>
@@ -1958,22 +1958,22 @@
     <t xml:space="preserve">12.7308397293091</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6900367736816</t>
+    <t xml:space="preserve">12.6900358200073</t>
   </si>
   <si>
     <t xml:space="preserve">12.9756631851196</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7716436386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8526458740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2606859207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.423900604248</t>
+    <t xml:space="preserve">12.7716426849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8526468276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2606868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4239025115967</t>
   </si>
   <si>
     <t xml:space="preserve">16.0767669677734</t>
@@ -1982,19 +1982,19 @@
     <t xml:space="preserve">15.9135494232178</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5055103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6687288284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5871181488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3014888763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3830966949463</t>
+    <t xml:space="preserve">15.5055084228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6687269210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5871200561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3014898300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3830986022949</t>
   </si>
   <si>
     <t xml:space="preserve">15.3422937393188</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">15.7503328323364</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2198839187622</t>
+    <t xml:space="preserve">15.2198810577393</t>
   </si>
   <si>
     <t xml:space="preserve">15.1790800094604</t>
@@ -2012,22 +2012,22 @@
     <t xml:space="preserve">15.4647064208984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3215885162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.158374786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8112373352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7089233398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1376686096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3824920654297</t>
+    <t xml:space="preserve">16.321590423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1583709716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8112392425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7089252471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1376705169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3824939727783</t>
   </si>
   <si>
     <t xml:space="preserve">16.8928451538086</t>
@@ -2039,34 +2039,34 @@
     <t xml:space="preserve">16.484806060791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.648021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5664138793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2399787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4031982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7296276092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2192764282227</t>
+    <t xml:space="preserve">16.6480197906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5664119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2399806976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4031963348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7296295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2192783355713</t>
   </si>
   <si>
     <t xml:space="preserve">17.4641017913818</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5457096099854</t>
+    <t xml:space="preserve">17.5457077026367</t>
   </si>
   <si>
     <t xml:space="preserve">17.9537487030029</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0353584289551</t>
+    <t xml:space="preserve">18.0353546142578</t>
   </si>
   <si>
     <t xml:space="preserve">16.9744529724121</t>
@@ -2075,16 +2075,16 @@
     <t xml:space="preserve">17.8721408843994</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1169662475586</t>
+    <t xml:space="preserve">18.11696434021</t>
   </si>
   <si>
     <t xml:space="preserve">18.1985702514648</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3617877960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1778678894043</t>
+    <t xml:space="preserve">18.3617897033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1778659820557</t>
   </si>
   <si>
     <t xml:space="preserve">18.8514366149902</t>
@@ -2099,10 +2099,10 @@
     <t xml:space="preserve">18.6066112518311</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9330463409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2594738006592</t>
+    <t xml:space="preserve">18.9330444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2594757080078</t>
   </si>
   <si>
     <t xml:space="preserve">19.3410835266113</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">19.4226913452148</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0146503448486</t>
+    <t xml:space="preserve">19.0146522521973</t>
   </si>
   <si>
     <t xml:space="preserve">19.9123401641846</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">19.8276062011719</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4886722564697</t>
+    <t xml:space="preserve">19.4886741638184</t>
   </si>
   <si>
     <t xml:space="preserve">19.6581401824951</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">19.0650062561035</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6413402557373</t>
+    <t xml:space="preserve">18.6413383483887</t>
   </si>
   <si>
     <t xml:space="preserve">19.7428722381592</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">20.9291400909424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1833400726318</t>
+    <t xml:space="preserve">21.1833381652832</t>
   </si>
   <si>
     <t xml:space="preserve">20.759672164917</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">22.0306720733643</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4543399810791</t>
+    <t xml:space="preserve">22.4543418884277</t>
   </si>
   <si>
     <t xml:space="preserve">22.2001399993896</t>
@@ -2198,10 +2198,10 @@
     <t xml:space="preserve">23.0474739074707</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6406059265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5558738708496</t>
+    <t xml:space="preserve">23.6406078338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.555871963501</t>
   </si>
   <si>
     <t xml:space="preserve">23.3016738891602</t>
@@ -2222,7 +2222,7 @@
     <t xml:space="preserve">23.2169399261475</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9459400177002</t>
+    <t xml:space="preserve">21.9459419250488</t>
   </si>
   <si>
     <t xml:space="preserve">22.8780059814453</t>
@@ -2234,7 +2234,7 @@
     <t xml:space="preserve">25.165807723999</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9116077423096</t>
+    <t xml:space="preserve">24.9116096496582</t>
   </si>
   <si>
     <t xml:space="preserve">24.2337417602539</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">24.5726737976074</t>
   </si>
   <si>
-    <t xml:space="preserve">24.403205871582</t>
+    <t xml:space="preserve">24.4032077789307</t>
   </si>
   <si>
     <t xml:space="preserve">24.4879417419434</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">25.5047435760498</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3352756500244</t>
+    <t xml:space="preserve">25.3352737426758</t>
   </si>
   <si>
     <t xml:space="preserve">25.4200077056885</t>
@@ -2276,22 +2276,22 @@
     <t xml:space="preserve">26.4368095397949</t>
   </si>
   <si>
-    <t xml:space="preserve">26.521541595459</t>
+    <t xml:space="preserve">26.5215396881104</t>
   </si>
   <si>
     <t xml:space="preserve">27.8772773742676</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5719451904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.317741394043</t>
+    <t xml:space="preserve">29.5719413757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3177394866943</t>
   </si>
   <si>
     <t xml:space="preserve">28.9788093566895</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1482753753662</t>
+    <t xml:space="preserve">29.1482772827148</t>
   </si>
   <si>
     <t xml:space="preserve">29.2330093383789</t>
@@ -2300,7 +2300,7 @@
     <t xml:space="preserve">27.9620094299316</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0299434661865</t>
+    <t xml:space="preserve">27.0299415588379</t>
   </si>
   <si>
     <t xml:space="preserve">28.4704093933105</t>
@@ -2309,7 +2309,7 @@
     <t xml:space="preserve">27.4536113739014</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3856773376465</t>
+    <t xml:space="preserve">28.3856735229492</t>
   </si>
   <si>
     <t xml:space="preserve">27.7078094482422</t>
@@ -2324,13 +2324,13 @@
     <t xml:space="preserve">25.6742057800293</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0131435394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8436756134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3520755767822</t>
+    <t xml:space="preserve">26.0131416320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8436737060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3520736694336</t>
   </si>
   <si>
     <t xml:space="preserve">26.606273651123</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">26.1826076507568</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0978717803955</t>
+    <t xml:space="preserve">26.0978736877441</t>
   </si>
   <si>
     <t xml:space="preserve">25.9284076690674</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">22.5390739440918</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0642738342285</t>
+    <t xml:space="preserve">24.0642719268799</t>
   </si>
   <si>
     <t xml:space="preserve">22.9627418518066</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">23.5261859893799</t>
   </si>
   <si>
-    <t xml:space="preserve">22.730188369751</t>
+    <t xml:space="preserve">22.7301864624023</t>
   </si>
   <si>
     <t xml:space="preserve">23.2608528137207</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">25.2066268920898</t>
   </si>
   <si>
-    <t xml:space="preserve">24.587516784668</t>
+    <t xml:space="preserve">24.5875148773193</t>
   </si>
   <si>
     <t xml:space="preserve">24.3221855163574</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">23.3492965698242</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2879657745361</t>
+    <t xml:space="preserve">22.2879676818848</t>
   </si>
   <si>
     <t xml:space="preserve">22.4648532867432</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">21.8457450866699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7572994232178</t>
+    <t xml:space="preserve">21.7573013305664</t>
   </si>
   <si>
     <t xml:space="preserve">21.4035224914551</t>
@@ -2447,28 +2447,28 @@
     <t xml:space="preserve">21.1381893157959</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1110782623291</t>
+    <t xml:space="preserve">22.1110763549805</t>
   </si>
   <si>
     <t xml:space="preserve">23.7915191650391</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1181831359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6759605407715</t>
+    <t xml:space="preserve">25.1181812286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6759624481201</t>
   </si>
   <si>
     <t xml:space="preserve">22.9955196380615</t>
   </si>
   <si>
-    <t xml:space="preserve">22.907075881958</t>
+    <t xml:space="preserve">22.9070777893066</t>
   </si>
   <si>
     <t xml:space="preserve">24.1452960968018</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4377422332764</t>
+    <t xml:space="preserve">23.437744140625</t>
   </si>
   <si>
     <t xml:space="preserve">23.614631652832</t>
@@ -2489,13 +2489,13 @@
     <t xml:space="preserve">22.1995220184326</t>
   </si>
   <si>
-    <t xml:space="preserve">22.022632598877</t>
+    <t xml:space="preserve">22.0226306915283</t>
   </si>
   <si>
     <t xml:space="preserve">21.0497455596924</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4919662475586</t>
+    <t xml:space="preserve">21.49196434021</t>
   </si>
   <si>
     <t xml:space="preserve">20.6959686279297</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">25.5604057312012</t>
   </si>
   <si>
-    <t xml:space="preserve">25.471960067749</t>
+    <t xml:space="preserve">25.4719619750977</t>
   </si>
   <si>
     <t xml:space="preserve">25.6488494873047</t>
@@ -2531,13 +2531,13 @@
     <t xml:space="preserve">27.0639591217041</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2408447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1524047851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5061817169189</t>
+    <t xml:space="preserve">27.2408466339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1524028778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5061798095703</t>
   </si>
   <si>
     <t xml:space="preserve">27.5946254730225</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">27.3292903900146</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7101802825928</t>
+    <t xml:space="preserve">26.7101821899414</t>
   </si>
   <si>
     <t xml:space="preserve">26.7986240386963</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">26.8870697021484</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9755153656006</t>
+    <t xml:space="preserve">26.975513458252</t>
   </si>
   <si>
     <t xml:space="preserve">27.4177360534668</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">26.0910720825195</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4448490142822</t>
+    <t xml:space="preserve">26.4448471069336</t>
   </si>
   <si>
     <t xml:space="preserve">26.3564033508301</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">25.8257389068604</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0026264190674</t>
+    <t xml:space="preserve">26.002628326416</t>
   </si>
   <si>
     <t xml:space="preserve">26.179515838623</t>
@@ -3678,6 +3678,9 @@
   </si>
   <si>
     <t xml:space="preserve">66.1999969482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.0999984741211</t>
   </si>
 </sst>
 </file>
@@ -20518,7 +20521,7 @@
         <v>25.5</v>
       </c>
       <c r="G635" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20544,7 +20547,7 @@
         <v>25.5</v>
       </c>
       <c r="G636" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20570,7 +20573,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G637" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20596,7 +20599,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G638" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20622,7 +20625,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G639" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20648,7 +20651,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G640" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20726,7 +20729,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G643" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20752,7 +20755,7 @@
         <v>25</v>
       </c>
       <c r="G644" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20778,7 +20781,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G645" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20804,7 +20807,7 @@
         <v>25</v>
       </c>
       <c r="G646" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20830,7 +20833,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G647" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20856,7 +20859,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G648" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20882,7 +20885,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G649" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20908,7 +20911,7 @@
         <v>24.75</v>
       </c>
       <c r="G650" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20934,7 +20937,7 @@
         <v>24.75</v>
       </c>
       <c r="G651" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20960,7 +20963,7 @@
         <v>24.75</v>
       </c>
       <c r="G652" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -21038,7 +21041,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G655" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -21064,7 +21067,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G656" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -21116,7 +21119,7 @@
         <v>25</v>
       </c>
       <c r="G658" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -21142,7 +21145,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G659" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -21194,7 +21197,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G661" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -21220,7 +21223,7 @@
         <v>25</v>
       </c>
       <c r="G662" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -21246,7 +21249,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G663" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -21272,7 +21275,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G664" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -21298,7 +21301,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G665" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21324,7 +21327,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G666" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21376,7 +21379,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G668" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21402,7 +21405,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G669" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21454,7 +21457,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G671" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21480,7 +21483,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G672" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21506,7 +21509,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G673" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21558,7 +21561,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21584,7 +21587,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G676" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21636,7 +21639,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G678" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21688,7 +21691,7 @@
         <v>25</v>
       </c>
       <c r="G680" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21714,7 +21717,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G681" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21740,7 +21743,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G682" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21766,7 +21769,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G683" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21792,7 +21795,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G684" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21818,7 +21821,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21948,7 +21951,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G690" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21974,7 +21977,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G691" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -22000,7 +22003,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G692" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -22026,7 +22029,7 @@
         <v>25</v>
       </c>
       <c r="G693" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -22052,7 +22055,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G694" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -22104,7 +22107,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G696" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -22130,7 +22133,7 @@
         <v>24.75</v>
       </c>
       <c r="G697" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -22156,7 +22159,7 @@
         <v>24.75</v>
       </c>
       <c r="G698" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -22182,7 +22185,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G699" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -22208,7 +22211,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -22234,7 +22237,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G701" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -22260,7 +22263,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G702" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -22286,7 +22289,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G703" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22312,7 +22315,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G704" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -22338,7 +22341,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G705" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -22390,7 +22393,7 @@
         <v>23</v>
       </c>
       <c r="G707" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22416,7 +22419,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G708" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22442,7 +22445,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G709" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22468,7 +22471,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G710" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22494,7 +22497,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G711" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22520,7 +22523,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G712" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22546,7 +22549,7 @@
         <v>21.5</v>
       </c>
       <c r="G713" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22572,7 +22575,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22598,7 +22601,7 @@
         <v>21</v>
       </c>
       <c r="G715" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22624,7 +22627,7 @@
         <v>20.25</v>
       </c>
       <c r="G716" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22650,7 +22653,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22676,7 +22679,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G718" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22702,7 +22705,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G719" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22728,7 +22731,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G720" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22754,7 +22757,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G721" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22780,7 +22783,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G722" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22806,7 +22809,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G723" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22832,7 +22835,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G724" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22858,7 +22861,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G725" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22884,7 +22887,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G726" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22910,7 +22913,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G727" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22936,7 +22939,7 @@
         <v>21</v>
       </c>
       <c r="G728" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22962,7 +22965,7 @@
         <v>21.5</v>
       </c>
       <c r="G729" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22988,7 +22991,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G730" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -23014,7 +23017,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G731" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -23040,7 +23043,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G732" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -23066,7 +23069,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G733" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -23092,7 +23095,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G734" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -23118,7 +23121,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -23144,7 +23147,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G736" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -23170,7 +23173,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G737" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -23196,7 +23199,7 @@
         <v>20.5</v>
       </c>
       <c r="G738" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -23222,7 +23225,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G739" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -23248,7 +23251,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G740" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -23274,7 +23277,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G741" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -23300,7 +23303,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G742" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23326,7 +23329,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23352,7 +23355,7 @@
         <v>21.25</v>
       </c>
       <c r="G744" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23378,7 +23381,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G745" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23404,7 +23407,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G746" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23430,7 +23433,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G747" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23456,7 +23459,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G748" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23482,7 +23485,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G749" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23508,7 +23511,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G750" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23534,7 +23537,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G751" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23560,7 +23563,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G752" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23586,7 +23589,7 @@
         <v>21</v>
       </c>
       <c r="G753" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23612,7 +23615,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G754" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23638,7 +23641,7 @@
         <v>21</v>
       </c>
       <c r="G755" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23664,7 +23667,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G756" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23690,7 +23693,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G757" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23716,7 +23719,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G758" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23742,7 +23745,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G759" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23768,7 +23771,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G760" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23794,7 +23797,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G761" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23820,7 +23823,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G762" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23846,7 +23849,7 @@
         <v>20.25</v>
       </c>
       <c r="G763" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23872,7 +23875,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G764" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23898,7 +23901,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G765" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23924,7 +23927,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G766" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23950,7 +23953,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G767" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23976,7 +23979,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G768" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -24002,7 +24005,7 @@
         <v>21</v>
       </c>
       <c r="G769" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -24028,7 +24031,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G770" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -24054,7 +24057,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G771" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -24080,7 +24083,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G772" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -24106,7 +24109,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G773" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -24132,7 +24135,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G774" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -24158,7 +24161,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G775" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -24184,7 +24187,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G776" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -24210,7 +24213,7 @@
         <v>22.5</v>
       </c>
       <c r="G777" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -24236,7 +24239,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G778" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -24262,7 +24265,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G779" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -24288,7 +24291,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G780" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -24314,7 +24317,7 @@
         <v>21.5</v>
       </c>
       <c r="G781" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -24340,7 +24343,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G782" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -24366,7 +24369,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G783" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -24392,7 +24395,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G784" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -24418,7 +24421,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G785" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -24444,7 +24447,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G786" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -24470,7 +24473,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G787" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -24496,7 +24499,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G788" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -24522,7 +24525,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G789" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -24548,7 +24551,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G790" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -24574,7 +24577,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G791" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -24600,7 +24603,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G792" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -24626,7 +24629,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G793" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24652,7 +24655,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G794" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24678,7 +24681,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G795" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24704,7 +24707,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G796" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24730,7 +24733,7 @@
         <v>20.25</v>
       </c>
       <c r="G797" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24756,7 +24759,7 @@
         <v>20</v>
       </c>
       <c r="G798" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24782,7 +24785,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G799" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24808,7 +24811,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G800" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24834,7 +24837,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G801" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24860,7 +24863,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G802" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24886,7 +24889,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G803" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24912,7 +24915,7 @@
         <v>20.25</v>
       </c>
       <c r="G804" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24938,7 +24941,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G805" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24964,7 +24967,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G806" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24990,7 +24993,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G807" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -25016,7 +25019,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G808" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -25042,7 +25045,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G809" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -25068,7 +25071,7 @@
         <v>20.5</v>
       </c>
       <c r="G810" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -25094,7 +25097,7 @@
         <v>20</v>
       </c>
       <c r="G811" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -25120,7 +25123,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G812" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -25146,7 +25149,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G813" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -25172,7 +25175,7 @@
         <v>20.25</v>
       </c>
       <c r="G814" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -25198,7 +25201,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G815" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -25224,7 +25227,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G816" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -25250,7 +25253,7 @@
         <v>20.25</v>
       </c>
       <c r="G817" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -25276,7 +25279,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -25302,7 +25305,7 @@
         <v>21</v>
       </c>
       <c r="G819" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -25328,7 +25331,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G820" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -25354,7 +25357,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G821" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -25380,7 +25383,7 @@
         <v>21.5</v>
       </c>
       <c r="G822" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -25406,7 +25409,7 @@
         <v>22</v>
       </c>
       <c r="G823" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -25432,7 +25435,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G824" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -25458,7 +25461,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G825" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -25484,7 +25487,7 @@
         <v>21.75</v>
       </c>
       <c r="G826" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -25510,7 +25513,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G827" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -25536,7 +25539,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G828" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -25562,7 +25565,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G829" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -25588,7 +25591,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -25614,7 +25617,7 @@
         <v>21.75</v>
       </c>
       <c r="G831" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25640,7 +25643,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G832" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25666,7 +25669,7 @@
         <v>22</v>
       </c>
       <c r="G833" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25692,7 +25695,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G834" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25718,7 +25721,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G835" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25744,7 +25747,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G836" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25770,7 +25773,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G837" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25796,7 +25799,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G838" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25822,7 +25825,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G839" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25848,7 +25851,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25874,7 +25877,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G841" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25900,7 +25903,7 @@
         <v>22.5</v>
       </c>
       <c r="G842" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25926,7 +25929,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G843" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25952,7 +25955,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G844" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25978,7 +25981,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G845" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -26004,7 +26007,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G846" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -26030,7 +26033,7 @@
         <v>23.5</v>
       </c>
       <c r="G847" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -26056,7 +26059,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -26082,7 +26085,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G849" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -26108,7 +26111,7 @@
         <v>21.5</v>
       </c>
       <c r="G850" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -26134,7 +26137,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -26160,7 +26163,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -26186,7 +26189,7 @@
         <v>20.75</v>
       </c>
       <c r="G853" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -26212,7 +26215,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G854" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -26238,7 +26241,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G855" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -26264,7 +26267,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G856" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -26290,7 +26293,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G857" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26316,7 +26319,7 @@
         <v>20.25</v>
       </c>
       <c r="G858" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26342,7 +26345,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G859" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -26368,7 +26371,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G860" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -26394,7 +26397,7 @@
         <v>20</v>
       </c>
       <c r="G861" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -26420,7 +26423,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G862" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -26446,7 +26449,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G863" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -26472,7 +26475,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G864" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -26498,7 +26501,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G865" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26524,7 +26527,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G866" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -26550,7 +26553,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G867" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -26576,7 +26579,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G868" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -26602,7 +26605,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G869" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -26628,7 +26631,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -26654,7 +26657,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G871" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -26680,7 +26683,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G872" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26706,7 +26709,7 @@
         <v>20</v>
       </c>
       <c r="G873" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -26732,7 +26735,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G874" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26758,7 +26761,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G875" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26784,7 +26787,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G876" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26810,7 +26813,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G877" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26836,7 +26839,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G878" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26862,7 +26865,7 @@
         <v>20.25</v>
       </c>
       <c r="G879" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26888,7 +26891,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26914,7 +26917,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G881" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26940,7 +26943,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G882" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26966,7 +26969,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G883" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26992,7 +26995,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G884" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -27018,7 +27021,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G885" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -27044,7 +27047,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G886" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -27070,7 +27073,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G887" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -27096,7 +27099,7 @@
         <v>20.25</v>
       </c>
       <c r="G888" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -27122,7 +27125,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G889" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -27148,7 +27151,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G890" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -27174,7 +27177,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G891" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -27200,7 +27203,7 @@
         <v>20.5</v>
       </c>
       <c r="G892" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -27226,7 +27229,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G893" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -27252,7 +27255,7 @@
         <v>20.25</v>
       </c>
       <c r="G894" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -27278,7 +27281,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -27304,7 +27307,7 @@
         <v>20.25</v>
       </c>
       <c r="G896" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -27330,7 +27333,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G897" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -27356,7 +27359,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G898" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -27382,7 +27385,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G899" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -27408,7 +27411,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G900" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -27434,7 +27437,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G901" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -27460,7 +27463,7 @@
         <v>20.25</v>
       </c>
       <c r="G902" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -27486,7 +27489,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G903" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -27512,7 +27515,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G904" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -27538,7 +27541,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G905" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -27564,7 +27567,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G906" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -27590,7 +27593,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G907" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -27616,7 +27619,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G908" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -27642,7 +27645,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G909" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -27668,7 +27671,7 @@
         <v>21.25</v>
       </c>
       <c r="G910" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27694,7 +27697,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G911" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27720,7 +27723,7 @@
         <v>21.5</v>
       </c>
       <c r="G912" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27746,7 +27749,7 @@
         <v>21.5</v>
       </c>
       <c r="G913" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27772,7 +27775,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G914" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27798,7 +27801,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G915" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27824,7 +27827,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G916" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27850,7 +27853,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G917" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -27876,7 +27879,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G918" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27902,7 +27905,7 @@
         <v>21</v>
       </c>
       <c r="G919" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27928,7 +27931,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G920" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27954,7 +27957,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G921" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27980,7 +27983,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G922" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -28006,7 +28009,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G923" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -28032,7 +28035,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G924" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -28058,7 +28061,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G925" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -28084,7 +28087,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G926" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -28110,7 +28113,7 @@
         <v>20</v>
       </c>
       <c r="G927" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -28136,7 +28139,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G928" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -28162,7 +28165,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G929" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -28188,7 +28191,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G930" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -28214,7 +28217,7 @@
         <v>20</v>
       </c>
       <c r="G931" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -28240,7 +28243,7 @@
         <v>20</v>
       </c>
       <c r="G932" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -28266,7 +28269,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G933" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -28292,7 +28295,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G934" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -28318,7 +28321,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G935" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -28344,7 +28347,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G936" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -28370,7 +28373,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G937" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -28396,7 +28399,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G938" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -28422,7 +28425,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G939" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -28448,7 +28451,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G940" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -28474,7 +28477,7 @@
         <v>21.25</v>
       </c>
       <c r="G941" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -28500,7 +28503,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G942" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -28526,7 +28529,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G943" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -28552,7 +28555,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G944" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -28578,7 +28581,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G945" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -28604,7 +28607,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G946" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -28630,7 +28633,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G947" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -28656,7 +28659,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G948" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -28682,7 +28685,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G949" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -28708,7 +28711,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G950" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -28734,7 +28737,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G951" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28760,7 +28763,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G952" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -28786,7 +28789,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G953" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28812,7 +28815,7 @@
         <v>21.25</v>
       </c>
       <c r="G954" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -28838,7 +28841,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G955" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28864,7 +28867,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28890,7 +28893,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G957" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28916,7 +28919,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G958" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28942,7 +28945,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G959" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28968,7 +28971,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G960" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28994,7 +28997,7 @@
         <v>21.25</v>
       </c>
       <c r="G961" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -29020,7 +29023,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G962" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -29046,7 +29049,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G963" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -29072,7 +29075,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G964" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -29098,7 +29101,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G965" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -29124,7 +29127,7 @@
         <v>21.5</v>
       </c>
       <c r="G966" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -29150,7 +29153,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G967" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -29176,7 +29179,7 @@
         <v>21.25</v>
       </c>
       <c r="G968" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -29202,7 +29205,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G969" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -29228,7 +29231,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G970" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -29254,7 +29257,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G971" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -29280,7 +29283,7 @@
         <v>21.5</v>
       </c>
       <c r="G972" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -29306,7 +29309,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G973" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -29332,7 +29335,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G974" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -29358,7 +29361,7 @@
         <v>21</v>
       </c>
       <c r="G975" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -29384,7 +29387,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G976" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -29410,7 +29413,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G977" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -29436,7 +29439,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G978" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -29462,7 +29465,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G979" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -29488,7 +29491,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G980" t="s">
-        <v>487</v>
+        <v>539</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -29514,7 +29517,7 @@
         <v>23</v>
       </c>
       <c r="G981" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -29540,7 +29543,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G982" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -29566,7 +29569,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G983" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -29592,7 +29595,7 @@
         <v>24</v>
       </c>
       <c r="G984" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -29618,7 +29621,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G985" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -29644,7 +29647,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G986" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -29670,7 +29673,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G987" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29696,7 +29699,7 @@
         <v>24</v>
       </c>
       <c r="G988" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29722,7 +29725,7 @@
         <v>24</v>
       </c>
       <c r="G989" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29748,7 +29751,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G990" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29774,7 +29777,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G991" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29800,7 +29803,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G992" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29826,7 +29829,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G993" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29852,7 +29855,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G994" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29878,7 +29881,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G995" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29904,7 +29907,7 @@
         <v>24.5</v>
       </c>
       <c r="G996" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29930,7 +29933,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G997" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29956,7 +29959,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G998" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29982,7 +29985,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G999" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -30008,7 +30011,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1000" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -30034,7 +30037,7 @@
         <v>23.25</v>
       </c>
       <c r="G1001" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -30060,7 +30063,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1002" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -30086,7 +30089,7 @@
         <v>23.5</v>
       </c>
       <c r="G1003" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -30112,7 +30115,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1004" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -30138,7 +30141,7 @@
         <v>23.75</v>
       </c>
       <c r="G1005" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -30164,7 +30167,7 @@
         <v>23.75</v>
       </c>
       <c r="G1006" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -30190,7 +30193,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1007" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -30216,7 +30219,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1008" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -30242,7 +30245,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1009" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -30268,7 +30271,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1010" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -30294,7 +30297,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1011" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -30320,7 +30323,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1012" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -30346,7 +30349,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1013" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -30372,7 +30375,7 @@
         <v>24.25</v>
       </c>
       <c r="G1014" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -30398,7 +30401,7 @@
         <v>24</v>
       </c>
       <c r="G1015" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -30424,7 +30427,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1016" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -30450,7 +30453,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1017" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -30476,7 +30479,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1018" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -30502,7 +30505,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1019" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -30528,7 +30531,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1020" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -30554,7 +30557,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1021" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -30580,7 +30583,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G1022" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -30606,7 +30609,7 @@
         <v>23.5</v>
       </c>
       <c r="G1023" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -30632,7 +30635,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1024" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -30658,7 +30661,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1025" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -30684,7 +30687,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1026" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -30710,7 +30713,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1027" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -30736,7 +30739,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1028" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30762,7 +30765,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1029" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30788,7 +30791,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1030" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30814,7 +30817,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1031" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30840,7 +30843,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1032" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30866,7 +30869,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1033" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -30892,7 +30895,7 @@
         <v>22.75</v>
       </c>
       <c r="G1034" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -30918,7 +30921,7 @@
         <v>23.25</v>
       </c>
       <c r="G1035" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -30944,7 +30947,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1036" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -30970,7 +30973,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1037" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -30996,7 +30999,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1038" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -31022,7 +31025,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1039" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -31048,7 +31051,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1040" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -31074,7 +31077,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1041" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -31100,7 +31103,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1042" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -31126,7 +31129,7 @@
         <v>23.75</v>
       </c>
       <c r="G1043" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -31152,7 +31155,7 @@
         <v>23.75</v>
       </c>
       <c r="G1044" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -31178,7 +31181,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1045" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -31204,7 +31207,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1046" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -31230,7 +31233,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1047" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -31256,7 +31259,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1048" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -31282,7 +31285,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1049" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -31308,7 +31311,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1050" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -31334,7 +31337,7 @@
         <v>23.25</v>
       </c>
       <c r="G1051" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -31360,7 +31363,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1052" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -31386,7 +31389,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1053" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -31412,7 +31415,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1054" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -31438,7 +31441,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1055" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -31464,7 +31467,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1056" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -31490,7 +31493,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -31516,7 +31519,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1058" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -31542,7 +31545,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1059" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -31568,7 +31571,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1060" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -31594,7 +31597,7 @@
         <v>20.75</v>
       </c>
       <c r="G1061" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -31620,7 +31623,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1062" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -31646,7 +31649,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1063" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -31672,7 +31675,7 @@
         <v>19.5</v>
       </c>
       <c r="G1064" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -31698,7 +31701,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1065" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31724,7 +31727,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1066" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31750,7 +31753,7 @@
         <v>18</v>
       </c>
       <c r="G1067" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31776,7 +31779,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1068" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31802,7 +31805,7 @@
         <v>17</v>
       </c>
       <c r="G1069" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -31828,7 +31831,7 @@
         <v>17</v>
       </c>
       <c r="G1070" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -31854,7 +31857,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1071" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31880,7 +31883,7 @@
         <v>17.5</v>
       </c>
       <c r="G1072" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31906,7 +31909,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1073" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -31932,7 +31935,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1074" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -31958,7 +31961,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1075" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31984,7 +31987,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1076" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -32010,7 +32013,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1077" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -32036,7 +32039,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1078" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -32062,7 +32065,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1079" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -32088,7 +32091,7 @@
         <v>14</v>
       </c>
       <c r="G1080" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -32114,7 +32117,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1081" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -32140,7 +32143,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1082" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -32166,7 +32169,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1083" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -32192,7 +32195,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1084" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -32218,7 +32221,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1085" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32244,7 +32247,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1086" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -32270,7 +32273,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1087" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -32296,7 +32299,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1088" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -32322,7 +32325,7 @@
         <v>15</v>
       </c>
       <c r="G1089" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -32348,7 +32351,7 @@
         <v>15.5</v>
       </c>
       <c r="G1090" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -32374,7 +32377,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1091" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -32400,7 +32403,7 @@
         <v>15.25</v>
       </c>
       <c r="G1092" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -32426,7 +32429,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1093" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -32452,7 +32455,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1094" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -32478,7 +32481,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1095" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -32504,7 +32507,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1096" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -32530,7 +32533,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1097" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -32556,7 +32559,7 @@
         <v>15</v>
       </c>
       <c r="G1098" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -32582,7 +32585,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1099" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -32608,7 +32611,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1100" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -32634,7 +32637,7 @@
         <v>15</v>
       </c>
       <c r="G1101" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -32660,7 +32663,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1102" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -32686,7 +32689,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1103" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -32712,7 +32715,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1104" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32738,7 +32741,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1105" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -32764,7 +32767,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1106" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32790,7 +32793,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1107" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32816,7 +32819,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1108" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32842,7 +32845,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1109" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32868,7 +32871,7 @@
         <v>13.75</v>
       </c>
       <c r="G1110" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32894,7 +32897,7 @@
         <v>14</v>
       </c>
       <c r="G1111" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32920,7 +32923,7 @@
         <v>14</v>
       </c>
       <c r="G1112" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32946,7 +32949,7 @@
         <v>14.5</v>
       </c>
       <c r="G1113" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32972,7 +32975,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1114" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -32998,7 +33001,7 @@
         <v>15</v>
       </c>
       <c r="G1115" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -33024,7 +33027,7 @@
         <v>15.75</v>
       </c>
       <c r="G1116" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -33050,7 +33053,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1117" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -33076,7 +33079,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1118" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -33102,7 +33105,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1119" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -33128,7 +33131,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1120" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -33154,7 +33157,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1121" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -33180,7 +33183,7 @@
         <v>17</v>
       </c>
       <c r="G1122" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -33206,7 +33209,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1123" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -33232,7 +33235,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1124" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -33258,7 +33261,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1125" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -33284,7 +33287,7 @@
         <v>17.5</v>
       </c>
       <c r="G1126" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -33310,7 +33313,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1127" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -33336,7 +33339,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1128" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -33362,7 +33365,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1129" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -33388,7 +33391,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1130" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -33414,7 +33417,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1131" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -33440,7 +33443,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1132" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -33466,7 +33469,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1133" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -33492,7 +33495,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1134" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -33518,7 +33521,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1135" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -33544,7 +33547,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1136" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -33570,7 +33573,7 @@
         <v>18</v>
       </c>
       <c r="G1137" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -33596,7 +33599,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1138" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -33622,7 +33625,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1139" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -33648,7 +33651,7 @@
         <v>17.5</v>
       </c>
       <c r="G1140" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -33674,7 +33677,7 @@
         <v>17</v>
       </c>
       <c r="G1141" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33700,7 +33703,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1142" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33726,7 +33729,7 @@
         <v>16.5</v>
       </c>
       <c r="G1143" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33752,7 +33755,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1144" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33778,7 +33781,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1145" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33804,7 +33807,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1146" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33830,7 +33833,7 @@
         <v>17.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33856,7 +33859,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1148" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33882,7 +33885,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1149" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33908,7 +33911,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1150" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33934,7 +33937,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1151" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33960,7 +33963,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1152" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33986,7 +33989,7 @@
         <v>17.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -34012,7 +34015,7 @@
         <v>17</v>
       </c>
       <c r="G1154" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -34038,7 +34041,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1155" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -34064,7 +34067,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1156" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -34090,7 +34093,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1157" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -34116,7 +34119,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1158" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -34142,7 +34145,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1159" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -34168,7 +34171,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1160" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -34194,7 +34197,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1161" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -34220,7 +34223,7 @@
         <v>16.5</v>
       </c>
       <c r="G1162" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -34246,7 +34249,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1163" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -34272,7 +34275,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1164" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -34298,7 +34301,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1165" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -34324,7 +34327,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1166" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -34350,7 +34353,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1167" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -34376,7 +34379,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1168" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -34402,7 +34405,7 @@
         <v>17.25</v>
       </c>
       <c r="G1169" t="s">
-        <v>638</v>
+        <v>612</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34428,7 +34431,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1170" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -34454,7 +34457,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1171" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -34480,7 +34483,7 @@
         <v>17</v>
       </c>
       <c r="G1172" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -34506,7 +34509,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1173" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -34532,7 +34535,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1174" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -34558,7 +34561,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1175" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -34584,7 +34587,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -34610,7 +34613,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1177" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34636,7 +34639,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1178" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -34662,7 +34665,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1179" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34688,7 +34691,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1180" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34714,7 +34717,7 @@
         <v>17</v>
       </c>
       <c r="G1181" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34740,7 +34743,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1182" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34766,7 +34769,7 @@
         <v>17</v>
       </c>
       <c r="G1183" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34792,7 +34795,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1184" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34818,7 +34821,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1185" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34844,7 +34847,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1186" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34870,7 +34873,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1187" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34896,7 +34899,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1188" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34922,7 +34925,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1189" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34948,7 +34951,7 @@
         <v>17.25</v>
       </c>
       <c r="G1190" t="s">
-        <v>638</v>
+        <v>612</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34974,7 +34977,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1191" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -35000,7 +35003,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1192" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -35026,7 +35029,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1193" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -35052,7 +35055,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1194" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -35078,7 +35081,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1195" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -35104,7 +35107,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1196" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -35130,7 +35133,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1197" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35156,7 +35159,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -35182,7 +35185,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1199" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35208,7 +35211,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1200" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -35234,7 +35237,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1201" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -35260,7 +35263,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1202" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -35286,7 +35289,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1203" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -35312,7 +35315,7 @@
         <v>16</v>
       </c>
       <c r="G1204" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -35338,7 +35341,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1205" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -35364,7 +35367,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1206" t="s">
-        <v>642</v>
+        <v>578</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35390,7 +35393,7 @@
         <v>16</v>
       </c>
       <c r="G1207" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -35416,7 +35419,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1208" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -35468,7 +35471,7 @@
         <v>16.5</v>
       </c>
       <c r="G1210" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -35494,7 +35497,7 @@
         <v>16.5</v>
       </c>
       <c r="G1211" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -35520,7 +35523,7 @@
         <v>17.25</v>
       </c>
       <c r="G1212" t="s">
-        <v>638</v>
+        <v>612</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -35546,7 +35549,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1213" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -35572,7 +35575,7 @@
         <v>17</v>
       </c>
       <c r="G1214" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -35598,7 +35601,7 @@
         <v>17.25</v>
       </c>
       <c r="G1215" t="s">
-        <v>638</v>
+        <v>612</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35624,7 +35627,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1216" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35650,7 +35653,7 @@
         <v>17</v>
       </c>
       <c r="G1217" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -35676,7 +35679,7 @@
         <v>17</v>
       </c>
       <c r="G1218" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35702,7 +35705,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1219" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35728,7 +35731,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1220" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35754,7 +35757,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1221" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35780,7 +35783,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1222" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35858,7 +35861,7 @@
         <v>16</v>
       </c>
       <c r="G1225" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -36066,7 +36069,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -36118,7 +36121,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1235" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -36144,7 +36147,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1236" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -36170,7 +36173,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1237" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -38536,7 +38539,7 @@
         <v>23</v>
       </c>
       <c r="G1328" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -39238,7 +39241,7 @@
         <v>23</v>
       </c>
       <c r="G1355" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39264,7 +39267,7 @@
         <v>23</v>
       </c>
       <c r="G1356" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -39290,7 +39293,7 @@
         <v>23</v>
       </c>
       <c r="G1357" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39316,7 +39319,7 @@
         <v>23</v>
       </c>
       <c r="G1358" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39368,7 +39371,7 @@
         <v>23</v>
       </c>
       <c r="G1360" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -70290,7 +70293,7 @@
     </row>
     <row r="2550">
       <c r="A2550" s="1" t="n">
-        <v>46036.6909953704</v>
+        <v>46036.3333333333</v>
       </c>
       <c r="B2550" t="n">
         <v>6345</v>
@@ -70311,6 +70314,32 @@
         <v>1201</v>
       </c>
       <c r="H2550" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2551">
+      <c r="A2551" s="1" t="n">
+        <v>46037.6911342593</v>
+      </c>
+      <c r="B2551" t="n">
+        <v>5683</v>
+      </c>
+      <c r="C2551" t="n">
+        <v>67.5999984741211</v>
+      </c>
+      <c r="D2551" t="n">
+        <v>65.6999969482422</v>
+      </c>
+      <c r="E2551" t="n">
+        <v>66.3000030517578</v>
+      </c>
+      <c r="F2551" t="n">
+        <v>67.0999984741211</v>
+      </c>
+      <c r="G2551" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H2551" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="1225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="1226">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23958683013916</t>
+    <t xml:space="preserve">9.23958778381348</t>
   </si>
   <si>
     <t xml:space="preserve">CMB.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55656719207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31377506256104</t>
+    <t xml:space="preserve">9.55656814575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31377410888672</t>
   </si>
   <si>
     <t xml:space="preserve">9.40144920349121</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">9.44191455841064</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36098384857178</t>
+    <t xml:space="preserve">9.36098575592041</t>
   </si>
   <si>
     <t xml:space="preserve">9.13842487335205</t>
@@ -68,64 +68,64 @@
     <t xml:space="preserve">9.32051849365234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26656627655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34075164794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27331066131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19237899780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19912338256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10470485687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84167861938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77423667907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84842395782471</t>
+    <t xml:space="preserve">9.26656436920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3407506942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27330875396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19237995147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19912242889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10470294952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84167766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77423858642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84842300415039</t>
   </si>
   <si>
     <t xml:space="preserve">8.36283874511719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3291187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61912059783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45051383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4302806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63260650634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80121326446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22609901428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25982189178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07098293304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87540054321289</t>
+    <t xml:space="preserve">8.32911777496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61911869049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45051288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43027973175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63260746002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80121421813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22610092163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25982093811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0709810256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87539958953857</t>
   </si>
   <si>
     <t xml:space="preserve">8.96981906890869</t>
@@ -134,25 +134,25 @@
     <t xml:space="preserve">8.71353816986084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6663293838501</t>
+    <t xml:space="preserve">8.66632843017578</t>
   </si>
   <si>
     <t xml:space="preserve">8.89563274383545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8147029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99679660797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01028347015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90237712860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97656440734863</t>
+    <t xml:space="preserve">8.81470108032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99679756164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01028251647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90237617492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97656345367432</t>
   </si>
   <si>
     <t xml:space="preserve">9.18563461303711</t>
@@ -170,16 +170,16 @@
     <t xml:space="preserve">9.25307655334473</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15865802764893</t>
+    <t xml:space="preserve">9.15865612030029</t>
   </si>
   <si>
     <t xml:space="preserve">9.08447074890137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16540050506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98330688476562</t>
+    <t xml:space="preserve">9.16540145874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98330593109131</t>
   </si>
   <si>
     <t xml:space="preserve">8.78772449493408</t>
@@ -188,28 +188,28 @@
     <t xml:space="preserve">8.78098106384277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1249361038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03726005554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21261119842529</t>
+    <t xml:space="preserve">9.12493515014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03726100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21261024475098</t>
   </si>
   <si>
     <t xml:space="preserve">9.04400539398193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09796047210693</t>
+    <t xml:space="preserve">9.0979585647583</t>
   </si>
   <si>
     <t xml:space="preserve">9.20586585998535</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38121700286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28679847717285</t>
+    <t xml:space="preserve">9.38121604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28679752349854</t>
   </si>
   <si>
     <t xml:space="preserve">9.22100830078125</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">9.22798919677734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19308757781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35363483428955</t>
+    <t xml:space="preserve">9.19308662414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35363292694092</t>
   </si>
   <si>
     <t xml:space="preserve">9.40947723388672</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">9.52116298675537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49324226379395</t>
+    <t xml:space="preserve">9.49324131011963</t>
   </si>
   <si>
     <t xml:space="preserve">9.38853645324707</t>
@@ -239,46 +239,46 @@
     <t xml:space="preserve">9.94696140289307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76547336578369</t>
+    <t xml:space="preserve">9.76547241210938</t>
   </si>
   <si>
     <t xml:space="preserve">9.77245330810547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66774940490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82829570770264</t>
+    <t xml:space="preserve">9.66774845123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82829666137695</t>
   </si>
   <si>
     <t xml:space="preserve">9.75151348114014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57002258300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57700443267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55606365203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47928142547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42343807220459</t>
+    <t xml:space="preserve">9.57002449035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57700538635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55606269836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47928047180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42343711853027</t>
   </si>
   <si>
     <t xml:space="preserve">9.39551544189453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41645812988281</t>
+    <t xml:space="preserve">9.41645622253418</t>
   </si>
   <si>
     <t xml:space="preserve">9.34665393829346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.583984375</t>
+    <t xml:space="preserve">9.58398532867432</t>
   </si>
   <si>
     <t xml:space="preserve">9.62586688995361</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">9.46531963348389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48626136779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59096527099609</t>
+    <t xml:space="preserve">9.48626041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59096431732178</t>
   </si>
   <si>
     <t xml:space="preserve">9.56304359436035</t>
@@ -302,19 +302,19 @@
     <t xml:space="preserve">9.53512287139893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1232852935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30477237701416</t>
+    <t xml:space="preserve">9.12328338623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30477142333984</t>
   </si>
   <si>
     <t xml:space="preserve">9.28383159637451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20704746246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27685165405273</t>
+    <t xml:space="preserve">9.2070484161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27685070037842</t>
   </si>
   <si>
     <t xml:space="preserve">9.36061477661133</t>
@@ -326,52 +326,52 @@
     <t xml:space="preserve">9.29779243469238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31873226165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36759471893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47230052947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52814197540283</t>
+    <t xml:space="preserve">9.31873321533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36759376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47229957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52814102172852</t>
   </si>
   <si>
     <t xml:space="preserve">9.5072021484375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44437885284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50022125244141</t>
+    <t xml:space="preserve">9.44437789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50022029876709</t>
   </si>
   <si>
     <t xml:space="preserve">9.33269309997559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32571315765381</t>
+    <t xml:space="preserve">9.32571220397949</t>
   </si>
   <si>
     <t xml:space="preserve">9.13724517822266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14422512054443</t>
+    <t xml:space="preserve">9.14422416687012</t>
   </si>
   <si>
     <t xml:space="preserve">9.15120506286621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10932350158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03952026367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92783355712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01159858703613</t>
+    <t xml:space="preserve">9.1093225479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03951930999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92783546447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01159763336182</t>
   </si>
   <si>
     <t xml:space="preserve">9.07442092895508</t>
@@ -383,37 +383,37 @@
     <t xml:space="preserve">8.86501121520996</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85105037689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.934814453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92085552215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95575618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96971607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00461959838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91387462615967</t>
+    <t xml:space="preserve">8.85105228424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93481540679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92085361480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95575523376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9697151184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00461864471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91387557983398</t>
   </si>
   <si>
     <t xml:space="preserve">8.87897205352783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80916881561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59975910186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56485748291016</t>
+    <t xml:space="preserve">8.80916976928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59975814819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56485843658447</t>
   </si>
   <si>
     <t xml:space="preserve">8.81614875793457</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">8.83709049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8999137878418</t>
+    <t xml:space="preserve">8.89991283416748</t>
   </si>
   <si>
     <t xml:space="preserve">8.99763679504395</t>
@@ -431,49 +431,49 @@
     <t xml:space="preserve">8.83010959625244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96273612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08838272094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04650020599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09536266326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66076850891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64680767059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70264911651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79339408874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92602157592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98186302185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.051664352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4146432876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.19127368927</t>
+    <t xml:space="preserve">8.96273708343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08838176727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04649925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09536361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66076946258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64680862426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70265007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79339599609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92602062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9818639755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0516662597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4146451950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1912746429443</t>
   </si>
   <si>
     <t xml:space="preserve">10.2471160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1493911743164</t>
+    <t xml:space="preserve">10.1493902206421</t>
   </si>
   <si>
     <t xml:space="preserve">10.1354312896729</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">10.393702507019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5402889251709</t>
+    <t xml:space="preserve">10.5402898788452</t>
   </si>
   <si>
     <t xml:space="preserve">10.5891523361206</t>
@@ -494,16 +494,16 @@
     <t xml:space="preserve">10.484447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6310338973999</t>
+    <t xml:space="preserve">10.6310329437256</t>
   </si>
   <si>
     <t xml:space="preserve">10.3588008880615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98884391784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95394229888916</t>
+    <t xml:space="preserve">9.98884296417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95394325256348</t>
   </si>
   <si>
     <t xml:space="preserve">10.1005296707153</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">10.3867225646973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5472688674927</t>
+    <t xml:space="preserve">10.547269821167</t>
   </si>
   <si>
     <t xml:space="preserve">10.3448400497437</t>
@@ -524,34 +524,34 @@
     <t xml:space="preserve">10.4774675369263</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4006814956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.435583114624</t>
+    <t xml:space="preserve">10.4006834030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4355821609497</t>
   </si>
   <si>
     <t xml:space="preserve">10.3727607727051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3657817840576</t>
+    <t xml:space="preserve">10.3657808303833</t>
   </si>
   <si>
     <t xml:space="preserve">10.3378610610962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2820167541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3797426223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6100931167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5542488098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6938571929932</t>
+    <t xml:space="preserve">10.2820177078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3797416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6100921630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5542497634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6938562393188</t>
   </si>
   <si>
     <t xml:space="preserve">11.0917348861694</t>
@@ -560,22 +560,22 @@
     <t xml:space="preserve">11.0428714752197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0358915328979</t>
+    <t xml:space="preserve">11.0358934402466</t>
   </si>
   <si>
     <t xml:space="preserve">11.0638132095337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.084755897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3569860458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5175342559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0899229049683</t>
+    <t xml:space="preserve">11.0847549438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.356987953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5175361633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0899219512939</t>
   </si>
   <si>
     <t xml:space="preserve">11.9991769790649</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">12.0689811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1038818359375</t>
+    <t xml:space="preserve">12.1038827896118</t>
   </si>
   <si>
     <t xml:space="preserve">12.2853708267212</t>
@@ -605,76 +605,76 @@
     <t xml:space="preserve">13.1090488433838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.123007774353</t>
+    <t xml:space="preserve">13.1230096817017</t>
   </si>
   <si>
     <t xml:space="preserve">12.8926591873169</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9135999679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8437976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9624624252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1928129196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.39524269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8978261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9815893173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9327259063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0234699249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0304517745972</t>
+    <t xml:space="preserve">12.9135990142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8437957763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9624614715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1928119659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3952436447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8978242874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9815883636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9327239990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0234708786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0304508209229</t>
   </si>
   <si>
     <t xml:space="preserve">14.1351566314697</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0723333358765</t>
+    <t xml:space="preserve">14.0723314285278</t>
   </si>
   <si>
     <t xml:space="preserve">14.0025300979614</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2112531661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197374343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1461639404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0810747146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.994291305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6688423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3558988571167</t>
+    <t xml:space="preserve">14.2112550735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197393417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1461658477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.081075668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9942893981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6688404083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3559007644653</t>
   </si>
   <si>
     <t xml:space="preserve">13.6833057403564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.001522064209</t>
+    <t xml:space="preserve">14.0015230178833</t>
   </si>
   <si>
     <t xml:space="preserve">13.9870586395264</t>
@@ -686,67 +686,67 @@
     <t xml:space="preserve">14.348669052124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3414354324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2763442993164</t>
+    <t xml:space="preserve">14.3414363861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.276346206665</t>
   </si>
   <si>
     <t xml:space="preserve">14.42822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5656328201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3322458267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8457326889038</t>
+    <t xml:space="preserve">14.565634727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3322448730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8457317352295</t>
   </si>
   <si>
     <t xml:space="preserve">15.7589464187622</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3611755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1876001358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9200105667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6307210922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636749267578</t>
+    <t xml:space="preserve">15.3611745834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1876049041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9200115203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6307220458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636768341064</t>
   </si>
   <si>
     <t xml:space="preserve">15.3105506896973</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9272422790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0718879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5492105484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4551944732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2671585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1731367111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8332233428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1369781494141</t>
+    <t xml:space="preserve">14.9272441864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0718860626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5492115020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4551935195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2671527862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1731386184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8332242965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1369762420654</t>
   </si>
   <si>
     <t xml:space="preserve">15.1152801513672</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">15.1514406204224</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0284938812256</t>
+    <t xml:space="preserve">15.0284948348999</t>
   </si>
   <si>
     <t xml:space="preserve">15.2092981338501</t>
@@ -767,46 +767,46 @@
     <t xml:space="preserve">15.664924621582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6938552856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7661771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9325189590454</t>
+    <t xml:space="preserve">15.6938562393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7661781311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9325180053711</t>
   </si>
   <si>
     <t xml:space="preserve">16.0410003662109</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9469795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6432294845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2816181182861</t>
+    <t xml:space="preserve">15.9469814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6432304382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2816200256348</t>
   </si>
   <si>
     <t xml:space="preserve">15.2888517379761</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2599229812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3250141143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2382259368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1586751937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0574245452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1803693771362</t>
+    <t xml:space="preserve">15.2599220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3250102996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2382287979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1586713790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0574226379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1803703308105</t>
   </si>
   <si>
     <t xml:space="preserve">15.2454595565796</t>
@@ -815,91 +815,91 @@
     <t xml:space="preserve">14.8983125686646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.869384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8259925842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9634037017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9706354141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6813468933105</t>
+    <t xml:space="preserve">14.8693857192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8259935379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9634046554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9706373214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6813488006592</t>
   </si>
   <si>
     <t xml:space="preserve">14.7536697387695</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6958141326904</t>
+    <t xml:space="preserve">14.6958131790161</t>
   </si>
   <si>
     <t xml:space="preserve">14.8910808563232</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4933109283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8549213409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6524181365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6090269088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8476905822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1948356628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3394765853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4334964752197</t>
+    <t xml:space="preserve">14.493311882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.854923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6524200439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6090278625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8476886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1948337554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3394784927368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4334955215454</t>
   </si>
   <si>
     <t xml:space="preserve">16.2651977539062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9956493377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5742244720459</t>
+    <t xml:space="preserve">16.9956512451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5742263793945</t>
   </si>
   <si>
     <t xml:space="preserve">18.6879825592041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3986949920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4420871734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2178936004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0804805755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1889610290527</t>
+    <t xml:space="preserve">18.3986968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4420890808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2178916931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0804786682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1889572143555</t>
   </si>
   <si>
     <t xml:space="preserve">17.9719944000244</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0081577301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8562812805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9647655487061</t>
+    <t xml:space="preserve">18.0081539154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8562831878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9647636413574</t>
   </si>
   <si>
     <t xml:space="preserve">17.6393146514893</t>
@@ -914,16 +914,16 @@
     <t xml:space="preserve">17.5886878967285</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5380630493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5019035339355</t>
+    <t xml:space="preserve">17.538064956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5019054412842</t>
   </si>
   <si>
     <t xml:space="preserve">17.3861885070801</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3210983276367</t>
+    <t xml:space="preserve">17.321102142334</t>
   </si>
   <si>
     <t xml:space="preserve">17.2849369049072</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">17.0462741851807</t>
   </si>
   <si>
-    <t xml:space="preserve">17.263240814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0968971252441</t>
+    <t xml:space="preserve">17.2632427215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0969009399414</t>
   </si>
   <si>
     <t xml:space="preserve">17.3283290863037</t>
@@ -944,13 +944,13 @@
     <t xml:space="preserve">17.3572597503662</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4006500244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3789539337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2921676635742</t>
+    <t xml:space="preserve">17.4006538391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3789577484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2921695709229</t>
   </si>
   <si>
     <t xml:space="preserve">17.342794418335</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">17.1692199707031</t>
   </si>
   <si>
-    <t xml:space="preserve">16.590648651123</t>
+    <t xml:space="preserve">16.5906467437744</t>
   </si>
   <si>
     <t xml:space="preserve">16.6268081665039</t>
@@ -968,49 +968,49 @@
     <t xml:space="preserve">16.9233264923096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3447532653809</t>
+    <t xml:space="preserve">16.3447513580322</t>
   </si>
   <si>
     <t xml:space="preserve">15.7083206176758</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1133251190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9180545806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.650463104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4749355316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3013610839844</t>
+    <t xml:space="preserve">16.1133213043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9180517196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6504611968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4749336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3013591766357</t>
   </si>
   <si>
     <t xml:space="preserve">16.5761814117432</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5110950469971</t>
+    <t xml:space="preserve">16.5110931396484</t>
   </si>
   <si>
     <t xml:space="preserve">16.5617179870605</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0699310302734</t>
+    <t xml:space="preserve">16.0699291229248</t>
   </si>
   <si>
     <t xml:space="preserve">16.5255584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4098453521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2073440551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8746585845947</t>
+    <t xml:space="preserve">16.4098415374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2073402404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8746614456177</t>
   </si>
   <si>
     <t xml:space="preserve">16.2435035705566</t>
@@ -1028,34 +1028,34 @@
     <t xml:space="preserve">15.8601961135864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8529653549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6287660598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4696569442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4624261856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6215324401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9976100921631</t>
+    <t xml:space="preserve">15.8529644012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6287670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.469654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4624242782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6215353012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9976110458374</t>
   </si>
   <si>
     <t xml:space="preserve">16.236270904541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1639499664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2724304199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7786846160889</t>
+    <t xml:space="preserve">16.1639461517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2724323272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7786865234375</t>
   </si>
   <si>
     <t xml:space="preserve">16.6340408325195</t>
@@ -1064,40 +1064,40 @@
     <t xml:space="preserve">16.4532375335693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7425231933594</t>
+    <t xml:space="preserve">16.7425212860107</t>
   </si>
   <si>
     <t xml:space="preserve">16.5978813171387</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7063636779785</t>
+    <t xml:space="preserve">16.7063617706299</t>
   </si>
   <si>
     <t xml:space="preserve">16.8510055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.031810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2126140594482</t>
+    <t xml:space="preserve">17.0318126678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2126178741455</t>
   </si>
   <si>
     <t xml:space="preserve">17.4295825958252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9594898223877</t>
+    <t xml:space="preserve">16.9594917297363</t>
   </si>
   <si>
     <t xml:space="preserve">16.3809146881104</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9831399917603</t>
+    <t xml:space="preserve">15.9831447601318</t>
   </si>
   <si>
     <t xml:space="preserve">15.9108200073242</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7300157546997</t>
+    <t xml:space="preserve">15.730016708374</t>
   </si>
   <si>
     <t xml:space="preserve">15.368408203125</t>
@@ -1106,70 +1106,70 @@
     <t xml:space="preserve">15.4045677185059</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4768905639648</t>
+    <t xml:space="preserve">15.4768896102905</t>
   </si>
   <si>
     <t xml:space="preserve">15.8023386001587</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6702003479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1402969360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1041355133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8148441314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0679740905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8871650695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8273525238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6827068328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3934211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2487773895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7550277709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8996753692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5867328643799</t>
+    <t xml:space="preserve">16.670202255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1402950286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1041316986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8148460388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0679721832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8871669769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8273506164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.682710647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3934192657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2487754821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7550296783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8996734619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5867309570312</t>
   </si>
   <si>
     <t xml:space="preserve">18.6590538024902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0206642150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5428009033203</t>
+    <t xml:space="preserve">19.0206623077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5427989959717</t>
   </si>
   <si>
     <t xml:space="preserve">19.2444362640381</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9157524108887</t>
+    <t xml:space="preserve">19.9157543182373</t>
   </si>
   <si>
     <t xml:space="preserve">20.4378890991211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6546878814697</t>
+    <t xml:space="preserve">19.6546859741211</t>
   </si>
   <si>
     <t xml:space="preserve">19.4682102203369</t>
@@ -1184,13 +1184,13 @@
     <t xml:space="preserve">18.8714809417725</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9460697174072</t>
+    <t xml:space="preserve">18.9460735321045</t>
   </si>
   <si>
     <t xml:space="preserve">18.7968921661377</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9018001556396</t>
+    <t xml:space="preserve">17.9018020629883</t>
   </si>
   <si>
     <t xml:space="preserve">17.3050746917725</t>
@@ -1211,22 +1211,22 @@
     <t xml:space="preserve">19.5055046081543</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8038673400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8784599304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6919822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3190269470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4239368438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1325511932373</t>
+    <t xml:space="preserve">19.8038654327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8784580230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6919803619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3190231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4239349365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.13254737854</t>
   </si>
   <si>
     <t xml:space="preserve">19.3563232421875</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">19.7292766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7223014831543</t>
+    <t xml:space="preserve">18.7222995758057</t>
   </si>
   <si>
     <t xml:space="preserve">18.9087753295898</t>
@@ -1250,28 +1250,28 @@
     <t xml:space="preserve">18.5358238220215</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9763946533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1255722045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4612350463867</t>
+    <t xml:space="preserve">17.9763927459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1255741119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4612331390381</t>
   </si>
   <si>
     <t xml:space="preserve">18.7595958709717</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6104145050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3493480682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6850051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.312047958374</t>
+    <t xml:space="preserve">18.6104125976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.34934425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6850032806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3120517730713</t>
   </si>
   <si>
     <t xml:space="preserve">18.4985275268555</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">19.2817325592041</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0579605102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1628684997559</t>
+    <t xml:space="preserve">19.0579586029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1628704071045</t>
   </si>
   <si>
     <t xml:space="preserve">18.0136890411377</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">18.3866424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1558933258057</t>
+    <t xml:space="preserve">17.155891418457</t>
   </si>
   <si>
     <t xml:space="preserve">16.1862125396729</t>
@@ -1301,19 +1301,19 @@
     <t xml:space="preserve">15.589485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1419401168823</t>
+    <t xml:space="preserve">15.141942024231</t>
   </si>
   <si>
     <t xml:space="preserve">14.9554634094238</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0370311737061</t>
+    <t xml:space="preserve">16.0370292663574</t>
   </si>
   <si>
     <t xml:space="preserve">16.5218696594238</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6640748977661</t>
+    <t xml:space="preserve">15.6640777587891</t>
   </si>
   <si>
     <t xml:space="preserve">15.1046438217163</t>
@@ -1322,10 +1322,10 @@
     <t xml:space="preserve">14.9927597045898</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0300531387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7689847946167</t>
+    <t xml:space="preserve">15.0300540924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.768985748291</t>
   </si>
   <si>
     <t xml:space="preserve">14.3661947250366</t>
@@ -1334,64 +1334,64 @@
     <t xml:space="preserve">14.5153760910034</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6198034286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.888331413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2538270950317</t>
+    <t xml:space="preserve">14.6198053359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8883295059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2538261413574</t>
   </si>
   <si>
     <t xml:space="preserve">16.2608032226562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9251461029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7759628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7013692855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.552188873291</t>
+    <t xml:space="preserve">15.9251432418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7759618759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7013731002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5521898269653</t>
   </si>
   <si>
     <t xml:space="preserve">15.6267805099487</t>
   </si>
   <si>
-    <t xml:space="preserve">15.514892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2911233901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2165288925171</t>
+    <t xml:space="preserve">15.5148944854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2911214828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2165307998657</t>
   </si>
   <si>
     <t xml:space="preserve">15.1792364120483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8505544662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8132600784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0743255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8878488540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4030084609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.903247833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7093114852905</t>
+    <t xml:space="preserve">15.8505525588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8132591247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0743274688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8878479003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4030094146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9032497406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7093124389648</t>
   </si>
   <si>
     <t xml:space="preserve">15.4403047561646</t>
@@ -1406,52 +1406,52 @@
     <t xml:space="preserve">16.5591678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3726902008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4845752716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7829399108887</t>
+    <t xml:space="preserve">16.3726921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4845771789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.78293800354</t>
   </si>
   <si>
     <t xml:space="preserve">16.8948249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7386665344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657131195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8435754776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8584957122803</t>
+    <t xml:space="preserve">15.7386684417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657121658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8435745239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8584976196289</t>
   </si>
   <si>
     <t xml:space="preserve">15.0673513412476</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8734130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9181690216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4099864959717</t>
+    <t xml:space="preserve">14.8734140396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9181671142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.409984588623</t>
   </si>
   <si>
     <t xml:space="preserve">16.2235069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2980976104736</t>
+    <t xml:space="preserve">16.2980995178223</t>
   </si>
   <si>
     <t xml:space="preserve">16.6710529327393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7083473205566</t>
+    <t xml:space="preserve">16.7083492279053</t>
   </si>
   <si>
     <t xml:space="preserve">16.7456436157227</t>
@@ -1463,22 +1463,22 @@
     <t xml:space="preserve">16.9321231842041</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8575305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0067119598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3796653747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2304840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5288467407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.343240737915</t>
+    <t xml:space="preserve">16.8575286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0067100524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3796634674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2304859161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5288486480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3432388305664</t>
   </si>
   <si>
     <t xml:space="preserve">17.7227516174316</t>
@@ -1496,13 +1496,13 @@
     <t xml:space="preserve">16.0939655303955</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6673755645752</t>
+    <t xml:space="preserve">15.6673784255981</t>
   </si>
   <si>
     <t xml:space="preserve">15.6285972595215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0468854904175</t>
+    <t xml:space="preserve">15.0468883514404</t>
   </si>
   <si>
     <t xml:space="preserve">15.2640600204468</t>
@@ -1511,28 +1511,28 @@
     <t xml:space="preserve">15.7061567306519</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5898151397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5122537612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7449388504028</t>
+    <t xml:space="preserve">15.5898160934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5122528076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7449398040771</t>
   </si>
   <si>
     <t xml:space="preserve">15.2950820922852</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0158634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1864967346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4191789627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4967432022095</t>
+    <t xml:space="preserve">15.0158624649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1864957809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4191818237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4967393875122</t>
   </si>
   <si>
     <t xml:space="preserve">15.5510339736938</t>
@@ -1541,16 +1541,16 @@
     <t xml:space="preserve">15.3261079788208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2795734405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8612804412842</t>
+    <t xml:space="preserve">15.2795715332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8612785339355</t>
   </si>
   <si>
     <t xml:space="preserve">16.0164012908936</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9388399124146</t>
+    <t xml:space="preserve">15.9388418197632</t>
   </si>
   <si>
     <t xml:space="preserve">15.9000616073608</t>
@@ -1559,55 +1559,55 @@
     <t xml:space="preserve">15.7837190628052</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8225002288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3266468048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7920169830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0247020721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9083576202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4817714691162</t>
+    <t xml:space="preserve">15.8224992752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3266487121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7920150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0247001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9083557128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4817695617676</t>
   </si>
   <si>
     <t xml:space="preserve">16.5593318939209</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0551815032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4042091369629</t>
+    <t xml:space="preserve">16.0551853179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4042072296143</t>
   </si>
   <si>
     <t xml:space="preserve">16.1327438354492</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2878684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1715259552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9776220321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3881568908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346942901611</t>
+    <t xml:space="preserve">16.2878665924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1715240478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9776210784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3881578445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346933364868</t>
   </si>
   <si>
     <t xml:space="preserve">16.2103061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4429893493652</t>
+    <t xml:space="preserve">16.4429931640625</t>
   </si>
   <si>
     <t xml:space="preserve">16.5981121063232</t>
@@ -1616,25 +1616,25 @@
     <t xml:space="preserve">16.5205497741699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6368942260742</t>
+    <t xml:space="preserve">16.6368923187256</t>
   </si>
   <si>
     <t xml:space="preserve">16.2490863800049</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8307952880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9859199523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8390941619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5676250457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9942150115967</t>
+    <t xml:space="preserve">16.8307991027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9859180450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8390922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.567626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9942169189453</t>
   </si>
   <si>
     <t xml:space="preserve">18.6147041320801</t>
@@ -1643,472 +1643,475 @@
     <t xml:space="preserve">18.2656803131104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8473892211914</t>
+    <t xml:space="preserve">18.8473873138428</t>
   </si>
   <si>
     <t xml:space="preserve">18.5371437072754</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0717754364014</t>
+    <t xml:space="preserve">18.0717735290527</t>
   </si>
   <si>
     <t xml:space="preserve">18.4595813751221</t>
   </si>
   <si>
+    <t xml:space="preserve">18.7698287963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9249515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1576347351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0025119781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0412921905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3044605255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1493396759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0329971313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2268981933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.420804977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.498363494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1105575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.683967590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8086090087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3820190429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.188117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.916654586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9554328918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.606409072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6451892852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.141040802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1022605895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.29616355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1244478225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7676687240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5577096939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9610280990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0302934646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1854162216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1388807296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.573221206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2629776000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.169903755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9527339935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5649271011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7582883834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5566291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8585786819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7810163497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3156490325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8197975158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1300430297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7893133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2546815872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9056568145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6341905593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0219974517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0607776641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8280935287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4790687561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7117528915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6729717254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5954103469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2851648330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4015073776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7505321502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9749193191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5095520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5871124267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6646738052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2463855743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2159004211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3710222244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0773706436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1181735992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0365686416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8733520507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8325481414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1997833251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6078224182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2813901901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4245090484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5469188690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5061149597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7509393692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9549589157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5262126922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7710380554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6894302368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3221960067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4038028717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5877237319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4653120040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6285285949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9141540527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2405872344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9957618713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1589784622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7917423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3837032318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2204885482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0773725509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3429002761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7101335525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0572710037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.138879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2612915039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0980749130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4860153198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8532514572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7308406829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6900358200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9756631851196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7716436386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8526468276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2606859207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.423903465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0767650604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9135503768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5055093765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6687269210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5871171951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3014898300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3830976486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3422918319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7503328323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2198829650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1790771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4647054672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3215885162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1583728790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8112354278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7089233398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1376705169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3824920654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8928470611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1991767883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.484806060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.648021697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5664138793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2399806976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4031982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7296295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2192764282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4641017913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5457077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9537487030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0353565216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9744529724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8721408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.11696434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1985721588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3617897033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1778659820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8514366149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6882209777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0962600708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6066112518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9330444335938</t>
+  </si>
+  <si>
     <t xml:space="preserve">18.7698268890381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9249515533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1576347351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0025119781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0412921905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3044605255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1493377685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.032995223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2268981933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4208011627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.498363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1105575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6839714050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8086090087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3820209503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1881198883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.916654586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9554328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6064109802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6451892852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1410427093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.102258682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.29616355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1244478225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7676668167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5577096939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9610280990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0302934646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1854152679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.138879776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5732221603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.262978553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1699028015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.952733039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5649261474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7582893371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5566282272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8585786819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7810173034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3156490325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8197965621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1300420761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7893142700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2546796798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9056558609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6341905593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0219964981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0607767105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8280935287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4790687561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7117538452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6729717254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5954103469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2851657867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4015064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7505321502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9749202728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5095529556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5871133804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6646747589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2463836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2159004211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3710222244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0773706436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1181735992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.036566734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8733501434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8325471878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.199782371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6078214645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2813901901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4245080947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5469198226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5061140060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7509393692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9549598693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5262145996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7710380554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6894292831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3221921920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4038038253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.587721824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4653120040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6285276412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.914155960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2405872344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9957637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1589794158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7917432785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3837032318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2204875946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3428993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7101345062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0572719573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1388788223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2612915039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0980749130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4860153198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8532514572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7308397293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.690034866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9756631851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7716436386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8526487350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.260687828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4238996505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0767688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9135494232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5055103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6687269210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5871171951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3014898300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3831005096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3422937393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7503356933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2198829650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1790781021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4647064208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3215885162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1583728790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8112373352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7089233398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1376705169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3824920654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.89284324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1991786956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4848041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.648021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5664138793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2399826049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4031963348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7296295166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2192764282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4640998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5457096099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9537467956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0353584289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9744529724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8721408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.11696434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1985721588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3617877960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1778659820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8514366149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6882190704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0962600708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6066131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9330444335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7698287963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2594757080078</t>
+    <t xml:space="preserve">19.2594738006592</t>
   </si>
   <si>
     <t xml:space="preserve">19.3410835266113</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4226894378662</t>
+    <t xml:space="preserve">19.4226913452148</t>
   </si>
   <si>
     <t xml:space="preserve">19.0146503448486</t>
@@ -2120,13 +2123,10 @@
     <t xml:space="preserve">19.8276062011719</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9123382568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4886741638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6581401824951</t>
+    <t xml:space="preserve">19.4886722564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6581420898438</t>
   </si>
   <si>
     <t xml:space="preserve">19.5734062194824</t>
@@ -2135,16 +2135,16 @@
     <t xml:space="preserve">19.403938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9970722198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3360061645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1665382385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.319206237793</t>
+    <t xml:space="preserve">19.9970741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3360080718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.166540145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3192043304443</t>
   </si>
   <si>
     <t xml:space="preserve">19.0650062561035</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">18.6413383483887</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7428722381592</t>
+    <t xml:space="preserve">19.7428703308105</t>
   </si>
   <si>
     <t xml:space="preserve">20.0818061828613</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">20.5054721832275</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6749401092529</t>
+    <t xml:space="preserve">20.6749382019043</t>
   </si>
   <si>
     <t xml:space="preserve">20.9291400909424</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">21.1833400726318</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7596740722656</t>
+    <t xml:space="preserve">20.759672164917</t>
   </si>
   <si>
     <t xml:space="preserve">21.4375381469727</t>
@@ -2192,10 +2192,10 @@
     <t xml:space="preserve">22.2001419067383</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6238098144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7932720184326</t>
+    <t xml:space="preserve">22.6238079071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7932739257812</t>
   </si>
   <si>
     <t xml:space="preserve">23.0474739074707</t>
@@ -2210,13 +2210,13 @@
     <t xml:space="preserve">23.3016719818115</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4711418151855</t>
+    <t xml:space="preserve">23.4711399078369</t>
   </si>
   <si>
     <t xml:space="preserve">23.3864078521729</t>
   </si>
   <si>
-    <t xml:space="preserve">23.725341796875</t>
+    <t xml:space="preserve">23.7253398895264</t>
   </si>
   <si>
     <t xml:space="preserve">23.1322059631348</t>
@@ -2225,31 +2225,31 @@
     <t xml:space="preserve">23.2169399261475</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9459381103516</t>
+    <t xml:space="preserve">21.9459400177002</t>
   </si>
   <si>
     <t xml:space="preserve">22.8780059814453</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1490058898926</t>
+    <t xml:space="preserve">24.1490077972412</t>
   </si>
   <si>
     <t xml:space="preserve">25.1658096313477</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9116058349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2337417602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2505397796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8100738525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5726737976074</t>
+    <t xml:space="preserve">24.9116077423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2337398529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2505416870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8100757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5726757049561</t>
   </si>
   <si>
     <t xml:space="preserve">24.403205871582</t>
@@ -2258,43 +2258,43 @@
     <t xml:space="preserve">24.4879417419434</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0810737609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5047416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3352737426758</t>
+    <t xml:space="preserve">25.081075668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5047397613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3352718353271</t>
   </si>
   <si>
     <t xml:space="preserve">25.4200077056885</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7589416503906</t>
+    <t xml:space="preserve">25.758939743042</t>
   </si>
   <si>
     <t xml:space="preserve">26.2673397064209</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4368076324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.521541595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8772773742676</t>
+    <t xml:space="preserve">26.4368095397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5215396881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8772754669189</t>
   </si>
   <si>
     <t xml:space="preserve">29.5719432830811</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3177394866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9788112640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1482753753662</t>
+    <t xml:space="preserve">29.317741394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9788093566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1482791900635</t>
   </si>
   <si>
     <t xml:space="preserve">29.2330093383789</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">27.0299415588379</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4704074859619</t>
+    <t xml:space="preserve">28.4704055786133</t>
   </si>
   <si>
     <t xml:space="preserve">27.4536094665527</t>
@@ -2315,13 +2315,13 @@
     <t xml:space="preserve">28.3856754302979</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7078075408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.131477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2841396331787</t>
+    <t xml:space="preserve">27.7078094482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1314735412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.284143447876</t>
   </si>
   <si>
     <t xml:space="preserve">25.6742076873779</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">25.8436737060547</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3520736694336</t>
+    <t xml:space="preserve">26.3520755767822</t>
   </si>
   <si>
     <t xml:space="preserve">26.6062755584717</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">26.1826076507568</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0978755950928</t>
+    <t xml:space="preserve">26.0978736877441</t>
   </si>
   <si>
     <t xml:space="preserve">25.9284076690674</t>
@@ -2360,10 +2360,10 @@
     <t xml:space="preserve">24.0642738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9627418518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.318473815918</t>
+    <t xml:space="preserve">22.962739944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3184757232666</t>
   </si>
   <si>
     <t xml:space="preserve">23.8948078155518</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">23.7030735015869</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0568523406982</t>
+    <t xml:space="preserve">24.0568542480469</t>
   </si>
   <si>
     <t xml:space="preserve">23.8799629211426</t>
@@ -2396,13 +2396,13 @@
     <t xml:space="preserve">24.4106292724609</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4990749359131</t>
+    <t xml:space="preserve">24.4990730285645</t>
   </si>
   <si>
     <t xml:space="preserve">24.8528518676758</t>
   </si>
   <si>
-    <t xml:space="preserve">25.295072555542</t>
+    <t xml:space="preserve">25.2950706481934</t>
   </si>
   <si>
     <t xml:space="preserve">25.2066287994385</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">24.587516784668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3221836090088</t>
+    <t xml:space="preserve">24.3221855163574</t>
   </si>
   <si>
     <t xml:space="preserve">23.3492965698242</t>
@@ -2420,31 +2420,31 @@
     <t xml:space="preserve">22.2879676818848</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4648532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8457469940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7572994232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4035224914551</t>
+    <t xml:space="preserve">22.4648551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8457450866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7573013305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4035243988037</t>
   </si>
   <si>
     <t xml:space="preserve">21.6688556671143</t>
   </si>
   <si>
-    <t xml:space="preserve">21.226634979248</t>
+    <t xml:space="preserve">21.2266330718994</t>
   </si>
   <si>
     <t xml:space="preserve">21.9341869354248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5804119110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1381874084473</t>
+    <t xml:space="preserve">21.5804100036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1381893157959</t>
   </si>
   <si>
     <t xml:space="preserve">22.1110782623291</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">25.1181831359863</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6759605407715</t>
+    <t xml:space="preserve">24.6759624481201</t>
   </si>
   <si>
     <t xml:space="preserve">22.9955196380615</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">22.907075881958</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1452960968018</t>
+    <t xml:space="preserve">24.1452941894531</t>
   </si>
   <si>
     <t xml:space="preserve">23.4377422332764</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">23.614631652832</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6417446136475</t>
+    <t xml:space="preserve">22.6417427062988</t>
   </si>
   <si>
     <t xml:space="preserve">23.0839653015137</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">23.1724109649658</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3764095306396</t>
+    <t xml:space="preserve">22.376407623291</t>
   </si>
   <si>
     <t xml:space="preserve">22.1995220184326</t>
@@ -2501,10 +2501,10 @@
     <t xml:space="preserve">20.6959686279297</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3150806427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7644081115723</t>
+    <t xml:space="preserve">21.3150787353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7644062042236</t>
   </si>
   <si>
     <t xml:space="preserve">25.7372951507568</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">24.9412956237793</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5604057312012</t>
+    <t xml:space="preserve">25.5604038238525</t>
   </si>
   <si>
     <t xml:space="preserve">25.471960067749</t>
@@ -2528,10 +2528,10 @@
     <t xml:space="preserve">25.9141807556152</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0639591217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2408447265625</t>
+    <t xml:space="preserve">27.0639572143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2408466339111</t>
   </si>
   <si>
     <t xml:space="preserve">27.1524028778076</t>
@@ -2543,22 +2543,22 @@
     <t xml:space="preserve">27.5946254730225</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3292922973633</t>
+    <t xml:space="preserve">27.3292903900146</t>
   </si>
   <si>
     <t xml:space="preserve">26.7101821899414</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7986259460449</t>
+    <t xml:space="preserve">26.7986240386963</t>
   </si>
   <si>
     <t xml:space="preserve">26.8870697021484</t>
   </si>
   <si>
-    <t xml:space="preserve">26.975513458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4177360534668</t>
+    <t xml:space="preserve">26.9755153656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4177341461182</t>
   </si>
   <si>
     <t xml:space="preserve">26.5332927703857</t>
@@ -2570,10 +2570,10 @@
     <t xml:space="preserve">26.4448471069336</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3564052581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8257389068604</t>
+    <t xml:space="preserve">26.3564033508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.825740814209</t>
   </si>
   <si>
     <t xml:space="preserve">26.0026264190674</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">26.179515838623</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6217365264893</t>
+    <t xml:space="preserve">26.6217384338379</t>
   </si>
   <si>
     <t xml:space="preserve">26.2679595947266</t>
@@ -3687,6 +3687,9 @@
   </si>
   <si>
     <t xml:space="preserve">67.9000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5999984741211</t>
   </si>
 </sst>
 </file>
@@ -34411,7 +34414,7 @@
         <v>17.25</v>
       </c>
       <c r="G1169" t="s">
-        <v>610</v>
+        <v>638</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34645,7 +34648,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1178" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -34853,7 +34856,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1186" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34957,7 +34960,7 @@
         <v>17.25</v>
       </c>
       <c r="G1190" t="s">
-        <v>610</v>
+        <v>638</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -35139,7 +35142,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1197" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35165,7 +35168,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -35217,7 +35220,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1200" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -35321,7 +35324,7 @@
         <v>16</v>
       </c>
       <c r="G1204" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -35373,7 +35376,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1206" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35399,7 +35402,7 @@
         <v>16</v>
       </c>
       <c r="G1207" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -35425,7 +35428,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1208" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -35451,7 +35454,7 @@
         <v>16.25</v>
       </c>
       <c r="G1209" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -35529,7 +35532,7 @@
         <v>17.25</v>
       </c>
       <c r="G1212" t="s">
-        <v>610</v>
+        <v>638</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -35607,7 +35610,7 @@
         <v>17.25</v>
       </c>
       <c r="G1215" t="s">
-        <v>610</v>
+        <v>638</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35815,7 +35818,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1223" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35841,7 +35844,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1224" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35867,7 +35870,7 @@
         <v>16</v>
       </c>
       <c r="G1225" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35893,7 +35896,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1226" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35919,7 +35922,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35945,7 +35948,7 @@
         <v>15.75</v>
       </c>
       <c r="G1228" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35971,7 +35974,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1229" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35997,7 +36000,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1230" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -36023,7 +36026,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1231" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -36049,7 +36052,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -36101,7 +36104,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1234" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -36127,7 +36130,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1235" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -36205,7 +36208,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1238" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -36231,7 +36234,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1239" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -36257,7 +36260,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -36283,7 +36286,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1241" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -36309,7 +36312,7 @@
         <v>19.5</v>
       </c>
       <c r="G1242" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -36335,7 +36338,7 @@
         <v>19</v>
       </c>
       <c r="G1243" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -36361,7 +36364,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1244" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -36387,7 +36390,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1245" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -36413,7 +36416,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1246" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -36439,7 +36442,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1247" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -36465,7 +36468,7 @@
         <v>18.75</v>
       </c>
       <c r="G1248" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -36491,7 +36494,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1249" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -36517,7 +36520,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1250" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -36543,7 +36546,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1251" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -36569,7 +36572,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -36595,7 +36598,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1253" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -36621,7 +36624,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -36647,7 +36650,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1255" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -36673,7 +36676,7 @@
         <v>19</v>
       </c>
       <c r="G1256" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36699,7 +36702,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36725,7 +36728,7 @@
         <v>19</v>
       </c>
       <c r="G1258" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36751,7 +36754,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1259" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36777,7 +36780,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1260" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36803,7 +36806,7 @@
         <v>19</v>
       </c>
       <c r="G1261" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36829,7 +36832,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1262" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36855,7 +36858,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36881,7 +36884,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1264" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36907,7 +36910,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1265" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36933,7 +36936,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1266" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36959,7 +36962,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1267" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36985,7 +36988,7 @@
         <v>18.75</v>
       </c>
       <c r="G1268" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -37011,7 +37014,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1269" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -37037,7 +37040,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1270" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -37063,7 +37066,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1271" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -37089,7 +37092,7 @@
         <v>19</v>
       </c>
       <c r="G1272" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -37115,7 +37118,7 @@
         <v>20</v>
       </c>
       <c r="G1273" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -37141,7 +37144,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1274" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -37167,7 +37170,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1275" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -37193,7 +37196,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1276" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -37219,7 +37222,7 @@
         <v>21</v>
       </c>
       <c r="G1277" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -37245,7 +37248,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1278" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -37271,7 +37274,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1279" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -37297,7 +37300,7 @@
         <v>20</v>
       </c>
       <c r="G1280" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -37323,7 +37326,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1281" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -37349,7 +37352,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1282" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -37375,7 +37378,7 @@
         <v>20</v>
       </c>
       <c r="G1283" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -37401,7 +37404,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1284" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -37427,7 +37430,7 @@
         <v>20</v>
       </c>
       <c r="G1285" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -37453,7 +37456,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1286" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -37479,7 +37482,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1287" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -37505,7 +37508,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -37531,7 +37534,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1289" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -37557,7 +37560,7 @@
         <v>20</v>
       </c>
       <c r="G1290" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -37583,7 +37586,7 @@
         <v>20</v>
       </c>
       <c r="G1291" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -37609,7 +37612,7 @@
         <v>20.5</v>
       </c>
       <c r="G1292" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -37635,7 +37638,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1293" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -37661,7 +37664,7 @@
         <v>21</v>
       </c>
       <c r="G1294" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -37687,7 +37690,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1295" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -37713,7 +37716,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1296" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -37739,7 +37742,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1297" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37765,7 +37768,7 @@
         <v>21.5</v>
       </c>
       <c r="G1298" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -37791,7 +37794,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1299" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37817,7 +37820,7 @@
         <v>22</v>
       </c>
       <c r="G1300" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -37843,7 +37846,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1301" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37869,7 +37872,7 @@
         <v>22</v>
       </c>
       <c r="G1302" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37895,7 +37898,7 @@
         <v>21.5</v>
       </c>
       <c r="G1303" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37921,7 +37924,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1304" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37947,7 +37950,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1305" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37973,7 +37976,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -37999,7 +38002,7 @@
         <v>21</v>
       </c>
       <c r="G1307" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -38025,7 +38028,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1308" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -38051,7 +38054,7 @@
         <v>21</v>
       </c>
       <c r="G1309" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -38077,7 +38080,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1310" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -38103,7 +38106,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -38129,7 +38132,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1312" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -38155,7 +38158,7 @@
         <v>21.5</v>
       </c>
       <c r="G1313" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -38181,7 +38184,7 @@
         <v>21.5</v>
       </c>
       <c r="G1314" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -38207,7 +38210,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1315" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -38233,7 +38236,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1316" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -38259,7 +38262,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1317" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -38285,7 +38288,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1318" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -38311,7 +38314,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1319" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -38337,7 +38340,7 @@
         <v>22.5</v>
       </c>
       <c r="G1320" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38363,7 +38366,7 @@
         <v>23.5</v>
       </c>
       <c r="G1321" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -38389,7 +38392,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1322" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -38415,7 +38418,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1323" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -38441,7 +38444,7 @@
         <v>23.5</v>
       </c>
       <c r="G1324" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -38467,7 +38470,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1325" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -38493,7 +38496,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1326" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -38519,7 +38522,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -38545,7 +38548,7 @@
         <v>23</v>
       </c>
       <c r="G1328" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -38571,7 +38574,7 @@
         <v>23.5</v>
       </c>
       <c r="G1329" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -38597,7 +38600,7 @@
         <v>23.5</v>
       </c>
       <c r="G1330" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38623,7 +38626,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1331" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -38649,7 +38652,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1332" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -38675,7 +38678,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1333" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -38701,7 +38704,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -38727,7 +38730,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1335" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -38753,7 +38756,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -38779,7 +38782,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1337" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -38805,7 +38808,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1338" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -38831,7 +38834,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1339" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -38857,7 +38860,7 @@
         <v>23.5</v>
       </c>
       <c r="G1340" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -38883,7 +38886,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1341" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -38909,7 +38912,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1342" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -38935,7 +38938,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1343" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -38961,7 +38964,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1344" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -38987,7 +38990,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1345" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -39013,7 +39016,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1346" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -39039,7 +39042,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1347" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -39065,7 +39068,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1348" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -39091,7 +39094,7 @@
         <v>23.5</v>
       </c>
       <c r="G1349" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -39117,7 +39120,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1350" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -39143,7 +39146,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1351" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -39169,7 +39172,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1352" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -39195,7 +39198,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1353" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -39221,7 +39224,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -39247,7 +39250,7 @@
         <v>23</v>
       </c>
       <c r="G1355" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -39273,7 +39276,7 @@
         <v>23</v>
       </c>
       <c r="G1356" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -39299,7 +39302,7 @@
         <v>23</v>
       </c>
       <c r="G1357" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -39325,7 +39328,7 @@
         <v>23</v>
       </c>
       <c r="G1358" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -39351,7 +39354,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -39377,7 +39380,7 @@
         <v>23</v>
       </c>
       <c r="G1360" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -39403,7 +39406,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1361" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -39429,7 +39432,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1362" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -39455,7 +39458,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -39481,7 +39484,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -39507,7 +39510,7 @@
         <v>23.5</v>
       </c>
       <c r="G1365" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -39637,7 +39640,7 @@
         <v>23.5</v>
       </c>
       <c r="G1370" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -39663,7 +39666,7 @@
         <v>23.5</v>
       </c>
       <c r="G1371" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -39689,7 +39692,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1372" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -39741,7 +39744,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1374" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -39767,7 +39770,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1375" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -39793,7 +39796,7 @@
         <v>23.5</v>
       </c>
       <c r="G1376" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -39819,7 +39822,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1377" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -39871,7 +39874,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1379" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -39897,7 +39900,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1380" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -39923,7 +39926,7 @@
         <v>23.5</v>
       </c>
       <c r="G1381" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -39949,7 +39952,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1382" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -39975,7 +39978,7 @@
         <v>23.5</v>
       </c>
       <c r="G1383" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -40001,7 +40004,7 @@
         <v>23.5</v>
       </c>
       <c r="G1384" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -40131,7 +40134,7 @@
         <v>23.5</v>
       </c>
       <c r="G1389" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -40157,7 +40160,7 @@
         <v>23.5</v>
       </c>
       <c r="G1390" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -40261,7 +40264,7 @@
         <v>23.5</v>
       </c>
       <c r="G1394" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -40287,7 +40290,7 @@
         <v>23.5</v>
       </c>
       <c r="G1395" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -40833,7 +40836,7 @@
         <v>23.5</v>
       </c>
       <c r="G1416" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -40859,7 +40862,7 @@
         <v>23.5</v>
       </c>
       <c r="G1417" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -70377,7 +70380,7 @@
     </row>
     <row r="2553">
       <c r="A2553" s="1" t="n">
-        <v>46041.6912731481</v>
+        <v>46041.3333333333</v>
       </c>
       <c r="B2553" t="n">
         <v>13162</v>
@@ -70398,6 +70401,32 @@
         <v>1218</v>
       </c>
       <c r="H2553" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2554">
+      <c r="A2554" s="1" t="n">
+        <v>46042.6911226852</v>
+      </c>
+      <c r="B2554" t="n">
+        <v>3317</v>
+      </c>
+      <c r="C2554" t="n">
+        <v>67.8000030517578</v>
+      </c>
+      <c r="D2554" t="n">
+        <v>66.3000030517578</v>
+      </c>
+      <c r="E2554" t="n">
+        <v>67.5999984741211</v>
+      </c>
+      <c r="F2554" t="n">
+        <v>66.5999984741211</v>
+      </c>
+      <c r="G2554" t="s">
+        <v>1225</v>
+      </c>
+      <c r="H2554" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CMB.MI.xlsx
+++ b/data/CMB.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23958683013916</t>
+    <t xml:space="preserve">9.23958873748779</t>
   </si>
   <si>
     <t xml:space="preserve">CMB.MI</t>
@@ -47,16 +47,16 @@
     <t xml:space="preserve">9.55656623840332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3137731552124</t>
+    <t xml:space="preserve">9.31377601623535</t>
   </si>
   <si>
     <t xml:space="preserve">9.40145015716553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40819358825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44191455841064</t>
+    <t xml:space="preserve">9.40819454193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44191360473633</t>
   </si>
   <si>
     <t xml:space="preserve">9.36098480224609</t>
@@ -71,10 +71,10 @@
     <t xml:space="preserve">9.26656532287598</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3407506942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27330875396729</t>
+    <t xml:space="preserve">9.34075164794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2733097076416</t>
   </si>
   <si>
     <t xml:space="preserve">9.19237804412842</t>
@@ -83,34 +83,34 @@
     <t xml:space="preserve">9.19912242889404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10470390319824</t>
+    <t xml:space="preserve">9.10470104217529</t>
   </si>
   <si>
     <t xml:space="preserve">8.84167766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77423572540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84842300415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3628396987915</t>
+    <t xml:space="preserve">8.77423763275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84842205047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36283779144287</t>
   </si>
   <si>
     <t xml:space="preserve">8.3291187286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61912059783936</t>
+    <t xml:space="preserve">8.61911964416504</t>
   </si>
   <si>
     <t xml:space="preserve">8.45051383972168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43028163909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63260841369629</t>
+    <t xml:space="preserve">8.43028259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63260746002197</t>
   </si>
   <si>
     <t xml:space="preserve">8.80121421813965</t>
@@ -119,52 +119,52 @@
     <t xml:space="preserve">9.22609901428223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25981998443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07098293304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87540054321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96981811523438</t>
+    <t xml:space="preserve">9.25982093811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07098197937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87539958953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96981716156006</t>
   </si>
   <si>
     <t xml:space="preserve">8.71353816986084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66632843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89563274383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81470203399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99679660797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01028347015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90237522125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97656345367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18563461303711</t>
+    <t xml:space="preserve">8.66633033752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89563179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81470012664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99679565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01028442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90237712860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18563365936279</t>
   </si>
   <si>
     <t xml:space="preserve">9.17214679718018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13167953491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34749507904053</t>
+    <t xml:space="preserve">9.13168048858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34749412536621</t>
   </si>
   <si>
     <t xml:space="preserve">9.25307655334473</t>
@@ -176,40 +176,40 @@
     <t xml:space="preserve">9.08446979522705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16540145874023</t>
+    <t xml:space="preserve">9.16540241241455</t>
   </si>
   <si>
     <t xml:space="preserve">8.98330688476562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78772258758545</t>
+    <t xml:space="preserve">8.78772449493408</t>
   </si>
   <si>
     <t xml:space="preserve">8.78098106384277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12493515014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03726005554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21261024475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04400634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09795951843262</t>
+    <t xml:space="preserve">9.12493801116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03726100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21260929107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04400444030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09795761108398</t>
   </si>
   <si>
     <t xml:space="preserve">9.20586681365967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38121700286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28679847717285</t>
+    <t xml:space="preserve">9.38121604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28679752349854</t>
   </si>
   <si>
     <t xml:space="preserve">9.22100734710693</t>
@@ -218,13 +218,13 @@
     <t xml:space="preserve">9.22798919677734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19308567047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35363292694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4094762802124</t>
+    <t xml:space="preserve">9.19308662414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35363388061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40947818756104</t>
   </si>
   <si>
     <t xml:space="preserve">9.52116298675537</t>
@@ -233,22 +233,22 @@
     <t xml:space="preserve">9.49324131011963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38853740692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94696140289307</t>
+    <t xml:space="preserve">9.38853454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94696235656738</t>
   </si>
   <si>
     <t xml:space="preserve">9.76547336578369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77245235443115</t>
+    <t xml:space="preserve">9.77245426177979</t>
   </si>
   <si>
     <t xml:space="preserve">9.66774845123291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82829570770264</t>
+    <t xml:space="preserve">9.82829666137695</t>
   </si>
   <si>
     <t xml:space="preserve">9.75151252746582</t>
@@ -257,34 +257,34 @@
     <t xml:space="preserve">9.57002353668213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57700538635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55606365203857</t>
+    <t xml:space="preserve">9.57700443267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55606269836426</t>
   </si>
   <si>
     <t xml:space="preserve">9.47927951812744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42343807220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39551639556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41645622253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34665393829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62586688995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63284873962402</t>
+    <t xml:space="preserve">9.42343711853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39551734924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4164571762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34665298461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58398532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62586879730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63284778594971</t>
   </si>
   <si>
     <t xml:space="preserve">9.46531963348389</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">9.48626041412354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59096622467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56304264068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53512191772461</t>
+    <t xml:space="preserve">9.59096527099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56304454803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53512287139893</t>
   </si>
   <si>
     <t xml:space="preserve">9.12328338623047</t>
@@ -308,202 +308,202 @@
     <t xml:space="preserve">9.30477237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2838306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20704746246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27685165405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36061477661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29081249237061</t>
+    <t xml:space="preserve">9.28383159637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20704650878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27685070037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36061382293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29081153869629</t>
   </si>
   <si>
     <t xml:space="preserve">9.29779148101807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31873226165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36759567260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47230052947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52814197540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50720119476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44437885284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50022220611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33269309997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32571220397949</t>
+    <t xml:space="preserve">9.31873321533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36759662628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47229957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52814102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5072021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44437789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50022029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33269214630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32571315765381</t>
   </si>
   <si>
     <t xml:space="preserve">9.13724422454834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14422512054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15120410919189</t>
+    <t xml:space="preserve">9.14422416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15120601654053</t>
   </si>
   <si>
     <t xml:space="preserve">9.1093225479126</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03952026367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92783451080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01159858703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07442188262939</t>
+    <t xml:space="preserve">9.03951835632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92783546447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01159763336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07442092895508</t>
   </si>
   <si>
     <t xml:space="preserve">8.97669696807861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86501121520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85105133056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93481540679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92085552215576</t>
+    <t xml:space="preserve">8.86501216888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85105228424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.934814453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92085361480713</t>
   </si>
   <si>
     <t xml:space="preserve">8.95575618743896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96971607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00461864471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91387367248535</t>
+    <t xml:space="preserve">8.96971702575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00461769104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91387462615967</t>
   </si>
   <si>
     <t xml:space="preserve">8.87897205352783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80916976928711</t>
+    <t xml:space="preserve">8.80916881561279</t>
   </si>
   <si>
     <t xml:space="preserve">8.59975910186768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56485843658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81614971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83708953857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89991283416748</t>
+    <t xml:space="preserve">8.56485939025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8161506652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83709049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8999137878418</t>
   </si>
   <si>
     <t xml:space="preserve">8.99763774871826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83010959625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96273708343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08838272094727</t>
+    <t xml:space="preserve">8.83011054992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96273612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08838176727295</t>
   </si>
   <si>
     <t xml:space="preserve">9.04650115966797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09536075592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66076946258545</t>
+    <t xml:space="preserve">9.09536170959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66076850891113</t>
   </si>
   <si>
     <t xml:space="preserve">9.64680767059326</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70264911651611</t>
+    <t xml:space="preserve">9.70265102386475</t>
   </si>
   <si>
     <t xml:space="preserve">9.79339504241943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92602157592773</t>
+    <t xml:space="preserve">9.92602062225342</t>
   </si>
   <si>
     <t xml:space="preserve">9.9818639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0516662597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4146432876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1912727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2471160888672</t>
+    <t xml:space="preserve">10.0516653060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4146423339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.19127368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2471141815186</t>
   </si>
   <si>
     <t xml:space="preserve">10.1493911743164</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1354303359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2680568695068</t>
+    <t xml:space="preserve">10.1354293823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2680559158325</t>
   </si>
   <si>
     <t xml:space="preserve">10.3937034606934</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5402889251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5891513824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4844484329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6310329437256</t>
+    <t xml:space="preserve">10.5402908325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5891523361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4844465255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6310338973999</t>
   </si>
   <si>
     <t xml:space="preserve">10.3588018417358</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98884391784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95394325256348</t>
+    <t xml:space="preserve">9.98884582519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95394229888916</t>
   </si>
   <si>
     <t xml:space="preserve">10.1005296707153</t>
@@ -512,19 +512,19 @@
     <t xml:space="preserve">10.4704856872559</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3867225646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5472688674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3448400497437</t>
+    <t xml:space="preserve">10.3867235183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5472707748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.344841003418</t>
   </si>
   <si>
     <t xml:space="preserve">10.477466583252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4006834030151</t>
+    <t xml:space="preserve">10.4006824493408</t>
   </si>
   <si>
     <t xml:space="preserve">10.4355850219727</t>
@@ -533,34 +533,34 @@
     <t xml:space="preserve">10.3727617263794</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3657817840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3378601074219</t>
+    <t xml:space="preserve">10.3657827377319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3378591537476</t>
   </si>
   <si>
     <t xml:space="preserve">10.2820167541504</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3797416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6100921630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5542497634888</t>
+    <t xml:space="preserve">10.3797426223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6100912094116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5542507171631</t>
   </si>
   <si>
     <t xml:space="preserve">10.6938562393188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0917339324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0428743362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0358924865723</t>
+    <t xml:space="preserve">11.0917348861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.042872428894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0358915328979</t>
   </si>
   <si>
     <t xml:space="preserve">11.063814163208</t>
@@ -575,85 +575,85 @@
     <t xml:space="preserve">11.5175352096558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0899219512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9991779327393</t>
+    <t xml:space="preserve">12.0899209976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9991769790649</t>
   </si>
   <si>
     <t xml:space="preserve">12.0689811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1038818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2853698730469</t>
+    <t xml:space="preserve">12.1038808822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2853708267212</t>
   </si>
   <si>
     <t xml:space="preserve">12.8228549957275</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9764223098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.990382194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2486553192139</t>
+    <t xml:space="preserve">12.9764213562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9903831481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2486562728882</t>
   </si>
   <si>
     <t xml:space="preserve">13.1090488433838</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1230087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8926591873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9135980606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8437957763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9624624252319</t>
+    <t xml:space="preserve">13.1230096817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8926582336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9135999679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8437948226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9624614715576</t>
   </si>
   <si>
     <t xml:space="preserve">13.1928129196167</t>
   </si>
   <si>
-    <t xml:space="preserve">13.39524269104</t>
+    <t xml:space="preserve">13.3952436447144</t>
   </si>
   <si>
     <t xml:space="preserve">13.8978261947632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9815902709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9327268600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0234718322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0304536819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1351585388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0723342895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0025300979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2112560272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197374343872</t>
+    <t xml:space="preserve">13.9815883636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9327259063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0234727859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0304489135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1351566314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0723323822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0025291442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.211256980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197393417358</t>
   </si>
   <si>
     <t xml:space="preserve">14.146164894104</t>
@@ -662,16 +662,16 @@
     <t xml:space="preserve">14.0810747146606</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9942903518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6688423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3558988571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6833066940308</t>
+    <t xml:space="preserve">13.994291305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6688413619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.355899810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6833057403564</t>
   </si>
   <si>
     <t xml:space="preserve">14.001522064209</t>
@@ -680,13 +680,13 @@
     <t xml:space="preserve">13.9870576858521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2691144943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3486680984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3414354324341</t>
+    <t xml:space="preserve">14.2691125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3486661911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3414373397827</t>
   </si>
   <si>
     <t xml:space="preserve">14.2763452529907</t>
@@ -695,211 +695,211 @@
     <t xml:space="preserve">14.4282217025757</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5656337738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3322486877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8457317352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7589464187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3611726760864</t>
+    <t xml:space="preserve">14.5656328201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3322467803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8457288742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7589502334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3611736297607</t>
   </si>
   <si>
     <t xml:space="preserve">15.1876029968262</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9200105667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6307220458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636758804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3105497360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9272413253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0718879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5492124557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4551935195923</t>
+    <t xml:space="preserve">14.9200096130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6307229995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636777877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3105478286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9272422790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0718860626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5492115020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4551944732666</t>
   </si>
   <si>
     <t xml:space="preserve">15.2671566009521</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1731357574463</t>
+    <t xml:space="preserve">15.1731395721436</t>
   </si>
   <si>
     <t xml:space="preserve">14.8332242965698</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1369771957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1152820587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9851007461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1514415740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0284948348999</t>
+    <t xml:space="preserve">15.1369781494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1152811050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9851026535034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.151439666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0284938812256</t>
   </si>
   <si>
     <t xml:space="preserve">15.2093000411987</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6649265289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6938581466675</t>
+    <t xml:space="preserve">15.664924621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6938552856445</t>
   </si>
   <si>
     <t xml:space="preserve">15.7661771774292</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9325189590454</t>
+    <t xml:space="preserve">15.9325170516968</t>
   </si>
   <si>
     <t xml:space="preserve">16.0409984588623</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9469795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6432285308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2816190719604</t>
+    <t xml:space="preserve">15.9469833374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6432294845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2816200256348</t>
   </si>
   <si>
     <t xml:space="preserve">15.2888517379761</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2599229812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3250122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2382249832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1586713790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0574235916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1803703308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2454586029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8983144760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.869384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8259925842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9634056091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9706363677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6813488006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7536706924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6958112716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8910827636719</t>
+    <t xml:space="preserve">15.2599220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3250150680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.238226890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.158673286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0574226379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1803674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2454595565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8983154296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8693838119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8259916305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9634017944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9706354141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6813478469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7536697387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6958122253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8910808563232</t>
   </si>
   <si>
     <t xml:space="preserve">14.4933109283447</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8549222946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6524181365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6090278625488</t>
+    <t xml:space="preserve">14.8549203872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6524200439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6090269088745</t>
   </si>
   <si>
     <t xml:space="preserve">14.8476896286011</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1948356628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3394765853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4334955215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2651977539062</t>
+    <t xml:space="preserve">15.1948347091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3394746780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4334993362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2651996612549</t>
   </si>
   <si>
     <t xml:space="preserve">16.9956512451172</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5742244720459</t>
+    <t xml:space="preserve">17.5742263793945</t>
   </si>
   <si>
     <t xml:space="preserve">18.6879825592041</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3986930847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4420871734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.217887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0804786682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1889610290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9719982147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0081558227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8562793731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9647655487061</t>
+    <t xml:space="preserve">18.3986949920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4420890808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2178859710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0804805755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1889629364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.971996307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0081539154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8562812805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9647636413574</t>
   </si>
   <si>
     <t xml:space="preserve">17.6393146514893</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">17.7622623443604</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6031551361084</t>
+    <t xml:space="preserve">17.6031532287598</t>
   </si>
   <si>
     <t xml:space="preserve">17.5886898040771</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5380630493164</t>
+    <t xml:space="preserve">17.538064956665</t>
   </si>
   <si>
     <t xml:space="preserve">17.5019035339355</t>
@@ -923,22 +923,22 @@
     <t xml:space="preserve">17.3861885070801</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3210983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2849388122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0462741851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2632427215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0969009399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3283290863037</t>
+    <t xml:space="preserve">17.3211002349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2849369049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.046272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.263240814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0968990325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3283309936523</t>
   </si>
   <si>
     <t xml:space="preserve">17.3572597503662</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">17.4006519317627</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3789558410645</t>
+    <t xml:space="preserve">17.3789577484131</t>
   </si>
   <si>
     <t xml:space="preserve">17.2921695709229</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">16.590648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6268100738525</t>
+    <t xml:space="preserve">16.6268081665039</t>
   </si>
   <si>
     <t xml:space="preserve">16.9233283996582</t>
@@ -971,22 +971,22 @@
     <t xml:space="preserve">16.3447532653809</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7083177566528</t>
+    <t xml:space="preserve">15.7083187103271</t>
   </si>
   <si>
     <t xml:space="preserve">16.1133213043213</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9180536270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6504611968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4749355316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3013591766357</t>
+    <t xml:space="preserve">15.9180545806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6504621505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4749336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3013610839844</t>
   </si>
   <si>
     <t xml:space="preserve">16.5761814117432</t>
@@ -1004,46 +1004,46 @@
     <t xml:space="preserve">16.5255584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4098453521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2073402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8746614456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.243501663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4460067749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2001094818115</t>
+    <t xml:space="preserve">16.4098415374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2073421478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8746604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2434997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4460029602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2001075744629</t>
   </si>
   <si>
     <t xml:space="preserve">15.8312664031982</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8601980209351</t>
+    <t xml:space="preserve">15.8601970672607</t>
   </si>
   <si>
     <t xml:space="preserve">15.8529634475708</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6287670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4696578979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4624261856079</t>
+    <t xml:space="preserve">15.6287631988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4696569442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4624252319336</t>
   </si>
   <si>
     <t xml:space="preserve">15.6215343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9976100921631</t>
+    <t xml:space="preserve">15.9976081848145</t>
   </si>
   <si>
     <t xml:space="preserve">16.236270904541</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">16.163948059082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2724304199219</t>
+    <t xml:space="preserve">16.2724285125732</t>
   </si>
   <si>
     <t xml:space="preserve">16.7786846160889</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">16.6340408325195</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4532337188721</t>
+    <t xml:space="preserve">16.4532356262207</t>
   </si>
   <si>
     <t xml:space="preserve">16.7425231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5978813171387</t>
+    <t xml:space="preserve">16.59787940979</t>
   </si>
   <si>
     <t xml:space="preserve">16.7063636779785</t>
@@ -1076,64 +1076,64 @@
     <t xml:space="preserve">16.8510055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.031810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2126140594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4295825958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9594898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3809146881104</t>
+    <t xml:space="preserve">17.0318088531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2126159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4295806884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.959493637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3809127807617</t>
   </si>
   <si>
     <t xml:space="preserve">15.9831428527832</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9108209609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7300157546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.368408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4045677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4768886566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8023376464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6701984405518</t>
+    <t xml:space="preserve">15.9108219146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7300176620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3684062957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4045667648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4768896102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8023405075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6702003479004</t>
   </si>
   <si>
     <t xml:space="preserve">17.1402950286865</t>
   </si>
   <si>
-    <t xml:space="preserve">17.104133605957</t>
+    <t xml:space="preserve">17.1041297912598</t>
   </si>
   <si>
     <t xml:space="preserve">16.8148441314697</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0679721832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8871650695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8273506164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6827068328857</t>
+    <t xml:space="preserve">17.0679740905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8871669769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8273525238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6827087402344</t>
   </si>
   <si>
     <t xml:space="preserve">17.3934192657471</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">17.8996734619141</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5867309570312</t>
+    <t xml:space="preserve">18.5867328643799</t>
   </si>
   <si>
     <t xml:space="preserve">18.6590538024902</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">19.2444362640381</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9157543182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4378890991211</t>
+    <t xml:space="preserve">19.9157562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4378910064697</t>
   </si>
   <si>
     <t xml:space="preserve">19.6546859741211</t>
@@ -1184,10 +1184,10 @@
     <t xml:space="preserve">18.8714828491211</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9460716247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7968902587891</t>
+    <t xml:space="preserve">18.9460735321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7968921661377</t>
   </si>
   <si>
     <t xml:space="preserve">17.9018020629883</t>
@@ -1202,49 +1202,52 @@
     <t xml:space="preserve">18.8341865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1698436737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3936195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5055046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8038673400879</t>
+    <t xml:space="preserve">19.1698474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3936176300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5055027008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8038692474365</t>
   </si>
   <si>
     <t xml:space="preserve">19.8784599304199</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6919784545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3190269470215</t>
+    <t xml:space="preserve">19.6919822692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3190250396729</t>
   </si>
   <si>
     <t xml:space="preserve">18.4239387512207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.13254737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3563232421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7292785644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7223014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9087791442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6477088928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5731182098389</t>
+    <t xml:space="preserve">19.1325492858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3563213348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0206642150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7292766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7223033905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9087772369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6477127075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5731163024902</t>
   </si>
   <si>
     <t xml:space="preserve">18.5358257293701</t>
@@ -1256,31 +1259,31 @@
     <t xml:space="preserve">18.1255741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4612331390381</t>
+    <t xml:space="preserve">18.4612312316895</t>
   </si>
   <si>
     <t xml:space="preserve">18.7595958709717</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6104145050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3493480682373</t>
+    <t xml:space="preserve">18.6104164123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3493461608887</t>
   </si>
   <si>
     <t xml:space="preserve">18.6850051879883</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3120498657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4985275268555</t>
+    <t xml:space="preserve">18.3120517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4985294342041</t>
   </si>
   <si>
     <t xml:space="preserve">19.2817306518555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0579566955566</t>
+    <t xml:space="preserve">19.0579605102539</t>
   </si>
   <si>
     <t xml:space="preserve">18.1628684997559</t>
@@ -1295,7 +1298,7 @@
     <t xml:space="preserve">17.1558933258057</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1862144470215</t>
+    <t xml:space="preserve">16.1862125396729</t>
   </si>
   <si>
     <t xml:space="preserve">15.5894870758057</t>
@@ -1310,46 +1313,46 @@
     <t xml:space="preserve">16.0370311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5218696594238</t>
+    <t xml:space="preserve">16.5218715667725</t>
   </si>
   <si>
     <t xml:space="preserve">15.6640768051147</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1046457290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9927597045898</t>
+    <t xml:space="preserve">15.1046447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9927558898926</t>
   </si>
   <si>
     <t xml:space="preserve">15.0300531387329</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7689847946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3661956787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5153751373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6198072433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8883304595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2538261413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2608032226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9251441955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7759628295898</t>
+    <t xml:space="preserve">14.768985748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3661966323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5153779983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6198043823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.888331413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2538280487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2608013153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.925142288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7759609222412</t>
   </si>
   <si>
     <t xml:space="preserve">15.7013711929321</t>
@@ -1358,40 +1361,40 @@
     <t xml:space="preserve">15.5521898269653</t>
   </si>
   <si>
-    <t xml:space="preserve">15.626781463623</t>
+    <t xml:space="preserve">15.6267795562744</t>
   </si>
   <si>
     <t xml:space="preserve">15.5148935317993</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2911224365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.21653175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1792364120483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8505544662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8132610321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0743255615234</t>
+    <t xml:space="preserve">15.2911214828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2165298461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.179238319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8505525588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8132591247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0743236541748</t>
   </si>
   <si>
     <t xml:space="preserve">15.8878488540649</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4030065536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9032497406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7093124389648</t>
+    <t xml:space="preserve">15.4030075073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9032506942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7093152999878</t>
   </si>
   <si>
     <t xml:space="preserve">15.4403038024902</t>
@@ -1403,7 +1406,7 @@
     <t xml:space="preserve">15.962438583374</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5591678619385</t>
+    <t xml:space="preserve">16.5591640472412</t>
   </si>
   <si>
     <t xml:space="preserve">16.3726902008057</t>
@@ -1412,46 +1415,46 @@
     <t xml:space="preserve">16.4845752716064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.78293800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8948268890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7386665344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3657131195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8435754776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8584976196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0673503875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8734130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9181680679321</t>
+    <t xml:space="preserve">16.7829360961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8948230743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7386655807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3657140731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8435773849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.858494758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0673494338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8734140396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9181661605835</t>
   </si>
   <si>
     <t xml:space="preserve">16.409984588623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2235069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2980976104736</t>
+    <t xml:space="preserve">16.2235088348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2980995178223</t>
   </si>
   <si>
     <t xml:space="preserve">16.6710529327393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7083492279053</t>
+    <t xml:space="preserve">16.7083473205566</t>
   </si>
   <si>
     <t xml:space="preserve">16.7456455230713</t>
@@ -1460,13 +1463,13 @@
     <t xml:space="preserve">16.6337566375732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9321212768555</t>
+    <t xml:space="preserve">16.9321193695068</t>
   </si>
   <si>
     <t xml:space="preserve">16.8575305938721</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0067119598389</t>
+    <t xml:space="preserve">17.0067081451416</t>
   </si>
   <si>
     <t xml:space="preserve">17.3796653747559</t>
@@ -1475,172 +1478,175 @@
     <t xml:space="preserve">17.2304859161377</t>
   </si>
   <si>
+    <t xml:space="preserve">17.5288467407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.343240737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7227516174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6756725311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7532348632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3654289245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0939655303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6673784255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6285943984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0468854904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2640600204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7061576843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5898141860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5122547149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7449378967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950830459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0158634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1864967346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4191799163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4967422485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5510349273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3261089324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2795724868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8612813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0164012908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9388418197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9000597000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7837181091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8225002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3266468048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7920150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0246982574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9083557128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4817714691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5593318939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0551834106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4042091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1327438354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2878665924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1715259552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9776220321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3881559371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346923828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2103080749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4429893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5981121063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5205535888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6368942260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2490844726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8307971954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9859199523926</t>
+  </si>
+  <si>
     <t xml:space="preserve">17.5288486480713</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3432426452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7227516174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6756725311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7532348632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3654289245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0939636230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6673765182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6285963058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0468864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2640590667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7061567306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5898160934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5122547149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7449398040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950839996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0158643722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1864967346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4191808700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4967422485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5510349273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3261060714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2795715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8612785339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0164012908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9388418197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9000616073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7837200164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8224983215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3266487121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7920150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0247001647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9083557128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4817714691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5593318939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0551834106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4042072296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1327438354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2878665924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1715278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9776239395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3881559371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346923828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2103061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4429912567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5981101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5205516815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6368942260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2490844726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8307971954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9859180450439</t>
-  </si>
-  <si>
     <t xml:space="preserve">17.8390941619873</t>
   </si>
   <si>
-    <t xml:space="preserve">17.567626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9942169189453</t>
+    <t xml:space="preserve">17.5676250457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9942150115967</t>
   </si>
   <si>
     <t xml:space="preserve">18.6147060394287</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2656764984131</t>
+    <t xml:space="preserve">18.2656784057617</t>
   </si>
   <si>
     <t xml:space="preserve">18.8473873138428</t>
@@ -1649,37 +1655,37 @@
     <t xml:space="preserve">18.5371437072754</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0717735290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4595794677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7698307037354</t>
+    <t xml:space="preserve">18.0717754364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4595813751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7698287963867</t>
   </si>
   <si>
     <t xml:space="preserve">18.9249515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1576347351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0025100708008</t>
+    <t xml:space="preserve">19.1576366424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0025119781494</t>
   </si>
   <si>
     <t xml:space="preserve">19.0412921905518</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3044605255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1493377685547</t>
+    <t xml:space="preserve">18.30446434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1493358612061</t>
   </si>
   <si>
     <t xml:space="preserve">18.0329971313477</t>
   </si>
   <si>
-    <t xml:space="preserve">18.226900100708</t>
+    <t xml:space="preserve">18.2268981933594</t>
   </si>
   <si>
     <t xml:space="preserve">18.4208011627197</t>
@@ -1688,22 +1694,22 @@
     <t xml:space="preserve">18.498363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1105556488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6839714050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8086090087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.382022857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1881198883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9166526794434</t>
+    <t xml:space="preserve">18.1105575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.683967590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8086071014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3820209503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1881217956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.916654586792</t>
   </si>
   <si>
     <t xml:space="preserve">17.9554347991943</t>
@@ -1712,16 +1718,16 @@
     <t xml:space="preserve">17.606409072876</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6451892852783</t>
+    <t xml:space="preserve">17.645191192627</t>
   </si>
   <si>
     <t xml:space="preserve">17.141040802002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1022624969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2961654663086</t>
+    <t xml:space="preserve">17.1022605895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.29616355896</t>
   </si>
   <si>
     <t xml:space="preserve">15.1244478225708</t>
@@ -1730,22 +1736,22 @@
     <t xml:space="preserve">14.7676668167114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5577116012573</t>
+    <t xml:space="preserve">13.5577096939087</t>
   </si>
   <si>
     <t xml:space="preserve">13.9610290527344</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0302934646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.185417175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1388788223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5732221603394</t>
+    <t xml:space="preserve">13.0302925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1854162216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.138879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5732231140137</t>
   </si>
   <si>
     <t xml:space="preserve">13.262978553772</t>
@@ -1757,28 +1763,28 @@
     <t xml:space="preserve">12.9527339935303</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5649261474609</t>
+    <t xml:space="preserve">12.5649271011353</t>
   </si>
   <si>
     <t xml:space="preserve">11.7582883834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5566291809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8585777282715</t>
+    <t xml:space="preserve">11.5566301345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8585767745972</t>
   </si>
   <si>
     <t xml:space="preserve">10.7810163497925</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3156499862671</t>
+    <t xml:space="preserve">10.3156490325928</t>
   </si>
   <si>
     <t xml:space="preserve">10.8197975158691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1300430297852</t>
+    <t xml:space="preserve">11.1300439834595</t>
   </si>
   <si>
     <t xml:space="preserve">11.7893133163452</t>
@@ -1787,37 +1793,37 @@
     <t xml:space="preserve">12.2546806335449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9056549072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6341905593872</t>
+    <t xml:space="preserve">11.9056558609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6341896057129</t>
   </si>
   <si>
     <t xml:space="preserve">12.0219974517822</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0607786178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8280935287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4790687561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7117519378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6729717254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5954103469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2851657867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4015073776245</t>
+    <t xml:space="preserve">12.0607776641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8280944824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4790678024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7117528915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6729707717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5954113006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2851648330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4015064239502</t>
   </si>
   <si>
     <t xml:space="preserve">11.7505331039429</t>
@@ -1826,10 +1832,10 @@
     <t xml:space="preserve">10.9749202728271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5095529556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5871133804321</t>
+    <t xml:space="preserve">10.5095539093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5871124267578</t>
   </si>
   <si>
     <t xml:space="preserve">10.6646747589111</t>
@@ -1838,28 +1844,28 @@
     <t xml:space="preserve">11.2463846206665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2158994674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.371021270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.07737159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1181735992432</t>
+    <t xml:space="preserve">12.2159013748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3710222244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0773706436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1181745529175</t>
   </si>
   <si>
     <t xml:space="preserve">14.0365676879883</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8733520507812</t>
+    <t xml:space="preserve">13.8733501434326</t>
   </si>
   <si>
     <t xml:space="preserve">13.8325471878052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1997833251953</t>
+    <t xml:space="preserve">14.199782371521</t>
   </si>
   <si>
     <t xml:space="preserve">14.6078224182129</t>
@@ -1874,13 +1880,13 @@
     <t xml:space="preserve">13.5469188690186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5061149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.750940322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9549589157104</t>
+    <t xml:space="preserve">13.5061140060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7509393692017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9549598693848</t>
   </si>
   <si>
     <t xml:space="preserve">14.5262145996094</t>
@@ -1889,13 +1895,13 @@
     <t xml:space="preserve">14.7710380554199</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6894302368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3221950531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4038028717041</t>
+    <t xml:space="preserve">14.6894292831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3221940994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4038038253784</t>
   </si>
   <si>
     <t xml:space="preserve">13.5877227783203</t>
@@ -1907,13 +1913,13 @@
     <t xml:space="preserve">13.6285285949707</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9141540527344</t>
+    <t xml:space="preserve">13.9141550064087</t>
   </si>
   <si>
     <t xml:space="preserve">14.2405862808228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9957618713379</t>
+    <t xml:space="preserve">13.9957628250122</t>
   </si>
   <si>
     <t xml:space="preserve">14.1589784622192</t>
@@ -1922,22 +1928,19 @@
     <t xml:space="preserve">13.7917423248291</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3837032318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2204875946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3429002761841</t>
+    <t xml:space="preserve">13.3837022781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2204885482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3428993225098</t>
   </si>
   <si>
     <t xml:space="preserve">13.7101354598999</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0572719573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.138879776001</t>
+    <t xml:space="preserve">13.0572710037231</t>
   </si>
   <si>
     <t xml:space="preserve">13.2612915039062</t>
@@ -1949,28 +1952,28 @@
     <t xml:space="preserve">12.4860162734985</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8532514572144</t>
+    <t xml:space="preserve">12.8532524108887</t>
   </si>
   <si>
     <t xml:space="preserve">12.7308397293091</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6900367736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9756641387939</t>
+    <t xml:space="preserve">12.690034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9756631851196</t>
   </si>
   <si>
     <t xml:space="preserve">12.7716436386108</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8526458740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.260684967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4239025115967</t>
+    <t xml:space="preserve">14.8526487350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2606868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4239015579224</t>
   </si>
   <si>
     <t xml:space="preserve">16.0767669677734</t>
@@ -1982,16 +1985,16 @@
     <t xml:space="preserve">15.5055084228516</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6687259674072</t>
+    <t xml:space="preserve">15.6687278747559</t>
   </si>
   <si>
     <t xml:space="preserve">15.5871181488037</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3014907836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3830995559692</t>
+    <t xml:space="preserve">15.3014898300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3830976486206</t>
   </si>
   <si>
     <t xml:space="preserve">15.3422937393188</t>
@@ -2000,22 +2003,22 @@
     <t xml:space="preserve">15.7503337860107</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2198820114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1790800094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4647054672241</t>
+    <t xml:space="preserve">15.2198829650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1790771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4647073745728</t>
   </si>
   <si>
     <t xml:space="preserve">16.321590423584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1583728790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8112373352051</t>
+    <t xml:space="preserve">16.158374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8112354278564</t>
   </si>
   <si>
     <t xml:space="preserve">17.7089252471924</t>
@@ -2024,31 +2027,31 @@
     <t xml:space="preserve">17.1376686096191</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3824920654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8928451538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1991767883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.484806060791</t>
+    <t xml:space="preserve">17.3824939727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.89284324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1991786956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4848079681396</t>
   </si>
   <si>
     <t xml:space="preserve">16.6480197906494</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5664157867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2399806976318</t>
+    <t xml:space="preserve">16.5664138793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2399826049805</t>
   </si>
   <si>
     <t xml:space="preserve">16.4031982421875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7296295166016</t>
+    <t xml:space="preserve">16.7296276092529</t>
   </si>
   <si>
     <t xml:space="preserve">17.2192764282227</t>
@@ -2069,7 +2072,7 @@
     <t xml:space="preserve">16.9744510650635</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8721408843994</t>
+    <t xml:space="preserve">17.872142791748</t>
   </si>
   <si>
     <t xml:space="preserve">18.11696434021</t>
@@ -2078,37 +2081,34 @@
     <t xml:space="preserve">18.1985721588135</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3617877960205</t>
+    <t xml:space="preserve">18.3617858886719</t>
   </si>
   <si>
     <t xml:space="preserve">19.1778678894043</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8514347076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6882190704346</t>
+    <t xml:space="preserve">18.8514366149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6882209777832</t>
   </si>
   <si>
     <t xml:space="preserve">19.0962600708008</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6066131591797</t>
+    <t xml:space="preserve">18.6066093444824</t>
   </si>
   <si>
     <t xml:space="preserve">18.9330444335938</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7698287963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2594757080078</t>
+    <t xml:space="preserve">19.2594776153564</t>
   </si>
   <si>
     <t xml:space="preserve">19.34108543396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4226894378662</t>
+    <t xml:space="preserve">19.4226913452148</t>
   </si>
   <si>
     <t xml:space="preserve">19.0146503448486</t>
@@ -2120,16 +2120,16 @@
     <t xml:space="preserve">19.8276062011719</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4886741638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6581401824951</t>
+    <t xml:space="preserve">19.4886722564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6581382751465</t>
   </si>
   <si>
     <t xml:space="preserve">19.5734062194824</t>
   </si>
   <si>
-    <t xml:space="preserve">19.403938293457</t>
+    <t xml:space="preserve">19.4039402008057</t>
   </si>
   <si>
     <t xml:space="preserve">19.9970722198486</t>
@@ -2138,10 +2138,10 @@
     <t xml:space="preserve">20.3360061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">20.166540145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.319206237793</t>
+    <t xml:space="preserve">20.1665382385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3192043304443</t>
   </si>
   <si>
     <t xml:space="preserve">19.0650062561035</t>
@@ -2153,13 +2153,13 @@
     <t xml:space="preserve">19.7428703308105</t>
   </si>
   <si>
-    <t xml:space="preserve">20.08180809021</t>
+    <t xml:space="preserve">20.0818061828613</t>
   </si>
   <si>
     <t xml:space="preserve">20.4207401275635</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5054740905762</t>
+    <t xml:space="preserve">20.5054721832275</t>
   </si>
   <si>
     <t xml:space="preserve">20.6749401092529</t>
@@ -2183,58 +2183,58 @@
     <t xml:space="preserve">22.0306739807129</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4543418884277</t>
+    <t xml:space="preserve">22.4543399810791</t>
   </si>
   <si>
     <t xml:space="preserve">22.2001399993896</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6238079071045</t>
+    <t xml:space="preserve">22.6238059997559</t>
   </si>
   <si>
     <t xml:space="preserve">22.7932739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0474758148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6406078338623</t>
+    <t xml:space="preserve">23.0474739074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6406059265137</t>
   </si>
   <si>
     <t xml:space="preserve">23.555871963501</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3016738891602</t>
+    <t xml:space="preserve">23.3016719818115</t>
   </si>
   <si>
     <t xml:space="preserve">23.4711399078369</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3864059448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.725341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1322078704834</t>
+    <t xml:space="preserve">23.3864078521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7253398895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1322059631348</t>
   </si>
   <si>
     <t xml:space="preserve">23.2169399261475</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9459419250488</t>
+    <t xml:space="preserve">21.9459400177002</t>
   </si>
   <si>
     <t xml:space="preserve">22.8780059814453</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1490077972412</t>
+    <t xml:space="preserve">24.1490058898926</t>
   </si>
   <si>
     <t xml:space="preserve">25.165807723999</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9116096496582</t>
+    <t xml:space="preserve">24.9116077423096</t>
   </si>
   <si>
     <t xml:space="preserve">24.2337417602539</t>
@@ -2246,37 +2246,37 @@
     <t xml:space="preserve">23.8100757598877</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5726737976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4032077789307</t>
+    <t xml:space="preserve">24.5726718902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.403205871582</t>
   </si>
   <si>
     <t xml:space="preserve">24.4879398345947</t>
   </si>
   <si>
-    <t xml:space="preserve">25.081075668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5047416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3352718353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4200077056885</t>
+    <t xml:space="preserve">25.0810737609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5047397613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3352737426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4200057983398</t>
   </si>
   <si>
     <t xml:space="preserve">25.7589416503906</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2673416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4368076324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5215396881104</t>
+    <t xml:space="preserve">26.2673397064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4368057250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.521541595459</t>
   </si>
   <si>
     <t xml:space="preserve">27.8772773742676</t>
@@ -2288,43 +2288,43 @@
     <t xml:space="preserve">29.317741394043</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9788074493408</t>
+    <t xml:space="preserve">28.9788093566895</t>
   </si>
   <si>
     <t xml:space="preserve">29.1482772827148</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2330093383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9620094299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0299396514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4704093933105</t>
+    <t xml:space="preserve">29.2330074310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.962007522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0299415588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4704074859619</t>
   </si>
   <si>
     <t xml:space="preserve">27.4536094665527</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3856735229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7078094482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1314754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2841415405273</t>
+    <t xml:space="preserve">28.3856754302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7078075408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1314735412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2841396331787</t>
   </si>
   <si>
     <t xml:space="preserve">25.6742076873779</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0131397247314</t>
+    <t xml:space="preserve">26.0131416320801</t>
   </si>
   <si>
     <t xml:space="preserve">25.8436737060547</t>
@@ -2333,34 +2333,34 @@
     <t xml:space="preserve">26.3520736694336</t>
   </si>
   <si>
-    <t xml:space="preserve">26.606273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8268756866455</t>
+    <t xml:space="preserve">26.6062755584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8268737792969</t>
   </si>
   <si>
     <t xml:space="preserve">26.1826076507568</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0978755950928</t>
+    <t xml:space="preserve">26.0978736877441</t>
   </si>
   <si>
     <t xml:space="preserve">25.9284076690674</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6910095214844</t>
+    <t xml:space="preserve">26.6910076141357</t>
   </si>
   <si>
     <t xml:space="preserve">22.5390739440918</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0642719268799</t>
+    <t xml:space="preserve">24.0642738342285</t>
   </si>
   <si>
     <t xml:space="preserve">22.9627418518066</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3184757232666</t>
+    <t xml:space="preserve">24.318473815918</t>
   </si>
   <si>
     <t xml:space="preserve">23.8948078155518</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">23.5261859893799</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7301864624023</t>
+    <t xml:space="preserve">22.730188369751</t>
   </si>
   <si>
     <t xml:space="preserve">23.2608528137207</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">25.2066268920898</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5875148773193</t>
+    <t xml:space="preserve">24.587516784668</t>
   </si>
   <si>
     <t xml:space="preserve">24.3221855163574</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">23.3492965698242</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2879676818848</t>
+    <t xml:space="preserve">22.2879657745361</t>
   </si>
   <si>
     <t xml:space="preserve">22.4648532867432</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">21.8457450866699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7573013305664</t>
+    <t xml:space="preserve">21.7572994232178</t>
   </si>
   <si>
     <t xml:space="preserve">21.4035224914551</t>
@@ -2447,28 +2447,28 @@
     <t xml:space="preserve">21.1381893157959</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1110763549805</t>
+    <t xml:space="preserve">22.1110782623291</t>
   </si>
   <si>
     <t xml:space="preserve">23.7915191650391</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1181812286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6759624481201</t>
+    <t xml:space="preserve">25.1181831359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6759605407715</t>
   </si>
   <si>
     <t xml:space="preserve">22.9955196380615</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9070777893066</t>
+    <t xml:space="preserve">22.907075881958</t>
   </si>
   <si>
     <t xml:space="preserve">24.1452960968018</t>
   </si>
   <si>
-    <t xml:space="preserve">23.437744140625</t>
+    <t xml:space="preserve">23.4377422332764</t>
   </si>
   <si>
     <t xml:space="preserve">23.614631652832</t>
@@ -2489,13 +2489,13 @@
     <t xml:space="preserve">22.1995220184326</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0226306915283</t>
+    <t xml:space="preserve">22.022632598877</t>
   </si>
   <si>
     <t xml:space="preserve">21.0497455596924</t>
   </si>
   <si>
-    <t xml:space="preserve">21.49196434021</t>
+    <t xml:space="preserve">21.4919662475586</t>
   </si>
   <si>
     <t xml:space="preserve">20.6959686279297</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">25.5604057312012</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4719619750977</t>
+    <t xml:space="preserve">25.471960067749</t>
   </si>
   <si>
     <t xml:space="preserve">25.6488494873047</t>
@@ -2531,13 +2531,13 @@
     <t xml:space="preserve">27.0639591217041</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2408466339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1524028778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5061798095703</t>
+    <t xml:space="preserve">27.2408447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1524047851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5061817169189</t>
   </si>
   <si>
     <t xml:space="preserve">27.5946254730225</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">27.3292903900146</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7101821899414</t>
+    <t xml:space="preserve">26.7101802825928</t>
   </si>
   <si>
     <t xml:space="preserve">26.7986240386963</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">26.8870697021484</t>
   </si>
   <si>
-    <t xml:space="preserve">26.975513458252</t>
+    <t xml:space="preserve">26.9755153656006</t>
   </si>
   <si>
     <t xml:space="preserve">27.4177360534668</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">26.0910720825195</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4448471069336</t>
+    <t xml:space="preserve">26.4448490142822</t>
   </si>
   <si>
     <t xml:space="preserve">26.3564033508301</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">25.8257389068604</t>
   </si>
   <si>
-    <t xml:space="preserve">26.002628326416</t>
+    <t xml:space="preserve">26.0026264190674</t>
   </si>
   <si>
     <t xml:space="preserve">26.179515838623</t>
@@ -20533,7 +20533,7 @@
         <v>25.5</v>
       </c>
       <c r="G635" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20559,7 +20559,7 @@
         <v>25.5</v>
       </c>
       <c r="G636" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20585,7 +20585,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G637" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20611,7 +20611,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G638" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20637,7 +20637,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G639" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20663,7 +20663,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G640" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20741,7 +20741,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G643" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20767,7 +20767,7 @@
         <v>25</v>
       </c>
       <c r="G644" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20793,7 +20793,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G645" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20819,7 +20819,7 @@
         <v>25</v>
       </c>
       <c r="G646" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20845,7 +20845,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G647" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20871,7 +20871,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G648" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20897,7 +20897,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G649" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20923,7 +20923,7 @@
         <v>24.75</v>
       </c>
       <c r="G650" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20949,7 +20949,7 @@
         <v>24.75</v>
       </c>
       <c r="G651" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20975,7 +20975,7 @@
         <v>24.75</v>
       </c>
       <c r="G652" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -21053,7 +21053,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G655" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -21079,7 +21079,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G656" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -21131,7 +21131,7 @@
         <v>25</v>
       </c>
       <c r="G658" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -21157,7 +21157,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G659" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -21209,7 +21209,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G661" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -21235,7 +21235,7 @@
         <v>25</v>
       </c>
       <c r="G662" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -21261,7 +21261,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G663" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -21287,7 +21287,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G664" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -21313,7 +21313,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G665" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21339,7 +21339,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G666" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21391,7 +21391,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G668" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21417,7 +21417,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G669" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21469,7 +21469,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G671" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21495,7 +21495,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G672" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21521,7 +21521,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G673" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21573,7 +21573,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21599,7 +21599,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G676" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21651,7 +21651,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G678" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21703,7 +21703,7 @@
         <v>25</v>
       </c>
       <c r="G680" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21729,7 +21729,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G681" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21755,7 +21755,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G682" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21781,7 +21781,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G683" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21807,7 +21807,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G684" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21833,7 +21833,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21963,7 +21963,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G690" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21989,7 +21989,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G691" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -22015,7 +22015,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G692" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -22041,7 +22041,7 @@
         <v>25</v>
       </c>
       <c r="G693" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -22067,7 +22067,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G694" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -22119,7 +22119,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G696" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -22145,7 +22145,7 @@
         <v>24.75</v>
       </c>
       <c r="G697" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -22171,7 +22171,7 @@
         <v>24.75</v>
       </c>
       <c r="G698" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -22197,7 +22197,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G699" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -22223,7 +22223,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -22249,7 +22249,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G701" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -22275,7 +22275,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G702" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -22301,7 +22301,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G703" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22327,7 +22327,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G704" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -22353,7 +22353,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G705" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -22405,7 +22405,7 @@
         <v>23</v>
       </c>
       <c r="G707" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22431,7 +22431,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G708" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22457,7 +22457,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G709" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22483,7 +22483,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G710" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22509,7 +22509,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G711" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22535,7 +22535,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G712" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22561,7 +22561,7 @@
         <v>21.5</v>
       </c>
       <c r="G713" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22587,7 +22587,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22613,7 +22613,7 @@
         <v>21</v>
       </c>
       <c r="G715" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22639,7 +22639,7 @@
         <v>20.25</v>
       </c>
       <c r="G716" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22665,7 +22665,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22691,7 +22691,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G718" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22717,7 +22717,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G719" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22743,7 +22743,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G720" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22769,7 +22769,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G721" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22795,7 +22795,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G722" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22821,7 +22821,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G723" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22847,7 +22847,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G724" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22873,7 +22873,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G725" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22899,7 +22899,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G726" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22925,7 +22925,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G727" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22951,7 +22951,7 @@
         <v>21</v>
       </c>
       <c r="G728" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22977,7 +22977,7 @@
         <v>21.5</v>
       </c>
       <c r="G729" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -23003,7 +23003,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G730" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -23029,7 +23029,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G731" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -23055,7 +23055,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G732" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -23081,7 +23081,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G733" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -23107,7 +23107,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G734" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -23133,7 +23133,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -23159,7 +23159,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G736" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -23185,7 +23185,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G737" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -23211,7 +23211,7 @@
         <v>20.5</v>
       </c>
       <c r="G738" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -23237,7 +23237,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G739" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -23263,7 +23263,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G740" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -23289,7 +23289,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G741" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -23315,7 +23315,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G742" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23341,7 +23341,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23367,7 +23367,7 @@
         <v>21.25</v>
       </c>
       <c r="G744" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23393,7 +23393,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G745" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23419,7 +23419,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G746" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23445,7 +23445,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G747" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23471,7 +23471,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G748" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23497,7 +23497,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G749" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23523,7 +23523,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G750" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23549,7 +23549,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G751" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23575,7 +23575,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G752" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23601,7 +23601,7 @@
         <v>21</v>
       </c>
       <c r="G753" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23627,7 +23627,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G754" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23653,7 +23653,7 @@
         <v>21</v>
       </c>
       <c r="G755" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23679,7 +23679,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G756" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23705,7 +23705,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G757" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23731,7 +23731,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G758" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23757,7 +23757,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G759" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23783,7 +23783,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G760" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23809,7 +23809,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G761" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23835,7 +23835,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G762" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23861,7 +23861,7 @@
         <v>20.25</v>
       </c>
       <c r="G763" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23887,7 +23887,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G764" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23913,7 +23913,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G765" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23939,7 +23939,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G766" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23965,7 +23965,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G767" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23991,7 +23991,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G768" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -24017,7 +24017,7 @@
         <v>21</v>
       </c>
       <c r="G769" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -24043,7 +24043,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G770" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -24069,7 +24069,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G771" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -24095,7 +24095,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G772" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -24121,7 +24121,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G773" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -24147,7 +24147,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G774" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -24173,7 +24173,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G775" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -24199,7 +24199,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G776" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -24225,7 +24225,7 @@
         <v>22.5</v>
       </c>
       <c r="G777" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -24251,7 +24251,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G778" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -24277,7 +24277,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G779" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -24303,7 +24303,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G780" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -24329,7 +24329,7 @@
         <v>21.5</v>
       </c>
       <c r="G781" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -24355,7 +24355,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G782" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -24381,7 +24381,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G783" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -24407,7 +24407,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G784" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -24433,7 +24433,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G785" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -24459,7 +24459,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G786" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -24485,7 +24485,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G787" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -24511,7 +24511,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G788" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -24537,7 +24537,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G789" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -24563,7 +24563,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G790" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -24589,7 +24589,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G791" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -24615,7 +24615,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G792" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -24641,7 +24641,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G793" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24667,7 +24667,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G794" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24693,7 +24693,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G795" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24719,7 +24719,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G796" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24745,7 +24745,7 @@
         <v>20.25</v>
       </c>
       <c r="G797" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24771,7 +24771,7 @@
         <v>20</v>
       </c>
       <c r="G798" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24797,7 +24797,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G799" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24823,7 +24823,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G800" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24849,7 +24849,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G801" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24875,7 +24875,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G802" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24901,7 +24901,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G803" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24927,7 +24927,7 @@
         <v>20.25</v>
       </c>
       <c r="G804" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24953,7 +24953,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G805" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24979,7 +24979,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G806" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -25005,7 +25005,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G807" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -25031,7 +25031,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G808" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -25057,7 +25057,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G809" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -25083,7 +25083,7 @@
         <v>20.5</v>
       </c>
       <c r="G810" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -25109,7 +25109,7 @@
         <v>20</v>
       </c>
       <c r="G811" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -25135,7 +25135,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G812" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -25161,7 +25161,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G813" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -25187,7 +25187,7 @@
         <v>20.25</v>
       </c>
       <c r="G814" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -25213,7 +25213,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G815" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -25239,7 +25239,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G816" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -25265,7 +25265,7 @@
         <v>20.25</v>
       </c>
       <c r="G817" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -25291,7 +25291,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -25317,7 +25317,7 @@
         <v>21</v>
       </c>
       <c r="G819" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -25343,7 +25343,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G820" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -25369,7 +25369,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G821" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -25395,7 +25395,7 @@
         <v>21.5</v>
       </c>
       <c r="G822" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -25421,7 +25421,7 @@
         <v>22</v>
       </c>
       <c r="G823" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -25447,7 +25447,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G824" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -25473,7 +25473,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G825" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -25499,7 +25499,7 @@
         <v>21.75</v>
       </c>
       <c r="G826" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -25525,7 +25525,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G827" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -25551,7 +25551,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G828" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -25577,7 +25577,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G829" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -25603,7 +25603,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -25629,7 +25629,7 @@
         <v>21.75</v>
       </c>
       <c r="G831" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25655,7 +25655,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G832" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25681,7 +25681,7 @@
         <v>22</v>
       </c>
       <c r="G833" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25707,7 +25707,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G834" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25733,7 +25733,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G835" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25759,7 +25759,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G836" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25785,7 +25785,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G837" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25811,7 +25811,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G838" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25837,7 +25837,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G839" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25863,7 +25863,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25889,7 +25889,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G841" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25915,7 +25915,7 @@
         <v>22.5</v>
       </c>
       <c r="G842" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25941,7 +25941,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G843" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25967,7 +25967,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G844" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25993,7 +25993,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G845" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -26019,7 +26019,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G846" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -26045,7 +26045,7 @@
         <v>23.5</v>
       </c>
       <c r="G847" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -26071,7 +26071,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -26097,7 +26097,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G849" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -26123,7 +26123,7 @@
         <v>21.5</v>
       </c>
       <c r="G850" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -26149,7 +26149,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -26175,7 +26175,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -26201,7 +26201,7 @@
         <v>20.75</v>
       </c>
       <c r="G853" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -26227,7 +26227,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G854" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -26253,7 +26253,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G855" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -26279,7 +26279,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G856" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -26305,7 +26305,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G857" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26331,7 +26331,7 @@
         <v>20.25</v>
       </c>
       <c r="G858" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26357,7 +26357,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G859" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -26383,7 +26383,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G860" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -26409,7 +26409,7 @@
         <v>20</v>
       </c>
       <c r="G861" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -26435,7 +26435,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G862" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -26461,7 +26461,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G863" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -26487,7 +26487,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G864" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -26513,7 +26513,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G865" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26539,7 +26539,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G866" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -26565,7 +26565,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G867" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -26591,7 +26591,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G868" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -26617,7 +26617,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G869" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -26643,7 +26643,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -26669,7 +26669,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G871" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -26695,7 +26695,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G872" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26721,7 +26721,7 @@
         <v>20</v>
       </c>
       <c r="G873" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -26747,7 +26747,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G874" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26773,7 +26773,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G875" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26799,7 +26799,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G876" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26825,7 +26825,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G877" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26851,7 +26851,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G878" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26877,7 +26877,7 @@
         <v>20.25</v>
       </c>
       <c r="G879" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26903,7 +26903,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26929,7 +26929,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G881" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26955,7 +26955,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G882" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26981,7 +26981,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G883" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -27007,7 +27007,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G884" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -27033,7 +27033,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G885" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -27059,7 +27059,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G886" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -27085,7 +27085,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G887" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -27111,7 +27111,7 @@
         <v>20.25</v>
       </c>
       <c r="G888" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -27137,7 +27137,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G889" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -27163,7 +27163,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G890" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -27189,7 +27189,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G891" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -27215,7 +27215,7 @@
         <v>20.5</v>
       </c>
       <c r="G892" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -27241,7 +27241,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G893" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -27267,7 +27267,7 @@
         <v>20.25</v>
       </c>
       <c r="G894" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -27293,7 +27293,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -27319,7 +27319,7 @@
         <v>20.25</v>
       </c>
       <c r="G896" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -27345,7 +27345,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G897" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -27371,7 +27371,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G898" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -27397,7 +27397,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G899" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -27423,7 +27423,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G900" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -27449,7 +27449,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G901" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -27475,7 +27475,7 @@
         <v>20.25</v>
       </c>
       <c r="G902" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -27501,7 +27501,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G903" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -27527,7 +27527,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G904" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -27553,7 +27553,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G905" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -27579,7 +27579,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G906" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -27605,7 +27605,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G907" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -27631,7 +27631,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G908" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -27657,7 +27657,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G909" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -27683,7 +27683,7 @@
         <v>21.25</v>
       </c>
       <c r="G910" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27709,7 +27709,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G911" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27735,7 +27735,7 @@
         <v>21.5</v>
       </c>
       <c r="G912" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27761,7 +27761,7 @@
         <v>21.5</v>
       </c>
       <c r="G913" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27787,7 +27787,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G914" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27813,7 +27813,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G915" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27839,7 +27839,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G916" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27865,7 +27865,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G917" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -27891,7 +27891,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G918" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27917,7 +27917,7 @@
         <v>21</v>
       </c>
       <c r="G919" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27943,7 +27943,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G920" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27969,7 +27969,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G921" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27995,7 +27995,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G922" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -28021,7 +28021,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G923" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -28047,7 +28047,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G924" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -28073,7 +28073,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G925" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -28099,7 +28099,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G926" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -28125,7 +28125,7 @@
         <v>20</v>
       </c>
       <c r="G927" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -28151,7 +28151,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G928" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -28177,7 +28177,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G929" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -28203,7 +28203,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G930" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -28229,7 +28229,7 @@
         <v>20</v>
       </c>
       <c r="G931" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -28255,7 +28255,7 @@
         <v>20</v>
       </c>
       <c r="G932" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -28281,7 +28281,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G933" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -28307,7 +28307,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G934" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -28333,7 +28333,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G935" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -28359,7 +28359,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G936" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -28385,7 +28385,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G937" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -28411,7 +28411,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G938" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -28437,7 +28437,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G939" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -28463,7 +28463,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G940" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -28489,7 +28489,7 @@
         <v>21.25</v>
       </c>
       <c r="G941" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -28515,7 +28515,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G942" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -28541,7 +28541,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G943" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -28567,7 +28567,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G944" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -28593,7 +28593,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G945" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -28619,7 +28619,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G946" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -28645,7 +28645,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G947" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -28671,7 +28671,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G948" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -28697,7 +28697,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G949" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -28723,7 +28723,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G950" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -28749,7 +28749,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G951" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28775,7 +28775,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G952" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -28801,7 +28801,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G953" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28827,7 +28827,7 @@
         <v>21.25</v>
       </c>
       <c r="G954" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -28853,7 +28853,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G955" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28879,7 +28879,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G956" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28905,7 +28905,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G957" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28931,7 +28931,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G958" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28957,7 +28957,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G959" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28983,7 +28983,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G960" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -29009,7 +29009,7 @@
         <v>21.25</v>
       </c>
       <c r="G961" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -29035,7 +29035,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G962" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -29061,7 +29061,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G963" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -29087,7 +29087,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G964" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -29113,7 +29113,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G965" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -29139,7 +29139,7 @@
         <v>21.5</v>
       </c>
       <c r="G966" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -29165,7 +29165,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G967" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -29191,7 +29191,7 @@
         <v>21.25</v>
       </c>
       <c r="G968" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -29217,7 +29217,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G969" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -29243,7 +29243,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G970" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -29269,7 +29269,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G971" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -29295,7 +29295,7 @@
         <v>21.5</v>
       </c>
       <c r="G972" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -29321,7 +29321,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G973" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -29347,7 +29347,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G974" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -29373,7 +29373,7 @@
         <v>21</v>
       </c>
       <c r="G975" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -29399,7 +29399,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G976" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -29425,7 +29425,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G977" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -29451,7 +29451,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G978" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -29477,7 +29477,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G979" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -29503,7 +29503,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G980" t="s">
-        <v>487</v>
+        <v>539</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -29529,7 +29529,7 @@
         <v>23</v>
       </c>
       <c r="G981" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -29555,7 +29555,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G982" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -29581,7 +29581,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G983" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -29607,7 +29607,7 @@
         <v>24</v>
       </c>
       <c r="G984" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -29633,7 +29633,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G985" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -29659,7 +29659,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G986" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -29685,7 +29685,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G987" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29711,7 +29711,7 @@
         <v>24</v>
       </c>
       <c r="G988" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29737,7 +29737,7 @@
         <v>24</v>
       </c>
       <c r="G989" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29763,7 +29763,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G990" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29789,7 +29789,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G991" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29815,7 +29815,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G992" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29841,7 +29841,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G993" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29867,7 +29867,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G994" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29893,7 +29893,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G995" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29919,7 +29919,7 @@
         <v>24.5</v>
       </c>
       <c r="G996" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29945,7 +29945,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G997" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29971,7 +29971,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G998" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29997,7 +29997,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G999" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -30023,7 +30023,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1000" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -30049,7 +30049,7 @@
         <v>23.25</v>
       </c>
       <c r="G1001" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -30075,7 +30075,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1002" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -30101,7 +30101,7 @@
         <v>23.5</v>
       </c>
       <c r="G1003" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -30127,7 +30127,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1004" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -30153,7 +30153,7 @@
         <v>23.75</v>
       </c>
       <c r="G1005" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -30179,7 +30179,7 @@
         <v>23.75</v>
       </c>
       <c r="G1006" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -30205,7 +30205,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1007" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -30231,7 +30231,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1008" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -30257,7 +30257,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1009" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -30283,7 +30283,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1010" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -30309,7 +30309,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1011" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -30335,7 +30335,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1012" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -30361,7 +30361,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1013" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -30387,7 +30387,7 @@
         <v>24.25</v>
       </c>
       <c r="G1014" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -30413,7 +30413,7 @@
         <v>24</v>
       </c>
       <c r="G1015" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -30439,7 +30439,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1016" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -30465,7 +30465,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1017" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -30491,7 +30491,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1018" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -30517,7 +30517,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1019" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -30543,7 +30543,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1020" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -30569,7 +30569,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1021" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -30595,7 +30595,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G1022" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -30621,7 +30621,7 @@
         <v>23.5</v>
       </c>
       <c r="G1023" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -30647,7 +30647,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1024" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -30673,7 +30673,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1025" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -30699,7 +30699,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1026" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -30725,7 +30725,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1027" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -30751,7 +30751,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1028" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30777,7 +30777,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1029" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30803,7 +30803,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1030" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30829,7 +30829,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1031" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30855,7 +30855,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1032" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30881,7 +30881,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1033" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -30907,7 +30907,7 @@
         <v>22.75</v>
       </c>
       <c r="G1034" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -30933,7 +30933,7 @@
         <v>23.25</v>
       </c>
       <c r="G1035" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -30959,7 +30959,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1036" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -30985,7 +30985,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1037" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -31011,7 +31011,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1038" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -31037,7 +31037,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1039" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -31063,7 +31063,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1040" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -31089,7 +31089,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1041" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -31115,7 +31115,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1042" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -31141,7 +31141,7 @@
         <v>23.75</v>
       </c>
       <c r="G1043" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -31167,7 +31167,7 @@
         <v>23.75</v>
       </c>
       <c r="G1044" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -31193,7 +31193,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1045" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -31219,7 +31219,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1046" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -31245,7 +31245,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1047" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -31271,7 +31271,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1048" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -31297,7 +31297,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1049" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -31323,7 +31323,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1050" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -31349,7 +31349,7 @@
         <v>23.25</v>
       </c>
       <c r="G1051" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -31375,7 +31375,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1052" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -31401,7 +31401,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1053" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -31427,7 +31427,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1054" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -31453,7 +31453,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1055" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -31479,7 +31479,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1056" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -31505,7 +31505,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -31531,7 +31531,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1058" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -31557,7 +31557,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1059" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -31583,7 +31583,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1060" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -31609,7 +31609,7 @@
         <v>20.75</v>
       </c>
       <c r="G1061" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -31635,7 +31635,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1062" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -31661,7 +31661,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1063" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -31687,7 +31687,7 @@
         <v>19.5</v>
       </c>
       <c r="G1064" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -31713,7 +31713,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1065" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31739,7 +31739,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1066" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31765,7 +31765,7 @@
         <v>18</v>
       </c>
       <c r="G1067" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31791,7 +31791,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1068" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31817,7 +31817,7 @@
         <v>17</v>
       </c>
       <c r="G1069" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -31843,7 +31843,7 @@
         <v>17</v>
       </c>
       <c r="G1070" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -31869,7 +31869,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1071" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31895,7 +31895,7 @@
         <v>17.5</v>
       </c>
       <c r="G1072" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31921,7 +31921,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1073" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -31947,7 +31947,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1074" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -31973,7 +31973,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1075" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31999,7 +31999,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1076" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -32025,7 +32025,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1077" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -32051,7 +32051,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G1078" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -32077,7 +32077,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1079" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -32103,7 +32103,7 @@
         <v>14</v>
       </c>
       <c r="G1080" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -32129,7 +32129,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1081" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -32155,7 +32155,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1082" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -32181,7 +32181,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1083" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -32207,7 +32207,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1084" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -32233,7 +32233,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1085" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32259,7 +32259,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1086" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -32285,7 +32285,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1087" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -32311,7 +32311,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1088" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -32337,7 +32337,7 @@
         <v>15</v>
       </c>
       <c r="G1089" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -32363,7 +32363,7 @@
         <v>15.5</v>
       </c>
       <c r="G1090" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -32389,7 +32389,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1091" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -32415,7 +32415,7 @@
         <v>15.25</v>
       </c>
       <c r="G1092" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -32441,7 +32441,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1093" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -32467,7 +32467,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1094" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -32493,7 +32493,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1095" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -32519,7 +32519,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1096" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -32545,7 +32545,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1097" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -32571,7 +32571,7 @@
         <v>15</v>
       </c>
       <c r="G1098" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -32597,7 +32597,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1099" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -32623,7 +32623,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1100" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -32649,7 +32649,7 @@
         <v>15</v>
       </c>
       <c r="G1101" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -32675,7 +32675,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1102" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -32701,7 +32701,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1103" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -32727,7 +32727,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1104" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32753,7 +32753,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1105" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -32779,7 +32779,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1106" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32805,7 +32805,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1107" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32831,7 +32831,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1108" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32857,7 +32857,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1109" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32883,7 +32883,7 @@
         <v>13.75</v>
       </c>
       <c r="G1110" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32909,7 +32909,7 @@
         <v>14</v>
       </c>
       <c r="G1111" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32935,7 +32935,7 @@
         <v>14</v>
       </c>
       <c r="G1112" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32961,7 +32961,7 @@
         <v>14.5</v>
       </c>
       <c r="G1113" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32987,7 +32987,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1114" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -33013,7 +33013,7 @@
         <v>15</v>
       </c>
       <c r="G1115" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -33039,7 +33039,7 @@
         <v>15.75</v>
       </c>
       <c r="G1116" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -33065,7 +33065,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1117" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -33091,7 +33091,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1118" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -33117,7 +33117,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1119" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -33143,7 +33143,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1120" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -33169,7 +33169,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1121" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -33195,7 +33195,7 @@
         <v>17</v>
       </c>
       <c r="G1122" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -33221,7 +33221,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1123" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -33247,7 +33247,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1124" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -33273,7 +33273,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1125" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -33299,7 +33299,7 @@
         <v>17.5</v>
       </c>
       <c r="G1126" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -33325,7 +33325,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1127" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -33351,7 +33351,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1128" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -33377,7 +33377,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1129" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -33403,7 +33403,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1130" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -33429,7 +33429,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1131" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -33455,7 +33455,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1132" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -33481,7 +33481,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1133" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -33507,7 +33507,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1134" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -33533,7 +33533,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1135" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -33559,7 +33559,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1136" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -33585,7 +33585,7 @@
         <v>18</v>
       </c>
       <c r="G1137" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -33611,7 +33611,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1138" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -33637,7 +33637,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1139" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -33663,7 +33663,7 @@
         <v>17.5</v>
       </c>
       <c r="G1140" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -33689,7 +33689,7 @@
         <v>17</v>
       </c>
       <c r="G1141" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33715,7 +33715,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1142" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33741,7 +33741,7 @@
         <v>16.5</v>
       </c>
       <c r="G1143" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33767,7 +33767,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1144" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33793,7 +33793,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1145" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33819,7 +33819,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1146" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33845,7 +33845,7 @@
         <v>17.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33871,7 +33871,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1148" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33897,7 +33897,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1149" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33923,7 +33923,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1150" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33949,7 +33949,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1151" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33975,7 +33975,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1152" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -34001,7 +34001,7 @@
         <v>17.5</v>
       </c>
       <c r="G1153" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -34027,7 +34027,7 @@
         <v>17</v>
       </c>
       <c r="G1154" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -34053,7 +34053,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1155" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -34079,7 +34079,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1156" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -34105,7 +34105,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1157" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -34131,7 +34131,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1158" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -34157,7 +34157,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1159" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -34183,7 +34183,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1160" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -34209,7 +34209,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1161" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -34235,7 +34235,7 @@
         <v>16.5</v>
       </c>
       <c r="G1162" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -34261,7 +34261,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1163" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -34287,7 +34287,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1164" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -34313,7 +34313,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1165" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -34339,7 +34339,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1166" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -34365,7 +34365,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1167" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -34391,7 +34391,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1168" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -34417,7 +34417,7 @@
         <v>17.25</v>
       </c>
       <c r="G1169" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -34443,7 +34443,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1170" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -34469,7 +34469,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1171" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -34495,7 +34495,7 @@
         <v>17</v>
       </c>
       <c r="G1172" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -34521,7 +34521,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1173" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -34547,7 +34547,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1174" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -34573,7 +34573,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1175" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -34599,7 +34599,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1176" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -34625,7 +34625,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1177" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34651,7 +34651,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1178" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -34677,7 +34677,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1179" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34703,7 +34703,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1180" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34729,7 +34729,7 @@
         <v>17</v>
       </c>
       <c r="G1181" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34755,7 +34755,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1182" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34781,7 +34781,7 @@
         <v>17</v>
       </c>
       <c r="G1183" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34807,7 +34807,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1184" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34833,7 +34833,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1185" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34859,7 +34859,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1186" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34885,7 +34885,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1187" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34911,7 +34911,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1188" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34937,7 +34937,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1189" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34963,7 +34963,7 @@
         <v>17.25</v>
       </c>
       <c r="G1190" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34989,7 +34989,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1191" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -35015,7 +35015,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1192" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -35041,7 +35041,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1193" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -35067,7 +35067,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1194" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -35093,7 +35093,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1195" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -35119,7 +35119,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1196" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -35145,7 +35145,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1197" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -35171,7 +35171,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -35197,7 +35197,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1199" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -35223,7 +35223,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1200" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -35249,7 +35249,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1201" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -35275,7 +35275,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1202" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -35301,7 +35301,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1203" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -35327,7 +35327,7 @@
         <v>16</v>
       </c>
       <c r="G1204" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -35353,7 +35353,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1205" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -35379,7 +35379,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1206" t="s">
-        <v>641</v>
+        <v>578</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -35405,7 +35405,7 @@
         <v>16</v>
       </c>
       <c r="G1207" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -35431,7 +35431,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1208" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -35457,7 +35457,7 @@
         <v>16.25</v>
       </c>
       <c r="G1209" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -35483,7 +35483,7 @@
         <v>16.5</v>
       </c>
       <c r="G1210" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -35509,7 +35509,7 @@
         <v>16.5</v>
       </c>
       <c r="G1211" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -35535,7 +35535,7 @@
         <v>17.25</v>
       </c>
       <c r="G1212" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -35561,7 +35561,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1213" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -35587,7 +35587,7 @@
         <v>17</v>
       </c>
       <c r="G1214" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -35613,7 +35613,7 @@
         <v>17.25</v>
       </c>
       <c r="G1215" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35639,7 +35639,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1216" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35665,7 +35665,7 @@
         <v>17</v>
       </c>
       <c r="G1217" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -35691,7 +35691,7 @@
         <v>17</v>
       </c>
       <c r="G1218" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35717,7 +35717,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1219" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35743,7 +35743,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1220" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35769,7 +35769,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1221" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35795,7 +35795,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1222" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35821,7 +35821,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1223" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35847,7 +35847,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1224" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35873,7 +35873,7 @@
         <v>16</v>
       </c>
       <c r="G1225" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35899,7 +35899,7 @@
         <v>16.0499992370605</v>
       </c>
       <